--- a/ELC_data_Spain.xlsx
+++ b/ELC_data_Spain.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://politoit-my.sharepoint.com/personal/s347160_studenti_polito_it/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{76AE923E-6FFF-4F14-83BA-5326F1D8B3E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="54" documentId="8_{76AE923E-6FFF-4F14-83BA-5326F1D8B3E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC5A3932-19C3-454E-BF7C-61EE67DA7F33}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{8BBF5E45-81C8-439F-BD27-48A9AF2DFBEB}"/>
   </bookViews>
@@ -17,13 +17,27 @@
     <sheet name="ImpExp" sheetId="2" r:id="rId2"/>
     <sheet name="Emissions" sheetId="3" r:id="rId3"/>
     <sheet name="ELC_Consumption" sheetId="4" r:id="rId4"/>
+    <sheet name="Computations" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="964" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="969" uniqueCount="33">
   <si>
     <t>electricity generation sources in Spain</t>
   </si>
@@ -116,6 +130,12 @@
   </si>
   <si>
     <t>TWh</t>
+  </si>
+  <si>
+    <t>PJ</t>
+  </si>
+  <si>
+    <t>CONVERTITORE PJ GWh</t>
   </si>
 </sst>
 </file>
@@ -610,9 +630,11 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Colore 1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -874,79 +896,79 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>80858</c:v>
+                  <c:v>291.08879999999999</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>71734</c:v>
+                  <c:v>258.24239999999998</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>82457</c:v>
+                  <c:v>296.84519999999998</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>75955</c:v>
+                  <c:v>273.43799999999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>80323</c:v>
+                  <c:v>289.1628</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>80767</c:v>
+                  <c:v>290.76119999999997</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>67978</c:v>
+                  <c:v>244.7208</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>74085</c:v>
+                  <c:v>266.70600000000002</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>49973</c:v>
+                  <c:v>179.90279999999998</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>36938</c:v>
+                  <c:v>132.9768</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>26323</c:v>
+                  <c:v>94.762799999999999</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>45126</c:v>
+                  <c:v>162.45359999999999</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>55991</c:v>
+                  <c:v>201.5676</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>41332</c:v>
+                  <c:v>148.79519999999999</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>45295</c:v>
+                  <c:v>163.06199999999998</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>52676</c:v>
+                  <c:v>189.6336</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>37453</c:v>
+                  <c:v>134.83079999999998</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>46349</c:v>
+                  <c:v>166.85640000000001</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>38716</c:v>
+                  <c:v>139.3776</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>13982</c:v>
+                  <c:v>50.3352</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>6149</c:v>
+                  <c:v>22.136399999999998</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>6014</c:v>
+                  <c:v>21.650399999999998</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>8696</c:v>
+                  <c:v>31.305599999999998</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>4450</c:v>
+                  <c:v>16.02</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>3466</c:v>
+                  <c:v>12.477599999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1072,79 +1094,79 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>22578</c:v>
+                  <c:v>81.280799999999999</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>24632</c:v>
+                  <c:v>88.675200000000004</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>28593</c:v>
+                  <c:v>102.9348</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>24002</c:v>
+                  <c:v>86.407200000000003</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>23839</c:v>
+                  <c:v>85.820399999999992</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>24420</c:v>
+                  <c:v>87.911999999999992</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>23829</c:v>
+                  <c:v>85.784399999999991</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>18508</c:v>
+                  <c:v>66.628799999999998</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>18002</c:v>
+                  <c:v>64.807199999999995</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>19242</c:v>
+                  <c:v>69.271199999999993</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>16562</c:v>
+                  <c:v>59.623199999999997</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>14692</c:v>
+                  <c:v>52.891199999999998</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>15321</c:v>
+                  <c:v>55.1556</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>13763</c:v>
+                  <c:v>49.546799999999998</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>14121</c:v>
+                  <c:v>50.835599999999999</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>17241</c:v>
+                  <c:v>62.067599999999999</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>16921</c:v>
+                  <c:v>60.915599999999998</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>15766</c:v>
+                  <c:v>56.757599999999996</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>14498</c:v>
+                  <c:v>52.192799999999998</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>12883</c:v>
+                  <c:v>46.378799999999998</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>10704</c:v>
+                  <c:v>38.534399999999998</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>10044</c:v>
+                  <c:v>36.1584</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>10590</c:v>
+                  <c:v>38.124000000000002</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>9288</c:v>
+                  <c:v>33.436799999999998</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>9123</c:v>
+                  <c:v>32.842799999999997</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1270,79 +1292,79 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>20178</c:v>
+                  <c:v>72.640799999999999</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>23358</c:v>
+                  <c:v>84.088799999999992</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>32386</c:v>
+                  <c:v>116.58959999999999</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>39368</c:v>
+                  <c:v>141.72479999999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>55460</c:v>
+                  <c:v>199.65600000000001</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>79011</c:v>
+                  <c:v>284.43959999999998</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>90570</c:v>
+                  <c:v>326.05199999999996</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>94799</c:v>
+                  <c:v>341.27639999999997</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>120798</c:v>
+                  <c:v>434.87279999999998</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>107746</c:v>
+                  <c:v>387.88560000000001</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>94851</c:v>
+                  <c:v>341.46359999999999</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>85508</c:v>
+                  <c:v>307.8288</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>73308</c:v>
+                  <c:v>263.90879999999999</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>57536</c:v>
+                  <c:v>207.12959999999998</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>47273</c:v>
+                  <c:v>170.18279999999999</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>52498</c:v>
+                  <c:v>188.99279999999999</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>52820</c:v>
+                  <c:v>190.15199999999999</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>64037</c:v>
+                  <c:v>230.53319999999999</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>58004</c:v>
+                  <c:v>208.81440000000001</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>83703</c:v>
+                  <c:v>301.33080000000001</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>69739</c:v>
+                  <c:v>251.06039999999999</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>71502</c:v>
+                  <c:v>257.40719999999999</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>85975</c:v>
+                  <c:v>309.51</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>64272</c:v>
+                  <c:v>231.3792</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>52329</c:v>
+                  <c:v>188.3844</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1468,79 +1490,79 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>62206</c:v>
+                  <c:v>223.94159999999999</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>63708</c:v>
+                  <c:v>229.34879999999998</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>63016</c:v>
+                  <c:v>226.85759999999999</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>61875</c:v>
+                  <c:v>222.75</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>63606</c:v>
+                  <c:v>228.98159999999999</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>57539</c:v>
+                  <c:v>207.1404</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>60126</c:v>
+                  <c:v>216.45359999999999</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>55103</c:v>
+                  <c:v>198.3708</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>58973</c:v>
+                  <c:v>212.30279999999999</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>52761</c:v>
+                  <c:v>189.93959999999998</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>61990</c:v>
+                  <c:v>223.16399999999999</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>57718</c:v>
+                  <c:v>207.78479999999999</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>61470</c:v>
+                  <c:v>221.292</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>56726</c:v>
+                  <c:v>204.21359999999999</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>57305</c:v>
+                  <c:v>206.298</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>57196</c:v>
+                  <c:v>205.90559999999999</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>58633</c:v>
+                  <c:v>211.0788</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>58039</c:v>
+                  <c:v>208.94039999999998</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>55766</c:v>
+                  <c:v>200.7576</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>58349</c:v>
+                  <c:v>210.0564</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>58299</c:v>
+                  <c:v>209.87639999999999</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>56564</c:v>
+                  <c:v>203.63039999999998</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>58590</c:v>
+                  <c:v>210.92400000000001</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>56873</c:v>
+                  <c:v>204.74279999999999</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>54532</c:v>
+                  <c:v>196.3152</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1666,79 +1688,79 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>31807</c:v>
+                  <c:v>114.5052</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>43864</c:v>
+                  <c:v>157.91040000000001</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>26270</c:v>
+                  <c:v>94.572000000000003</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>43897</c:v>
+                  <c:v>158.0292</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>34439</c:v>
+                  <c:v>123.9804</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>23025</c:v>
+                  <c:v>82.89</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>29831</c:v>
+                  <c:v>107.3916</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>30522</c:v>
+                  <c:v>109.8792</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>26144</c:v>
+                  <c:v>94.118399999999994</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>29162</c:v>
+                  <c:v>104.9832</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>45511</c:v>
+                  <c:v>163.83959999999999</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>32911</c:v>
+                  <c:v>118.47959999999999</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>24162</c:v>
+                  <c:v>86.983199999999997</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>41052</c:v>
+                  <c:v>147.78719999999998</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>42969</c:v>
+                  <c:v>154.6884</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>31368</c:v>
+                  <c:v>112.92479999999999</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>39865</c:v>
+                  <c:v>143.51400000000001</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>21070</c:v>
+                  <c:v>75.852000000000004</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>36803</c:v>
+                  <c:v>132.49080000000001</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>26874</c:v>
+                  <c:v>96.746399999999994</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>33998</c:v>
+                  <c:v>122.39279999999999</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>32847</c:v>
+                  <c:v>118.2492</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>22102</c:v>
+                  <c:v>79.5672</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>31105</c:v>
+                  <c:v>111.97799999999999</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>40821</c:v>
+                  <c:v>146.9556</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1921,22 +1943,22 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>20</c:v>
+                  <c:v>7.1999999999999995E-2</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>27</c:v>
+                  <c:v>9.7199999999999995E-2</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>19</c:v>
+                  <c:v>6.8400000000000002E-2</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>23</c:v>
+                  <c:v>8.2799999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>12</c:v>
+                  <c:v>4.3200000000000002E-2</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>8</c:v>
+                  <c:v>2.8799999999999999E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2064,79 +2086,79 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>1159</c:v>
+                  <c:v>4.1723999999999997</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1297</c:v>
+                  <c:v>4.6692</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2303</c:v>
+                  <c:v>8.2907999999999991</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2853</c:v>
+                  <c:v>10.270799999999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3039</c:v>
+                  <c:v>10.9404</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2202</c:v>
+                  <c:v>7.9272</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2173</c:v>
+                  <c:v>7.8228</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2161</c:v>
+                  <c:v>7.7795999999999994</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2473</c:v>
+                  <c:v>8.9027999999999992</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2727</c:v>
+                  <c:v>9.8171999999999997</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>3356</c:v>
+                  <c:v>12.0816</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>3814</c:v>
+                  <c:v>13.730399999999999</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>4262</c:v>
+                  <c:v>15.3432</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>5116</c:v>
+                  <c:v>18.4176</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>4728</c:v>
+                  <c:v>17.020800000000001</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>4996</c:v>
+                  <c:v>17.985599999999998</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>4954</c:v>
+                  <c:v>17.834399999999999</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>5306</c:v>
+                  <c:v>19.101600000000001</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>5156</c:v>
+                  <c:v>18.561599999999999</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>4802</c:v>
+                  <c:v>17.287199999999999</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>5435</c:v>
+                  <c:v>19.565999999999999</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>6088</c:v>
+                  <c:v>21.916799999999999</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>5935</c:v>
+                  <c:v>21.366</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>5062</c:v>
+                  <c:v>18.223199999999999</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>5319</c:v>
+                  <c:v>19.148399999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2264,79 +2286,79 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>941</c:v>
+                  <c:v>3.3875999999999999</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>667</c:v>
+                  <c:v>2.4011999999999998</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>566</c:v>
+                  <c:v>2.0375999999999999</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>661</c:v>
+                  <c:v>2.3795999999999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>582</c:v>
+                  <c:v>2.0951999999999997</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>902</c:v>
+                  <c:v>3.2471999999999999</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1202</c:v>
+                  <c:v>4.3271999999999995</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1474</c:v>
+                  <c:v>5.3064</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1564</c:v>
+                  <c:v>5.6303999999999998</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1522</c:v>
+                  <c:v>5.4791999999999996</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1318</c:v>
+                  <c:v>4.7447999999999997</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1590</c:v>
+                  <c:v>5.7240000000000002</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1430</c:v>
+                  <c:v>5.1479999999999997</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1364</c:v>
+                  <c:v>4.9104000000000001</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1372</c:v>
+                  <c:v>4.9391999999999996</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1536</c:v>
+                  <c:v>5.5296000000000003</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1470</c:v>
+                  <c:v>5.2919999999999998</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1544</c:v>
+                  <c:v>5.5583999999999998</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1775</c:v>
+                  <c:v>6.39</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1755</c:v>
+                  <c:v>6.3179999999999996</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1751</c:v>
+                  <c:v>6.3035999999999994</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1795</c:v>
+                  <c:v>6.4619999999999997</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1754</c:v>
+                  <c:v>6.3144</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1683</c:v>
+                  <c:v>6.0587999999999997</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1686</c:v>
+                  <c:v>6.0695999999999994</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2464,79 +2486,79 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>4727</c:v>
+                  <c:v>17.017199999999999</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6759</c:v>
+                  <c:v>24.3324</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>9342</c:v>
+                  <c:v>33.6312</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>12075</c:v>
+                  <c:v>43.47</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>15700</c:v>
+                  <c:v>56.519999999999996</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>21176</c:v>
+                  <c:v>76.233599999999996</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>23297</c:v>
+                  <c:v>83.869199999999992</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>27568</c:v>
+                  <c:v>99.244799999999998</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>32946</c:v>
+                  <c:v>118.6056</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>38117</c:v>
+                  <c:v>137.22120000000001</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>44271</c:v>
+                  <c:v>159.37559999999999</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>42918</c:v>
+                  <c:v>154.50479999999999</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>49472</c:v>
+                  <c:v>178.0992</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>55646</c:v>
+                  <c:v>200.32560000000001</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>52013</c:v>
+                  <c:v>187.24680000000001</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>49325</c:v>
+                  <c:v>177.57</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>48905</c:v>
+                  <c:v>176.05799999999999</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>49127</c:v>
+                  <c:v>176.85720000000001</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>50896</c:v>
+                  <c:v>183.22559999999999</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>55647</c:v>
+                  <c:v>200.32919999999999</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>56444</c:v>
+                  <c:v>203.19839999999999</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>62061</c:v>
+                  <c:v>223.4196</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>62784</c:v>
+                  <c:v>226.0224</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>64275</c:v>
+                  <c:v>231.39</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>62089</c:v>
+                  <c:v>223.5204</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2664,79 +2686,79 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>14</c:v>
+                  <c:v>5.04E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>17</c:v>
+                  <c:v>6.1199999999999997E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>18</c:v>
+                  <c:v>6.4799999999999996E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>20</c:v>
+                  <c:v>7.1999999999999995E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>23</c:v>
+                  <c:v>8.2799999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>47</c:v>
+                  <c:v>0.16919999999999999</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>124</c:v>
+                  <c:v>0.44639999999999996</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>507</c:v>
+                  <c:v>1.8251999999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2562</c:v>
+                  <c:v>9.2232000000000003</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>5961</c:v>
+                  <c:v>21.459599999999998</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>6425</c:v>
+                  <c:v>23.13</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>7440</c:v>
+                  <c:v>26.783999999999999</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>8192</c:v>
+                  <c:v>29.491199999999999</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>8326</c:v>
+                  <c:v>29.973599999999998</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>8217</c:v>
+                  <c:v>29.581199999999999</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>8266</c:v>
+                  <c:v>29.7576</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>8063</c:v>
+                  <c:v>29.026799999999998</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>8514</c:v>
+                  <c:v>30.650399999999998</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>7877</c:v>
+                  <c:v>28.357199999999999</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>9420</c:v>
+                  <c:v>33.911999999999999</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>15675</c:v>
+                  <c:v>56.43</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>21922</c:v>
+                  <c:v>78.919200000000004</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>31187</c:v>
+                  <c:v>112.2732</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>43421</c:v>
+                  <c:v>156.31559999999999</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>53752</c:v>
+                  <c:v>193.50719999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2885,58 +2907,58 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>8</c:v>
+                  <c:v>2.8799999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>16</c:v>
+                  <c:v>5.7599999999999998E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>103</c:v>
+                  <c:v>0.37079999999999996</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>761</c:v>
+                  <c:v>2.7395999999999998</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1959</c:v>
+                  <c:v>7.0523999999999996</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>3775</c:v>
+                  <c:v>13.59</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>4769</c:v>
+                  <c:v>17.168399999999998</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>5454</c:v>
+                  <c:v>19.634399999999999</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>5593</c:v>
+                  <c:v>20.134799999999998</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>5579</c:v>
+                  <c:v>20.084399999999999</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>5883</c:v>
+                  <c:v>21.178799999999999</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>4867</c:v>
+                  <c:v>17.5212</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>5683</c:v>
+                  <c:v>20.4588</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>4992</c:v>
+                  <c:v>17.9712</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>5176</c:v>
+                  <c:v>18.633599999999998</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>4536</c:v>
+                  <c:v>16.329599999999999</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>5165</c:v>
+                  <c:v>18.594000000000001</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>4540</c:v>
+                  <c:v>16.344000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3076,31 +3098,31 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2963</c:v>
+                  <c:v>10.6668</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4994</c:v>
+                  <c:v>17.978400000000001</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>329</c:v>
+                  <c:v>1.1843999999999999</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>324</c:v>
+                  <c:v>1.1663999999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>307</c:v>
+                  <c:v>1.1052</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>341</c:v>
+                  <c:v>1.2276</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>159</c:v>
+                  <c:v>0.57240000000000002</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>171</c:v>
+                  <c:v>0.61560000000000004</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>175</c:v>
+                  <c:v>0.63</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>0</c:v>
@@ -3109,34 +3131,34 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>216</c:v>
+                  <c:v>0.77759999999999996</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>108</c:v>
+                  <c:v>0.38879999999999998</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>91</c:v>
+                  <c:v>0.3276</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>94</c:v>
+                  <c:v>0.33839999999999998</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>139</c:v>
+                  <c:v>0.50039999999999996</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>160</c:v>
+                  <c:v>0.57599999999999996</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>280</c:v>
+                  <c:v>1.008</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>282</c:v>
+                  <c:v>1.0151999999999999</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>273</c:v>
+                  <c:v>0.98280000000000001</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>244</c:v>
+                  <c:v>0.87839999999999996</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3308,7 +3330,7 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="it-IT"/>
-                  <a:t> Generation (GWh)</a:t>
+                  <a:t> Generation (PJ)</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -3662,79 +3684,79 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>12268</c:v>
+                  <c:v>44.1648</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>10177</c:v>
+                  <c:v>36.6372</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>12504</c:v>
+                  <c:v>45.014400000000002</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>9520</c:v>
+                  <c:v>34.271999999999998</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>8111</c:v>
+                  <c:v>29.1996</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>10212</c:v>
+                  <c:v>36.763199999999998</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>9093</c:v>
+                  <c:v>32.7348</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>8773</c:v>
+                  <c:v>31.582799999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>5881</c:v>
+                  <c:v>21.171599999999998</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>6751</c:v>
+                  <c:v>24.303599999999999</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>5206</c:v>
+                  <c:v>18.741599999999998</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>7932</c:v>
+                  <c:v>28.555199999999999</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>7787</c:v>
+                  <c:v>28.033200000000001</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>9887</c:v>
+                  <c:v>35.593199999999996</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>12310</c:v>
+                  <c:v>44.315999999999995</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>14956</c:v>
+                  <c:v>53.8416</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>21845</c:v>
+                  <c:v>78.641999999999996</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>23762</c:v>
+                  <c:v>85.543199999999999</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>24018</c:v>
+                  <c:v>86.464799999999997</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>18720</c:v>
+                  <c:v>67.391999999999996</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>17928</c:v>
+                  <c:v>64.540800000000004</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>17411</c:v>
+                  <c:v>62.679600000000001</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>8031</c:v>
+                  <c:v>28.9116</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>11316</c:v>
+                  <c:v>40.7376</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>14354</c:v>
+                  <c:v>51.674399999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3860,79 +3882,79 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>-7827</c:v>
+                  <c:v>-28.177199999999999</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-6727</c:v>
+                  <c:v>-24.217199999999998</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-7175</c:v>
+                  <c:v>-25.83</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-8257</c:v>
+                  <c:v>-29.725200000000001</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-11139</c:v>
+                  <c:v>-40.1004</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-11555</c:v>
+                  <c:v>-41.597999999999999</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-12373</c:v>
+                  <c:v>-44.5428</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-14524</c:v>
+                  <c:v>-52.2864</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-16920</c:v>
+                  <c:v>-60.911999999999999</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-14855</c:v>
+                  <c:v>-53.478000000000002</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-13539</c:v>
+                  <c:v>-48.740400000000001</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-14023</c:v>
+                  <c:v>-50.482799999999997</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-18986</c:v>
+                  <c:v>-68.349599999999995</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-16638</c:v>
+                  <c:v>-59.896799999999999</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-15716</c:v>
+                  <c:v>-56.577599999999997</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-15089</c:v>
+                  <c:v>-54.320399999999999</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-14178</c:v>
+                  <c:v>-51.040799999999997</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-14593</c:v>
+                  <c:v>-52.534799999999997</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-12916</c:v>
+                  <c:v>-46.497599999999998</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-11858</c:v>
+                  <c:v>-42.688800000000001</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-14648</c:v>
+                  <c:v>-52.732799999999997</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>-16558</c:v>
+                  <c:v>-59.608799999999995</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>-27833</c:v>
+                  <c:v>-100.19879999999999</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>-25272</c:v>
+                  <c:v>-90.979199999999992</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>-24581</c:v>
+                  <c:v>-88.491599999999991</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3991,79 +4013,79 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>4441</c:v>
+                  <c:v>15.9876</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3450</c:v>
+                  <c:v>12.420000000000002</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5329</c:v>
+                  <c:v>19.184400000000004</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1263</c:v>
+                  <c:v>4.5467999999999975</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-3028</c:v>
+                  <c:v>-10.9008</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-1343</c:v>
+                  <c:v>-4.8348000000000013</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-3280</c:v>
+                  <c:v>-11.808</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-5751</c:v>
+                  <c:v>-20.703600000000002</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-11039</c:v>
+                  <c:v>-39.740400000000001</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-8104</c:v>
+                  <c:v>-29.174400000000002</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-8333</c:v>
+                  <c:v>-29.998800000000003</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-6091</c:v>
+                  <c:v>-21.927599999999998</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-11199</c:v>
+                  <c:v>-40.316399999999994</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-6751</c:v>
+                  <c:v>-24.303600000000003</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-3406</c:v>
+                  <c:v>-12.261600000000001</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-133</c:v>
+                  <c:v>-0.47879999999999967</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>7667</c:v>
+                  <c:v>27.601199999999999</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>9169</c:v>
+                  <c:v>33.008400000000002</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>11102</c:v>
+                  <c:v>39.967199999999998</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>6862</c:v>
+                  <c:v>24.703199999999995</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3280</c:v>
+                  <c:v>11.808000000000007</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>853</c:v>
+                  <c:v>3.0708000000000055</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>-19802</c:v>
+                  <c:v>-71.287199999999984</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>-13956</c:v>
+                  <c:v>-50.241599999999991</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>-10227</c:v>
+                  <c:v>-36.817199999999993</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4188,6 +4210,7 @@
           </a:p>
         </c:txPr>
         <c:crossAx val="157084656"/>
+        <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
@@ -4239,7 +4262,7 @@
                 </a:r>
                 <a:r>
                   <a:rPr lang="it-IT" baseline="0"/>
-                  <a:t> (GWh)</a:t>
+                  <a:t> (PJ)</a:t>
                 </a:r>
                 <a:endParaRPr lang="it-IT"/>
               </a:p>
@@ -4306,6 +4329,7 @@
           </a:p>
         </c:txPr>
         <c:crossAx val="157081776"/>
+        <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:spPr>
@@ -5739,79 +5763,79 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>209.643</c:v>
+                  <c:v>754.71479999999997</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>221.505</c:v>
+                  <c:v>797.41800000000001</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>231.03299999999999</c:v>
+                  <c:v>831.71879999999999</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>239.44200000000001</c:v>
+                  <c:v>861.99119999999994</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>252.87700000000001</c:v>
+                  <c:v>910.35719999999992</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>266.78100000000001</c:v>
+                  <c:v>960.41160000000002</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>271.05500000000001</c:v>
+                  <c:v>975.79799999999989</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>273.827</c:v>
+                  <c:v>985.77719999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>276.90899999999999</c:v>
+                  <c:v>996.87239999999997</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>262.07100000000003</c:v>
+                  <c:v>943.4556</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>265.79399999999998</c:v>
+                  <c:v>956.85839999999985</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>261.72899999999998</c:v>
+                  <c:v>942.22439999999995</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>260.685</c:v>
+                  <c:v>938.46600000000001</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>252.18600000000001</c:v>
+                  <c:v>907.8696000000001</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>248.95</c:v>
+                  <c:v>896.21999999999991</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>254.26900000000001</c:v>
+                  <c:v>915.36839999999995</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>255.71899999999999</c:v>
+                  <c:v>920.58839999999998</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>261.072</c:v>
+                  <c:v>939.85919999999999</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>259.95800000000003</c:v>
+                  <c:v>935.84879999999998</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>255.32900000000001</c:v>
+                  <c:v>919.18439999999998</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>241.02199999999999</c:v>
+                  <c:v>867.67920000000004</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>248.43600000000001</c:v>
+                  <c:v>894.36959999999999</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>247.52099999999999</c:v>
+                  <c:v>891.07560000000001</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>247.46</c:v>
+                  <c:v>890.85599999999999</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>253.74799999999999</c:v>
+                  <c:v>913.49279999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5983,7 +6007,7 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="it-IT"/>
-                  <a:t>Consumption (TWh)</a:t>
+                  <a:t>Consumption (PJ)</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -8303,16 +8327,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>1363980</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>91440</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>297180</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>24765</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>542925</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>428625</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -8817,7 +8841,7 @@
       <c r="F2" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="1" t="s">
         <v>18</v>
       </c>
       <c r="L2">
@@ -8909,108 +8933,108 @@
       <c r="D3" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K3" t="s">
         <v>4</v>
       </c>
       <c r="L3">
-        <f>SUMIFS($B:$B,$A:$A,$K3,$C:$C,L$2)</f>
-        <v>80858</v>
+        <f>SUMIFS($B:$B,$A:$A,$K3,$C:$C,L$2)*0.0036</f>
+        <v>291.08879999999999</v>
       </c>
       <c r="M3">
-        <f t="shared" ref="M3:AJ13" si="0">SUMIFS($B:$B,$A:$A,$K3,$C:$C,M$2)</f>
-        <v>71734</v>
+        <f t="shared" ref="M3:AJ13" si="0">SUMIFS($B:$B,$A:$A,$K3,$C:$C,M$2)*0.0036</f>
+        <v>258.24239999999998</v>
       </c>
       <c r="N3">
         <f t="shared" si="0"/>
-        <v>82457</v>
+        <v>296.84519999999998</v>
       </c>
       <c r="O3">
         <f t="shared" si="0"/>
-        <v>75955</v>
+        <v>273.43799999999999</v>
       </c>
       <c r="P3">
         <f t="shared" si="0"/>
-        <v>80323</v>
+        <v>289.1628</v>
       </c>
       <c r="Q3">
         <f t="shared" si="0"/>
-        <v>80767</v>
+        <v>290.76119999999997</v>
       </c>
       <c r="R3">
         <f t="shared" si="0"/>
-        <v>67978</v>
+        <v>244.7208</v>
       </c>
       <c r="S3">
         <f t="shared" si="0"/>
-        <v>74085</v>
+        <v>266.70600000000002</v>
       </c>
       <c r="T3">
         <f t="shared" si="0"/>
-        <v>49973</v>
+        <v>179.90279999999998</v>
       </c>
       <c r="U3">
         <f t="shared" si="0"/>
-        <v>36938</v>
+        <v>132.9768</v>
       </c>
       <c r="V3">
         <f t="shared" si="0"/>
-        <v>26323</v>
+        <v>94.762799999999999</v>
       </c>
       <c r="W3">
         <f t="shared" si="0"/>
-        <v>45126</v>
+        <v>162.45359999999999</v>
       </c>
       <c r="X3">
         <f t="shared" si="0"/>
-        <v>55991</v>
+        <v>201.5676</v>
       </c>
       <c r="Y3">
         <f t="shared" si="0"/>
-        <v>41332</v>
+        <v>148.79519999999999</v>
       </c>
       <c r="Z3">
         <f t="shared" si="0"/>
-        <v>45295</v>
+        <v>163.06199999999998</v>
       </c>
       <c r="AA3">
         <f t="shared" si="0"/>
-        <v>52676</v>
+        <v>189.6336</v>
       </c>
       <c r="AB3">
         <f t="shared" si="0"/>
-        <v>37453</v>
+        <v>134.83079999999998</v>
       </c>
       <c r="AC3">
         <f t="shared" si="0"/>
-        <v>46349</v>
+        <v>166.85640000000001</v>
       </c>
       <c r="AD3">
         <f t="shared" si="0"/>
-        <v>38716</v>
+        <v>139.3776</v>
       </c>
       <c r="AE3">
         <f t="shared" si="0"/>
-        <v>13982</v>
+        <v>50.3352</v>
       </c>
       <c r="AF3">
         <f t="shared" si="0"/>
-        <v>6149</v>
+        <v>22.136399999999998</v>
       </c>
       <c r="AG3">
         <f t="shared" si="0"/>
-        <v>6014</v>
+        <v>21.650399999999998</v>
       </c>
       <c r="AH3">
         <f t="shared" si="0"/>
-        <v>8696</v>
+        <v>31.305599999999998</v>
       </c>
       <c r="AI3">
         <f t="shared" si="0"/>
-        <v>4450</v>
+        <v>16.02</v>
       </c>
       <c r="AJ3">
         <f t="shared" si="0"/>
-        <v>3466</v>
+        <v>12.477599999999999</v>
       </c>
     </row>
     <row r="4" spans="1:36" x14ac:dyDescent="0.3">
@@ -9026,108 +9050,108 @@
       <c r="D4" t="s">
         <v>5</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="K4" t="s">
         <v>6</v>
       </c>
       <c r="L4">
-        <f t="shared" ref="L4:AA20" si="1">SUMIFS($B:$B,$A:$A,$K4,$C:$C,L$2)</f>
-        <v>22578</v>
+        <f t="shared" ref="L4:AA14" si="1">SUMIFS($B:$B,$A:$A,$K4,$C:$C,L$2)*0.0036</f>
+        <v>81.280799999999999</v>
       </c>
       <c r="M4">
         <f t="shared" si="0"/>
-        <v>24632</v>
+        <v>88.675200000000004</v>
       </c>
       <c r="N4">
         <f t="shared" si="0"/>
-        <v>28593</v>
+        <v>102.9348</v>
       </c>
       <c r="O4">
         <f t="shared" si="0"/>
-        <v>24002</v>
+        <v>86.407200000000003</v>
       </c>
       <c r="P4">
         <f t="shared" si="0"/>
-        <v>23839</v>
+        <v>85.820399999999992</v>
       </c>
       <c r="Q4">
         <f t="shared" si="0"/>
-        <v>24420</v>
+        <v>87.911999999999992</v>
       </c>
       <c r="R4">
         <f t="shared" si="0"/>
-        <v>23829</v>
+        <v>85.784399999999991</v>
       </c>
       <c r="S4">
         <f t="shared" si="0"/>
-        <v>18508</v>
+        <v>66.628799999999998</v>
       </c>
       <c r="T4">
         <f t="shared" si="0"/>
-        <v>18002</v>
+        <v>64.807199999999995</v>
       </c>
       <c r="U4">
         <f t="shared" si="0"/>
-        <v>19242</v>
+        <v>69.271199999999993</v>
       </c>
       <c r="V4">
         <f t="shared" si="0"/>
-        <v>16562</v>
+        <v>59.623199999999997</v>
       </c>
       <c r="W4">
         <f t="shared" si="0"/>
-        <v>14692</v>
+        <v>52.891199999999998</v>
       </c>
       <c r="X4">
         <f t="shared" si="0"/>
-        <v>15321</v>
+        <v>55.1556</v>
       </c>
       <c r="Y4">
         <f t="shared" si="0"/>
-        <v>13763</v>
+        <v>49.546799999999998</v>
       </c>
       <c r="Z4">
         <f t="shared" si="0"/>
-        <v>14121</v>
+        <v>50.835599999999999</v>
       </c>
       <c r="AA4">
         <f t="shared" si="0"/>
-        <v>17241</v>
+        <v>62.067599999999999</v>
       </c>
       <c r="AB4">
         <f t="shared" si="0"/>
-        <v>16921</v>
+        <v>60.915599999999998</v>
       </c>
       <c r="AC4">
         <f t="shared" si="0"/>
-        <v>15766</v>
+        <v>56.757599999999996</v>
       </c>
       <c r="AD4">
         <f t="shared" si="0"/>
-        <v>14498</v>
+        <v>52.192799999999998</v>
       </c>
       <c r="AE4">
         <f t="shared" si="0"/>
-        <v>12883</v>
+        <v>46.378799999999998</v>
       </c>
       <c r="AF4">
         <f t="shared" si="0"/>
-        <v>10704</v>
+        <v>38.534399999999998</v>
       </c>
       <c r="AG4">
         <f t="shared" si="0"/>
-        <v>10044</v>
+        <v>36.1584</v>
       </c>
       <c r="AH4">
         <f t="shared" si="0"/>
-        <v>10590</v>
+        <v>38.124000000000002</v>
       </c>
       <c r="AI4">
         <f t="shared" si="0"/>
-        <v>9288</v>
+        <v>33.436799999999998</v>
       </c>
       <c r="AJ4">
         <f t="shared" si="0"/>
-        <v>9123</v>
+        <v>32.842799999999997</v>
       </c>
     </row>
     <row r="5" spans="1:36" x14ac:dyDescent="0.3">
@@ -9143,108 +9167,108 @@
       <c r="D5" t="s">
         <v>5</v>
       </c>
-      <c r="K5" s="1" t="s">
+      <c r="K5" t="s">
         <v>7</v>
       </c>
       <c r="L5">
         <f t="shared" si="1"/>
-        <v>20178</v>
+        <v>72.640799999999999</v>
       </c>
       <c r="M5">
         <f t="shared" si="0"/>
-        <v>23358</v>
+        <v>84.088799999999992</v>
       </c>
       <c r="N5">
         <f t="shared" si="0"/>
-        <v>32386</v>
+        <v>116.58959999999999</v>
       </c>
       <c r="O5">
         <f t="shared" si="0"/>
-        <v>39368</v>
+        <v>141.72479999999999</v>
       </c>
       <c r="P5">
         <f t="shared" si="0"/>
-        <v>55460</v>
+        <v>199.65600000000001</v>
       </c>
       <c r="Q5">
         <f t="shared" si="0"/>
-        <v>79011</v>
+        <v>284.43959999999998</v>
       </c>
       <c r="R5">
         <f t="shared" si="0"/>
-        <v>90570</v>
+        <v>326.05199999999996</v>
       </c>
       <c r="S5">
         <f t="shared" si="0"/>
-        <v>94799</v>
+        <v>341.27639999999997</v>
       </c>
       <c r="T5">
         <f t="shared" si="0"/>
-        <v>120798</v>
+        <v>434.87279999999998</v>
       </c>
       <c r="U5">
         <f t="shared" si="0"/>
-        <v>107746</v>
+        <v>387.88560000000001</v>
       </c>
       <c r="V5">
         <f t="shared" si="0"/>
-        <v>94851</v>
+        <v>341.46359999999999</v>
       </c>
       <c r="W5">
         <f t="shared" si="0"/>
-        <v>85508</v>
+        <v>307.8288</v>
       </c>
       <c r="X5">
         <f t="shared" si="0"/>
-        <v>73308</v>
+        <v>263.90879999999999</v>
       </c>
       <c r="Y5">
         <f t="shared" si="0"/>
-        <v>57536</v>
+        <v>207.12959999999998</v>
       </c>
       <c r="Z5">
         <f t="shared" si="0"/>
-        <v>47273</v>
+        <v>170.18279999999999</v>
       </c>
       <c r="AA5">
         <f t="shared" si="0"/>
-        <v>52498</v>
+        <v>188.99279999999999</v>
       </c>
       <c r="AB5">
         <f t="shared" si="0"/>
-        <v>52820</v>
+        <v>190.15199999999999</v>
       </c>
       <c r="AC5">
         <f t="shared" si="0"/>
-        <v>64037</v>
+        <v>230.53319999999999</v>
       </c>
       <c r="AD5">
         <f t="shared" si="0"/>
-        <v>58004</v>
+        <v>208.81440000000001</v>
       </c>
       <c r="AE5">
         <f t="shared" si="0"/>
-        <v>83703</v>
+        <v>301.33080000000001</v>
       </c>
       <c r="AF5">
         <f t="shared" si="0"/>
-        <v>69739</v>
+        <v>251.06039999999999</v>
       </c>
       <c r="AG5">
         <f t="shared" si="0"/>
-        <v>71502</v>
+        <v>257.40719999999999</v>
       </c>
       <c r="AH5">
         <f t="shared" si="0"/>
-        <v>85975</v>
+        <v>309.51</v>
       </c>
       <c r="AI5">
         <f t="shared" si="0"/>
-        <v>64272</v>
+        <v>231.3792</v>
       </c>
       <c r="AJ5">
         <f t="shared" si="0"/>
-        <v>52329</v>
+        <v>188.3844</v>
       </c>
     </row>
     <row r="6" spans="1:36" x14ac:dyDescent="0.3">
@@ -9260,108 +9284,108 @@
       <c r="D6" t="s">
         <v>5</v>
       </c>
-      <c r="K6" s="1" t="s">
+      <c r="K6" t="s">
         <v>8</v>
       </c>
       <c r="L6">
         <f t="shared" si="1"/>
-        <v>62206</v>
+        <v>223.94159999999999</v>
       </c>
       <c r="M6">
         <f t="shared" si="0"/>
-        <v>63708</v>
+        <v>229.34879999999998</v>
       </c>
       <c r="N6">
         <f t="shared" si="0"/>
-        <v>63016</v>
+        <v>226.85759999999999</v>
       </c>
       <c r="O6">
         <f t="shared" si="0"/>
-        <v>61875</v>
+        <v>222.75</v>
       </c>
       <c r="P6">
         <f t="shared" si="0"/>
-        <v>63606</v>
+        <v>228.98159999999999</v>
       </c>
       <c r="Q6">
         <f t="shared" si="0"/>
-        <v>57539</v>
+        <v>207.1404</v>
       </c>
       <c r="R6">
         <f t="shared" si="0"/>
-        <v>60126</v>
+        <v>216.45359999999999</v>
       </c>
       <c r="S6">
         <f t="shared" si="0"/>
-        <v>55103</v>
+        <v>198.3708</v>
       </c>
       <c r="T6">
         <f t="shared" si="0"/>
-        <v>58973</v>
+        <v>212.30279999999999</v>
       </c>
       <c r="U6">
         <f t="shared" si="0"/>
-        <v>52761</v>
+        <v>189.93959999999998</v>
       </c>
       <c r="V6">
         <f t="shared" si="0"/>
-        <v>61990</v>
+        <v>223.16399999999999</v>
       </c>
       <c r="W6">
         <f t="shared" si="0"/>
-        <v>57718</v>
+        <v>207.78479999999999</v>
       </c>
       <c r="X6">
         <f t="shared" si="0"/>
-        <v>61470</v>
+        <v>221.292</v>
       </c>
       <c r="Y6">
         <f t="shared" si="0"/>
-        <v>56726</v>
+        <v>204.21359999999999</v>
       </c>
       <c r="Z6">
         <f t="shared" si="0"/>
-        <v>57305</v>
+        <v>206.298</v>
       </c>
       <c r="AA6">
         <f t="shared" si="0"/>
-        <v>57196</v>
+        <v>205.90559999999999</v>
       </c>
       <c r="AB6">
         <f t="shared" si="0"/>
-        <v>58633</v>
+        <v>211.0788</v>
       </c>
       <c r="AC6">
         <f t="shared" si="0"/>
-        <v>58039</v>
+        <v>208.94039999999998</v>
       </c>
       <c r="AD6">
         <f t="shared" si="0"/>
-        <v>55766</v>
+        <v>200.7576</v>
       </c>
       <c r="AE6">
         <f t="shared" si="0"/>
-        <v>58349</v>
+        <v>210.0564</v>
       </c>
       <c r="AF6">
         <f t="shared" si="0"/>
-        <v>58299</v>
+        <v>209.87639999999999</v>
       </c>
       <c r="AG6">
         <f t="shared" si="0"/>
-        <v>56564</v>
+        <v>203.63039999999998</v>
       </c>
       <c r="AH6">
         <f t="shared" si="0"/>
-        <v>58590</v>
+        <v>210.92400000000001</v>
       </c>
       <c r="AI6">
         <f t="shared" si="0"/>
-        <v>56873</v>
+        <v>204.74279999999999</v>
       </c>
       <c r="AJ6">
         <f t="shared" si="0"/>
-        <v>54532</v>
+        <v>196.3152</v>
       </c>
     </row>
     <row r="7" spans="1:36" x14ac:dyDescent="0.3">
@@ -9377,108 +9401,108 @@
       <c r="D7" t="s">
         <v>5</v>
       </c>
-      <c r="K7" s="1" t="s">
+      <c r="K7" t="s">
         <v>9</v>
       </c>
       <c r="L7">
         <f t="shared" si="1"/>
-        <v>31807</v>
+        <v>114.5052</v>
       </c>
       <c r="M7">
         <f t="shared" si="0"/>
-        <v>43864</v>
+        <v>157.91040000000001</v>
       </c>
       <c r="N7">
         <f t="shared" si="0"/>
-        <v>26270</v>
+        <v>94.572000000000003</v>
       </c>
       <c r="O7">
         <f t="shared" si="0"/>
-        <v>43897</v>
+        <v>158.0292</v>
       </c>
       <c r="P7">
         <f t="shared" si="0"/>
-        <v>34439</v>
+        <v>123.9804</v>
       </c>
       <c r="Q7">
         <f t="shared" si="0"/>
-        <v>23025</v>
+        <v>82.89</v>
       </c>
       <c r="R7">
         <f t="shared" si="0"/>
-        <v>29831</v>
+        <v>107.3916</v>
       </c>
       <c r="S7">
         <f t="shared" si="0"/>
-        <v>30522</v>
+        <v>109.8792</v>
       </c>
       <c r="T7">
         <f t="shared" si="0"/>
-        <v>26144</v>
+        <v>94.118399999999994</v>
       </c>
       <c r="U7">
         <f t="shared" si="0"/>
-        <v>29162</v>
+        <v>104.9832</v>
       </c>
       <c r="V7">
         <f t="shared" si="0"/>
-        <v>45511</v>
+        <v>163.83959999999999</v>
       </c>
       <c r="W7">
         <f t="shared" si="0"/>
-        <v>32911</v>
+        <v>118.47959999999999</v>
       </c>
       <c r="X7">
         <f t="shared" si="0"/>
-        <v>24162</v>
+        <v>86.983199999999997</v>
       </c>
       <c r="Y7">
         <f t="shared" si="0"/>
-        <v>41052</v>
+        <v>147.78719999999998</v>
       </c>
       <c r="Z7">
         <f t="shared" si="0"/>
-        <v>42969</v>
+        <v>154.6884</v>
       </c>
       <c r="AA7">
         <f t="shared" si="0"/>
-        <v>31368</v>
+        <v>112.92479999999999</v>
       </c>
       <c r="AB7">
         <f t="shared" si="0"/>
-        <v>39865</v>
+        <v>143.51400000000001</v>
       </c>
       <c r="AC7">
         <f t="shared" si="0"/>
-        <v>21070</v>
+        <v>75.852000000000004</v>
       </c>
       <c r="AD7">
         <f t="shared" si="0"/>
-        <v>36803</v>
+        <v>132.49080000000001</v>
       </c>
       <c r="AE7">
         <f t="shared" si="0"/>
-        <v>26874</v>
+        <v>96.746399999999994</v>
       </c>
       <c r="AF7">
         <f t="shared" si="0"/>
-        <v>33998</v>
+        <v>122.39279999999999</v>
       </c>
       <c r="AG7">
         <f t="shared" si="0"/>
-        <v>32847</v>
+        <v>118.2492</v>
       </c>
       <c r="AH7">
         <f t="shared" si="0"/>
-        <v>22102</v>
+        <v>79.5672</v>
       </c>
       <c r="AI7">
         <f t="shared" si="0"/>
-        <v>31105</v>
+        <v>111.97799999999999</v>
       </c>
       <c r="AJ7">
         <f t="shared" si="0"/>
-        <v>40821</v>
+        <v>146.9556</v>
       </c>
     </row>
     <row r="8" spans="1:36" x14ac:dyDescent="0.3">
@@ -9494,7 +9518,7 @@
       <c r="D8" t="s">
         <v>5</v>
       </c>
-      <c r="K8" s="1" t="s">
+      <c r="K8" t="s">
         <v>10</v>
       </c>
       <c r="L8">
@@ -9575,27 +9599,27 @@
       </c>
       <c r="AE8">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>7.1999999999999995E-2</v>
       </c>
       <c r="AF8">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>9.7199999999999995E-2</v>
       </c>
       <c r="AG8">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>6.8400000000000002E-2</v>
       </c>
       <c r="AH8">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>8.2799999999999999E-2</v>
       </c>
       <c r="AI8">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>4.3200000000000002E-2</v>
       </c>
       <c r="AJ8">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>2.8799999999999999E-2</v>
       </c>
     </row>
     <row r="9" spans="1:36" x14ac:dyDescent="0.3">
@@ -9611,108 +9635,108 @@
       <c r="D9" t="s">
         <v>5</v>
       </c>
-      <c r="K9" s="1" t="s">
+      <c r="K9" t="s">
         <v>11</v>
       </c>
       <c r="L9">
         <f t="shared" si="1"/>
-        <v>1159</v>
+        <v>4.1723999999999997</v>
       </c>
       <c r="M9">
         <f t="shared" si="0"/>
-        <v>1297</v>
+        <v>4.6692</v>
       </c>
       <c r="N9">
         <f t="shared" si="0"/>
-        <v>2303</v>
+        <v>8.2907999999999991</v>
       </c>
       <c r="O9">
         <f t="shared" si="0"/>
-        <v>2853</v>
+        <v>10.270799999999999</v>
       </c>
       <c r="P9">
         <f t="shared" si="0"/>
-        <v>3039</v>
+        <v>10.9404</v>
       </c>
       <c r="Q9">
         <f t="shared" si="0"/>
-        <v>2202</v>
+        <v>7.9272</v>
       </c>
       <c r="R9">
         <f t="shared" si="0"/>
-        <v>2173</v>
+        <v>7.8228</v>
       </c>
       <c r="S9">
         <f t="shared" si="0"/>
-        <v>2161</v>
+        <v>7.7795999999999994</v>
       </c>
       <c r="T9">
         <f t="shared" si="0"/>
-        <v>2473</v>
+        <v>8.9027999999999992</v>
       </c>
       <c r="U9">
         <f t="shared" si="0"/>
-        <v>2727</v>
+        <v>9.8171999999999997</v>
       </c>
       <c r="V9">
         <f t="shared" si="0"/>
-        <v>3356</v>
+        <v>12.0816</v>
       </c>
       <c r="W9">
         <f t="shared" si="0"/>
-        <v>3814</v>
+        <v>13.730399999999999</v>
       </c>
       <c r="X9">
         <f t="shared" si="0"/>
-        <v>4262</v>
+        <v>15.3432</v>
       </c>
       <c r="Y9">
         <f t="shared" si="0"/>
-        <v>5116</v>
+        <v>18.4176</v>
       </c>
       <c r="Z9">
         <f t="shared" si="0"/>
-        <v>4728</v>
+        <v>17.020800000000001</v>
       </c>
       <c r="AA9">
         <f t="shared" si="0"/>
-        <v>4996</v>
+        <v>17.985599999999998</v>
       </c>
       <c r="AB9">
         <f t="shared" si="0"/>
-        <v>4954</v>
+        <v>17.834399999999999</v>
       </c>
       <c r="AC9">
         <f t="shared" si="0"/>
-        <v>5306</v>
+        <v>19.101600000000001</v>
       </c>
       <c r="AD9">
         <f t="shared" si="0"/>
-        <v>5156</v>
+        <v>18.561599999999999</v>
       </c>
       <c r="AE9">
         <f t="shared" si="0"/>
-        <v>4802</v>
+        <v>17.287199999999999</v>
       </c>
       <c r="AF9">
         <f t="shared" si="0"/>
-        <v>5435</v>
+        <v>19.565999999999999</v>
       </c>
       <c r="AG9">
         <f t="shared" si="0"/>
-        <v>6088</v>
+        <v>21.916799999999999</v>
       </c>
       <c r="AH9">
         <f t="shared" si="0"/>
-        <v>5935</v>
+        <v>21.366</v>
       </c>
       <c r="AI9">
         <f t="shared" si="0"/>
-        <v>5062</v>
+        <v>18.223199999999999</v>
       </c>
       <c r="AJ9">
         <f t="shared" si="0"/>
-        <v>5319</v>
+        <v>19.148399999999999</v>
       </c>
     </row>
     <row r="10" spans="1:36" x14ac:dyDescent="0.3">
@@ -9728,108 +9752,108 @@
       <c r="D10" t="s">
         <v>5</v>
       </c>
-      <c r="K10" s="1" t="s">
+      <c r="K10" t="s">
         <v>12</v>
       </c>
       <c r="L10">
         <f t="shared" si="1"/>
-        <v>941</v>
+        <v>3.3875999999999999</v>
       </c>
       <c r="M10">
         <f t="shared" si="0"/>
-        <v>667</v>
+        <v>2.4011999999999998</v>
       </c>
       <c r="N10">
         <f t="shared" si="0"/>
-        <v>566</v>
+        <v>2.0375999999999999</v>
       </c>
       <c r="O10">
         <f t="shared" si="0"/>
-        <v>661</v>
+        <v>2.3795999999999999</v>
       </c>
       <c r="P10">
         <f t="shared" si="0"/>
-        <v>582</v>
+        <v>2.0951999999999997</v>
       </c>
       <c r="Q10">
         <f t="shared" si="0"/>
-        <v>902</v>
+        <v>3.2471999999999999</v>
       </c>
       <c r="R10">
         <f t="shared" si="0"/>
-        <v>1202</v>
+        <v>4.3271999999999995</v>
       </c>
       <c r="S10">
         <f t="shared" si="0"/>
-        <v>1474</v>
+        <v>5.3064</v>
       </c>
       <c r="T10">
         <f t="shared" si="0"/>
-        <v>1564</v>
+        <v>5.6303999999999998</v>
       </c>
       <c r="U10">
         <f t="shared" si="0"/>
-        <v>1522</v>
+        <v>5.4791999999999996</v>
       </c>
       <c r="V10">
         <f t="shared" si="0"/>
-        <v>1318</v>
+        <v>4.7447999999999997</v>
       </c>
       <c r="W10">
         <f t="shared" si="0"/>
-        <v>1590</v>
+        <v>5.7240000000000002</v>
       </c>
       <c r="X10">
         <f t="shared" si="0"/>
-        <v>1430</v>
+        <v>5.1479999999999997</v>
       </c>
       <c r="Y10">
         <f t="shared" si="0"/>
-        <v>1364</v>
+        <v>4.9104000000000001</v>
       </c>
       <c r="Z10">
         <f t="shared" si="0"/>
-        <v>1372</v>
+        <v>4.9391999999999996</v>
       </c>
       <c r="AA10">
         <f t="shared" si="0"/>
-        <v>1536</v>
+        <v>5.5296000000000003</v>
       </c>
       <c r="AB10">
         <f t="shared" si="0"/>
-        <v>1470</v>
+        <v>5.2919999999999998</v>
       </c>
       <c r="AC10">
         <f t="shared" si="0"/>
-        <v>1544</v>
+        <v>5.5583999999999998</v>
       </c>
       <c r="AD10">
         <f t="shared" si="0"/>
-        <v>1775</v>
+        <v>6.39</v>
       </c>
       <c r="AE10">
         <f t="shared" si="0"/>
-        <v>1755</v>
+        <v>6.3179999999999996</v>
       </c>
       <c r="AF10">
         <f t="shared" si="0"/>
-        <v>1751</v>
+        <v>6.3035999999999994</v>
       </c>
       <c r="AG10">
         <f t="shared" si="0"/>
-        <v>1795</v>
+        <v>6.4619999999999997</v>
       </c>
       <c r="AH10">
         <f t="shared" si="0"/>
-        <v>1754</v>
+        <v>6.3144</v>
       </c>
       <c r="AI10">
         <f t="shared" si="0"/>
-        <v>1683</v>
+        <v>6.0587999999999997</v>
       </c>
       <c r="AJ10">
         <f t="shared" si="0"/>
-        <v>1686</v>
+        <v>6.0695999999999994</v>
       </c>
     </row>
     <row r="11" spans="1:36" x14ac:dyDescent="0.3">
@@ -9845,108 +9869,108 @@
       <c r="D11" t="s">
         <v>5</v>
       </c>
-      <c r="K11" s="1" t="s">
+      <c r="K11" t="s">
         <v>13</v>
       </c>
       <c r="L11">
         <f t="shared" si="1"/>
-        <v>4727</v>
+        <v>17.017199999999999</v>
       </c>
       <c r="M11">
         <f t="shared" si="0"/>
-        <v>6759</v>
+        <v>24.3324</v>
       </c>
       <c r="N11">
         <f t="shared" si="0"/>
-        <v>9342</v>
+        <v>33.6312</v>
       </c>
       <c r="O11">
         <f t="shared" si="0"/>
-        <v>12075</v>
+        <v>43.47</v>
       </c>
       <c r="P11">
         <f t="shared" si="0"/>
-        <v>15700</v>
+        <v>56.519999999999996</v>
       </c>
       <c r="Q11">
         <f t="shared" si="0"/>
-        <v>21176</v>
+        <v>76.233599999999996</v>
       </c>
       <c r="R11">
         <f t="shared" si="0"/>
-        <v>23297</v>
+        <v>83.869199999999992</v>
       </c>
       <c r="S11">
         <f t="shared" si="0"/>
-        <v>27568</v>
+        <v>99.244799999999998</v>
       </c>
       <c r="T11">
         <f t="shared" si="0"/>
-        <v>32946</v>
+        <v>118.6056</v>
       </c>
       <c r="U11">
         <f t="shared" si="0"/>
-        <v>38117</v>
+        <v>137.22120000000001</v>
       </c>
       <c r="V11">
         <f t="shared" si="0"/>
-        <v>44271</v>
+        <v>159.37559999999999</v>
       </c>
       <c r="W11">
         <f t="shared" si="0"/>
-        <v>42918</v>
+        <v>154.50479999999999</v>
       </c>
       <c r="X11">
         <f t="shared" si="0"/>
-        <v>49472</v>
+        <v>178.0992</v>
       </c>
       <c r="Y11">
         <f t="shared" si="0"/>
-        <v>55646</v>
+        <v>200.32560000000001</v>
       </c>
       <c r="Z11">
         <f t="shared" si="0"/>
-        <v>52013</v>
+        <v>187.24680000000001</v>
       </c>
       <c r="AA11">
         <f t="shared" si="0"/>
-        <v>49325</v>
+        <v>177.57</v>
       </c>
       <c r="AB11">
         <f t="shared" si="0"/>
-        <v>48905</v>
+        <v>176.05799999999999</v>
       </c>
       <c r="AC11">
         <f t="shared" si="0"/>
-        <v>49127</v>
+        <v>176.85720000000001</v>
       </c>
       <c r="AD11">
         <f t="shared" si="0"/>
-        <v>50896</v>
+        <v>183.22559999999999</v>
       </c>
       <c r="AE11">
         <f t="shared" si="0"/>
-        <v>55647</v>
+        <v>200.32919999999999</v>
       </c>
       <c r="AF11">
         <f t="shared" si="0"/>
-        <v>56444</v>
+        <v>203.19839999999999</v>
       </c>
       <c r="AG11">
         <f t="shared" si="0"/>
-        <v>62061</v>
+        <v>223.4196</v>
       </c>
       <c r="AH11">
         <f t="shared" si="0"/>
-        <v>62784</v>
+        <v>226.0224</v>
       </c>
       <c r="AI11">
         <f t="shared" si="0"/>
-        <v>64275</v>
+        <v>231.39</v>
       </c>
       <c r="AJ11">
         <f t="shared" si="0"/>
-        <v>62089</v>
+        <v>223.5204</v>
       </c>
     </row>
     <row r="12" spans="1:36" x14ac:dyDescent="0.3">
@@ -9962,108 +9986,108 @@
       <c r="D12" t="s">
         <v>5</v>
       </c>
-      <c r="K12" s="1" t="s">
+      <c r="K12" t="s">
         <v>14</v>
       </c>
       <c r="L12">
         <f t="shared" si="1"/>
-        <v>14</v>
+        <v>5.04E-2</v>
       </c>
       <c r="M12">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>6.1199999999999997E-2</v>
       </c>
       <c r="N12">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>6.4799999999999996E-2</v>
       </c>
       <c r="O12">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>7.1999999999999995E-2</v>
       </c>
       <c r="P12">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>8.2799999999999999E-2</v>
       </c>
       <c r="Q12">
         <f t="shared" si="0"/>
-        <v>47</v>
+        <v>0.16919999999999999</v>
       </c>
       <c r="R12">
         <f t="shared" si="0"/>
-        <v>124</v>
+        <v>0.44639999999999996</v>
       </c>
       <c r="S12">
         <f t="shared" si="0"/>
-        <v>507</v>
+        <v>1.8251999999999999</v>
       </c>
       <c r="T12">
         <f t="shared" si="0"/>
-        <v>2562</v>
+        <v>9.2232000000000003</v>
       </c>
       <c r="U12">
         <f t="shared" si="0"/>
-        <v>5961</v>
+        <v>21.459599999999998</v>
       </c>
       <c r="V12">
         <f t="shared" si="0"/>
-        <v>6425</v>
+        <v>23.13</v>
       </c>
       <c r="W12">
         <f t="shared" si="0"/>
-        <v>7440</v>
+        <v>26.783999999999999</v>
       </c>
       <c r="X12">
         <f t="shared" si="0"/>
-        <v>8192</v>
+        <v>29.491199999999999</v>
       </c>
       <c r="Y12">
         <f t="shared" si="0"/>
-        <v>8326</v>
+        <v>29.973599999999998</v>
       </c>
       <c r="Z12">
         <f t="shared" si="0"/>
-        <v>8217</v>
+        <v>29.581199999999999</v>
       </c>
       <c r="AA12">
         <f t="shared" si="0"/>
-        <v>8266</v>
+        <v>29.7576</v>
       </c>
       <c r="AB12">
         <f t="shared" si="0"/>
-        <v>8063</v>
+        <v>29.026799999999998</v>
       </c>
       <c r="AC12">
         <f t="shared" si="0"/>
-        <v>8514</v>
+        <v>30.650399999999998</v>
       </c>
       <c r="AD12">
         <f t="shared" si="0"/>
-        <v>7877</v>
+        <v>28.357199999999999</v>
       </c>
       <c r="AE12">
         <f t="shared" si="0"/>
-        <v>9420</v>
+        <v>33.911999999999999</v>
       </c>
       <c r="AF12">
         <f t="shared" si="0"/>
-        <v>15675</v>
+        <v>56.43</v>
       </c>
       <c r="AG12">
         <f t="shared" si="0"/>
-        <v>21922</v>
+        <v>78.919200000000004</v>
       </c>
       <c r="AH12">
         <f t="shared" si="0"/>
-        <v>31187</v>
+        <v>112.2732</v>
       </c>
       <c r="AI12">
         <f t="shared" si="0"/>
-        <v>43421</v>
+        <v>156.31559999999999</v>
       </c>
       <c r="AJ12">
         <f t="shared" si="0"/>
-        <v>53752</v>
+        <v>193.50719999999998</v>
       </c>
     </row>
     <row r="13" spans="1:36" x14ac:dyDescent="0.3">
@@ -10079,7 +10103,7 @@
       <c r="D13" t="s">
         <v>5</v>
       </c>
-      <c r="K13" s="1" t="s">
+      <c r="K13" t="s">
         <v>15</v>
       </c>
       <c r="L13">
@@ -10112,75 +10136,75 @@
       </c>
       <c r="S13">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>2.8799999999999999E-2</v>
       </c>
       <c r="T13">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>5.7599999999999998E-2</v>
       </c>
       <c r="U13">
         <f t="shared" si="0"/>
-        <v>103</v>
+        <v>0.37079999999999996</v>
       </c>
       <c r="V13">
         <f t="shared" si="0"/>
-        <v>761</v>
+        <v>2.7395999999999998</v>
       </c>
       <c r="W13">
         <f t="shared" si="0"/>
-        <v>1959</v>
+        <v>7.0523999999999996</v>
       </c>
       <c r="X13">
         <f t="shared" si="0"/>
-        <v>3775</v>
+        <v>13.59</v>
       </c>
       <c r="Y13">
         <f t="shared" si="0"/>
-        <v>4769</v>
+        <v>17.168399999999998</v>
       </c>
       <c r="Z13">
         <f t="shared" si="0"/>
-        <v>5454</v>
+        <v>19.634399999999999</v>
       </c>
       <c r="AA13">
         <f t="shared" si="0"/>
-        <v>5593</v>
+        <v>20.134799999999998</v>
       </c>
       <c r="AB13">
-        <f t="shared" ref="AB13:AJ20" si="2">SUMIFS($B:$B,$A:$A,$K13,$C:$C,AB$2)</f>
-        <v>5579</v>
+        <f t="shared" ref="AB13:AJ14" si="2">SUMIFS($B:$B,$A:$A,$K13,$C:$C,AB$2)*0.0036</f>
+        <v>20.084399999999999</v>
       </c>
       <c r="AC13">
         <f t="shared" si="2"/>
-        <v>5883</v>
+        <v>21.178799999999999</v>
       </c>
       <c r="AD13">
         <f t="shared" si="2"/>
-        <v>4867</v>
+        <v>17.5212</v>
       </c>
       <c r="AE13">
         <f t="shared" si="2"/>
-        <v>5683</v>
+        <v>20.4588</v>
       </c>
       <c r="AF13">
         <f t="shared" si="2"/>
-        <v>4992</v>
+        <v>17.9712</v>
       </c>
       <c r="AG13">
         <f t="shared" si="2"/>
-        <v>5176</v>
+        <v>18.633599999999998</v>
       </c>
       <c r="AH13">
         <f t="shared" si="2"/>
-        <v>4536</v>
+        <v>16.329599999999999</v>
       </c>
       <c r="AI13">
         <f t="shared" si="2"/>
-        <v>5165</v>
+        <v>18.594000000000001</v>
       </c>
       <c r="AJ13">
         <f t="shared" si="2"/>
-        <v>4540</v>
+        <v>16.344000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:36" x14ac:dyDescent="0.3">
@@ -10196,7 +10220,7 @@
       <c r="D14" t="s">
         <v>5</v>
       </c>
-      <c r="K14" s="1" t="s">
+      <c r="K14" t="s">
         <v>16</v>
       </c>
       <c r="L14">
@@ -10217,39 +10241,39 @@
       </c>
       <c r="P14">
         <f t="shared" si="1"/>
-        <v>2963</v>
+        <v>10.6668</v>
       </c>
       <c r="Q14">
         <f t="shared" si="1"/>
-        <v>4994</v>
+        <v>17.978400000000001</v>
       </c>
       <c r="R14">
         <f t="shared" si="1"/>
-        <v>329</v>
+        <v>1.1843999999999999</v>
       </c>
       <c r="S14">
         <f t="shared" si="1"/>
-        <v>324</v>
+        <v>1.1663999999999999</v>
       </c>
       <c r="T14">
         <f t="shared" si="1"/>
-        <v>307</v>
+        <v>1.1052</v>
       </c>
       <c r="U14">
         <f t="shared" si="1"/>
-        <v>341</v>
+        <v>1.2276</v>
       </c>
       <c r="V14">
         <f t="shared" si="1"/>
-        <v>159</v>
+        <v>0.57240000000000002</v>
       </c>
       <c r="W14">
         <f t="shared" si="1"/>
-        <v>171</v>
+        <v>0.61560000000000004</v>
       </c>
       <c r="X14">
         <f t="shared" si="1"/>
-        <v>175</v>
+        <v>0.63</v>
       </c>
       <c r="Y14">
         <f t="shared" si="1"/>
@@ -10261,43 +10285,43 @@
       </c>
       <c r="AA14">
         <f t="shared" si="1"/>
-        <v>216</v>
+        <v>0.77759999999999996</v>
       </c>
       <c r="AB14">
         <f t="shared" si="2"/>
-        <v>108</v>
+        <v>0.38879999999999998</v>
       </c>
       <c r="AC14">
         <f t="shared" si="2"/>
-        <v>91</v>
+        <v>0.3276</v>
       </c>
       <c r="AD14">
         <f t="shared" si="2"/>
-        <v>94</v>
+        <v>0.33839999999999998</v>
       </c>
       <c r="AE14">
         <f t="shared" si="2"/>
-        <v>139</v>
+        <v>0.50039999999999996</v>
       </c>
       <c r="AF14">
         <f t="shared" si="2"/>
-        <v>160</v>
+        <v>0.57599999999999996</v>
       </c>
       <c r="AG14">
         <f t="shared" si="2"/>
-        <v>280</v>
+        <v>1.008</v>
       </c>
       <c r="AH14">
         <f t="shared" si="2"/>
-        <v>282</v>
+        <v>1.0151999999999999</v>
       </c>
       <c r="AI14">
         <f t="shared" si="2"/>
-        <v>273</v>
+        <v>0.98280000000000001</v>
       </c>
       <c r="AJ14">
         <f t="shared" si="2"/>
-        <v>244</v>
+        <v>0.87839999999999996</v>
       </c>
     </row>
     <row r="15" spans="1:36" x14ac:dyDescent="0.3">
@@ -14365,104 +14389,104 @@
         <v>20</v>
       </c>
       <c r="J3">
-        <f>SUMIFS($B:$B,$A:$A,$I3,$C:$C,J$2)</f>
-        <v>12268</v>
+        <f>SUMIFS($B:$B,$A:$A,$I3,$C:$C,J$2)*0.0036</f>
+        <v>44.1648</v>
       </c>
       <c r="K3">
-        <f t="shared" ref="K3:AH4" si="0">SUMIFS($B:$B,$A:$A,$I3,$C:$C,K$2)</f>
-        <v>10177</v>
+        <f t="shared" ref="K3:AH4" si="0">SUMIFS($B:$B,$A:$A,$I3,$C:$C,K$2)*0.0036</f>
+        <v>36.6372</v>
       </c>
       <c r="L3">
         <f t="shared" si="0"/>
-        <v>12504</v>
+        <v>45.014400000000002</v>
       </c>
       <c r="M3">
         <f t="shared" si="0"/>
-        <v>9520</v>
+        <v>34.271999999999998</v>
       </c>
       <c r="N3">
         <f t="shared" si="0"/>
-        <v>8111</v>
+        <v>29.1996</v>
       </c>
       <c r="O3">
         <f t="shared" si="0"/>
-        <v>10212</v>
+        <v>36.763199999999998</v>
       </c>
       <c r="P3">
         <f t="shared" si="0"/>
-        <v>9093</v>
+        <v>32.7348</v>
       </c>
       <c r="Q3">
         <f t="shared" si="0"/>
-        <v>8773</v>
+        <v>31.582799999999999</v>
       </c>
       <c r="R3">
         <f t="shared" si="0"/>
-        <v>5881</v>
+        <v>21.171599999999998</v>
       </c>
       <c r="S3">
         <f t="shared" si="0"/>
-        <v>6751</v>
+        <v>24.303599999999999</v>
       </c>
       <c r="T3">
         <f t="shared" si="0"/>
-        <v>5206</v>
+        <v>18.741599999999998</v>
       </c>
       <c r="U3">
         <f t="shared" si="0"/>
-        <v>7932</v>
+        <v>28.555199999999999</v>
       </c>
       <c r="V3">
         <f t="shared" si="0"/>
-        <v>7787</v>
+        <v>28.033200000000001</v>
       </c>
       <c r="W3">
         <f t="shared" si="0"/>
-        <v>9887</v>
+        <v>35.593199999999996</v>
       </c>
       <c r="X3">
         <f t="shared" si="0"/>
-        <v>12310</v>
+        <v>44.315999999999995</v>
       </c>
       <c r="Y3">
         <f t="shared" si="0"/>
-        <v>14956</v>
+        <v>53.8416</v>
       </c>
       <c r="Z3">
         <f t="shared" si="0"/>
-        <v>21845</v>
+        <v>78.641999999999996</v>
       </c>
       <c r="AA3">
         <f t="shared" si="0"/>
-        <v>23762</v>
+        <v>85.543199999999999</v>
       </c>
       <c r="AB3">
         <f t="shared" si="0"/>
-        <v>24018</v>
+        <v>86.464799999999997</v>
       </c>
       <c r="AC3">
         <f t="shared" si="0"/>
-        <v>18720</v>
+        <v>67.391999999999996</v>
       </c>
       <c r="AD3">
         <f t="shared" si="0"/>
-        <v>17928</v>
+        <v>64.540800000000004</v>
       </c>
       <c r="AE3">
         <f t="shared" si="0"/>
-        <v>17411</v>
+        <v>62.679600000000001</v>
       </c>
       <c r="AF3">
         <f t="shared" si="0"/>
-        <v>8031</v>
+        <v>28.9116</v>
       </c>
       <c r="AG3">
         <f t="shared" si="0"/>
-        <v>11316</v>
+        <v>40.7376</v>
       </c>
       <c r="AH3">
         <f t="shared" si="0"/>
-        <v>14354</v>
+        <v>51.674399999999999</v>
       </c>
     </row>
     <row r="4" spans="1:34" x14ac:dyDescent="0.3">
@@ -14482,104 +14506,104 @@
         <v>21</v>
       </c>
       <c r="J4">
-        <f>SUMIFS($B:$B,$A:$A,$I4,$C:$C,J$2)</f>
-        <v>-7827</v>
+        <f>SUMIFS($B:$B,$A:$A,$I4,$C:$C,J$2)*0.0036</f>
+        <v>-28.177199999999999</v>
       </c>
       <c r="K4">
         <f t="shared" si="0"/>
-        <v>-6727</v>
+        <v>-24.217199999999998</v>
       </c>
       <c r="L4">
         <f t="shared" si="0"/>
-        <v>-7175</v>
+        <v>-25.83</v>
       </c>
       <c r="M4">
         <f t="shared" si="0"/>
-        <v>-8257</v>
+        <v>-29.725200000000001</v>
       </c>
       <c r="N4">
         <f t="shared" si="0"/>
-        <v>-11139</v>
+        <v>-40.1004</v>
       </c>
       <c r="O4">
         <f t="shared" si="0"/>
-        <v>-11555</v>
+        <v>-41.597999999999999</v>
       </c>
       <c r="P4">
         <f t="shared" si="0"/>
-        <v>-12373</v>
+        <v>-44.5428</v>
       </c>
       <c r="Q4">
         <f t="shared" si="0"/>
-        <v>-14524</v>
+        <v>-52.2864</v>
       </c>
       <c r="R4">
         <f t="shared" si="0"/>
-        <v>-16920</v>
+        <v>-60.911999999999999</v>
       </c>
       <c r="S4">
         <f t="shared" si="0"/>
-        <v>-14855</v>
+        <v>-53.478000000000002</v>
       </c>
       <c r="T4">
         <f t="shared" si="0"/>
-        <v>-13539</v>
+        <v>-48.740400000000001</v>
       </c>
       <c r="U4">
         <f t="shared" si="0"/>
-        <v>-14023</v>
+        <v>-50.482799999999997</v>
       </c>
       <c r="V4">
         <f t="shared" si="0"/>
-        <v>-18986</v>
+        <v>-68.349599999999995</v>
       </c>
       <c r="W4">
         <f t="shared" si="0"/>
-        <v>-16638</v>
+        <v>-59.896799999999999</v>
       </c>
       <c r="X4">
         <f t="shared" si="0"/>
-        <v>-15716</v>
+        <v>-56.577599999999997</v>
       </c>
       <c r="Y4">
         <f t="shared" si="0"/>
-        <v>-15089</v>
+        <v>-54.320399999999999</v>
       </c>
       <c r="Z4">
         <f t="shared" si="0"/>
-        <v>-14178</v>
+        <v>-51.040799999999997</v>
       </c>
       <c r="AA4">
         <f t="shared" si="0"/>
-        <v>-14593</v>
+        <v>-52.534799999999997</v>
       </c>
       <c r="AB4">
         <f t="shared" si="0"/>
-        <v>-12916</v>
+        <v>-46.497599999999998</v>
       </c>
       <c r="AC4">
         <f t="shared" si="0"/>
-        <v>-11858</v>
+        <v>-42.688800000000001</v>
       </c>
       <c r="AD4">
         <f t="shared" si="0"/>
-        <v>-14648</v>
+        <v>-52.732799999999997</v>
       </c>
       <c r="AE4">
         <f t="shared" si="0"/>
-        <v>-16558</v>
+        <v>-59.608799999999995</v>
       </c>
       <c r="AF4">
         <f t="shared" si="0"/>
-        <v>-27833</v>
+        <v>-100.19879999999999</v>
       </c>
       <c r="AG4">
         <f t="shared" si="0"/>
-        <v>-25272</v>
+        <v>-90.979199999999992</v>
       </c>
       <c r="AH4">
         <f t="shared" si="0"/>
-        <v>-24581</v>
+        <v>-88.491599999999991</v>
       </c>
     </row>
     <row r="5" spans="1:34" x14ac:dyDescent="0.3">
@@ -14600,103 +14624,103 @@
       </c>
       <c r="J5">
         <f>SUM(J3,J4)</f>
-        <v>4441</v>
+        <v>15.9876</v>
       </c>
       <c r="K5">
         <f>SUM(K3,K4)</f>
-        <v>3450</v>
+        <v>12.420000000000002</v>
       </c>
       <c r="L5">
         <f t="shared" ref="L5:AH5" si="1">SUM(L3,L4)</f>
-        <v>5329</v>
+        <v>19.184400000000004</v>
       </c>
       <c r="M5">
         <f t="shared" si="1"/>
-        <v>1263</v>
+        <v>4.5467999999999975</v>
       </c>
       <c r="N5">
         <f t="shared" si="1"/>
-        <v>-3028</v>
+        <v>-10.9008</v>
       </c>
       <c r="O5">
         <f t="shared" si="1"/>
-        <v>-1343</v>
+        <v>-4.8348000000000013</v>
       </c>
       <c r="P5">
         <f t="shared" si="1"/>
-        <v>-3280</v>
+        <v>-11.808</v>
       </c>
       <c r="Q5">
         <f t="shared" si="1"/>
-        <v>-5751</v>
+        <v>-20.703600000000002</v>
       </c>
       <c r="R5">
         <f t="shared" si="1"/>
-        <v>-11039</v>
+        <v>-39.740400000000001</v>
       </c>
       <c r="S5">
         <f t="shared" si="1"/>
-        <v>-8104</v>
+        <v>-29.174400000000002</v>
       </c>
       <c r="T5">
         <f t="shared" si="1"/>
-        <v>-8333</v>
+        <v>-29.998800000000003</v>
       </c>
       <c r="U5">
         <f t="shared" si="1"/>
-        <v>-6091</v>
+        <v>-21.927599999999998</v>
       </c>
       <c r="V5">
         <f t="shared" si="1"/>
-        <v>-11199</v>
+        <v>-40.316399999999994</v>
       </c>
       <c r="W5">
         <f t="shared" si="1"/>
-        <v>-6751</v>
+        <v>-24.303600000000003</v>
       </c>
       <c r="X5">
         <f t="shared" si="1"/>
-        <v>-3406</v>
+        <v>-12.261600000000001</v>
       </c>
       <c r="Y5">
         <f t="shared" si="1"/>
-        <v>-133</v>
+        <v>-0.47879999999999967</v>
       </c>
       <c r="Z5">
         <f t="shared" si="1"/>
-        <v>7667</v>
+        <v>27.601199999999999</v>
       </c>
       <c r="AA5">
         <f t="shared" si="1"/>
-        <v>9169</v>
+        <v>33.008400000000002</v>
       </c>
       <c r="AB5">
         <f t="shared" si="1"/>
-        <v>11102</v>
+        <v>39.967199999999998</v>
       </c>
       <c r="AC5">
         <f t="shared" si="1"/>
-        <v>6862</v>
+        <v>24.703199999999995</v>
       </c>
       <c r="AD5">
         <f t="shared" si="1"/>
-        <v>3280</v>
+        <v>11.808000000000007</v>
       </c>
       <c r="AE5">
         <f t="shared" si="1"/>
-        <v>853</v>
+        <v>3.0708000000000055</v>
       </c>
       <c r="AF5">
         <f t="shared" si="1"/>
-        <v>-19802</v>
+        <v>-71.287199999999984</v>
       </c>
       <c r="AG5">
         <f t="shared" si="1"/>
-        <v>-13956</v>
+        <v>-50.241599999999991</v>
       </c>
       <c r="AH5">
         <f t="shared" si="1"/>
-        <v>-10227</v>
+        <v>-36.817199999999993</v>
       </c>
     </row>
     <row r="6" spans="1:34" x14ac:dyDescent="0.3">
@@ -15475,99 +15499,99 @@
       <c r="I3" t="s">
         <v>4</v>
       </c>
-      <c r="J3" s="3">
+      <c r="J3" s="2">
         <f>SUMIFS($B:$B,$A:$A,$I3,$C:$C,J$2)</f>
         <v>75.856999999999999</v>
       </c>
-      <c r="K3" s="3">
+      <c r="K3" s="2">
         <f t="shared" ref="K3:AG6" si="0">SUMIFS($B:$B,$A:$A,$I3,$C:$C,K$2)</f>
         <v>67.123999999999995</v>
       </c>
-      <c r="L3" s="3">
+      <c r="L3" s="2">
         <f t="shared" si="0"/>
         <v>76.909000000000006</v>
       </c>
-      <c r="M3" s="3">
+      <c r="M3" s="2">
         <f t="shared" si="0"/>
         <v>70.673000000000002</v>
       </c>
-      <c r="N3" s="3">
+      <c r="N3" s="2">
         <f t="shared" si="0"/>
         <v>73.147000000000006</v>
       </c>
-      <c r="O3" s="3">
+      <c r="O3" s="2">
         <f t="shared" si="0"/>
         <v>73.171999999999997</v>
       </c>
-      <c r="P3" s="3">
+      <c r="P3" s="2">
         <f t="shared" si="0"/>
         <v>62.594999999999999</v>
       </c>
-      <c r="Q3" s="3">
+      <c r="Q3" s="2">
         <f t="shared" si="0"/>
         <v>71.436000000000007</v>
       </c>
-      <c r="R3" s="3">
+      <c r="R3" s="2">
         <f t="shared" si="0"/>
         <v>46.113999999999997</v>
       </c>
-      <c r="S3" s="3">
+      <c r="S3" s="2">
         <f t="shared" si="0"/>
         <v>35.026000000000003</v>
       </c>
-      <c r="T3" s="3">
+      <c r="T3" s="2">
         <f t="shared" si="0"/>
         <v>25.3</v>
       </c>
-      <c r="U3" s="3">
+      <c r="U3" s="2">
         <f t="shared" si="0"/>
         <v>44.177999999999997</v>
       </c>
-      <c r="V3" s="3">
+      <c r="V3" s="2">
         <f t="shared" si="0"/>
         <v>53.131999999999998</v>
       </c>
-      <c r="W3" s="3">
+      <c r="W3" s="2">
         <f t="shared" si="0"/>
         <v>38.640999999999998</v>
       </c>
-      <c r="X3" s="3">
+      <c r="X3" s="2">
         <f t="shared" si="0"/>
         <v>42.912999999999997</v>
       </c>
-      <c r="Y3" s="3">
+      <c r="Y3" s="2">
         <f t="shared" si="0"/>
         <v>49.125</v>
       </c>
-      <c r="Z3" s="3">
+      <c r="Z3" s="2">
         <f t="shared" si="0"/>
         <v>35.423000000000002</v>
       </c>
-      <c r="AA3" s="3">
+      <c r="AA3" s="2">
         <f t="shared" si="0"/>
         <v>44.04</v>
       </c>
-      <c r="AB3" s="3">
+      <c r="AB3" s="2">
         <f t="shared" si="0"/>
         <v>36.701999999999998</v>
       </c>
-      <c r="AC3" s="3">
+      <c r="AC3" s="2">
         <f t="shared" si="0"/>
         <v>14.217000000000001</v>
       </c>
-      <c r="AD3" s="3">
+      <c r="AD3" s="2">
         <f t="shared" si="0"/>
         <v>6.4909999999999997</v>
       </c>
-      <c r="AE3" s="3">
+      <c r="AE3" s="2">
         <f t="shared" si="0"/>
         <v>7.1749999999999998</v>
       </c>
-      <c r="AF3" s="3">
+      <c r="AF3" s="2">
         <f t="shared" si="0"/>
         <v>8.9670000000000005</v>
       </c>
-      <c r="AG3" s="3">
+      <c r="AG3" s="2">
         <f t="shared" si="0"/>
         <v>5.43</v>
       </c>
@@ -15588,99 +15612,99 @@
       <c r="I4" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="3">
+      <c r="J4" s="2">
         <f t="shared" ref="J4:J6" si="1">SUMIFS($B:$B,$A:$A,$I4,$C:$C,J$2)</f>
         <v>14.377000000000001</v>
       </c>
-      <c r="K4" s="3">
+      <c r="K4" s="2">
         <f t="shared" si="0"/>
         <v>16.364999999999998</v>
       </c>
-      <c r="L4" s="3">
+      <c r="L4" s="2">
         <f t="shared" si="0"/>
         <v>18.884</v>
       </c>
-      <c r="M4" s="3">
+      <c r="M4" s="2">
         <f t="shared" si="0"/>
         <v>15.645</v>
       </c>
-      <c r="N4" s="3">
+      <c r="N4" s="2">
         <f t="shared" si="0"/>
         <v>15.881</v>
       </c>
-      <c r="O4" s="3">
+      <c r="O4" s="2">
         <f t="shared" si="0"/>
         <v>17.149999999999999</v>
       </c>
-      <c r="P4" s="3">
+      <c r="P4" s="2">
         <f t="shared" si="0"/>
         <v>14.491</v>
       </c>
-      <c r="Q4" s="3">
+      <c r="Q4" s="2">
         <f t="shared" si="0"/>
         <v>13.48</v>
       </c>
-      <c r="R4" s="3">
+      <c r="R4" s="2">
         <f t="shared" si="0"/>
         <v>12.941000000000001</v>
       </c>
-      <c r="S4" s="3">
+      <c r="S4" s="2">
         <f t="shared" si="0"/>
         <v>12.904999999999999</v>
       </c>
-      <c r="T4" s="3">
+      <c r="T4" s="2">
         <f t="shared" si="0"/>
         <v>11.218</v>
       </c>
-      <c r="U4" s="3">
+      <c r="U4" s="2">
         <f t="shared" si="0"/>
         <v>10.52</v>
       </c>
-      <c r="V4" s="3">
+      <c r="V4" s="2">
         <f t="shared" si="0"/>
         <v>10.917</v>
       </c>
-      <c r="W4" s="3">
+      <c r="W4" s="2">
         <f t="shared" si="0"/>
         <v>9.4359999999999999</v>
       </c>
-      <c r="X4" s="3">
+      <c r="X4" s="2">
         <f t="shared" si="0"/>
         <v>9.9710000000000001</v>
       </c>
-      <c r="Y4" s="3">
+      <c r="Y4" s="2">
         <f t="shared" si="0"/>
         <v>11.891999999999999</v>
       </c>
-      <c r="Z4" s="3">
+      <c r="Z4" s="2">
         <f t="shared" si="0"/>
         <v>11.385999999999999</v>
       </c>
-      <c r="AA4" s="3">
+      <c r="AA4" s="2">
         <f t="shared" si="0"/>
         <v>10.512</v>
       </c>
-      <c r="AB4" s="3">
+      <c r="AB4" s="2">
         <f t="shared" si="0"/>
         <v>9.5120000000000005</v>
       </c>
-      <c r="AC4" s="3">
+      <c r="AC4" s="2">
         <f t="shared" si="0"/>
         <v>8.1780000000000008</v>
       </c>
-      <c r="AD4" s="3">
+      <c r="AD4" s="2">
         <f t="shared" si="0"/>
         <v>6.718</v>
       </c>
-      <c r="AE4" s="3">
+      <c r="AE4" s="2">
         <f t="shared" si="0"/>
         <v>6.3220000000000001</v>
       </c>
-      <c r="AF4" s="3">
+      <c r="AF4" s="2">
         <f t="shared" si="0"/>
         <v>6.7210000000000001</v>
       </c>
-      <c r="AG4" s="3">
+      <c r="AG4" s="2">
         <f t="shared" si="0"/>
         <v>6.24</v>
       </c>
@@ -15701,99 +15725,99 @@
       <c r="I5" t="s">
         <v>7</v>
       </c>
-      <c r="J5" s="3">
+      <c r="J5" s="2">
         <f t="shared" si="1"/>
         <v>6.3049999999999997</v>
       </c>
-      <c r="K5" s="3">
+      <c r="K5" s="2">
         <f t="shared" si="0"/>
         <v>6.5990000000000002</v>
       </c>
-      <c r="L5" s="3">
+      <c r="L5" s="2">
         <f t="shared" si="0"/>
         <v>10.571999999999999</v>
       </c>
-      <c r="M5" s="3">
+      <c r="M5" s="2">
         <f t="shared" si="0"/>
         <v>12.510999999999999</v>
       </c>
-      <c r="N5" s="3">
+      <c r="N5" s="2">
         <f t="shared" si="0"/>
         <v>18.088000000000001</v>
       </c>
-      <c r="O5" s="3">
+      <c r="O5" s="2">
         <f t="shared" si="0"/>
         <v>25.361999999999998</v>
       </c>
-      <c r="P5" s="3">
+      <c r="P5" s="2">
         <f t="shared" si="0"/>
         <v>32.406999999999996</v>
       </c>
-      <c r="Q5" s="3">
+      <c r="Q5" s="2">
         <f t="shared" si="0"/>
         <v>32.332999999999998</v>
       </c>
-      <c r="R5" s="3">
+      <c r="R5" s="2">
         <f t="shared" si="0"/>
         <v>42.374000000000002</v>
       </c>
-      <c r="S5" s="3">
+      <c r="S5" s="2">
         <f t="shared" si="0"/>
         <v>38.268000000000001</v>
       </c>
-      <c r="T5" s="3">
+      <c r="T5" s="2">
         <f t="shared" si="0"/>
         <v>34.341999999999999</v>
       </c>
-      <c r="U5" s="3">
+      <c r="U5" s="2">
         <f t="shared" si="0"/>
         <v>30.934000000000001</v>
       </c>
-      <c r="V5" s="3">
+      <c r="V5" s="2">
         <f t="shared" si="0"/>
         <v>26.295999999999999</v>
       </c>
-      <c r="W5" s="3">
+      <c r="W5" s="2">
         <f t="shared" si="0"/>
         <v>20.146999999999998</v>
       </c>
-      <c r="X5" s="3">
+      <c r="X5" s="2">
         <f t="shared" si="0"/>
         <v>16.512</v>
       </c>
-      <c r="Y5" s="3">
+      <c r="Y5" s="2">
         <f t="shared" si="0"/>
         <v>19.401</v>
       </c>
-      <c r="Z5" s="3">
+      <c r="Z5" s="2">
         <f t="shared" si="0"/>
         <v>19.056999999999999</v>
       </c>
-      <c r="AA5" s="3">
+      <c r="AA5" s="2">
         <f t="shared" si="0"/>
         <v>23.382999999999999</v>
       </c>
-      <c r="AB5" s="3">
+      <c r="AB5" s="2">
         <f t="shared" si="0"/>
         <v>21.161999999999999</v>
       </c>
-      <c r="AC5" s="3">
+      <c r="AC5" s="2">
         <f t="shared" si="0"/>
         <v>30.029</v>
       </c>
-      <c r="AD5" s="3">
+      <c r="AD5" s="2">
         <f t="shared" si="0"/>
         <v>25.106999999999999</v>
       </c>
-      <c r="AE5" s="3">
+      <c r="AE5" s="2">
         <f t="shared" si="0"/>
         <v>25.800999999999998</v>
       </c>
-      <c r="AF5" s="3">
+      <c r="AF5" s="2">
         <f t="shared" si="0"/>
         <v>32.043999999999997</v>
       </c>
-      <c r="AG5" s="3">
+      <c r="AG5" s="2">
         <f t="shared" si="0"/>
         <v>24.222999999999999</v>
       </c>
@@ -15814,99 +15838,99 @@
       <c r="I6" t="s">
         <v>25</v>
       </c>
-      <c r="J6" s="3">
+      <c r="J6" s="2">
         <f t="shared" si="1"/>
         <v>0.88800000000000001</v>
       </c>
-      <c r="K6" s="3">
+      <c r="K6" s="2">
         <f t="shared" si="0"/>
         <v>0.53400000000000003</v>
       </c>
-      <c r="L6" s="3">
+      <c r="L6" s="2">
         <f t="shared" si="0"/>
         <v>0.374</v>
       </c>
-      <c r="M6" s="3">
+      <c r="M6" s="2">
         <f t="shared" si="0"/>
         <v>0.436</v>
       </c>
-      <c r="N6" s="3">
+      <c r="N6" s="2">
         <f t="shared" si="0"/>
         <v>0.46899999999999997</v>
       </c>
-      <c r="O6" s="3">
+      <c r="O6" s="2">
         <f t="shared" si="0"/>
         <v>0.72599999999999998</v>
       </c>
-      <c r="P6" s="3">
+      <c r="P6" s="2">
         <f t="shared" si="0"/>
         <v>0.96699999999999997</v>
       </c>
-      <c r="Q6" s="3">
+      <c r="Q6" s="2">
         <f t="shared" si="0"/>
         <v>1.1870000000000001</v>
       </c>
-      <c r="R6" s="3">
+      <c r="R6" s="2">
         <f t="shared" si="0"/>
         <v>1.2589999999999999</v>
       </c>
-      <c r="S6" s="3">
+      <c r="S6" s="2">
         <f t="shared" si="0"/>
         <v>1.2250000000000001</v>
       </c>
-      <c r="T6" s="3">
+      <c r="T6" s="2">
         <f t="shared" si="0"/>
         <v>0.66800000000000004</v>
       </c>
-      <c r="U6" s="3">
+      <c r="U6" s="2">
         <f t="shared" si="0"/>
         <v>0.748</v>
       </c>
-      <c r="V6" s="3">
+      <c r="V6" s="2">
         <f t="shared" si="0"/>
         <v>0.67400000000000004</v>
       </c>
-      <c r="W6" s="3">
+      <c r="W6" s="2">
         <f t="shared" si="0"/>
         <v>0.76600000000000001</v>
       </c>
-      <c r="X6" s="3">
+      <c r="X6" s="2">
         <f t="shared" si="0"/>
         <v>0.78300000000000003</v>
       </c>
-      <c r="Y6" s="3">
+      <c r="Y6" s="2">
         <f t="shared" si="0"/>
         <v>0.95799999999999996</v>
       </c>
-      <c r="Z6" s="3">
+      <c r="Z6" s="2">
         <f t="shared" si="0"/>
         <v>0.88100000000000001</v>
       </c>
-      <c r="AA6" s="3">
+      <c r="AA6" s="2">
         <f t="shared" si="0"/>
         <v>0.97</v>
       </c>
-      <c r="AB6" s="3">
+      <c r="AB6" s="2">
         <f t="shared" si="0"/>
         <v>1.3839999999999999</v>
       </c>
-      <c r="AC6" s="3">
+      <c r="AC6" s="2">
         <f t="shared" si="0"/>
         <v>1.3080000000000001</v>
       </c>
-      <c r="AD6" s="3">
+      <c r="AD6" s="2">
         <f t="shared" si="0"/>
         <v>1.5760000000000001</v>
       </c>
-      <c r="AE6" s="3">
+      <c r="AE6" s="2">
         <f t="shared" si="0"/>
         <v>1.323</v>
       </c>
-      <c r="AF6" s="3">
+      <c r="AF6" s="2">
         <f t="shared" si="0"/>
         <v>1.3180000000000001</v>
       </c>
-      <c r="AG6" s="3">
+      <c r="AG6" s="2">
         <f t="shared" si="0"/>
         <v>1.22</v>
       </c>
@@ -17430,8 +17454,8 @@
         <v>2000</v>
       </c>
       <c r="G7">
-        <f>SUMIFS($B:$B,$A:$A,$F7)</f>
-        <v>209.643</v>
+        <f>SUMIFS($B:$B,$A:$A,$F7)*0.0036*1000</f>
+        <v>754.71479999999997</v>
       </c>
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.3">
@@ -17448,8 +17472,8 @@
         <v>2001</v>
       </c>
       <c r="G8">
-        <f>SUMIFS($B:$B,$A:$A,$F8)</f>
-        <v>221.505</v>
+        <f t="shared" ref="G8:G31" si="1">SUMIFS($B:$B,$A:$A,$F8)*0.0036*1000</f>
+        <v>797.41800000000001</v>
       </c>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.3">
@@ -17466,8 +17490,8 @@
         <v>2002</v>
       </c>
       <c r="G9">
-        <f>SUMIFS($B:$B,$A:$A,$F9)</f>
-        <v>231.03299999999999</v>
+        <f t="shared" si="1"/>
+        <v>831.71879999999999</v>
       </c>
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.3">
@@ -17484,8 +17508,8 @@
         <v>2003</v>
       </c>
       <c r="G10">
-        <f>SUMIFS($B:$B,$A:$A,$F10)</f>
-        <v>239.44200000000001</v>
+        <f t="shared" si="1"/>
+        <v>861.99119999999994</v>
       </c>
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.3">
@@ -17502,8 +17526,8 @@
         <v>2004</v>
       </c>
       <c r="G11">
-        <f>SUMIFS($B:$B,$A:$A,$F11)</f>
-        <v>252.87700000000001</v>
+        <f t="shared" si="1"/>
+        <v>910.35719999999992</v>
       </c>
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.3">
@@ -17520,8 +17544,8 @@
         <v>2005</v>
       </c>
       <c r="G12">
-        <f>SUMIFS($B:$B,$A:$A,$F12)</f>
-        <v>266.78100000000001</v>
+        <f t="shared" si="1"/>
+        <v>960.41160000000002</v>
       </c>
     </row>
     <row r="13" spans="1:30" x14ac:dyDescent="0.3">
@@ -17538,8 +17562,8 @@
         <v>2006</v>
       </c>
       <c r="G13">
-        <f>SUMIFS($B:$B,$A:$A,$F13)</f>
-        <v>271.05500000000001</v>
+        <f t="shared" si="1"/>
+        <v>975.79799999999989</v>
       </c>
     </row>
     <row r="14" spans="1:30" x14ac:dyDescent="0.3">
@@ -17556,8 +17580,8 @@
         <v>2007</v>
       </c>
       <c r="G14">
-        <f>SUMIFS($B:$B,$A:$A,$F14)</f>
-        <v>273.827</v>
+        <f t="shared" si="1"/>
+        <v>985.77719999999999</v>
       </c>
     </row>
     <row r="15" spans="1:30" x14ac:dyDescent="0.3">
@@ -17574,8 +17598,8 @@
         <v>2008</v>
       </c>
       <c r="G15">
-        <f>SUMIFS($B:$B,$A:$A,$F15)</f>
-        <v>276.90899999999999</v>
+        <f t="shared" si="1"/>
+        <v>996.87239999999997</v>
       </c>
     </row>
     <row r="16" spans="1:30" x14ac:dyDescent="0.3">
@@ -17592,8 +17616,8 @@
         <v>2009</v>
       </c>
       <c r="G16">
-        <f>SUMIFS($B:$B,$A:$A,$F16)</f>
-        <v>262.07100000000003</v>
+        <f t="shared" si="1"/>
+        <v>943.4556</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
@@ -17610,8 +17634,8 @@
         <v>2010</v>
       </c>
       <c r="G17">
-        <f>SUMIFS($B:$B,$A:$A,$F17)</f>
-        <v>265.79399999999998</v>
+        <f t="shared" si="1"/>
+        <v>956.85839999999985</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
@@ -17628,8 +17652,8 @@
         <v>2011</v>
       </c>
       <c r="G18">
-        <f>SUMIFS($B:$B,$A:$A,$F18)</f>
-        <v>261.72899999999998</v>
+        <f t="shared" si="1"/>
+        <v>942.22439999999995</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
@@ -17646,8 +17670,8 @@
         <v>2012</v>
       </c>
       <c r="G19">
-        <f>SUMIFS($B:$B,$A:$A,$F19)</f>
-        <v>260.685</v>
+        <f t="shared" si="1"/>
+        <v>938.46600000000001</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
@@ -17664,8 +17688,8 @@
         <v>2013</v>
       </c>
       <c r="G20">
-        <f>SUMIFS($B:$B,$A:$A,$F20)</f>
-        <v>252.18600000000001</v>
+        <f t="shared" si="1"/>
+        <v>907.8696000000001</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
@@ -17682,8 +17706,8 @@
         <v>2014</v>
       </c>
       <c r="G21">
-        <f>SUMIFS($B:$B,$A:$A,$F21)</f>
-        <v>248.95</v>
+        <f t="shared" si="1"/>
+        <v>896.21999999999991</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
@@ -17700,8 +17724,8 @@
         <v>2015</v>
       </c>
       <c r="G22">
-        <f>SUMIFS($B:$B,$A:$A,$F22)</f>
-        <v>254.26900000000001</v>
+        <f t="shared" si="1"/>
+        <v>915.36839999999995</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
@@ -17718,8 +17742,8 @@
         <v>2016</v>
       </c>
       <c r="G23">
-        <f>SUMIFS($B:$B,$A:$A,$F23)</f>
-        <v>255.71899999999999</v>
+        <f t="shared" si="1"/>
+        <v>920.58839999999998</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
@@ -17736,8 +17760,8 @@
         <v>2017</v>
       </c>
       <c r="G24">
-        <f>SUMIFS($B:$B,$A:$A,$F24)</f>
-        <v>261.072</v>
+        <f t="shared" si="1"/>
+        <v>939.85919999999999</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
@@ -17754,8 +17778,8 @@
         <v>2018</v>
       </c>
       <c r="G25">
-        <f>SUMIFS($B:$B,$A:$A,$F25)</f>
-        <v>259.95800000000003</v>
+        <f t="shared" si="1"/>
+        <v>935.84879999999998</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -17772,8 +17796,8 @@
         <v>2019</v>
       </c>
       <c r="G26">
-        <f>SUMIFS($B:$B,$A:$A,$F26)</f>
-        <v>255.32900000000001</v>
+        <f t="shared" si="1"/>
+        <v>919.18439999999998</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
@@ -17790,8 +17814,8 @@
         <v>2020</v>
       </c>
       <c r="G27">
-        <f>SUMIFS($B:$B,$A:$A,$F27)</f>
-        <v>241.02199999999999</v>
+        <f t="shared" si="1"/>
+        <v>867.67920000000004</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
@@ -17808,8 +17832,8 @@
         <v>2021</v>
       </c>
       <c r="G28">
-        <f>SUMIFS($B:$B,$A:$A,$F28)</f>
-        <v>248.43600000000001</v>
+        <f t="shared" si="1"/>
+        <v>894.36959999999999</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
@@ -17826,8 +17850,8 @@
         <v>2022</v>
       </c>
       <c r="G29">
-        <f>SUMIFS($B:$B,$A:$A,$F29)</f>
-        <v>247.52099999999999</v>
+        <f t="shared" si="1"/>
+        <v>891.07560000000001</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -17844,8 +17868,8 @@
         <v>2023</v>
       </c>
       <c r="G30">
-        <f>SUMIFS($B:$B,$A:$A,$F30)</f>
-        <v>247.46</v>
+        <f t="shared" si="1"/>
+        <v>890.85599999999999</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
@@ -17862,8 +17886,8 @@
         <v>2024</v>
       </c>
       <c r="G31">
-        <f>SUMIFS($B:$B,$A:$A,$F31)</f>
-        <v>253.74799999999999</v>
+        <f t="shared" si="1"/>
+        <v>913.49279999999999</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
@@ -17958,4 +17982,65 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB763C44-0720-4A5D-A285-14210CC2296D}">
+  <dimension ref="A2:D7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2">
+        <f>0.036</f>
+        <v>3.5999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>15.5</v>
+      </c>
+      <c r="B4">
+        <f>A4*(1/D2)</f>
+        <v>430.55555555555554</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>50000</v>
+      </c>
+      <c r="B7">
+        <f>A7*D2</f>
+        <v>1799.9999999999998</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/ELC_data_Spain.xlsx
+++ b/ELC_data_Spain.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://politoit-my.sharepoint.com/personal/s347160_studenti_polito_it/Documents/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Documents\TEMOA\PROJECT\Models-and-scenarios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="410" documentId="8_{76AE923E-6FFF-4F14-83BA-5326F1D8B3E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E4C704E8-03F1-40E4-8D91-BCD077C2E809}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{393074A5-B2D7-41DE-BD95-587F9BD4F59F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="6" xr2:uid="{8BBF5E45-81C8-439F-BD27-48A9AF2DFBEB}"/>
   </bookViews>
@@ -38,8 +38,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1140" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1153" uniqueCount="76">
   <si>
     <t>electricity generation sources in Spain</t>
   </si>
@@ -246,6 +268,27 @@
   </si>
   <si>
     <t>Others</t>
+  </si>
+  <si>
+    <t>ELC_DST_TURB_E</t>
+  </si>
+  <si>
+    <t>ELC_NGA_E</t>
+  </si>
+  <si>
+    <t>ELC_PV_GRO_CNT_N</t>
+  </si>
+  <si>
+    <t>ELC_PV_GRO_NRD_N</t>
+  </si>
+  <si>
+    <t>Error</t>
+  </si>
+  <si>
+    <t>Production (GWh)</t>
+  </si>
+  <si>
+    <t>ELC_CHP_NGA_TAP_N</t>
   </si>
 </sst>
 </file>
@@ -714,7 +757,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="43">
+  <cellStyleXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -758,22 +801,24 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="43" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="43">
+  <cellStyles count="44">
     <cellStyle name="20% - Colore 1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Colore 2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - Colore 3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -807,6 +852,7 @@
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
     <cellStyle name="Nota" xfId="15" builtinId="10" customBuiltin="1"/>
     <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Percentuale" xfId="43" builtinId="5"/>
     <cellStyle name="Testo avviso" xfId="14" builtinId="11" customBuiltin="1"/>
     <cellStyle name="Testo descrittivo" xfId="16" builtinId="53" customBuiltin="1"/>
     <cellStyle name="Titolo" xfId="1" builtinId="15" customBuiltin="1"/>
@@ -6972,7 +7018,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Cal_Generation!$A$27</c:f>
+              <c:f>Cal_Generation!$N$15</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -6993,7 +7039,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>Cal_Generation!$B$26:$G$26</c:f>
+              <c:f>Cal_Generation!$O$14:$T$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -7020,7 +7066,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Cal_Generation!$B$27:$G$27</c:f>
+              <c:f>Cal_Generation!$O$15:$T$15</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -7056,7 +7102,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Cal_Generation!$A$28</c:f>
+              <c:f>Cal_Generation!$N$16</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -7077,7 +7123,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>Cal_Generation!$B$26:$G$26</c:f>
+              <c:f>Cal_Generation!$O$14:$T$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -7104,7 +7150,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Cal_Generation!$B$28:$G$28</c:f>
+              <c:f>Cal_Generation!$O$16:$T$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -7140,7 +7186,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Cal_Generation!$A$29</c:f>
+              <c:f>Cal_Generation!$N$17</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -7161,7 +7207,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>Cal_Generation!$B$26:$G$26</c:f>
+              <c:f>Cal_Generation!$O$14:$T$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -7188,7 +7234,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Cal_Generation!$B$29:$G$29</c:f>
+              <c:f>Cal_Generation!$O$17:$T$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -7224,7 +7270,7 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>Cal_Generation!$A$30</c:f>
+              <c:f>Cal_Generation!$N$18</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -7245,7 +7291,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>Cal_Generation!$B$26:$G$26</c:f>
+              <c:f>Cal_Generation!$O$14:$T$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -7272,7 +7318,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Cal_Generation!$B$30:$G$30</c:f>
+              <c:f>Cal_Generation!$O$18:$T$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -7308,7 +7354,7 @@
           <c:order val="4"/>
           <c:tx>
             <c:strRef>
-              <c:f>Cal_Generation!$A$31</c:f>
+              <c:f>Cal_Generation!$N$19</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -7329,7 +7375,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>Cal_Generation!$B$26:$G$26</c:f>
+              <c:f>Cal_Generation!$O$14:$T$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -7356,7 +7402,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Cal_Generation!$B$31:$G$31</c:f>
+              <c:f>Cal_Generation!$O$19:$T$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -7392,7 +7438,7 @@
           <c:order val="5"/>
           <c:tx>
             <c:strRef>
-              <c:f>Cal_Generation!$A$32</c:f>
+              <c:f>Cal_Generation!$N$20</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -7413,7 +7459,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>Cal_Generation!$B$26:$G$26</c:f>
+              <c:f>Cal_Generation!$O$14:$T$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -7440,7 +7486,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Cal_Generation!$B$32:$G$32</c:f>
+              <c:f>Cal_Generation!$O$20:$T$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -7476,7 +7522,7 @@
           <c:order val="6"/>
           <c:tx>
             <c:strRef>
-              <c:f>Cal_Generation!$A$33</c:f>
+              <c:f>Cal_Generation!$N$21</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -7499,7 +7545,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>Cal_Generation!$B$26:$G$26</c:f>
+              <c:f>Cal_Generation!$O$14:$T$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -7526,7 +7572,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Cal_Generation!$B$33:$G$33</c:f>
+              <c:f>Cal_Generation!$O$21:$T$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -7562,7 +7608,7 @@
           <c:order val="7"/>
           <c:tx>
             <c:strRef>
-              <c:f>Cal_Generation!$A$34</c:f>
+              <c:f>Cal_Generation!$N$22</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -7585,7 +7631,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>Cal_Generation!$B$26:$G$26</c:f>
+              <c:f>Cal_Generation!$O$14:$T$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -7612,7 +7658,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Cal_Generation!$B$34:$G$34</c:f>
+              <c:f>Cal_Generation!$O$22:$T$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -7648,7 +7694,7 @@
           <c:order val="8"/>
           <c:tx>
             <c:strRef>
-              <c:f>Cal_Generation!$A$35</c:f>
+              <c:f>Cal_Generation!$N$23</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -7671,7 +7717,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>Cal_Generation!$B$26:$G$26</c:f>
+              <c:f>Cal_Generation!$O$14:$T$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -7698,7 +7744,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Cal_Generation!$B$35:$G$35</c:f>
+              <c:f>Cal_Generation!$O$23:$T$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -8185,19 +8231,19 @@
                   <c:v>253.37450000000001</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>211.61250000000001</c:v>
+                  <c:v>90.021999999999991</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>155.92983333333333</c:v>
+                  <c:v>159.79</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>74.560750000000056</c:v>
+                  <c:v>132.37299999999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>15.659800000000001</c:v>
+                  <c:v>29.73500000000001</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>7.6000000000000014</c:v>
+                  <c:v>11.856</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8266,22 +8312,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>63.297359999999998</c:v>
+                  <c:v>63.297359999999983</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>56.642040000000001</c:v>
+                  <c:v>56.642039999999987</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>58.964219999999997</c:v>
+                  <c:v>48.293819999999997</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>49.583159999999992</c:v>
+                  <c:v>49.583160000000007</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>36.217799999999997</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>31.200659999999989</c:v>
+                  <c:v>30.513999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8350,22 +8396,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>324.21258000000006</c:v>
+                  <c:v>324.21258</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>324.39042000000001</c:v>
+                  <c:v>350.71539729176556</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>179.54316000000006</c:v>
+                  <c:v>182.28242640844772</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>229.62703228639168</c:v>
+                  <c:v>202.4825796126716</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>309.47796479916542</c:v>
+                  <c:v>327.79714840445774</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>232.24285212650787</c:v>
+                  <c:v>199.63436915522325</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8434,22 +8480,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>188.45150000000001</c:v>
+                  <c:v>217.0010537154852</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>213.11779999999999</c:v>
+                  <c:v>218.93267982188161</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>199.12396169457489</c:v>
+                  <c:v>200.18459503119641</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>210.798</c:v>
+                  <c:v>218.93267982188161</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>195.79920000000001</c:v>
+                  <c:v>218.93267982188161</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>158.93700000000001</c:v>
+                  <c:v>215.941</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8518,22 +8564,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>92.380978162960034</c:v>
+                  <c:v>109.87920000000004</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>67.483020009096066</c:v>
+                  <c:v>163.83959999999993</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>116.44010998089969</c:v>
+                  <c:v>154.68839999999989</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>116.44010998089969</c:v>
+                  <c:v>132.95339999999996</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>115.74206993773153</c:v>
+                  <c:v>87.523920000000032</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>139.60781999999995</c:v>
+                  <c:v>161.65115999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8602,22 +8648,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>7.3906200000000002</c:v>
+                  <c:v>7.3906199999999993</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>11.47752</c:v>
+                  <c:v>11.47751999999999</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>16.16976</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>16.422840000000001</c:v>
+                  <c:v>16.42283999999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>19.505970000000001</c:v>
+                  <c:v>19.505970000000008</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>18.19098000000001</c:v>
+                  <c:v>18.19098</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8688,22 +8734,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>94.277999999999963</c:v>
+                  <c:v>94.278000000000006</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>151.411</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>177.88749999999999</c:v>
+                  <c:v>177.88750000000005</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>174.0685</c:v>
+                  <c:v>174.78847091302663</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>203.83199999999999</c:v>
+                  <c:v>234.69599999999997</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>220.02</c:v>
+                  <c:v>234.69599999999997</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8777,7 +8823,7 @@
                   <c:v>1.7613000000000001</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>24.576120000000003</c:v>
+                  <c:v>24.576119999999985</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>47.397779999999997</c:v>
@@ -8786,7 +8832,7 @@
                   <c:v>51.652259999999991</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>122.17265999999989</c:v>
+                  <c:v>122.17266000000001</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>199.34496000000007</c:v>
@@ -8860,22 +8906,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>0.1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>0.7</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6.9900000000000011</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6.24125</c:v>
+                  <c:v>0.39749999999999996</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5.6796875</c:v>
+                  <c:v>0.37624999999999997</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13826,16 +13872,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>118533</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>50799</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>283633</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>112183</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>258232</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>120649</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -13862,16 +13908,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>408938</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>67733</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>239606</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>143933</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>499532</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>121497</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>118533</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>11430</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -14219,8 +14265,8 @@
   <dimension ref="A1:AD301"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="31.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="34.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:30" x14ac:dyDescent="0.3">
@@ -14335,75 +14381,75 @@
         <v>244.7208</v>
       </c>
       <c r="M3">
-        <f>SUMIFS($B:$B,$A:$A,$K3,$C:$C,M$2)*0.0036</f>
+        <f t="shared" ref="L3:U14" si="0">SUMIFS($B:$B,$A:$A,$K3,$C:$C,M$2)*0.0036</f>
         <v>266.70600000000002</v>
       </c>
       <c r="N3">
-        <f>SUMIFS($B:$B,$A:$A,$K3,$C:$C,N$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>179.90279999999998</v>
       </c>
       <c r="O3">
-        <f>SUMIFS($B:$B,$A:$A,$K3,$C:$C,O$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>132.9768</v>
       </c>
       <c r="P3">
-        <f>SUMIFS($B:$B,$A:$A,$K3,$C:$C,P$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>94.762799999999999</v>
       </c>
       <c r="Q3">
-        <f>SUMIFS($B:$B,$A:$A,$K3,$C:$C,Q$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>162.45359999999999</v>
       </c>
       <c r="R3">
-        <f>SUMIFS($B:$B,$A:$A,$K3,$C:$C,R$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>201.5676</v>
       </c>
       <c r="S3">
-        <f>SUMIFS($B:$B,$A:$A,$K3,$C:$C,S$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>148.79519999999999</v>
       </c>
       <c r="T3">
-        <f>SUMIFS($B:$B,$A:$A,$K3,$C:$C,T$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>163.06199999999998</v>
       </c>
       <c r="U3">
-        <f>SUMIFS($B:$B,$A:$A,$K3,$C:$C,U$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>189.6336</v>
       </c>
       <c r="V3">
-        <f>SUMIFS($B:$B,$A:$A,$K3,$C:$C,V$2)*0.0036</f>
+        <f t="shared" ref="V3:AD14" si="1">SUMIFS($B:$B,$A:$A,$K3,$C:$C,V$2)*0.0036</f>
         <v>134.83079999999998</v>
       </c>
       <c r="W3">
-        <f>SUMIFS($B:$B,$A:$A,$K3,$C:$C,W$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>166.85640000000001</v>
       </c>
       <c r="X3">
-        <f>SUMIFS($B:$B,$A:$A,$K3,$C:$C,X$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>139.3776</v>
       </c>
       <c r="Y3">
-        <f>SUMIFS($B:$B,$A:$A,$K3,$C:$C,Y$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>50.3352</v>
       </c>
       <c r="Z3">
-        <f>SUMIFS($B:$B,$A:$A,$K3,$C:$C,Z$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>22.136399999999998</v>
       </c>
       <c r="AA3">
-        <f>SUMIFS($B:$B,$A:$A,$K3,$C:$C,AA$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>21.650399999999998</v>
       </c>
       <c r="AB3">
-        <f>SUMIFS($B:$B,$A:$A,$K3,$C:$C,AB$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>31.305599999999998</v>
       </c>
       <c r="AC3">
-        <f>SUMIFS($B:$B,$A:$A,$K3,$C:$C,AC$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>16.02</v>
       </c>
       <c r="AD3">
-        <f>SUMIFS($B:$B,$A:$A,$K3,$C:$C,AD$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>12.477599999999999</v>
       </c>
     </row>
@@ -14424,79 +14470,79 @@
         <v>6</v>
       </c>
       <c r="L4">
-        <f>SUMIFS($B:$B,$A:$A,$K4,$C:$C,L$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>85.784399999999991</v>
       </c>
       <c r="M4">
-        <f>SUMIFS($B:$B,$A:$A,$K4,$C:$C,M$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>66.628799999999998</v>
       </c>
       <c r="N4">
-        <f>SUMIFS($B:$B,$A:$A,$K4,$C:$C,N$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>64.807199999999995</v>
       </c>
       <c r="O4">
-        <f>SUMIFS($B:$B,$A:$A,$K4,$C:$C,O$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>69.271199999999993</v>
       </c>
       <c r="P4">
-        <f>SUMIFS($B:$B,$A:$A,$K4,$C:$C,P$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>59.623199999999997</v>
       </c>
       <c r="Q4">
-        <f>SUMIFS($B:$B,$A:$A,$K4,$C:$C,Q$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>52.891199999999998</v>
       </c>
       <c r="R4">
-        <f>SUMIFS($B:$B,$A:$A,$K4,$C:$C,R$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>55.1556</v>
       </c>
       <c r="S4">
-        <f>SUMIFS($B:$B,$A:$A,$K4,$C:$C,S$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>49.546799999999998</v>
       </c>
       <c r="T4">
-        <f>SUMIFS($B:$B,$A:$A,$K4,$C:$C,T$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>50.835599999999999</v>
       </c>
       <c r="U4">
-        <f>SUMIFS($B:$B,$A:$A,$K4,$C:$C,U$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>62.067599999999999</v>
       </c>
       <c r="V4">
-        <f>SUMIFS($B:$B,$A:$A,$K4,$C:$C,V$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>60.915599999999998</v>
       </c>
       <c r="W4">
-        <f>SUMIFS($B:$B,$A:$A,$K4,$C:$C,W$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>56.757599999999996</v>
       </c>
       <c r="X4">
-        <f>SUMIFS($B:$B,$A:$A,$K4,$C:$C,X$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>52.192799999999998</v>
       </c>
       <c r="Y4">
-        <f>SUMIFS($B:$B,$A:$A,$K4,$C:$C,Y$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>46.378799999999998</v>
       </c>
       <c r="Z4">
-        <f>SUMIFS($B:$B,$A:$A,$K4,$C:$C,Z$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>38.534399999999998</v>
       </c>
       <c r="AA4">
-        <f>SUMIFS($B:$B,$A:$A,$K4,$C:$C,AA$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>36.1584</v>
       </c>
       <c r="AB4">
-        <f>SUMIFS($B:$B,$A:$A,$K4,$C:$C,AB$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>38.124000000000002</v>
       </c>
       <c r="AC4">
-        <f>SUMIFS($B:$B,$A:$A,$K4,$C:$C,AC$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>33.436799999999998</v>
       </c>
       <c r="AD4">
-        <f>SUMIFS($B:$B,$A:$A,$K4,$C:$C,AD$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>32.842799999999997</v>
       </c>
     </row>
@@ -14517,79 +14563,79 @@
         <v>7</v>
       </c>
       <c r="L5">
-        <f>SUMIFS($B:$B,$A:$A,$K5,$C:$C,L$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>326.05199999999996</v>
       </c>
       <c r="M5">
-        <f>SUMIFS($B:$B,$A:$A,$K5,$C:$C,M$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>341.27639999999997</v>
       </c>
       <c r="N5">
-        <f>SUMIFS($B:$B,$A:$A,$K5,$C:$C,N$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>434.87279999999998</v>
       </c>
       <c r="O5">
-        <f>SUMIFS($B:$B,$A:$A,$K5,$C:$C,O$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>387.88560000000001</v>
       </c>
       <c r="P5">
-        <f>SUMIFS($B:$B,$A:$A,$K5,$C:$C,P$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>341.46359999999999</v>
       </c>
       <c r="Q5">
-        <f>SUMIFS($B:$B,$A:$A,$K5,$C:$C,Q$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>307.8288</v>
       </c>
       <c r="R5">
-        <f>SUMIFS($B:$B,$A:$A,$K5,$C:$C,R$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>263.90879999999999</v>
       </c>
       <c r="S5">
-        <f>SUMIFS($B:$B,$A:$A,$K5,$C:$C,S$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>207.12959999999998</v>
       </c>
       <c r="T5">
-        <f>SUMIFS($B:$B,$A:$A,$K5,$C:$C,T$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>170.18279999999999</v>
       </c>
       <c r="U5">
-        <f>SUMIFS($B:$B,$A:$A,$K5,$C:$C,U$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>188.99279999999999</v>
       </c>
       <c r="V5">
-        <f>SUMIFS($B:$B,$A:$A,$K5,$C:$C,V$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>190.15199999999999</v>
       </c>
       <c r="W5">
-        <f>SUMIFS($B:$B,$A:$A,$K5,$C:$C,W$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>230.53319999999999</v>
       </c>
       <c r="X5">
-        <f>SUMIFS($B:$B,$A:$A,$K5,$C:$C,X$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>208.81440000000001</v>
       </c>
       <c r="Y5">
-        <f>SUMIFS($B:$B,$A:$A,$K5,$C:$C,Y$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>301.33080000000001</v>
       </c>
       <c r="Z5">
-        <f>SUMIFS($B:$B,$A:$A,$K5,$C:$C,Z$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>251.06039999999999</v>
       </c>
       <c r="AA5">
-        <f>SUMIFS($B:$B,$A:$A,$K5,$C:$C,AA$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>257.40719999999999</v>
       </c>
       <c r="AB5">
-        <f>SUMIFS($B:$B,$A:$A,$K5,$C:$C,AB$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>309.51</v>
       </c>
       <c r="AC5">
-        <f>SUMIFS($B:$B,$A:$A,$K5,$C:$C,AC$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>231.3792</v>
       </c>
       <c r="AD5">
-        <f>SUMIFS($B:$B,$A:$A,$K5,$C:$C,AD$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>188.3844</v>
       </c>
     </row>
@@ -14610,79 +14656,79 @@
         <v>8</v>
       </c>
       <c r="L6">
-        <f>SUMIFS($B:$B,$A:$A,$K6,$C:$C,L$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>216.45359999999999</v>
       </c>
       <c r="M6">
-        <f>SUMIFS($B:$B,$A:$A,$K6,$C:$C,M$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>198.3708</v>
       </c>
       <c r="N6">
-        <f>SUMIFS($B:$B,$A:$A,$K6,$C:$C,N$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>212.30279999999999</v>
       </c>
       <c r="O6">
-        <f>SUMIFS($B:$B,$A:$A,$K6,$C:$C,O$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>189.93959999999998</v>
       </c>
       <c r="P6">
-        <f>SUMIFS($B:$B,$A:$A,$K6,$C:$C,P$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>223.16399999999999</v>
       </c>
       <c r="Q6">
-        <f>SUMIFS($B:$B,$A:$A,$K6,$C:$C,Q$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>207.78479999999999</v>
       </c>
       <c r="R6">
-        <f>SUMIFS($B:$B,$A:$A,$K6,$C:$C,R$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>221.292</v>
       </c>
       <c r="S6">
-        <f>SUMIFS($B:$B,$A:$A,$K6,$C:$C,S$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>204.21359999999999</v>
       </c>
       <c r="T6">
-        <f>SUMIFS($B:$B,$A:$A,$K6,$C:$C,T$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>206.298</v>
       </c>
       <c r="U6">
-        <f>SUMIFS($B:$B,$A:$A,$K6,$C:$C,U$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>205.90559999999999</v>
       </c>
       <c r="V6">
-        <f>SUMIFS($B:$B,$A:$A,$K6,$C:$C,V$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>211.0788</v>
       </c>
       <c r="W6">
-        <f>SUMIFS($B:$B,$A:$A,$K6,$C:$C,W$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>208.94039999999998</v>
       </c>
       <c r="X6">
-        <f>SUMIFS($B:$B,$A:$A,$K6,$C:$C,X$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>200.7576</v>
       </c>
       <c r="Y6">
-        <f>SUMIFS($B:$B,$A:$A,$K6,$C:$C,Y$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>210.0564</v>
       </c>
       <c r="Z6">
-        <f>SUMIFS($B:$B,$A:$A,$K6,$C:$C,Z$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>209.87639999999999</v>
       </c>
       <c r="AA6">
-        <f>SUMIFS($B:$B,$A:$A,$K6,$C:$C,AA$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>203.63039999999998</v>
       </c>
       <c r="AB6">
-        <f>SUMIFS($B:$B,$A:$A,$K6,$C:$C,AB$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>210.92400000000001</v>
       </c>
       <c r="AC6">
-        <f>SUMIFS($B:$B,$A:$A,$K6,$C:$C,AC$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>204.74279999999999</v>
       </c>
       <c r="AD6">
-        <f>SUMIFS($B:$B,$A:$A,$K6,$C:$C,AD$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>196.3152</v>
       </c>
     </row>
@@ -14703,79 +14749,79 @@
         <v>9</v>
       </c>
       <c r="L7">
-        <f>SUMIFS($B:$B,$A:$A,$K7,$C:$C,L$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>107.3916</v>
       </c>
       <c r="M7">
-        <f>SUMIFS($B:$B,$A:$A,$K7,$C:$C,M$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>109.8792</v>
       </c>
       <c r="N7">
-        <f>SUMIFS($B:$B,$A:$A,$K7,$C:$C,N$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>94.118399999999994</v>
       </c>
       <c r="O7">
-        <f>SUMIFS($B:$B,$A:$A,$K7,$C:$C,O$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>104.9832</v>
       </c>
       <c r="P7">
-        <f>SUMIFS($B:$B,$A:$A,$K7,$C:$C,P$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>163.83959999999999</v>
       </c>
       <c r="Q7">
-        <f>SUMIFS($B:$B,$A:$A,$K7,$C:$C,Q$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>118.47959999999999</v>
       </c>
       <c r="R7">
-        <f>SUMIFS($B:$B,$A:$A,$K7,$C:$C,R$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>86.983199999999997</v>
       </c>
       <c r="S7">
-        <f>SUMIFS($B:$B,$A:$A,$K7,$C:$C,S$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>147.78719999999998</v>
       </c>
       <c r="T7">
-        <f>SUMIFS($B:$B,$A:$A,$K7,$C:$C,T$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>154.6884</v>
       </c>
       <c r="U7">
-        <f>SUMIFS($B:$B,$A:$A,$K7,$C:$C,U$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>112.92479999999999</v>
       </c>
       <c r="V7">
-        <f>SUMIFS($B:$B,$A:$A,$K7,$C:$C,V$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>143.51400000000001</v>
       </c>
       <c r="W7">
-        <f>SUMIFS($B:$B,$A:$A,$K7,$C:$C,W$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>75.852000000000004</v>
       </c>
       <c r="X7">
-        <f>SUMIFS($B:$B,$A:$A,$K7,$C:$C,X$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>132.49080000000001</v>
       </c>
       <c r="Y7">
-        <f>SUMIFS($B:$B,$A:$A,$K7,$C:$C,Y$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>96.746399999999994</v>
       </c>
       <c r="Z7">
-        <f>SUMIFS($B:$B,$A:$A,$K7,$C:$C,Z$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>122.39279999999999</v>
       </c>
       <c r="AA7">
-        <f>SUMIFS($B:$B,$A:$A,$K7,$C:$C,AA$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>118.2492</v>
       </c>
       <c r="AB7">
-        <f>SUMIFS($B:$B,$A:$A,$K7,$C:$C,AB$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>79.5672</v>
       </c>
       <c r="AC7">
-        <f>SUMIFS($B:$B,$A:$A,$K7,$C:$C,AC$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>111.97799999999999</v>
       </c>
       <c r="AD7">
-        <f>SUMIFS($B:$B,$A:$A,$K7,$C:$C,AD$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>146.9556</v>
       </c>
     </row>
@@ -14796,79 +14842,79 @@
         <v>10</v>
       </c>
       <c r="L8">
-        <f>SUMIFS($B:$B,$A:$A,$K8,$C:$C,L$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="M8">
-        <f>SUMIFS($B:$B,$A:$A,$K8,$C:$C,M$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="N8">
-        <f>SUMIFS($B:$B,$A:$A,$K8,$C:$C,N$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="O8">
-        <f>SUMIFS($B:$B,$A:$A,$K8,$C:$C,O$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="P8">
-        <f>SUMIFS($B:$B,$A:$A,$K8,$C:$C,P$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Q8">
-        <f>SUMIFS($B:$B,$A:$A,$K8,$C:$C,Q$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R8">
-        <f>SUMIFS($B:$B,$A:$A,$K8,$C:$C,R$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S8">
-        <f>SUMIFS($B:$B,$A:$A,$K8,$C:$C,S$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T8">
-        <f>SUMIFS($B:$B,$A:$A,$K8,$C:$C,T$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="U8">
-        <f>SUMIFS($B:$B,$A:$A,$K8,$C:$C,U$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="V8">
-        <f>SUMIFS($B:$B,$A:$A,$K8,$C:$C,V$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="W8">
-        <f>SUMIFS($B:$B,$A:$A,$K8,$C:$C,W$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X8">
-        <f>SUMIFS($B:$B,$A:$A,$K8,$C:$C,X$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Y8">
-        <f>SUMIFS($B:$B,$A:$A,$K8,$C:$C,Y$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>7.1999999999999995E-2</v>
       </c>
       <c r="Z8">
-        <f>SUMIFS($B:$B,$A:$A,$K8,$C:$C,Z$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>9.7199999999999995E-2</v>
       </c>
       <c r="AA8">
-        <f>SUMIFS($B:$B,$A:$A,$K8,$C:$C,AA$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>6.8400000000000002E-2</v>
       </c>
       <c r="AB8">
-        <f>SUMIFS($B:$B,$A:$A,$K8,$C:$C,AB$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>8.2799999999999999E-2</v>
       </c>
       <c r="AC8">
-        <f>SUMIFS($B:$B,$A:$A,$K8,$C:$C,AC$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>4.3200000000000002E-2</v>
       </c>
       <c r="AD8">
-        <f>SUMIFS($B:$B,$A:$A,$K8,$C:$C,AD$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>2.8799999999999999E-2</v>
       </c>
     </row>
@@ -14889,79 +14935,79 @@
         <v>11</v>
       </c>
       <c r="L9">
-        <f>SUMIFS($B:$B,$A:$A,$K9,$C:$C,L$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>7.8228</v>
       </c>
       <c r="M9">
-        <f>SUMIFS($B:$B,$A:$A,$K9,$C:$C,M$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>7.7795999999999994</v>
       </c>
       <c r="N9">
-        <f>SUMIFS($B:$B,$A:$A,$K9,$C:$C,N$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>8.9027999999999992</v>
       </c>
       <c r="O9">
-        <f>SUMIFS($B:$B,$A:$A,$K9,$C:$C,O$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>9.8171999999999997</v>
       </c>
       <c r="P9">
-        <f>SUMIFS($B:$B,$A:$A,$K9,$C:$C,P$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>12.0816</v>
       </c>
       <c r="Q9">
-        <f>SUMIFS($B:$B,$A:$A,$K9,$C:$C,Q$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>13.730399999999999</v>
       </c>
       <c r="R9">
-        <f>SUMIFS($B:$B,$A:$A,$K9,$C:$C,R$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>15.3432</v>
       </c>
       <c r="S9">
-        <f>SUMIFS($B:$B,$A:$A,$K9,$C:$C,S$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>18.4176</v>
       </c>
       <c r="T9">
-        <f>SUMIFS($B:$B,$A:$A,$K9,$C:$C,T$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>17.020800000000001</v>
       </c>
       <c r="U9">
-        <f>SUMIFS($B:$B,$A:$A,$K9,$C:$C,U$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>17.985599999999998</v>
       </c>
       <c r="V9">
-        <f>SUMIFS($B:$B,$A:$A,$K9,$C:$C,V$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>17.834399999999999</v>
       </c>
       <c r="W9">
-        <f>SUMIFS($B:$B,$A:$A,$K9,$C:$C,W$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>19.101600000000001</v>
       </c>
       <c r="X9">
-        <f>SUMIFS($B:$B,$A:$A,$K9,$C:$C,X$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>18.561599999999999</v>
       </c>
       <c r="Y9">
-        <f>SUMIFS($B:$B,$A:$A,$K9,$C:$C,Y$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>17.287199999999999</v>
       </c>
       <c r="Z9">
-        <f>SUMIFS($B:$B,$A:$A,$K9,$C:$C,Z$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>19.565999999999999</v>
       </c>
       <c r="AA9">
-        <f>SUMIFS($B:$B,$A:$A,$K9,$C:$C,AA$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>21.916799999999999</v>
       </c>
       <c r="AB9">
-        <f>SUMIFS($B:$B,$A:$A,$K9,$C:$C,AB$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>21.366</v>
       </c>
       <c r="AC9">
-        <f>SUMIFS($B:$B,$A:$A,$K9,$C:$C,AC$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>18.223199999999999</v>
       </c>
       <c r="AD9">
-        <f>SUMIFS($B:$B,$A:$A,$K9,$C:$C,AD$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>19.148399999999999</v>
       </c>
     </row>
@@ -14982,79 +15028,79 @@
         <v>12</v>
       </c>
       <c r="L10">
-        <f>SUMIFS($B:$B,$A:$A,$K10,$C:$C,L$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>4.3271999999999995</v>
       </c>
       <c r="M10">
-        <f>SUMIFS($B:$B,$A:$A,$K10,$C:$C,M$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>5.3064</v>
       </c>
       <c r="N10">
-        <f>SUMIFS($B:$B,$A:$A,$K10,$C:$C,N$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>5.6303999999999998</v>
       </c>
       <c r="O10">
-        <f>SUMIFS($B:$B,$A:$A,$K10,$C:$C,O$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>5.4791999999999996</v>
       </c>
       <c r="P10">
-        <f>SUMIFS($B:$B,$A:$A,$K10,$C:$C,P$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>4.7447999999999997</v>
       </c>
       <c r="Q10">
-        <f>SUMIFS($B:$B,$A:$A,$K10,$C:$C,Q$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>5.7240000000000002</v>
       </c>
       <c r="R10">
-        <f>SUMIFS($B:$B,$A:$A,$K10,$C:$C,R$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>5.1479999999999997</v>
       </c>
       <c r="S10">
-        <f>SUMIFS($B:$B,$A:$A,$K10,$C:$C,S$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>4.9104000000000001</v>
       </c>
       <c r="T10">
-        <f>SUMIFS($B:$B,$A:$A,$K10,$C:$C,T$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>4.9391999999999996</v>
       </c>
       <c r="U10">
-        <f>SUMIFS($B:$B,$A:$A,$K10,$C:$C,U$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>5.5296000000000003</v>
       </c>
       <c r="V10">
-        <f>SUMIFS($B:$B,$A:$A,$K10,$C:$C,V$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>5.2919999999999998</v>
       </c>
       <c r="W10">
-        <f>SUMIFS($B:$B,$A:$A,$K10,$C:$C,W$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>5.5583999999999998</v>
       </c>
       <c r="X10">
-        <f>SUMIFS($B:$B,$A:$A,$K10,$C:$C,X$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>6.39</v>
       </c>
       <c r="Y10">
-        <f>SUMIFS($B:$B,$A:$A,$K10,$C:$C,Y$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>6.3179999999999996</v>
       </c>
       <c r="Z10">
-        <f>SUMIFS($B:$B,$A:$A,$K10,$C:$C,Z$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>6.3035999999999994</v>
       </c>
       <c r="AA10">
-        <f>SUMIFS($B:$B,$A:$A,$K10,$C:$C,AA$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>6.4619999999999997</v>
       </c>
       <c r="AB10">
-        <f>SUMIFS($B:$B,$A:$A,$K10,$C:$C,AB$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>6.3144</v>
       </c>
       <c r="AC10">
-        <f>SUMIFS($B:$B,$A:$A,$K10,$C:$C,AC$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>6.0587999999999997</v>
       </c>
       <c r="AD10">
-        <f>SUMIFS($B:$B,$A:$A,$K10,$C:$C,AD$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>6.0695999999999994</v>
       </c>
     </row>
@@ -15075,79 +15121,79 @@
         <v>13</v>
       </c>
       <c r="L11">
-        <f>SUMIFS($B:$B,$A:$A,$K11,$C:$C,L$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>83.869199999999992</v>
       </c>
       <c r="M11">
-        <f>SUMIFS($B:$B,$A:$A,$K11,$C:$C,M$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>99.244799999999998</v>
       </c>
       <c r="N11">
-        <f>SUMIFS($B:$B,$A:$A,$K11,$C:$C,N$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>118.6056</v>
       </c>
       <c r="O11">
-        <f>SUMIFS($B:$B,$A:$A,$K11,$C:$C,O$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>137.22120000000001</v>
       </c>
       <c r="P11">
-        <f>SUMIFS($B:$B,$A:$A,$K11,$C:$C,P$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>159.37559999999999</v>
       </c>
       <c r="Q11">
-        <f>SUMIFS($B:$B,$A:$A,$K11,$C:$C,Q$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>154.50479999999999</v>
       </c>
       <c r="R11">
-        <f>SUMIFS($B:$B,$A:$A,$K11,$C:$C,R$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>178.0992</v>
       </c>
       <c r="S11">
-        <f>SUMIFS($B:$B,$A:$A,$K11,$C:$C,S$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>200.32560000000001</v>
       </c>
       <c r="T11">
-        <f>SUMIFS($B:$B,$A:$A,$K11,$C:$C,T$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>187.24680000000001</v>
       </c>
       <c r="U11">
-        <f>SUMIFS($B:$B,$A:$A,$K11,$C:$C,U$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>177.57</v>
       </c>
       <c r="V11">
-        <f>SUMIFS($B:$B,$A:$A,$K11,$C:$C,V$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>176.05799999999999</v>
       </c>
       <c r="W11">
-        <f>SUMIFS($B:$B,$A:$A,$K11,$C:$C,W$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>176.85720000000001</v>
       </c>
       <c r="X11">
-        <f>SUMIFS($B:$B,$A:$A,$K11,$C:$C,X$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>183.22559999999999</v>
       </c>
       <c r="Y11">
-        <f>SUMIFS($B:$B,$A:$A,$K11,$C:$C,Y$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>200.32919999999999</v>
       </c>
       <c r="Z11">
-        <f>SUMIFS($B:$B,$A:$A,$K11,$C:$C,Z$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>203.19839999999999</v>
       </c>
       <c r="AA11">
-        <f>SUMIFS($B:$B,$A:$A,$K11,$C:$C,AA$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>223.4196</v>
       </c>
       <c r="AB11">
-        <f>SUMIFS($B:$B,$A:$A,$K11,$C:$C,AB$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>226.0224</v>
       </c>
       <c r="AC11">
-        <f>SUMIFS($B:$B,$A:$A,$K11,$C:$C,AC$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>231.39</v>
       </c>
       <c r="AD11">
-        <f>SUMIFS($B:$B,$A:$A,$K11,$C:$C,AD$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>223.5204</v>
       </c>
     </row>
@@ -15168,79 +15214,79 @@
         <v>14</v>
       </c>
       <c r="L12">
-        <f>SUMIFS($B:$B,$A:$A,$K12,$C:$C,L$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>0.44639999999999996</v>
       </c>
       <c r="M12">
-        <f>SUMIFS($B:$B,$A:$A,$K12,$C:$C,M$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>1.8251999999999999</v>
       </c>
       <c r="N12">
-        <f>SUMIFS($B:$B,$A:$A,$K12,$C:$C,N$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>9.2232000000000003</v>
       </c>
       <c r="O12">
-        <f>SUMIFS($B:$B,$A:$A,$K12,$C:$C,O$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>21.459599999999998</v>
       </c>
       <c r="P12">
-        <f>SUMIFS($B:$B,$A:$A,$K12,$C:$C,P$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>23.13</v>
       </c>
       <c r="Q12">
-        <f>SUMIFS($B:$B,$A:$A,$K12,$C:$C,Q$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>26.783999999999999</v>
       </c>
       <c r="R12">
-        <f>SUMIFS($B:$B,$A:$A,$K12,$C:$C,R$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>29.491199999999999</v>
       </c>
       <c r="S12">
-        <f>SUMIFS($B:$B,$A:$A,$K12,$C:$C,S$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>29.973599999999998</v>
       </c>
       <c r="T12">
-        <f>SUMIFS($B:$B,$A:$A,$K12,$C:$C,T$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>29.581199999999999</v>
       </c>
       <c r="U12">
-        <f>SUMIFS($B:$B,$A:$A,$K12,$C:$C,U$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>29.7576</v>
       </c>
       <c r="V12">
-        <f>SUMIFS($B:$B,$A:$A,$K12,$C:$C,V$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>29.026799999999998</v>
       </c>
       <c r="W12">
-        <f>SUMIFS($B:$B,$A:$A,$K12,$C:$C,W$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>30.650399999999998</v>
       </c>
       <c r="X12">
-        <f>SUMIFS($B:$B,$A:$A,$K12,$C:$C,X$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>28.357199999999999</v>
       </c>
       <c r="Y12">
-        <f>SUMIFS($B:$B,$A:$A,$K12,$C:$C,Y$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>33.911999999999999</v>
       </c>
       <c r="Z12">
-        <f>SUMIFS($B:$B,$A:$A,$K12,$C:$C,Z$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>56.43</v>
       </c>
       <c r="AA12">
-        <f>SUMIFS($B:$B,$A:$A,$K12,$C:$C,AA$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>78.919200000000004</v>
       </c>
       <c r="AB12">
-        <f>SUMIFS($B:$B,$A:$A,$K12,$C:$C,AB$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>112.2732</v>
       </c>
       <c r="AC12">
-        <f>SUMIFS($B:$B,$A:$A,$K12,$C:$C,AC$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>156.31559999999999</v>
       </c>
       <c r="AD12">
-        <f>SUMIFS($B:$B,$A:$A,$K12,$C:$C,AD$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>193.50719999999998</v>
       </c>
     </row>
@@ -15261,79 +15307,79 @@
         <v>15</v>
       </c>
       <c r="L13">
-        <f>SUMIFS($B:$B,$A:$A,$K13,$C:$C,L$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="M13">
-        <f>SUMIFS($B:$B,$A:$A,$K13,$C:$C,M$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>2.8799999999999999E-2</v>
       </c>
       <c r="N13">
-        <f>SUMIFS($B:$B,$A:$A,$K13,$C:$C,N$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>5.7599999999999998E-2</v>
       </c>
       <c r="O13">
-        <f>SUMIFS($B:$B,$A:$A,$K13,$C:$C,O$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>0.37079999999999996</v>
       </c>
       <c r="P13">
-        <f>SUMIFS($B:$B,$A:$A,$K13,$C:$C,P$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>2.7395999999999998</v>
       </c>
       <c r="Q13">
-        <f>SUMIFS($B:$B,$A:$A,$K13,$C:$C,Q$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>7.0523999999999996</v>
       </c>
       <c r="R13">
-        <f>SUMIFS($B:$B,$A:$A,$K13,$C:$C,R$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>13.59</v>
       </c>
       <c r="S13">
-        <f>SUMIFS($B:$B,$A:$A,$K13,$C:$C,S$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>17.168399999999998</v>
       </c>
       <c r="T13">
-        <f>SUMIFS($B:$B,$A:$A,$K13,$C:$C,T$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>19.634399999999999</v>
       </c>
       <c r="U13">
-        <f>SUMIFS($B:$B,$A:$A,$K13,$C:$C,U$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>20.134799999999998</v>
       </c>
       <c r="V13">
-        <f>SUMIFS($B:$B,$A:$A,$K13,$C:$C,V$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>20.084399999999999</v>
       </c>
       <c r="W13">
-        <f>SUMIFS($B:$B,$A:$A,$K13,$C:$C,W$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>21.178799999999999</v>
       </c>
       <c r="X13">
-        <f>SUMIFS($B:$B,$A:$A,$K13,$C:$C,X$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>17.5212</v>
       </c>
       <c r="Y13">
-        <f>SUMIFS($B:$B,$A:$A,$K13,$C:$C,Y$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>20.4588</v>
       </c>
       <c r="Z13">
-        <f>SUMIFS($B:$B,$A:$A,$K13,$C:$C,Z$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>17.9712</v>
       </c>
       <c r="AA13">
-        <f>SUMIFS($B:$B,$A:$A,$K13,$C:$C,AA$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>18.633599999999998</v>
       </c>
       <c r="AB13">
-        <f>SUMIFS($B:$B,$A:$A,$K13,$C:$C,AB$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>16.329599999999999</v>
       </c>
       <c r="AC13">
-        <f>SUMIFS($B:$B,$A:$A,$K13,$C:$C,AC$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>18.594000000000001</v>
       </c>
       <c r="AD13">
-        <f>SUMIFS($B:$B,$A:$A,$K13,$C:$C,AD$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>16.344000000000001</v>
       </c>
     </row>
@@ -15354,79 +15400,79 @@
         <v>16</v>
       </c>
       <c r="L14">
-        <f>SUMIFS($B:$B,$A:$A,$K14,$C:$C,L$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>1.1843999999999999</v>
       </c>
       <c r="M14">
-        <f>SUMIFS($B:$B,$A:$A,$K14,$C:$C,M$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>1.1663999999999999</v>
       </c>
       <c r="N14">
-        <f>SUMIFS($B:$B,$A:$A,$K14,$C:$C,N$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>1.1052</v>
       </c>
       <c r="O14">
-        <f>SUMIFS($B:$B,$A:$A,$K14,$C:$C,O$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>1.2276</v>
       </c>
       <c r="P14">
-        <f>SUMIFS($B:$B,$A:$A,$K14,$C:$C,P$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>0.57240000000000002</v>
       </c>
       <c r="Q14">
-        <f>SUMIFS($B:$B,$A:$A,$K14,$C:$C,Q$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>0.61560000000000004</v>
       </c>
       <c r="R14">
-        <f>SUMIFS($B:$B,$A:$A,$K14,$C:$C,R$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>0.63</v>
       </c>
       <c r="S14">
-        <f>SUMIFS($B:$B,$A:$A,$K14,$C:$C,S$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T14">
-        <f>SUMIFS($B:$B,$A:$A,$K14,$C:$C,T$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="U14">
-        <f>SUMIFS($B:$B,$A:$A,$K14,$C:$C,U$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>0.77759999999999996</v>
       </c>
       <c r="V14">
-        <f>SUMIFS($B:$B,$A:$A,$K14,$C:$C,V$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>0.38879999999999998</v>
       </c>
       <c r="W14">
-        <f>SUMIFS($B:$B,$A:$A,$K14,$C:$C,W$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>0.3276</v>
       </c>
       <c r="X14">
-        <f>SUMIFS($B:$B,$A:$A,$K14,$C:$C,X$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>0.33839999999999998</v>
       </c>
       <c r="Y14">
-        <f>SUMIFS($B:$B,$A:$A,$K14,$C:$C,Y$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>0.50039999999999996</v>
       </c>
       <c r="Z14">
-        <f>SUMIFS($B:$B,$A:$A,$K14,$C:$C,Z$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>0.57599999999999996</v>
       </c>
       <c r="AA14">
-        <f>SUMIFS($B:$B,$A:$A,$K14,$C:$C,AA$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>1.008</v>
       </c>
       <c r="AB14">
-        <f>SUMIFS($B:$B,$A:$A,$K14,$C:$C,AB$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>1.0151999999999999</v>
       </c>
       <c r="AC14">
-        <f>SUMIFS($B:$B,$A:$A,$K14,$C:$C,AC$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>0.98280000000000001</v>
       </c>
       <c r="AD14">
-        <f>SUMIFS($B:$B,$A:$A,$K14,$C:$C,AD$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>0.87839999999999996</v>
       </c>
     </row>
@@ -15443,6 +15489,82 @@
       <c r="D15" t="s">
         <v>5</v>
       </c>
+      <c r="L15">
+        <f>SUM(L3:L14)</f>
+        <v>1078.0524000000003</v>
+      </c>
+      <c r="M15">
+        <f t="shared" ref="M15:AD15" si="2">SUM(M3:M14)</f>
+        <v>1098.2124000000001</v>
+      </c>
+      <c r="N15">
+        <f t="shared" si="2"/>
+        <v>1129.5287999999998</v>
+      </c>
+      <c r="O15">
+        <f t="shared" si="2"/>
+        <v>1060.6319999999998</v>
+      </c>
+      <c r="P15">
+        <f t="shared" si="2"/>
+        <v>1085.4972000000002</v>
+      </c>
+      <c r="Q15">
+        <f t="shared" si="2"/>
+        <v>1057.8492000000003</v>
+      </c>
+      <c r="R15">
+        <f t="shared" si="2"/>
+        <v>1071.2088000000001</v>
+      </c>
+      <c r="S15">
+        <f t="shared" si="2"/>
+        <v>1028.2679999999998</v>
+      </c>
+      <c r="T15">
+        <f t="shared" si="2"/>
+        <v>1003.4892</v>
+      </c>
+      <c r="U15">
+        <f t="shared" si="2"/>
+        <v>1011.2796000000001</v>
+      </c>
+      <c r="V15">
+        <f t="shared" si="2"/>
+        <v>989.17559999999992</v>
+      </c>
+      <c r="W15">
+        <f t="shared" si="2"/>
+        <v>992.61359999999991</v>
+      </c>
+      <c r="X15">
+        <f t="shared" si="2"/>
+        <v>988.02720000000011</v>
+      </c>
+      <c r="Y15">
+        <f t="shared" si="2"/>
+        <v>983.72520000000009</v>
+      </c>
+      <c r="Z15">
+        <f t="shared" si="2"/>
+        <v>948.14279999999997</v>
+      </c>
+      <c r="AA15">
+        <f t="shared" si="2"/>
+        <v>987.52319999999997</v>
+      </c>
+      <c r="AB15">
+        <f t="shared" si="2"/>
+        <v>1052.8344000000002</v>
+      </c>
+      <c r="AC15">
+        <f t="shared" si="2"/>
+        <v>1029.1643999999999</v>
+      </c>
+      <c r="AD15">
+        <f t="shared" si="2"/>
+        <v>1036.4724000000001</v>
+      </c>
     </row>
     <row r="16" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
@@ -15456,6 +15578,85 @@
       </c>
       <c r="D16" t="s">
         <v>5</v>
+      </c>
+      <c r="K16" t="s">
+        <v>74</v>
+      </c>
+      <c r="L16">
+        <f>L15/3.6</f>
+        <v>299.45900000000006</v>
+      </c>
+      <c r="M16">
+        <f t="shared" ref="M16:AD16" si="3">M15/3.6</f>
+        <v>305.05900000000003</v>
+      </c>
+      <c r="N16">
+        <f t="shared" si="3"/>
+        <v>313.75799999999992</v>
+      </c>
+      <c r="O16">
+        <f t="shared" si="3"/>
+        <v>294.61999999999995</v>
+      </c>
+      <c r="P16">
+        <f t="shared" si="3"/>
+        <v>301.52700000000004</v>
+      </c>
+      <c r="Q16">
+        <f t="shared" si="3"/>
+        <v>293.84700000000009</v>
+      </c>
+      <c r="R16">
+        <f t="shared" si="3"/>
+        <v>297.55800000000005</v>
+      </c>
+      <c r="S16">
+        <f t="shared" si="3"/>
+        <v>285.62999999999994</v>
+      </c>
+      <c r="T16">
+        <f t="shared" si="3"/>
+        <v>278.74700000000001</v>
+      </c>
+      <c r="U16">
+        <f t="shared" si="3"/>
+        <v>280.911</v>
+      </c>
+      <c r="V16">
+        <f t="shared" si="3"/>
+        <v>274.77099999999996</v>
+      </c>
+      <c r="W16">
+        <f t="shared" si="3"/>
+        <v>275.72599999999994</v>
+      </c>
+      <c r="X16">
+        <f t="shared" si="3"/>
+        <v>274.452</v>
+      </c>
+      <c r="Y16">
+        <f t="shared" si="3"/>
+        <v>273.25700000000001</v>
+      </c>
+      <c r="Z16">
+        <f t="shared" si="3"/>
+        <v>263.37299999999999</v>
+      </c>
+      <c r="AA16">
+        <f t="shared" si="3"/>
+        <v>274.31200000000001</v>
+      </c>
+      <c r="AB16">
+        <f t="shared" si="3"/>
+        <v>292.45400000000006</v>
+      </c>
+      <c r="AC16">
+        <f t="shared" si="3"/>
+        <v>285.87899999999996</v>
+      </c>
+      <c r="AD16">
+        <f t="shared" si="3"/>
+        <v>287.90900000000005</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -19477,79 +19678,79 @@
         <v>20</v>
       </c>
       <c r="J3">
-        <f>SUMIFS($B:$B,$A:$A,$I3,$C:$C,J$2)*0.0036</f>
+        <f t="shared" ref="J3:S4" si="0">SUMIFS($B:$B,$A:$A,$I3,$C:$C,J$2)*0.0036</f>
         <v>32.7348</v>
       </c>
       <c r="K3">
-        <f>SUMIFS($B:$B,$A:$A,$I3,$C:$C,K$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>31.582799999999999</v>
       </c>
       <c r="L3">
-        <f>SUMIFS($B:$B,$A:$A,$I3,$C:$C,L$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>21.171599999999998</v>
       </c>
       <c r="M3">
-        <f>SUMIFS($B:$B,$A:$A,$I3,$C:$C,M$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>24.303599999999999</v>
       </c>
       <c r="N3">
-        <f>SUMIFS($B:$B,$A:$A,$I3,$C:$C,N$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>18.741599999999998</v>
       </c>
       <c r="O3">
-        <f>SUMIFS($B:$B,$A:$A,$I3,$C:$C,O$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>28.555199999999999</v>
       </c>
       <c r="P3">
-        <f>SUMIFS($B:$B,$A:$A,$I3,$C:$C,P$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>28.033200000000001</v>
       </c>
       <c r="Q3">
-        <f>SUMIFS($B:$B,$A:$A,$I3,$C:$C,Q$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>35.593199999999996</v>
       </c>
       <c r="R3">
-        <f>SUMIFS($B:$B,$A:$A,$I3,$C:$C,R$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>44.315999999999995</v>
       </c>
       <c r="S3">
-        <f>SUMIFS($B:$B,$A:$A,$I3,$C:$C,S$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>53.8416</v>
       </c>
       <c r="T3">
-        <f>SUMIFS($B:$B,$A:$A,$I3,$C:$C,T$2)*0.0036</f>
+        <f t="shared" ref="T3:AB4" si="1">SUMIFS($B:$B,$A:$A,$I3,$C:$C,T$2)*0.0036</f>
         <v>78.641999999999996</v>
       </c>
       <c r="U3">
-        <f>SUMIFS($B:$B,$A:$A,$I3,$C:$C,U$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>85.543199999999999</v>
       </c>
       <c r="V3">
-        <f>SUMIFS($B:$B,$A:$A,$I3,$C:$C,V$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>86.464799999999997</v>
       </c>
       <c r="W3">
-        <f>SUMIFS($B:$B,$A:$A,$I3,$C:$C,W$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>67.391999999999996</v>
       </c>
       <c r="X3">
-        <f>SUMIFS($B:$B,$A:$A,$I3,$C:$C,X$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>64.540800000000004</v>
       </c>
       <c r="Y3">
-        <f>SUMIFS($B:$B,$A:$A,$I3,$C:$C,Y$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>62.679600000000001</v>
       </c>
       <c r="Z3">
-        <f>SUMIFS($B:$B,$A:$A,$I3,$C:$C,Z$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>28.9116</v>
       </c>
       <c r="AA3">
-        <f>SUMIFS($B:$B,$A:$A,$I3,$C:$C,AA$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>40.7376</v>
       </c>
       <c r="AB3">
-        <f>SUMIFS($B:$B,$A:$A,$I3,$C:$C,AB$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>51.674399999999999</v>
       </c>
     </row>
@@ -19570,79 +19771,79 @@
         <v>21</v>
       </c>
       <c r="J4">
-        <f>SUMIFS($B:$B,$A:$A,$I4,$C:$C,J$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>-44.5428</v>
       </c>
       <c r="K4">
-        <f>SUMIFS($B:$B,$A:$A,$I4,$C:$C,K$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>-52.2864</v>
       </c>
       <c r="L4">
-        <f>SUMIFS($B:$B,$A:$A,$I4,$C:$C,L$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>-60.911999999999999</v>
       </c>
       <c r="M4">
-        <f>SUMIFS($B:$B,$A:$A,$I4,$C:$C,M$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>-53.478000000000002</v>
       </c>
       <c r="N4">
-        <f>SUMIFS($B:$B,$A:$A,$I4,$C:$C,N$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>-48.740400000000001</v>
       </c>
       <c r="O4">
-        <f>SUMIFS($B:$B,$A:$A,$I4,$C:$C,O$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>-50.482799999999997</v>
       </c>
       <c r="P4">
-        <f>SUMIFS($B:$B,$A:$A,$I4,$C:$C,P$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>-68.349599999999995</v>
       </c>
       <c r="Q4">
-        <f>SUMIFS($B:$B,$A:$A,$I4,$C:$C,Q$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>-59.896799999999999</v>
       </c>
       <c r="R4">
-        <f>SUMIFS($B:$B,$A:$A,$I4,$C:$C,R$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>-56.577599999999997</v>
       </c>
       <c r="S4">
-        <f>SUMIFS($B:$B,$A:$A,$I4,$C:$C,S$2)*0.0036</f>
+        <f t="shared" si="0"/>
         <v>-54.320399999999999</v>
       </c>
       <c r="T4">
-        <f>SUMIFS($B:$B,$A:$A,$I4,$C:$C,T$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>-51.040799999999997</v>
       </c>
       <c r="U4">
-        <f>SUMIFS($B:$B,$A:$A,$I4,$C:$C,U$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>-52.534799999999997</v>
       </c>
       <c r="V4">
-        <f>SUMIFS($B:$B,$A:$A,$I4,$C:$C,V$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>-46.497599999999998</v>
       </c>
       <c r="W4">
-        <f>SUMIFS($B:$B,$A:$A,$I4,$C:$C,W$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>-42.688800000000001</v>
       </c>
       <c r="X4">
-        <f>SUMIFS($B:$B,$A:$A,$I4,$C:$C,X$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>-52.732799999999997</v>
       </c>
       <c r="Y4">
-        <f>SUMIFS($B:$B,$A:$A,$I4,$C:$C,Y$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>-59.608799999999995</v>
       </c>
       <c r="Z4">
-        <f>SUMIFS($B:$B,$A:$A,$I4,$C:$C,Z$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>-100.19879999999999</v>
       </c>
       <c r="AA4">
-        <f>SUMIFS($B:$B,$A:$A,$I4,$C:$C,AA$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>-90.979199999999992</v>
       </c>
       <c r="AB4">
-        <f>SUMIFS($B:$B,$A:$A,$I4,$C:$C,AB$2)*0.0036</f>
+        <f t="shared" si="1"/>
         <v>-88.491599999999991</v>
       </c>
     </row>
@@ -19663,79 +19864,79 @@
         <v>23</v>
       </c>
       <c r="J5">
-        <f>SUM(J3,J4)</f>
+        <f t="shared" ref="J5:AB5" si="2">SUM(J3,J4)</f>
         <v>-11.808</v>
       </c>
       <c r="K5">
-        <f>SUM(K3,K4)</f>
+        <f t="shared" si="2"/>
         <v>-20.703600000000002</v>
       </c>
       <c r="L5">
-        <f>SUM(L3,L4)</f>
+        <f t="shared" si="2"/>
         <v>-39.740400000000001</v>
       </c>
       <c r="M5">
-        <f>SUM(M3,M4)</f>
+        <f t="shared" si="2"/>
         <v>-29.174400000000002</v>
       </c>
       <c r="N5">
-        <f>SUM(N3,N4)</f>
+        <f t="shared" si="2"/>
         <v>-29.998800000000003</v>
       </c>
       <c r="O5">
-        <f>SUM(O3,O4)</f>
+        <f t="shared" si="2"/>
         <v>-21.927599999999998</v>
       </c>
       <c r="P5">
-        <f>SUM(P3,P4)</f>
+        <f t="shared" si="2"/>
         <v>-40.316399999999994</v>
       </c>
       <c r="Q5">
-        <f>SUM(Q3,Q4)</f>
+        <f t="shared" si="2"/>
         <v>-24.303600000000003</v>
       </c>
       <c r="R5">
-        <f>SUM(R3,R4)</f>
+        <f t="shared" si="2"/>
         <v>-12.261600000000001</v>
       </c>
       <c r="S5">
-        <f>SUM(S3,S4)</f>
+        <f t="shared" si="2"/>
         <v>-0.47879999999999967</v>
       </c>
       <c r="T5">
-        <f>SUM(T3,T4)</f>
+        <f t="shared" si="2"/>
         <v>27.601199999999999</v>
       </c>
       <c r="U5">
-        <f>SUM(U3,U4)</f>
+        <f t="shared" si="2"/>
         <v>33.008400000000002</v>
       </c>
       <c r="V5">
-        <f>SUM(V3,V4)</f>
+        <f t="shared" si="2"/>
         <v>39.967199999999998</v>
       </c>
       <c r="W5">
-        <f>SUM(W3,W4)</f>
+        <f t="shared" si="2"/>
         <v>24.703199999999995</v>
       </c>
       <c r="X5">
-        <f>SUM(X3,X4)</f>
+        <f t="shared" si="2"/>
         <v>11.808000000000007</v>
       </c>
       <c r="Y5">
-        <f>SUM(Y3,Y4)</f>
+        <f t="shared" si="2"/>
         <v>3.0708000000000055</v>
       </c>
       <c r="Z5">
-        <f>SUM(Z3,Z4)</f>
+        <f t="shared" si="2"/>
         <v>-71.287199999999984</v>
       </c>
       <c r="AA5">
-        <f>SUM(AA3,AA4)</f>
+        <f t="shared" si="2"/>
         <v>-50.241599999999991</v>
       </c>
       <c r="AB5">
-        <f>SUM(AB3,AB4)</f>
+        <f t="shared" si="2"/>
         <v>-36.817199999999993</v>
       </c>
     </row>
@@ -20498,75 +20699,75 @@
         <v>4</v>
       </c>
       <c r="J3" s="2">
-        <f>SUMIFS($B:$B,$A:$A,$I3,$C:$C,J$2)</f>
+        <f t="shared" ref="J3:S6" si="0">SUMIFS($B:$B,$A:$A,$I3,$C:$C,J$2)</f>
         <v>62.594999999999999</v>
       </c>
       <c r="K3" s="2">
-        <f>SUMIFS($B:$B,$A:$A,$I3,$C:$C,K$2)</f>
+        <f t="shared" si="0"/>
         <v>71.436000000000007</v>
       </c>
       <c r="L3" s="2">
-        <f>SUMIFS($B:$B,$A:$A,$I3,$C:$C,L$2)</f>
+        <f t="shared" si="0"/>
         <v>46.113999999999997</v>
       </c>
       <c r="M3" s="2">
-        <f>SUMIFS($B:$B,$A:$A,$I3,$C:$C,M$2)</f>
+        <f t="shared" si="0"/>
         <v>35.026000000000003</v>
       </c>
       <c r="N3" s="2">
-        <f>SUMIFS($B:$B,$A:$A,$I3,$C:$C,N$2)</f>
+        <f t="shared" si="0"/>
         <v>25.3</v>
       </c>
       <c r="O3" s="2">
-        <f>SUMIFS($B:$B,$A:$A,$I3,$C:$C,O$2)</f>
+        <f t="shared" si="0"/>
         <v>44.177999999999997</v>
       </c>
       <c r="P3" s="2">
-        <f>SUMIFS($B:$B,$A:$A,$I3,$C:$C,P$2)</f>
+        <f t="shared" si="0"/>
         <v>53.131999999999998</v>
       </c>
       <c r="Q3" s="2">
-        <f>SUMIFS($B:$B,$A:$A,$I3,$C:$C,Q$2)</f>
+        <f t="shared" si="0"/>
         <v>38.640999999999998</v>
       </c>
       <c r="R3" s="2">
-        <f>SUMIFS($B:$B,$A:$A,$I3,$C:$C,R$2)</f>
+        <f t="shared" si="0"/>
         <v>42.912999999999997</v>
       </c>
       <c r="S3" s="2">
-        <f>SUMIFS($B:$B,$A:$A,$I3,$C:$C,S$2)</f>
+        <f t="shared" si="0"/>
         <v>49.125</v>
       </c>
       <c r="T3" s="2">
-        <f>SUMIFS($B:$B,$A:$A,$I3,$C:$C,T$2)</f>
+        <f t="shared" ref="T3:AA6" si="1">SUMIFS($B:$B,$A:$A,$I3,$C:$C,T$2)</f>
         <v>35.423000000000002</v>
       </c>
       <c r="U3" s="2">
-        <f>SUMIFS($B:$B,$A:$A,$I3,$C:$C,U$2)</f>
+        <f t="shared" si="1"/>
         <v>44.04</v>
       </c>
       <c r="V3" s="2">
-        <f>SUMIFS($B:$B,$A:$A,$I3,$C:$C,V$2)</f>
+        <f t="shared" si="1"/>
         <v>36.701999999999998</v>
       </c>
       <c r="W3" s="2">
-        <f>SUMIFS($B:$B,$A:$A,$I3,$C:$C,W$2)</f>
+        <f t="shared" si="1"/>
         <v>14.217000000000001</v>
       </c>
       <c r="X3" s="2">
-        <f>SUMIFS($B:$B,$A:$A,$I3,$C:$C,X$2)</f>
+        <f t="shared" si="1"/>
         <v>6.4909999999999997</v>
       </c>
       <c r="Y3" s="2">
-        <f>SUMIFS($B:$B,$A:$A,$I3,$C:$C,Y$2)</f>
+        <f t="shared" si="1"/>
         <v>7.1749999999999998</v>
       </c>
       <c r="Z3" s="2">
-        <f>SUMIFS($B:$B,$A:$A,$I3,$C:$C,Z$2)</f>
+        <f t="shared" si="1"/>
         <v>8.9670000000000005</v>
       </c>
       <c r="AA3" s="2">
-        <f>SUMIFS($B:$B,$A:$A,$I3,$C:$C,AA$2)</f>
+        <f t="shared" si="1"/>
         <v>5.43</v>
       </c>
     </row>
@@ -20587,75 +20788,75 @@
         <v>6</v>
       </c>
       <c r="J4" s="2">
-        <f>SUMIFS($B:$B,$A:$A,$I4,$C:$C,J$2)</f>
+        <f t="shared" si="0"/>
         <v>14.491</v>
       </c>
       <c r="K4" s="2">
-        <f>SUMIFS($B:$B,$A:$A,$I4,$C:$C,K$2)</f>
+        <f t="shared" si="0"/>
         <v>13.48</v>
       </c>
       <c r="L4" s="2">
-        <f>SUMIFS($B:$B,$A:$A,$I4,$C:$C,L$2)</f>
+        <f t="shared" si="0"/>
         <v>12.941000000000001</v>
       </c>
       <c r="M4" s="2">
-        <f>SUMIFS($B:$B,$A:$A,$I4,$C:$C,M$2)</f>
+        <f t="shared" si="0"/>
         <v>12.904999999999999</v>
       </c>
       <c r="N4" s="2">
-        <f>SUMIFS($B:$B,$A:$A,$I4,$C:$C,N$2)</f>
+        <f t="shared" si="0"/>
         <v>11.218</v>
       </c>
       <c r="O4" s="2">
-        <f>SUMIFS($B:$B,$A:$A,$I4,$C:$C,O$2)</f>
+        <f t="shared" si="0"/>
         <v>10.52</v>
       </c>
       <c r="P4" s="2">
-        <f>SUMIFS($B:$B,$A:$A,$I4,$C:$C,P$2)</f>
+        <f t="shared" si="0"/>
         <v>10.917</v>
       </c>
       <c r="Q4" s="2">
-        <f>SUMIFS($B:$B,$A:$A,$I4,$C:$C,Q$2)</f>
+        <f t="shared" si="0"/>
         <v>9.4359999999999999</v>
       </c>
       <c r="R4" s="2">
-        <f>SUMIFS($B:$B,$A:$A,$I4,$C:$C,R$2)</f>
+        <f t="shared" si="0"/>
         <v>9.9710000000000001</v>
       </c>
       <c r="S4" s="2">
-        <f>SUMIFS($B:$B,$A:$A,$I4,$C:$C,S$2)</f>
+        <f t="shared" si="0"/>
         <v>11.891999999999999</v>
       </c>
       <c r="T4" s="2">
-        <f>SUMIFS($B:$B,$A:$A,$I4,$C:$C,T$2)</f>
+        <f t="shared" si="1"/>
         <v>11.385999999999999</v>
       </c>
       <c r="U4" s="2">
-        <f>SUMIFS($B:$B,$A:$A,$I4,$C:$C,U$2)</f>
+        <f t="shared" si="1"/>
         <v>10.512</v>
       </c>
       <c r="V4" s="2">
-        <f>SUMIFS($B:$B,$A:$A,$I4,$C:$C,V$2)</f>
+        <f t="shared" si="1"/>
         <v>9.5120000000000005</v>
       </c>
       <c r="W4" s="2">
-        <f>SUMIFS($B:$B,$A:$A,$I4,$C:$C,W$2)</f>
+        <f t="shared" si="1"/>
         <v>8.1780000000000008</v>
       </c>
       <c r="X4" s="2">
-        <f>SUMIFS($B:$B,$A:$A,$I4,$C:$C,X$2)</f>
+        <f t="shared" si="1"/>
         <v>6.718</v>
       </c>
       <c r="Y4" s="2">
-        <f>SUMIFS($B:$B,$A:$A,$I4,$C:$C,Y$2)</f>
+        <f t="shared" si="1"/>
         <v>6.3220000000000001</v>
       </c>
       <c r="Z4" s="2">
-        <f>SUMIFS($B:$B,$A:$A,$I4,$C:$C,Z$2)</f>
+        <f t="shared" si="1"/>
         <v>6.7210000000000001</v>
       </c>
       <c r="AA4" s="2">
-        <f>SUMIFS($B:$B,$A:$A,$I4,$C:$C,AA$2)</f>
+        <f t="shared" si="1"/>
         <v>6.24</v>
       </c>
     </row>
@@ -20676,75 +20877,75 @@
         <v>7</v>
       </c>
       <c r="J5" s="2">
-        <f>SUMIFS($B:$B,$A:$A,$I5,$C:$C,J$2)</f>
+        <f t="shared" si="0"/>
         <v>32.406999999999996</v>
       </c>
       <c r="K5" s="2">
-        <f>SUMIFS($B:$B,$A:$A,$I5,$C:$C,K$2)</f>
+        <f t="shared" si="0"/>
         <v>32.332999999999998</v>
       </c>
       <c r="L5" s="2">
-        <f>SUMIFS($B:$B,$A:$A,$I5,$C:$C,L$2)</f>
+        <f t="shared" si="0"/>
         <v>42.374000000000002</v>
       </c>
       <c r="M5" s="2">
-        <f>SUMIFS($B:$B,$A:$A,$I5,$C:$C,M$2)</f>
+        <f t="shared" si="0"/>
         <v>38.268000000000001</v>
       </c>
       <c r="N5" s="2">
-        <f>SUMIFS($B:$B,$A:$A,$I5,$C:$C,N$2)</f>
+        <f t="shared" si="0"/>
         <v>34.341999999999999</v>
       </c>
       <c r="O5" s="2">
-        <f>SUMIFS($B:$B,$A:$A,$I5,$C:$C,O$2)</f>
+        <f t="shared" si="0"/>
         <v>30.934000000000001</v>
       </c>
       <c r="P5" s="2">
-        <f>SUMIFS($B:$B,$A:$A,$I5,$C:$C,P$2)</f>
+        <f t="shared" si="0"/>
         <v>26.295999999999999</v>
       </c>
       <c r="Q5" s="2">
-        <f>SUMIFS($B:$B,$A:$A,$I5,$C:$C,Q$2)</f>
+        <f t="shared" si="0"/>
         <v>20.146999999999998</v>
       </c>
       <c r="R5" s="2">
-        <f>SUMIFS($B:$B,$A:$A,$I5,$C:$C,R$2)</f>
+        <f t="shared" si="0"/>
         <v>16.512</v>
       </c>
       <c r="S5" s="2">
-        <f>SUMIFS($B:$B,$A:$A,$I5,$C:$C,S$2)</f>
+        <f t="shared" si="0"/>
         <v>19.401</v>
       </c>
       <c r="T5" s="2">
-        <f>SUMIFS($B:$B,$A:$A,$I5,$C:$C,T$2)</f>
+        <f t="shared" si="1"/>
         <v>19.056999999999999</v>
       </c>
       <c r="U5" s="2">
-        <f>SUMIFS($B:$B,$A:$A,$I5,$C:$C,U$2)</f>
+        <f t="shared" si="1"/>
         <v>23.382999999999999</v>
       </c>
       <c r="V5" s="2">
-        <f>SUMIFS($B:$B,$A:$A,$I5,$C:$C,V$2)</f>
+        <f t="shared" si="1"/>
         <v>21.161999999999999</v>
       </c>
       <c r="W5" s="2">
-        <f>SUMIFS($B:$B,$A:$A,$I5,$C:$C,W$2)</f>
+        <f t="shared" si="1"/>
         <v>30.029</v>
       </c>
       <c r="X5" s="2">
-        <f>SUMIFS($B:$B,$A:$A,$I5,$C:$C,X$2)</f>
+        <f t="shared" si="1"/>
         <v>25.106999999999999</v>
       </c>
       <c r="Y5" s="2">
-        <f>SUMIFS($B:$B,$A:$A,$I5,$C:$C,Y$2)</f>
+        <f t="shared" si="1"/>
         <v>25.800999999999998</v>
       </c>
       <c r="Z5" s="2">
-        <f>SUMIFS($B:$B,$A:$A,$I5,$C:$C,Z$2)</f>
+        <f t="shared" si="1"/>
         <v>32.043999999999997</v>
       </c>
       <c r="AA5" s="2">
-        <f>SUMIFS($B:$B,$A:$A,$I5,$C:$C,AA$2)</f>
+        <f t="shared" si="1"/>
         <v>24.222999999999999</v>
       </c>
     </row>
@@ -20765,75 +20966,75 @@
         <v>25</v>
       </c>
       <c r="J6" s="2">
-        <f>SUMIFS($B:$B,$A:$A,$I6,$C:$C,J$2)</f>
+        <f t="shared" si="0"/>
         <v>0.96699999999999997</v>
       </c>
       <c r="K6" s="2">
-        <f>SUMIFS($B:$B,$A:$A,$I6,$C:$C,K$2)</f>
+        <f t="shared" si="0"/>
         <v>1.1870000000000001</v>
       </c>
       <c r="L6" s="2">
-        <f>SUMIFS($B:$B,$A:$A,$I6,$C:$C,L$2)</f>
+        <f t="shared" si="0"/>
         <v>1.2589999999999999</v>
       </c>
       <c r="M6" s="2">
-        <f>SUMIFS($B:$B,$A:$A,$I6,$C:$C,M$2)</f>
+        <f t="shared" si="0"/>
         <v>1.2250000000000001</v>
       </c>
       <c r="N6" s="2">
-        <f>SUMIFS($B:$B,$A:$A,$I6,$C:$C,N$2)</f>
+        <f t="shared" si="0"/>
         <v>0.66800000000000004</v>
       </c>
       <c r="O6" s="2">
-        <f>SUMIFS($B:$B,$A:$A,$I6,$C:$C,O$2)</f>
+        <f t="shared" si="0"/>
         <v>0.748</v>
       </c>
       <c r="P6" s="2">
-        <f>SUMIFS($B:$B,$A:$A,$I6,$C:$C,P$2)</f>
+        <f t="shared" si="0"/>
         <v>0.67400000000000004</v>
       </c>
       <c r="Q6" s="2">
-        <f>SUMIFS($B:$B,$A:$A,$I6,$C:$C,Q$2)</f>
+        <f t="shared" si="0"/>
         <v>0.76600000000000001</v>
       </c>
       <c r="R6" s="2">
-        <f>SUMIFS($B:$B,$A:$A,$I6,$C:$C,R$2)</f>
+        <f t="shared" si="0"/>
         <v>0.78300000000000003</v>
       </c>
       <c r="S6" s="2">
-        <f>SUMIFS($B:$B,$A:$A,$I6,$C:$C,S$2)</f>
+        <f t="shared" si="0"/>
         <v>0.95799999999999996</v>
       </c>
       <c r="T6" s="2">
-        <f>SUMIFS($B:$B,$A:$A,$I6,$C:$C,T$2)</f>
+        <f t="shared" si="1"/>
         <v>0.88100000000000001</v>
       </c>
       <c r="U6" s="2">
-        <f>SUMIFS($B:$B,$A:$A,$I6,$C:$C,U$2)</f>
+        <f t="shared" si="1"/>
         <v>0.97</v>
       </c>
       <c r="V6" s="2">
-        <f>SUMIFS($B:$B,$A:$A,$I6,$C:$C,V$2)</f>
+        <f t="shared" si="1"/>
         <v>1.3839999999999999</v>
       </c>
       <c r="W6" s="2">
-        <f>SUMIFS($B:$B,$A:$A,$I6,$C:$C,W$2)</f>
+        <f t="shared" si="1"/>
         <v>1.3080000000000001</v>
       </c>
       <c r="X6" s="2">
-        <f>SUMIFS($B:$B,$A:$A,$I6,$C:$C,X$2)</f>
+        <f t="shared" si="1"/>
         <v>1.5760000000000001</v>
       </c>
       <c r="Y6" s="2">
-        <f>SUMIFS($B:$B,$A:$A,$I6,$C:$C,Y$2)</f>
+        <f t="shared" si="1"/>
         <v>1.323</v>
       </c>
       <c r="Z6" s="2">
-        <f>SUMIFS($B:$B,$A:$A,$I6,$C:$C,Z$2)</f>
+        <f t="shared" si="1"/>
         <v>1.3180000000000001</v>
       </c>
       <c r="AA6" s="2">
-        <f>SUMIFS($B:$B,$A:$A,$I6,$C:$C,AA$2)</f>
+        <f t="shared" si="1"/>
         <v>1.22</v>
       </c>
     </row>
@@ -22895,11 +23096,11 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
       <c r="D2">
         <f>0.0036</f>
         <v>3.5999999999999999E-3</v>
@@ -22931,7 +23132,7 @@
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="4">
+      <c r="A7" s="3">
         <v>3971</v>
       </c>
       <c r="B7">
@@ -22959,37 +23160,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C1" s="5">
+      <c r="C1" s="4">
         <v>2007</v>
       </c>
-      <c r="D1" s="5">
+      <c r="D1" s="4">
         <v>2010</v>
       </c>
-      <c r="E1" s="5">
+      <c r="E1" s="4">
         <v>2014</v>
       </c>
-      <c r="F1" s="5">
+      <c r="F1" s="4">
         <v>2018</v>
       </c>
-      <c r="G1" s="5">
+      <c r="G1" s="4">
         <v>2022</v>
       </c>
-      <c r="H1" s="5">
+      <c r="H1" s="4">
         <v>2025</v>
       </c>
-      <c r="I1" s="5">
+      <c r="I1" s="4">
         <v>2030</v>
       </c>
-      <c r="J1" s="5">
+      <c r="J1" s="4">
         <v>2040</v>
       </c>
-      <c r="K1" s="5">
+      <c r="K1" s="4">
         <v>2050</v>
       </c>
     </row>
@@ -23027,31 +23228,31 @@
       <c r="K2">
         <v>20991.164775831501</v>
       </c>
-      <c r="O2" s="5">
+      <c r="O2" s="4">
         <v>2007</v>
       </c>
-      <c r="P2" s="5">
+      <c r="P2" s="4">
         <v>2010</v>
       </c>
-      <c r="Q2" s="5">
+      <c r="Q2" s="4">
         <v>2014</v>
       </c>
-      <c r="R2" s="5">
+      <c r="R2" s="4">
         <v>2018</v>
       </c>
-      <c r="S2" s="5">
+      <c r="S2" s="4">
         <v>2022</v>
       </c>
-      <c r="T2" s="5">
+      <c r="T2" s="4">
         <v>2025</v>
       </c>
-      <c r="U2" s="5">
+      <c r="U2" s="4">
         <v>2030</v>
       </c>
-      <c r="V2" s="5">
+      <c r="V2" s="4">
         <v>2040</v>
       </c>
-      <c r="W2" s="5">
+      <c r="W2" s="4">
         <v>2050</v>
       </c>
     </row>
@@ -24237,31 +24438,31 @@
       <c r="K21">
         <v>0</v>
       </c>
-      <c r="O21" s="5">
+      <c r="O21" s="4">
         <v>2007</v>
       </c>
-      <c r="P21" s="5">
+      <c r="P21" s="4">
         <v>2010</v>
       </c>
-      <c r="Q21" s="5">
+      <c r="Q21" s="4">
         <v>2014</v>
       </c>
-      <c r="R21" s="5">
+      <c r="R21" s="4">
         <v>2018</v>
       </c>
-      <c r="S21" s="5">
+      <c r="S21" s="4">
         <v>2022</v>
       </c>
-      <c r="T21" s="5">
+      <c r="T21" s="4">
         <v>2025</v>
       </c>
-      <c r="U21" s="5">
+      <c r="U21" s="4">
         <v>2030</v>
       </c>
-      <c r="V21" s="5">
+      <c r="V21" s="4">
         <v>2040</v>
       </c>
-      <c r="W21" s="5">
+      <c r="W21" s="4">
         <v>2050</v>
       </c>
     </row>
@@ -24303,39 +24504,39 @@
         <v>54</v>
       </c>
       <c r="O22">
-        <f>SUM(O6,O7,O8)/1000</f>
+        <f t="shared" ref="O22:W22" si="11">SUM(O6,O7,O8)/1000</f>
         <v>88.123870746745254</v>
       </c>
       <c r="P22">
-        <f>SUM(P6,P7,P8)/1000</f>
+        <f t="shared" si="11"/>
         <v>66.050147693349743</v>
       </c>
       <c r="Q22">
-        <f>SUM(Q6,Q7,Q8)/1000</f>
+        <f t="shared" si="11"/>
         <v>46.356168914408869</v>
       </c>
       <c r="R22">
-        <f>SUM(R6,R7,R8)/1000</f>
+        <f t="shared" si="11"/>
         <v>17.95848921428572</v>
       </c>
       <c r="S22">
-        <f>SUM(S6,S7,S8)/1000</f>
+        <f t="shared" si="11"/>
         <v>3.771774685714286</v>
       </c>
       <c r="T22">
-        <f>SUM(T6,T7,T8)/1000</f>
+        <f t="shared" si="11"/>
         <v>1.830514285714286</v>
       </c>
       <c r="U22">
-        <f>SUM(U6,U7,U8)/1000</f>
+        <f t="shared" si="11"/>
         <v>0.45762857142857138</v>
       </c>
       <c r="V22">
-        <f>SUM(V6,V7,V8)/1000</f>
+        <f t="shared" si="11"/>
         <v>0.2288142857142858</v>
       </c>
       <c r="W22">
-        <f>SUM(W6,W7,W8)/1000</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -24377,39 +24578,39 @@
         <v>52</v>
       </c>
       <c r="O23">
-        <f>SUM(O12,O13)/1000</f>
+        <f t="shared" ref="O23:W23" si="12">SUM(O12,O13)/1000</f>
         <v>13.9869583</v>
       </c>
       <c r="P23">
-        <f>SUM(P12,P13)/1000</f>
+        <f t="shared" si="12"/>
         <v>12.516317450000001</v>
       </c>
       <c r="Q23">
-        <f>SUM(Q12,Q13)/1000</f>
+        <f t="shared" si="12"/>
         <v>13.029454724999999</v>
       </c>
       <c r="R23">
-        <f>SUM(R12,R13)/1000</f>
+        <f t="shared" si="12"/>
         <v>10.95650105</v>
       </c>
       <c r="S23">
-        <f>SUM(S12,S13)/1000</f>
+        <f t="shared" si="12"/>
         <v>8.0031277500000009</v>
       </c>
       <c r="T23">
-        <f>SUM(T12,T13)/1000</f>
+        <f t="shared" si="12"/>
         <v>6.894479174999999</v>
       </c>
       <c r="U23">
-        <f>SUM(U12,U13)/1000</f>
+        <f t="shared" si="12"/>
         <v>5.2480902777777771</v>
       </c>
       <c r="V23">
-        <f>SUM(V12,V13)/1000</f>
+        <f t="shared" si="12"/>
         <v>2.8339687499999999</v>
       </c>
       <c r="W23">
-        <f>SUM(W12,W13)/1000</f>
+        <f t="shared" si="12"/>
         <v>0.3435113636363637</v>
       </c>
     </row>
@@ -24451,39 +24652,39 @@
         <v>53</v>
       </c>
       <c r="O24">
-        <f>SUM(O4,O5,O9,O10,O11,O12,O14,O15)/1000</f>
+        <f t="shared" ref="O24:W24" si="13">SUM(O4,O5,O9,O10,O11,O12,O14,O15)/1000</f>
         <v>51.169526347428565</v>
       </c>
       <c r="P24">
-        <f>SUM(P4,P5,P9,P10,P11,P12,P14,P15)/1000</f>
+        <f t="shared" si="13"/>
         <v>49.706871145428565</v>
       </c>
       <c r="Q24">
-        <f>SUM(Q4,Q5,Q9,Q10,Q11,Q12,Q14,Q15)/1000</f>
+        <f t="shared" si="13"/>
         <v>32.990978829433068</v>
       </c>
       <c r="R24">
-        <f>SUM(R4,R5,R9,R10,R11,R12,R14,R15)/1000</f>
+        <f t="shared" si="13"/>
         <v>35.004836961501162</v>
       </c>
       <c r="S24">
-        <f>SUM(S4,S5,S9,S10,S11,S12,S14,S15)/1000</f>
+        <f t="shared" si="13"/>
         <v>41.544492134145663</v>
       </c>
       <c r="T24">
-        <f>SUM(T4,T5,T9,T10,T11,T12,T14,T15)/1000</f>
+        <f t="shared" si="13"/>
         <v>29.010498141663621</v>
       </c>
       <c r="U24">
-        <f>SUM(U4,U5,U9,U10,U11,U12,U14,U15)/1000</f>
+        <f t="shared" si="13"/>
         <v>24.545216624187219</v>
       </c>
       <c r="V24">
-        <f>SUM(V4,V5,V9,V10,V11,V12,V14,V15)/1000</f>
+        <f t="shared" si="13"/>
         <v>15.472340498816662</v>
       </c>
       <c r="W24">
-        <f>SUM(W4,W5,W9,W10,W11,W12,W14,W15)/1000</f>
+        <f t="shared" si="13"/>
         <v>7.5995093549627253</v>
       </c>
     </row>
@@ -25202,50 +25403,57 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95A32E31-20CB-4056-864B-0FCE4F4387EC}">
-  <dimension ref="A1:T39"/>
+  <dimension ref="A1:AB26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="9.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C1" s="5">
+      <c r="C1" s="4">
         <v>2007</v>
       </c>
-      <c r="D1" s="5">
+      <c r="D1" s="4">
         <v>2010</v>
       </c>
-      <c r="E1" s="5">
+      <c r="E1" s="4">
         <v>2014</v>
       </c>
-      <c r="F1" s="5">
+      <c r="F1" s="4">
         <v>2018</v>
       </c>
-      <c r="G1" s="5">
+      <c r="G1" s="4">
         <v>2022</v>
       </c>
-      <c r="H1" s="5">
-        <v>2025</v>
-      </c>
-      <c r="I1" s="5">
+      <c r="H1" s="4">
+        <v>2024</v>
+      </c>
+      <c r="I1" s="4">
         <v>2030</v>
       </c>
-      <c r="J1" s="5">
+      <c r="J1" s="4">
         <v>2040</v>
       </c>
-      <c r="K1" s="5">
+      <c r="K1" s="4">
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>35</v>
       </c>
@@ -25253,31 +25461,31 @@
         <v>56</v>
       </c>
       <c r="C2">
-        <v>7.3906200000000002</v>
+        <v>7.3906199999999993</v>
       </c>
       <c r="D2">
-        <v>11.47752</v>
+        <v>11.47751999999999</v>
       </c>
       <c r="E2">
         <v>16.16976</v>
       </c>
       <c r="F2">
-        <v>16.422840000000001</v>
+        <v>16.42283999999999</v>
       </c>
       <c r="G2">
-        <v>19.505970000000001</v>
+        <v>19.505970000000008</v>
       </c>
       <c r="H2">
-        <v>18.19098000000001</v>
+        <v>18.19098</v>
       </c>
       <c r="I2">
-        <v>21.375000000000011</v>
+        <v>21.374999999999989</v>
       </c>
       <c r="J2">
-        <v>22.5625</v>
+        <v>22.562499999999989</v>
       </c>
       <c r="K2">
-        <v>25.189397730997801</v>
+        <v>5.7933717951093033</v>
       </c>
       <c r="O2">
         <v>2007</v>
@@ -25297,8 +25505,29 @@
       <c r="T2">
         <v>2024</v>
       </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="V2" t="s">
+        <v>73</v>
+      </c>
+      <c r="W2">
+        <v>2007</v>
+      </c>
+      <c r="X2">
+        <v>2010</v>
+      </c>
+      <c r="Y2">
+        <v>2014</v>
+      </c>
+      <c r="Z2">
+        <v>2018</v>
+      </c>
+      <c r="AA2">
+        <v>2022</v>
+      </c>
+      <c r="AB2">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>67</v>
       </c>
@@ -25330,37 +25559,64 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>1.0606022690022039</v>
+        <v>49.206628204890713</v>
       </c>
       <c r="N3" t="s">
         <v>4</v>
       </c>
       <c r="O3">
-        <f>SUM(C6,C7,C8)</f>
+        <f>SUM(C8,C7)</f>
         <v>253.37450000000001</v>
       </c>
       <c r="P3">
-        <f t="shared" ref="P3:T3" si="0">SUM(D6,D7,D8)</f>
-        <v>211.61250000000001</v>
+        <f t="shared" ref="P3:T3" si="0">SUM(D8,D7)</f>
+        <v>90.021999999999991</v>
       </c>
       <c r="Q3">
         <f t="shared" si="0"/>
-        <v>155.92983333333333</v>
+        <v>159.79</v>
       </c>
       <c r="R3">
         <f t="shared" si="0"/>
-        <v>74.560750000000056</v>
+        <v>132.37299999999999</v>
       </c>
       <c r="S3">
         <f t="shared" si="0"/>
-        <v>15.659800000000001</v>
+        <v>29.73500000000001</v>
       </c>
       <c r="T3">
         <f t="shared" si="0"/>
-        <v>7.6000000000000014</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+        <v>11.856</v>
+      </c>
+      <c r="V3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W3" s="6">
+        <f>(O3-O15)/O15</f>
+        <v>-4.9985752101565036E-2</v>
+      </c>
+      <c r="X3" s="6">
+        <f t="shared" ref="X3:AB11" si="1">(P3-P15)/P15</f>
+        <v>-5.0028070086574131E-2</v>
+      </c>
+      <c r="Y3" s="6">
+        <f t="shared" si="1"/>
+        <v>-2.0065987170524043E-2</v>
+      </c>
+      <c r="Z3" s="6">
+        <f t="shared" si="1"/>
+        <v>-5.0256282214645759E-2</v>
+      </c>
+      <c r="AA3" s="6">
+        <f t="shared" si="1"/>
+        <v>-5.0169937646938195E-2</v>
+      </c>
+      <c r="AB3" s="6">
+        <f t="shared" si="1"/>
+        <v>-4.9817272552413853E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>36</v>
       </c>
@@ -25374,55 +25630,82 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>2.7392664084480001</v>
       </c>
       <c r="F4">
-        <v>31.253352286391429</v>
+        <v>4.1088996126720003</v>
       </c>
       <c r="G4">
-        <v>15.443464799165501</v>
+        <v>3.9301941830400011</v>
       </c>
       <c r="H4">
-        <v>53.277672126507838</v>
+        <v>3.5727833237760018</v>
       </c>
       <c r="I4">
-        <v>71.997820776092382</v>
+        <v>8.9319583094400006</v>
       </c>
       <c r="J4">
-        <v>23.53376820086666</v>
+        <v>9.8254854576000028</v>
       </c>
       <c r="K4">
-        <v>19.145458654890991</v>
+        <v>6.5082742297919998</v>
       </c>
       <c r="N4" t="s">
         <v>6</v>
       </c>
       <c r="O4">
-        <f>SUM(C16,C17)</f>
-        <v>63.297359999999998</v>
+        <f>SUM(C16)</f>
+        <v>63.297359999999983</v>
       </c>
       <c r="P4">
-        <f t="shared" ref="P4:T4" si="1">SUM(D16,D17)</f>
-        <v>56.642040000000001</v>
+        <f t="shared" ref="P4:T4" si="2">SUM(D16)</f>
+        <v>56.642039999999987</v>
       </c>
       <c r="Q4">
+        <f t="shared" si="2"/>
+        <v>48.293819999999997</v>
+      </c>
+      <c r="R4">
+        <f t="shared" si="2"/>
+        <v>49.583160000000007</v>
+      </c>
+      <c r="S4">
+        <f t="shared" si="2"/>
+        <v>36.217799999999997</v>
+      </c>
+      <c r="T4">
+        <f t="shared" si="2"/>
+        <v>30.513999999999999</v>
+      </c>
+      <c r="V4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W4" s="6">
+        <f t="shared" ref="W4:W11" si="3">(O4-O16)/O16</f>
+        <v>-5.0000000000000225E-2</v>
+      </c>
+      <c r="X4" s="6">
         <f t="shared" si="1"/>
-        <v>58.964219999999997</v>
-      </c>
-      <c r="R4">
+        <v>-5.0000000000000169E-2</v>
+      </c>
+      <c r="Y4" s="6">
         <f t="shared" si="1"/>
-        <v>49.583159999999992</v>
-      </c>
-      <c r="S4">
+        <v>-5.0000000000000058E-2</v>
+      </c>
+      <c r="Z4" s="6">
         <f t="shared" si="1"/>
-        <v>36.217799999999997</v>
-      </c>
-      <c r="T4">
+        <v>-4.9999999999999843E-2</v>
+      </c>
+      <c r="AA4" s="6">
         <f t="shared" si="1"/>
-        <v>31.200659999999989</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+        <v>-5.0000000000000142E-2</v>
+      </c>
+      <c r="AB4" s="6">
+        <f t="shared" si="1"/>
+        <v>-7.0907474393169814E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>37</v>
       </c>
@@ -25439,128 +25722,182 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>11.923865542655999</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>16.332731711133619</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>16.092006761079251</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>18.532732622619921</v>
       </c>
       <c r="J5">
-        <v>20.336150101279038</v>
+        <v>18.138458556928249</v>
       </c>
       <c r="K5">
-        <v>5.4888618314261581</v>
+        <v>7.1341377993215982</v>
       </c>
       <c r="N5" t="s">
         <v>7</v>
       </c>
-      <c r="O5">
-        <f>SUM(C4+C5,C13,C14,C15,C18,C19)</f>
-        <v>324.21258000000006</v>
-      </c>
-      <c r="P5">
-        <f t="shared" ref="P5:T5" si="2">SUM(D4+D5,D13,D14,D15,D18,D19)</f>
-        <v>324.39042000000001</v>
-      </c>
-      <c r="Q5">
-        <f t="shared" si="2"/>
-        <v>179.54316000000006</v>
-      </c>
-      <c r="R5">
-        <f t="shared" si="2"/>
-        <v>229.62703228639168</v>
-      </c>
-      <c r="S5">
-        <f t="shared" si="2"/>
-        <v>309.47796479916542</v>
-      </c>
-      <c r="T5">
-        <f t="shared" si="2"/>
-        <v>232.24285212650787</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="O5" cm="1">
+        <f t="array" ref="O5">SUM(C4+C5:C6,C14:C15,C17:C18)</f>
+        <v>324.21258</v>
+      </c>
+      <c r="P5" cm="1">
+        <f t="array" ref="P5">SUM(D4+D5:D6,D14:D15,D17:D18)</f>
+        <v>350.71539729176556</v>
+      </c>
+      <c r="Q5" cm="1">
+        <f t="array" ref="Q5">SUM(E4+E5:E6,E14:E15,E17:E18)</f>
+        <v>182.28242640844772</v>
+      </c>
+      <c r="R5" cm="1">
+        <f t="array" ref="R5">SUM(F4+F5:F6,F14:F15,F17:F18)</f>
+        <v>202.4825796126716</v>
+      </c>
+      <c r="S5" cm="1">
+        <f t="array" ref="S5">SUM(G4+G5:G6,G14:G15,G17:G18)</f>
+        <v>327.79714840445774</v>
+      </c>
+      <c r="T5" cm="1">
+        <f t="array" ref="T5">SUM(H4+H5:H6,H14:H15,H17:H18)</f>
+        <v>199.63436915522325</v>
+      </c>
+      <c r="V5" t="s">
+        <v>7</v>
+      </c>
+      <c r="W5" s="6">
+        <f t="shared" si="3"/>
+        <v>-4.9999999999999899E-2</v>
+      </c>
+      <c r="X5" s="6">
+        <f t="shared" si="1"/>
+        <v>2.7094534503137584E-2</v>
+      </c>
+      <c r="Y5" s="6">
+        <f>(Q5-Q17)/Q17</f>
+        <v>7.1097821921179666E-2</v>
+      </c>
+      <c r="Z5" s="6">
+        <f t="shared" si="1"/>
+        <v>-3.032271906213559E-2</v>
+      </c>
+      <c r="AA5" s="6">
+        <f t="shared" si="1"/>
+        <v>5.9084192447603483E-2</v>
+      </c>
+      <c r="AB5" s="6">
+        <f t="shared" si="1"/>
+        <v>5.9718156892095392E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="B6" t="s">
         <v>57</v>
       </c>
       <c r="C6">
-        <v>213.3102142857143</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>107.88675000000001</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>65.599083333333297</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>61.425515860127703</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>174.0375236699584</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>176.39679574659201</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>240.4566559356511</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>323.21809405585572</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>281.14070738208392</v>
       </c>
       <c r="N6" t="s">
         <v>8</v>
       </c>
       <c r="O6">
-        <f>SUM(C20)</f>
-        <v>188.45150000000001</v>
+        <f>SUM(C19)</f>
+        <v>217.0010537154852</v>
       </c>
       <c r="P6">
-        <f t="shared" ref="P6:T6" si="3">SUM(D20)</f>
-        <v>213.11779999999999</v>
+        <f t="shared" ref="P6:T6" si="4">SUM(D19)</f>
+        <v>218.93267982188161</v>
       </c>
       <c r="Q6">
+        <f t="shared" si="4"/>
+        <v>200.18459503119641</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="4"/>
+        <v>218.93267982188161</v>
+      </c>
+      <c r="S6">
+        <f t="shared" si="4"/>
+        <v>218.93267982188161</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="4"/>
+        <v>215.941</v>
+      </c>
+      <c r="V6" t="s">
+        <v>8</v>
+      </c>
+      <c r="W6" s="6">
         <f t="shared" si="3"/>
-        <v>199.12396169457489</v>
-      </c>
-      <c r="R6">
-        <f t="shared" si="3"/>
-        <v>210.798</v>
-      </c>
-      <c r="S6">
-        <f t="shared" si="3"/>
-        <v>195.79920000000001</v>
-      </c>
-      <c r="T6">
-        <f t="shared" si="3"/>
-        <v>158.93700000000001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+        <v>9.391631084557403E-2</v>
+      </c>
+      <c r="X6" s="6">
+        <f t="shared" si="1"/>
+        <v>-1.8960585838748101E-2</v>
+      </c>
+      <c r="Y6" s="6">
+        <f t="shared" si="1"/>
+        <v>-2.9633854757698051E-2</v>
+      </c>
+      <c r="Z6" s="6">
+        <f t="shared" si="1"/>
+        <v>9.053246214281109E-2</v>
+      </c>
+      <c r="AA6" s="6">
+        <f t="shared" si="1"/>
+        <v>3.7969504759447006E-2</v>
+      </c>
+      <c r="AB6" s="6">
+        <f t="shared" si="1"/>
+        <v>9.9970863183288905E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B7" t="s">
         <v>57</v>
       </c>
       <c r="C7">
-        <v>37.349999999999987</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>31.54</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>15.77</v>
+        <v>0</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -25584,57 +25921,84 @@
         <v>9</v>
       </c>
       <c r="O7">
-        <f>SUM(C11,C12)</f>
-        <v>92.380978162960034</v>
+        <f>SUM(C13,C12)</f>
+        <v>109.87920000000004</v>
       </c>
       <c r="P7">
-        <f t="shared" ref="P7:T7" si="4">SUM(D11,D12)</f>
-        <v>67.483020009096066</v>
+        <f t="shared" ref="P7:T7" si="5">SUM(D13,D12)</f>
+        <v>163.83959999999993</v>
       </c>
       <c r="Q7">
-        <f t="shared" si="4"/>
-        <v>116.44010998089969</v>
+        <f t="shared" si="5"/>
+        <v>154.68839999999989</v>
       </c>
       <c r="R7">
-        <f t="shared" si="4"/>
-        <v>116.44010998089969</v>
+        <f t="shared" si="5"/>
+        <v>132.95339999999996</v>
       </c>
       <c r="S7">
-        <f t="shared" si="4"/>
-        <v>115.74206993773153</v>
+        <f t="shared" si="5"/>
+        <v>87.523920000000032</v>
       </c>
       <c r="T7">
-        <f t="shared" si="4"/>
-        <v>139.60781999999995</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+        <f t="shared" si="5"/>
+        <v>161.65115999999998</v>
+      </c>
+      <c r="V7" t="s">
+        <v>9</v>
+      </c>
+      <c r="W7" s="6">
+        <f t="shared" si="3"/>
+        <v>3.8799485385410537E-16</v>
+      </c>
+      <c r="X7" s="6">
+        <f t="shared" si="1"/>
+        <v>-3.4694554223037667E-16</v>
+      </c>
+      <c r="Y7" s="6">
+        <f t="shared" si="1"/>
+        <v>-7.3494093753388118E-16</v>
+      </c>
+      <c r="Z7" s="6">
+        <f t="shared" si="1"/>
+        <v>3.4915631877832434E-3</v>
+      </c>
+      <c r="AA7" s="6">
+        <f t="shared" si="1"/>
+        <v>0.10000000000000041</v>
+      </c>
+      <c r="AB7" s="6">
+        <f t="shared" si="1"/>
+        <v>9.9999999999999811E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B8" t="s">
         <v>57</v>
       </c>
       <c r="C8">
-        <v>2.7142857142857162</v>
+        <v>253.37450000000001</v>
       </c>
       <c r="D8">
-        <v>72.185750000000013</v>
+        <v>90.021999999999991</v>
       </c>
       <c r="E8">
-        <v>74.560750000000041</v>
+        <v>159.79</v>
       </c>
       <c r="F8">
-        <v>74.560750000000056</v>
+        <v>132.37299999999999</v>
       </c>
       <c r="G8">
-        <v>15.659800000000001</v>
+        <v>29.73500000000001</v>
       </c>
       <c r="H8">
-        <v>7.6000000000000014</v>
+        <v>11.856</v>
       </c>
       <c r="I8">
-        <v>1.899999999999999</v>
+        <v>1.9</v>
       </c>
       <c r="J8">
         <v>0.95000000000000007</v>
@@ -25647,30 +26011,57 @@
       </c>
       <c r="O8">
         <f>SUM(C2,C3)</f>
-        <v>7.3906200000000002</v>
+        <v>7.3906199999999993</v>
       </c>
       <c r="P8">
-        <f t="shared" ref="P8:T8" si="5">SUM(D2,D3)</f>
-        <v>11.47752</v>
+        <f t="shared" ref="P8:T8" si="6">SUM(D2,D3)</f>
+        <v>11.47751999999999</v>
       </c>
       <c r="Q8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>16.16976</v>
       </c>
       <c r="R8">
-        <f t="shared" si="5"/>
-        <v>16.422840000000001</v>
+        <f t="shared" si="6"/>
+        <v>16.42283999999999</v>
       </c>
       <c r="S8">
-        <f t="shared" si="5"/>
-        <v>19.505970000000001</v>
+        <f t="shared" si="6"/>
+        <v>19.505970000000008</v>
       </c>
       <c r="T8">
-        <f t="shared" si="5"/>
-        <v>18.19098000000001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+        <f t="shared" si="6"/>
+        <v>18.19098</v>
+      </c>
+      <c r="V8" t="s">
+        <v>11</v>
+      </c>
+      <c r="W8" s="6">
+        <f t="shared" si="3"/>
+        <v>-5.0000000000000017E-2</v>
+      </c>
+      <c r="X8" s="6">
+        <f t="shared" si="1"/>
+        <v>-5.0000000000000863E-2</v>
+      </c>
+      <c r="Y8" s="6">
+        <f t="shared" si="1"/>
+        <v>-5.0000000000000065E-2</v>
+      </c>
+      <c r="Z8" s="6">
+        <f t="shared" si="1"/>
+        <v>-0.11522498060512071</v>
+      </c>
+      <c r="AA8" s="6">
+        <f t="shared" si="1"/>
+        <v>-8.7055602358887541E-2</v>
+      </c>
+      <c r="AB8" s="6">
+        <f t="shared" si="1"/>
+        <v>-4.9999999999999954E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>58</v>
       </c>
@@ -25681,25 +26072,25 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
       <c r="F9">
-        <v>5.9900000000000011</v>
+        <v>0</v>
       </c>
       <c r="G9">
-        <v>5.24125</v>
+        <v>0.29749999999999999</v>
       </c>
       <c r="H9">
-        <v>4.6796875</v>
+        <v>0.27625</v>
       </c>
       <c r="I9">
-        <v>3.7437500000000008</v>
+        <v>0.21249999999999999</v>
       </c>
       <c r="J9">
-        <v>1.871875</v>
+        <v>0.10625</v>
       </c>
       <c r="K9">
         <v>0</v>
@@ -25708,33 +26099,60 @@
         <v>13</v>
       </c>
       <c r="O9">
-        <f>SUM(C23,C24)</f>
-        <v>94.277999999999963</v>
+        <f>SUM(C25,C24)</f>
+        <v>94.278000000000006</v>
       </c>
       <c r="P9">
-        <f t="shared" ref="P9:T9" si="6">SUM(D23,D24)</f>
+        <f t="shared" ref="P9:T9" si="7">SUM(D25,D24)</f>
         <v>151.411</v>
       </c>
       <c r="Q9">
-        <f t="shared" si="6"/>
-        <v>177.88749999999999</v>
+        <f t="shared" si="7"/>
+        <v>177.88750000000005</v>
       </c>
       <c r="R9">
-        <f t="shared" si="6"/>
-        <v>174.0685</v>
+        <f t="shared" si="7"/>
+        <v>174.78847091302663</v>
       </c>
       <c r="S9">
-        <f t="shared" si="6"/>
-        <v>203.83199999999999</v>
+        <f t="shared" si="7"/>
+        <v>234.69599999999997</v>
       </c>
       <c r="T9">
-        <f t="shared" si="6"/>
-        <v>220.02</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+        <f t="shared" si="7"/>
+        <v>234.69599999999997</v>
+      </c>
+      <c r="V9" t="s">
+        <v>13</v>
+      </c>
+      <c r="W9" s="6">
+        <f t="shared" si="3"/>
+        <v>-5.0045946991681099E-2</v>
+      </c>
+      <c r="X9" s="6">
+        <f t="shared" si="1"/>
+        <v>-4.9973772647757819E-2</v>
+      </c>
+      <c r="Y9" s="6">
+        <f t="shared" si="1"/>
+        <v>-4.9983764742574835E-2</v>
+      </c>
+      <c r="Z9" s="6">
+        <f t="shared" si="1"/>
+        <v>-4.6047763451031724E-2</v>
+      </c>
+      <c r="AA9" s="6">
+        <f t="shared" si="1"/>
+        <v>3.837495752633352E-2</v>
+      </c>
+      <c r="AB9" s="6">
+        <f t="shared" si="1"/>
+        <v>4.9998120976877163E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="B10" t="s">
         <v>57</v>
@@ -25749,221 +26167,293 @@
         <v>0</v>
       </c>
       <c r="F10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J10">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="K10">
-        <v>5</v>
+        <v>0.52999999999999992</v>
       </c>
       <c r="N10" t="s">
         <v>66</v>
       </c>
       <c r="O10">
-        <f>SUM(C22,C21)</f>
+        <f>SUM(C22:C23,C20:C21)</f>
         <v>1.7613000000000001</v>
       </c>
       <c r="P10">
-        <f t="shared" ref="P10:T10" si="7">SUM(D22,D21)</f>
-        <v>24.576120000000003</v>
+        <f t="shared" ref="P10:T10" si="8">SUM(D22:D23,D20:D21)</f>
+        <v>24.576119999999985</v>
       </c>
       <c r="Q10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>47.397779999999997</v>
       </c>
       <c r="R10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>51.652259999999991</v>
       </c>
       <c r="S10">
-        <f t="shared" si="7"/>
-        <v>122.17265999999989</v>
+        <f t="shared" si="8"/>
+        <v>122.17266000000001</v>
       </c>
       <c r="T10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>199.34496000000007</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="V10" t="s">
+        <v>66</v>
+      </c>
+      <c r="W10" s="6">
+        <f t="shared" si="3"/>
+        <v>-4.9999999999999885E-2</v>
+      </c>
+      <c r="X10" s="6">
+        <f t="shared" si="1"/>
+        <v>-5.0000000000000509E-2</v>
+      </c>
+      <c r="Y10" s="6">
+        <f t="shared" si="1"/>
+        <v>-3.6935849608660622E-2</v>
+      </c>
+      <c r="Z10" s="6">
+        <f t="shared" si="1"/>
+        <v>0.12585138104205884</v>
+      </c>
+      <c r="AA10" s="6">
+        <f t="shared" si="1"/>
+        <v>-4.9999999999999954E-2</v>
+      </c>
+      <c r="AB10" s="6">
+        <f t="shared" si="1"/>
+        <v>-5.006518904823945E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B11" t="s">
         <v>57</v>
       </c>
       <c r="C11">
-        <v>92.380978162960034</v>
+        <v>0.1</v>
       </c>
       <c r="D11">
-        <v>67.483020009096066</v>
+        <v>0.1</v>
       </c>
       <c r="E11">
-        <v>105.03380906816631</v>
+        <v>0</v>
       </c>
       <c r="F11">
-        <v>105.03380906816631</v>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>105.03380906816631</v>
+        <v>0.1</v>
       </c>
       <c r="H11">
-        <v>129.90390695652169</v>
+        <v>0.1</v>
       </c>
       <c r="I11">
-        <v>266.3724490133813</v>
+        <v>1</v>
       </c>
       <c r="J11">
-        <v>541.13352327690222</v>
+        <v>3</v>
       </c>
       <c r="K11">
-        <v>793.4158222158004</v>
+        <v>5</v>
       </c>
       <c r="N11" t="s">
         <v>68</v>
       </c>
       <c r="O11">
-        <f>SUM(C10,C9)</f>
-        <v>0</v>
+        <f>SUM(C10:C11,C9)</f>
+        <v>0.1</v>
       </c>
       <c r="P11">
-        <f t="shared" ref="P11:T11" si="8">SUM(D10,D9)</f>
-        <v>0</v>
+        <f t="shared" ref="P11:T11" si="9">SUM(D10:D11,D9)</f>
+        <v>0.7</v>
       </c>
       <c r="Q11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R11">
-        <f t="shared" si="8"/>
-        <v>6.9900000000000011</v>
+        <f t="shared" si="9"/>
+        <v>0</v>
       </c>
       <c r="S11">
-        <f t="shared" si="8"/>
-        <v>6.24125</v>
+        <f t="shared" si="9"/>
+        <v>0.39749999999999996</v>
       </c>
       <c r="T11">
-        <f t="shared" si="8"/>
-        <v>5.6796875</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+        <f t="shared" si="9"/>
+        <v>0.37624999999999997</v>
+      </c>
+      <c r="V11" t="s">
+        <v>68</v>
+      </c>
+      <c r="W11" s="6">
+        <f t="shared" si="3"/>
+        <v>-0.9142661179698216</v>
+      </c>
+      <c r="X11" s="6">
+        <f t="shared" si="1"/>
+        <v>0.22292103424178883</v>
+      </c>
+      <c r="Y11" s="6" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z11" s="6">
+        <f t="shared" si="1"/>
+        <v>-1</v>
+      </c>
+      <c r="AA11" s="6">
+        <f t="shared" si="1"/>
+        <v>-0.60845153664302598</v>
+      </c>
+      <c r="AB11" s="6">
+        <f t="shared" si="1"/>
+        <v>-0.57166438979963574</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>60</v>
+      </c>
+      <c r="B12" t="s">
+        <v>57</v>
+      </c>
+      <c r="C12">
+        <v>104.21285483422299</v>
+      </c>
+      <c r="D12">
+        <v>134.91126666666659</v>
+      </c>
+      <c r="E12">
+        <v>132.79641078009391</v>
+      </c>
+      <c r="F12">
+        <v>117.045387491673</v>
+      </c>
+      <c r="G12">
+        <v>64.263559361638556</v>
+      </c>
+      <c r="H12">
+        <v>132.75049333333331</v>
+      </c>
+      <c r="I12">
+        <v>200</v>
+      </c>
+      <c r="J12">
+        <v>200</v>
+      </c>
+      <c r="K12">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>33</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B13" t="s">
         <v>56</v>
       </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <v>11.406300912733389</v>
-      </c>
-      <c r="F12">
-        <v>11.406300912733389</v>
-      </c>
-      <c r="G12">
-        <v>10.708260869565221</v>
-      </c>
-      <c r="H12">
-        <v>9.703913043478261</v>
-      </c>
-      <c r="I12">
-        <v>8.0299999999999994</v>
-      </c>
-      <c r="J12">
-        <v>8.0299999999999994</v>
-      </c>
-      <c r="K12">
-        <v>8.0300000000000011</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="C13">
+        <v>5.6663451657770407</v>
+      </c>
+      <c r="D13">
+        <v>28.928333333333331</v>
+      </c>
+      <c r="E13">
+        <v>21.89198921990598</v>
+      </c>
+      <c r="F13">
+        <v>15.908012508326969</v>
+      </c>
+      <c r="G13">
+        <v>23.26036063836148</v>
+      </c>
+      <c r="H13">
+        <v>28.900666666666659</v>
+      </c>
+      <c r="I13">
+        <v>29.06666666666667</v>
+      </c>
+      <c r="J13">
+        <v>29.34333333333333</v>
+      </c>
+      <c r="K13">
+        <v>29.61999999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>41</v>
-      </c>
-      <c r="B13" t="s">
-        <v>57</v>
-      </c>
-      <c r="C13">
-        <v>286.50258000000002</v>
-      </c>
-      <c r="D13">
-        <v>287.24041999999997</v>
-      </c>
-      <c r="E13">
-        <v>160.93961820212871</v>
-      </c>
-      <c r="F13">
-        <v>182.40014581159701</v>
-      </c>
-      <c r="G13">
-        <v>256.08</v>
-      </c>
-      <c r="H13">
-        <v>71.375225078226237</v>
-      </c>
-      <c r="I13">
-        <v>47.050696900674247</v>
-      </c>
-      <c r="J13">
-        <v>27.2</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>42</v>
       </c>
       <c r="B14" t="s">
         <v>57</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>218.50257999999999</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>250.01994274631099</v>
       </c>
       <c r="E14">
-        <v>18.60354179787134</v>
+        <v>176.80389359155171</v>
       </c>
       <c r="F14">
-        <v>15.97353418840324</v>
+        <v>120.9153989845439</v>
       </c>
       <c r="G14">
-        <v>37.954499999999967</v>
+        <v>129.56650465728569</v>
       </c>
       <c r="H14">
-        <v>107.5899549217738</v>
+        <v>0</v>
       </c>
       <c r="I14">
-        <v>95.449303099325718</v>
+        <v>11.906861628833861</v>
       </c>
       <c r="J14">
-        <v>67.800000000000011</v>
+        <v>27.2</v>
       </c>
       <c r="K14">
-        <v>24.161136505546111</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>2007</v>
+      </c>
+      <c r="P14">
+        <v>2010</v>
+      </c>
+      <c r="Q14">
+        <v>2014</v>
+      </c>
+      <c r="R14">
+        <v>2018</v>
+      </c>
+      <c r="S14">
+        <v>2022</v>
+      </c>
+      <c r="T14">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="B15" t="s">
         <v>57</v>
@@ -25993,10 +26483,31 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>23.3388634944539</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="N15" t="s">
+        <v>4</v>
+      </c>
+      <c r="O15">
+        <v>266.70600000000002</v>
+      </c>
+      <c r="P15">
+        <v>94.762799999999999</v>
+      </c>
+      <c r="Q15">
+        <v>163.06199999999998</v>
+      </c>
+      <c r="R15">
+        <v>139.3776</v>
+      </c>
+      <c r="S15">
+        <v>31.305599999999998</v>
+      </c>
+      <c r="T15">
+        <v>12.477599999999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>44</v>
       </c>
@@ -26004,45 +26515,66 @@
         <v>57</v>
       </c>
       <c r="C16">
-        <v>63.297359999999998</v>
+        <v>63.297359999999983</v>
       </c>
       <c r="D16">
-        <v>56.642040000000001</v>
+        <v>56.642039999999987</v>
       </c>
       <c r="E16">
-        <v>58.964219999999997</v>
+        <v>48.293819999999997</v>
       </c>
       <c r="F16">
-        <v>49.583159999999992</v>
+        <v>49.583160000000007</v>
       </c>
       <c r="G16">
         <v>36.217799999999997</v>
       </c>
       <c r="H16">
-        <v>31.200659999999989</v>
+        <v>30.513999999999999</v>
       </c>
       <c r="I16">
-        <v>23.75</v>
+        <v>9.5</v>
       </c>
       <c r="J16">
-        <v>12.824999999999999</v>
+        <v>4.75</v>
       </c>
       <c r="K16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="N16" t="s">
+        <v>6</v>
+      </c>
+      <c r="O16">
+        <v>66.628799999999998</v>
+      </c>
+      <c r="P16">
+        <v>59.623199999999997</v>
+      </c>
+      <c r="Q16">
+        <v>50.835599999999999</v>
+      </c>
+      <c r="R16">
+        <v>52.192799999999998</v>
+      </c>
+      <c r="S16">
+        <v>38.124000000000002</v>
+      </c>
+      <c r="T16">
+        <v>32.842799999999997</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B17" t="s">
         <v>57</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>100.29</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>94.835454545454553</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -26063,21 +26595,42 @@
         <v>0</v>
       </c>
       <c r="K17">
-        <v>1.9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="N17" t="s">
+        <v>7</v>
+      </c>
+      <c r="O17">
+        <v>341.27639999999997</v>
+      </c>
+      <c r="P17">
+        <v>341.46359999999999</v>
+      </c>
+      <c r="Q17">
+        <v>170.18279999999999</v>
+      </c>
+      <c r="R17">
+        <v>208.81440000000001</v>
+      </c>
+      <c r="S17">
+        <v>309.51</v>
+      </c>
+      <c r="T17">
+        <v>188.3844</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B18" t="s">
         <v>57</v>
       </c>
       <c r="C18">
-        <v>36.29</v>
+        <v>5.42</v>
       </c>
       <c r="D18">
-        <v>36.29</v>
+        <v>5.86</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -26100,80 +26653,143 @@
       <c r="K18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="N18" t="s">
+        <v>8</v>
+      </c>
+      <c r="O18">
+        <v>198.3708</v>
+      </c>
+      <c r="P18">
+        <v>223.16399999999999</v>
+      </c>
+      <c r="Q18">
+        <v>206.298</v>
+      </c>
+      <c r="R18">
+        <v>200.7576</v>
+      </c>
+      <c r="S18">
+        <v>210.92400000000001</v>
+      </c>
+      <c r="T18">
+        <v>196.3152</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="B19" t="s">
         <v>57</v>
       </c>
       <c r="C19">
-        <v>1.42</v>
+        <v>217.0010537154852</v>
       </c>
       <c r="D19">
-        <v>0.86</v>
+        <v>218.93267982188161</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>200.18459503119641</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>218.93267982188161</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>218.93267982188161</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>215.941</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>136.5</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>68.25</v>
       </c>
       <c r="K19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="N19" t="s">
+        <v>9</v>
+      </c>
+      <c r="O19">
+        <v>109.8792</v>
+      </c>
+      <c r="P19">
+        <v>163.83959999999999</v>
+      </c>
+      <c r="Q19">
+        <v>154.6884</v>
+      </c>
+      <c r="R19">
+        <v>132.49080000000001</v>
+      </c>
+      <c r="S19">
+        <v>79.5672</v>
+      </c>
+      <c r="T19">
+        <v>146.9556</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="B20" t="s">
         <v>57</v>
       </c>
       <c r="C20">
-        <v>188.45150000000001</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>213.11779999999999</v>
+        <v>0</v>
       </c>
       <c r="E20">
-        <v>199.12396169457489</v>
+        <v>0</v>
       </c>
       <c r="F20">
-        <v>210.798</v>
+        <v>0</v>
       </c>
       <c r="G20">
-        <v>195.79920000000001</v>
+        <v>0</v>
       </c>
       <c r="H20">
-        <v>158.93700000000001</v>
+        <v>49.481560908852892</v>
       </c>
       <c r="I20">
-        <v>97.499999999999986</v>
+        <v>49.628895730560011</v>
       </c>
       <c r="J20">
-        <v>48.75</v>
+        <v>48.19925229350401</v>
       </c>
       <c r="K20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+        <v>43.910321982336008</v>
+      </c>
+      <c r="N20" t="s">
+        <v>11</v>
+      </c>
+      <c r="O20">
+        <v>7.7795999999999994</v>
+      </c>
+      <c r="P20">
+        <v>12.0816</v>
+      </c>
+      <c r="Q20">
+        <v>17.020800000000001</v>
+      </c>
+      <c r="R20">
+        <v>18.561599999999999</v>
+      </c>
+      <c r="S20">
+        <v>21.366</v>
+      </c>
+      <c r="T20">
+        <v>19.148399999999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="B21" t="s">
         <v>57</v>
@@ -26182,417 +26798,286 @@
         <v>0</v>
       </c>
       <c r="D21">
-        <v>15.80220695652174</v>
+        <v>0</v>
       </c>
       <c r="E21">
-        <v>40.378649565217387</v>
+        <v>0</v>
       </c>
       <c r="F21">
-        <v>46.387912173913037</v>
+        <v>0</v>
       </c>
       <c r="G21">
-        <v>118.6630947826086</v>
+        <v>0</v>
       </c>
       <c r="H21">
-        <v>197.1514817391305</v>
+        <v>15.112139945502481</v>
       </c>
       <c r="I21">
-        <v>237.5</v>
+        <v>13.606246993833469</v>
       </c>
       <c r="J21">
-        <v>270.74999999999989</v>
+        <v>15.736658564505611</v>
       </c>
       <c r="K21">
-        <v>303.99999999999989</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+        <v>14.97894754286593</v>
+      </c>
+      <c r="N21" t="s">
+        <v>13</v>
+      </c>
+      <c r="O21">
+        <v>99.244799999999998</v>
+      </c>
+      <c r="P21">
+        <v>159.37559999999999</v>
+      </c>
+      <c r="Q21">
+        <v>187.24680000000001</v>
+      </c>
+      <c r="R21">
+        <v>183.22559999999999</v>
+      </c>
+      <c r="S21">
+        <v>226.0224</v>
+      </c>
+      <c r="T21">
+        <v>223.5204</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>62</v>
+      </c>
+      <c r="B22" t="s">
+        <v>57</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>4.4761199999999937</v>
+      </c>
+      <c r="E22">
+        <v>27.327780000000001</v>
+      </c>
+      <c r="F22">
+        <v>31.57226</v>
+      </c>
+      <c r="G22">
+        <v>102.13266</v>
+      </c>
+      <c r="H22">
+        <v>114.7312591456447</v>
+      </c>
+      <c r="I22">
+        <v>174.2648572756066</v>
+      </c>
+      <c r="J22">
+        <v>201.4853547067687</v>
+      </c>
+      <c r="K22">
+        <v>226.1107304747982</v>
+      </c>
+      <c r="N22" t="s">
+        <v>66</v>
+      </c>
+      <c r="O22">
+        <f>SUM(P25+P26)</f>
+        <v>1.8539999999999999</v>
+      </c>
+      <c r="P22">
+        <f>SUM(Q25+Q26)</f>
+        <v>25.869599999999998</v>
+      </c>
+      <c r="Q22">
+        <f>SUM(R25+R26)</f>
+        <v>49.215599999999995</v>
+      </c>
+      <c r="R22">
+        <f>SUM(S25+S26)</f>
+        <v>45.878399999999999</v>
+      </c>
+      <c r="S22">
+        <f>SUM(T25+T26)</f>
+        <v>128.6028</v>
+      </c>
+      <c r="T22">
+        <f>SUM(U25+U26)</f>
+        <v>209.85119999999998</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
         <v>63</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B23" t="s">
         <v>56</v>
       </c>
-      <c r="C22">
+      <c r="C23">
         <v>1.7613000000000001</v>
       </c>
-      <c r="D22">
-        <v>8.7739130434782631</v>
-      </c>
-      <c r="E22">
-        <v>7.0191304347826113</v>
-      </c>
-      <c r="F22">
-        <v>5.2643478260869561</v>
-      </c>
-      <c r="G22">
-        <v>3.509565217391303</v>
-      </c>
-      <c r="H22">
-        <v>2.193478260869564</v>
-      </c>
-      <c r="I22">
-        <v>0</v>
-      </c>
-      <c r="J22">
-        <v>0</v>
-      </c>
-      <c r="K22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+      <c r="D23">
+        <v>20.099999999999991</v>
+      </c>
+      <c r="E23">
+        <v>20.07</v>
+      </c>
+      <c r="F23">
+        <v>20.079999999999991</v>
+      </c>
+      <c r="G23">
+        <v>20.04</v>
+      </c>
+      <c r="H23">
+        <v>20.019999999999989</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="N23" t="s">
+        <v>68</v>
+      </c>
+      <c r="O23">
+        <v>1.1663999999999999</v>
+      </c>
+      <c r="P23">
+        <v>0.57240000000000002</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23">
+        <v>0.33839999999999998</v>
+      </c>
+      <c r="S23">
+        <v>1.0151999999999999</v>
+      </c>
+      <c r="T23">
+        <v>0.87839999999999996</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
         <v>64</v>
-      </c>
-      <c r="B23" t="s">
-        <v>57</v>
-      </c>
-      <c r="C23">
-        <v>94.277999999999963</v>
-      </c>
-      <c r="D23">
-        <v>0</v>
-      </c>
-      <c r="E23">
-        <v>3.8189999999999951</v>
-      </c>
-      <c r="F23">
-        <v>0</v>
-      </c>
-      <c r="G23">
-        <v>0</v>
-      </c>
-      <c r="H23">
-        <v>0</v>
-      </c>
-      <c r="I23">
-        <v>0</v>
-      </c>
-      <c r="J23">
-        <v>0</v>
-      </c>
-      <c r="K23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>65</v>
       </c>
       <c r="B24" t="s">
         <v>57</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>75.369028573276282</v>
       </c>
       <c r="D24">
-        <v>151.411</v>
+        <v>79.673704630580659</v>
       </c>
       <c r="E24">
-        <v>174.0685</v>
+        <v>79.673704630580673</v>
       </c>
       <c r="F24">
-        <v>174.0685</v>
+        <v>78.814124698542045</v>
       </c>
       <c r="G24">
-        <v>203.83199999999999</v>
+        <v>79.673704630580659</v>
       </c>
       <c r="H24">
-        <v>220.02</v>
+        <v>79.673704630580659</v>
       </c>
       <c r="I24">
-        <v>273.00000000000011</v>
+        <v>12</v>
       </c>
       <c r="J24">
-        <v>289.39679509382029</v>
+        <v>12</v>
       </c>
       <c r="K24">
-        <v>336.00000000000011</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B26">
-        <v>2007</v>
-      </c>
-      <c r="C26">
-        <v>2010</v>
-      </c>
-      <c r="D26">
-        <v>2014</v>
-      </c>
-      <c r="E26">
-        <v>2018</v>
-      </c>
-      <c r="F26">
-        <v>2022</v>
-      </c>
-      <c r="G26">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>4</v>
-      </c>
-      <c r="B27">
-        <v>266.70600000000002</v>
-      </c>
-      <c r="C27">
-        <v>94.762799999999999</v>
-      </c>
-      <c r="D27">
-        <v>163.06199999999998</v>
-      </c>
-      <c r="E27">
-        <v>139.3776</v>
-      </c>
-      <c r="F27">
-        <v>31.305599999999998</v>
-      </c>
-      <c r="G27">
-        <v>12.477599999999999</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>6</v>
-      </c>
-      <c r="B28">
-        <v>66.628799999999998</v>
-      </c>
-      <c r="C28">
-        <v>59.623199999999997</v>
-      </c>
-      <c r="D28">
-        <v>50.835599999999999</v>
-      </c>
-      <c r="E28">
-        <v>52.192799999999998</v>
-      </c>
-      <c r="F28">
-        <v>38.124000000000002</v>
-      </c>
-      <c r="G28">
-        <v>32.842799999999997</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>7</v>
-      </c>
-      <c r="B29">
-        <v>341.27639999999997</v>
-      </c>
-      <c r="C29">
-        <v>341.46359999999999</v>
-      </c>
-      <c r="D29">
-        <v>170.18279999999999</v>
-      </c>
-      <c r="E29">
-        <v>208.81440000000001</v>
-      </c>
-      <c r="F29">
-        <v>309.51</v>
-      </c>
-      <c r="G29">
-        <v>188.3844</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>8</v>
-      </c>
-      <c r="B30">
-        <v>198.3708</v>
-      </c>
-      <c r="C30">
-        <v>223.16399999999999</v>
-      </c>
-      <c r="D30">
-        <v>206.298</v>
-      </c>
-      <c r="E30">
-        <v>200.7576</v>
-      </c>
-      <c r="F30">
-        <v>210.92400000000001</v>
-      </c>
-      <c r="G30">
-        <v>196.3152</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>9</v>
-      </c>
-      <c r="B31">
-        <v>109.8792</v>
-      </c>
-      <c r="C31">
-        <v>163.83959999999999</v>
-      </c>
-      <c r="D31">
-        <v>154.6884</v>
-      </c>
-      <c r="E31">
-        <v>132.49080000000001</v>
-      </c>
-      <c r="F31">
-        <v>79.5672</v>
-      </c>
-      <c r="G31">
-        <v>146.9556</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>11</v>
-      </c>
-      <c r="B32">
-        <v>7.7795999999999994</v>
-      </c>
-      <c r="C32">
-        <v>12.0816</v>
-      </c>
-      <c r="D32">
-        <v>17.020800000000001</v>
-      </c>
-      <c r="E32">
-        <v>18.561599999999999</v>
-      </c>
-      <c r="F32">
-        <v>21.366</v>
-      </c>
-      <c r="G32">
-        <v>19.148399999999999</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>13</v>
-      </c>
-      <c r="B33">
-        <v>99.244799999999998</v>
-      </c>
-      <c r="C33">
-        <v>159.37559999999999</v>
-      </c>
-      <c r="D33">
-        <v>187.24680000000001</v>
-      </c>
-      <c r="E33">
-        <v>183.22559999999999</v>
-      </c>
-      <c r="F33">
-        <v>226.0224</v>
-      </c>
-      <c r="G33">
-        <v>223.5204</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>66</v>
-      </c>
-      <c r="B34">
-        <f>SUM(C38+C39)</f>
-        <v>1.8539999999999999</v>
-      </c>
-      <c r="C34">
-        <f>SUM(D38+D39)</f>
-        <v>25.869599999999998</v>
-      </c>
-      <c r="D34">
-        <f>SUM(E38+E39)</f>
-        <v>49.215599999999995</v>
-      </c>
-      <c r="E34">
-        <f>SUM(F38+F39)</f>
-        <v>45.878399999999999</v>
-      </c>
-      <c r="F34">
-        <f>SUM(G38+G39)</f>
-        <v>128.6028</v>
-      </c>
-      <c r="G34">
-        <f>SUM(H38+H39)</f>
-        <v>209.85119999999998</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>68</v>
-      </c>
-      <c r="B35">
-        <v>1.1663999999999999</v>
-      </c>
-      <c r="C35">
-        <v>0.57240000000000002</v>
-      </c>
-      <c r="D35">
-        <v>0</v>
-      </c>
-      <c r="E35">
-        <v>0.33839999999999998</v>
-      </c>
-      <c r="F35">
-        <v>1.0151999999999999</v>
-      </c>
-      <c r="G35">
-        <v>0.87839999999999996</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>65</v>
+      </c>
+      <c r="B25" t="s">
+        <v>57</v>
+      </c>
+      <c r="C25">
+        <v>18.908971426723721</v>
+      </c>
+      <c r="D25">
+        <v>71.737295369419343</v>
+      </c>
+      <c r="E25">
+        <v>98.213795369419358</v>
+      </c>
+      <c r="F25">
+        <v>95.974346214484584</v>
+      </c>
+      <c r="G25">
+        <v>155.02229536941931</v>
+      </c>
+      <c r="H25">
+        <v>155.02229536941931</v>
+      </c>
+      <c r="I25">
+        <v>319.28615384615392</v>
+      </c>
+      <c r="J25">
+        <v>461.64307692307727</v>
+      </c>
+      <c r="K25">
+        <v>603.99999999999989</v>
+      </c>
+      <c r="N25" t="s">
         <v>14</v>
       </c>
-      <c r="B38">
+      <c r="O25">
         <v>0.44639999999999996</v>
       </c>
-      <c r="C38">
+      <c r="P25">
         <v>1.8251999999999999</v>
       </c>
-      <c r="D38">
+      <c r="Q25">
         <v>23.13</v>
       </c>
-      <c r="E38">
+      <c r="R25">
         <v>29.581199999999999</v>
       </c>
-      <c r="F38">
+      <c r="S25">
         <v>28.357199999999999</v>
       </c>
-      <c r="G38">
+      <c r="T25">
         <v>112.2732</v>
       </c>
-      <c r="H38">
+      <c r="U25">
         <v>193.50719999999998</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="N26" t="s">
         <v>15</v>
       </c>
-      <c r="B39">
-        <v>0</v>
-      </c>
-      <c r="C39">
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26">
         <v>2.8799999999999999E-2</v>
       </c>
-      <c r="D39">
+      <c r="Q26">
         <v>2.7395999999999998</v>
       </c>
-      <c r="E39">
+      <c r="R26">
         <v>19.634399999999999</v>
       </c>
-      <c r="F39">
+      <c r="S26">
         <v>17.5212</v>
       </c>
-      <c r="G39">
+      <c r="T26">
         <v>16.329599999999999</v>
       </c>
-      <c r="H39">
+      <c r="U26">
         <v>16.344000000000001</v>
       </c>
     </row>

--- a/ELC_data_Spain.xlsx
+++ b/ELC_data_Spain.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Documents\TEMOA\PROJECT\Models-and-scenarios\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Riccardo\PoliTo\anno4\Models and scenarios\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{393074A5-B2D7-41DE-BD95-587F9BD4F59F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="6" xr2:uid="{8BBF5E45-81C8-439F-BD27-48A9AF2DFBEB}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="1" activeTab="6" xr2:uid="{8BBF5E45-81C8-439F-BD27-48A9AF2DFBEB}"/>
   </bookViews>
   <sheets>
     <sheet name="ELC_Generation" sheetId="1" r:id="rId1"/>
@@ -813,10 +813,10 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="43" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="43" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="20% - Colore 1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -14263,13 +14263,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29F0DB51-B7D9-4ADC-AB31-B7E4C1F96502}">
   <dimension ref="A1:AD301"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34.109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="34.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -14283,7 +14283,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -14360,7 +14360,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -14453,7 +14453,7 @@
         <v>12.477599999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -14546,7 +14546,7 @@
         <v>32.842799999999997</v>
       </c>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -14639,7 +14639,7 @@
         <v>188.3844</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -14732,7 +14732,7 @@
         <v>196.3152</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -14825,7 +14825,7 @@
         <v>146.9556</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -14918,7 +14918,7 @@
         <v>2.8799999999999999E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -15011,7 +15011,7 @@
         <v>19.148399999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -15104,7 +15104,7 @@
         <v>6.0695999999999994</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -15197,7 +15197,7 @@
         <v>223.5204</v>
       </c>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -15290,7 +15290,7 @@
         <v>193.50719999999998</v>
       </c>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>4</v>
       </c>
@@ -15383,7 +15383,7 @@
         <v>16.344000000000001</v>
       </c>
     </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -15476,7 +15476,7 @@
         <v>0.87839999999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -15566,7 +15566,7 @@
         <v>1036.4724000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>4</v>
       </c>
@@ -15659,7 +15659,7 @@
         <v>287.90900000000005</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>4</v>
       </c>
@@ -15673,7 +15673,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -15687,7 +15687,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>4</v>
       </c>
@@ -15701,7 +15701,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>4</v>
       </c>
@@ -15715,7 +15715,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>4</v>
       </c>
@@ -15729,7 +15729,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>4</v>
       </c>
@@ -15743,7 +15743,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>4</v>
       </c>
@@ -15757,7 +15757,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>4</v>
       </c>
@@ -15771,7 +15771,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>4</v>
       </c>
@@ -15785,7 +15785,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>4</v>
       </c>
@@ -15799,7 +15799,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>6</v>
       </c>
@@ -15813,7 +15813,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>6</v>
       </c>
@@ -15827,7 +15827,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>6</v>
       </c>
@@ -15841,7 +15841,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>6</v>
       </c>
@@ -15855,7 +15855,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>6</v>
       </c>
@@ -15869,7 +15869,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>6</v>
       </c>
@@ -15883,7 +15883,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>6</v>
       </c>
@@ -15897,7 +15897,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>6</v>
       </c>
@@ -15911,7 +15911,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>6</v>
       </c>
@@ -15925,7 +15925,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>6</v>
       </c>
@@ -15939,7 +15939,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>6</v>
       </c>
@@ -15953,7 +15953,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>6</v>
       </c>
@@ -15967,7 +15967,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>6</v>
       </c>
@@ -15981,7 +15981,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>6</v>
       </c>
@@ -15995,7 +15995,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>6</v>
       </c>
@@ -16009,7 +16009,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>6</v>
       </c>
@@ -16023,7 +16023,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>6</v>
       </c>
@@ -16037,7 +16037,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>6</v>
       </c>
@@ -16051,7 +16051,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>6</v>
       </c>
@@ -16065,7 +16065,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>6</v>
       </c>
@@ -16079,7 +16079,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>6</v>
       </c>
@@ -16093,7 +16093,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>6</v>
       </c>
@@ -16107,7 +16107,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>6</v>
       </c>
@@ -16121,7 +16121,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>6</v>
       </c>
@@ -16135,7 +16135,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>6</v>
       </c>
@@ -16149,7 +16149,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>7</v>
       </c>
@@ -16163,7 +16163,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>7</v>
       </c>
@@ -16177,7 +16177,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>7</v>
       </c>
@@ -16191,7 +16191,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>7</v>
       </c>
@@ -16205,7 +16205,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>7</v>
       </c>
@@ -16219,7 +16219,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>7</v>
       </c>
@@ -16233,7 +16233,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>7</v>
       </c>
@@ -16247,7 +16247,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>7</v>
       </c>
@@ -16261,7 +16261,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>7</v>
       </c>
@@ -16275,7 +16275,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>7</v>
       </c>
@@ -16289,7 +16289,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>7</v>
       </c>
@@ -16303,7 +16303,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>7</v>
       </c>
@@ -16317,7 +16317,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>7</v>
       </c>
@@ -16331,7 +16331,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>7</v>
       </c>
@@ -16345,7 +16345,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>7</v>
       </c>
@@ -16359,7 +16359,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>7</v>
       </c>
@@ -16373,7 +16373,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>7</v>
       </c>
@@ -16387,7 +16387,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>7</v>
       </c>
@@ -16401,7 +16401,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>7</v>
       </c>
@@ -16415,7 +16415,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>7</v>
       </c>
@@ -16429,7 +16429,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>7</v>
       </c>
@@ -16443,7 +16443,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>7</v>
       </c>
@@ -16457,7 +16457,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>7</v>
       </c>
@@ -16471,7 +16471,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>7</v>
       </c>
@@ -16485,7 +16485,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>7</v>
       </c>
@@ -16499,7 +16499,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>8</v>
       </c>
@@ -16513,7 +16513,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>8</v>
       </c>
@@ -16527,7 +16527,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>8</v>
       </c>
@@ -16541,7 +16541,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>8</v>
       </c>
@@ -16555,7 +16555,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>8</v>
       </c>
@@ -16569,7 +16569,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>8</v>
       </c>
@@ -16583,7 +16583,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>8</v>
       </c>
@@ -16597,7 +16597,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>8</v>
       </c>
@@ -16611,7 +16611,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>8</v>
       </c>
@@ -16625,7 +16625,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>8</v>
       </c>
@@ -16639,7 +16639,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>8</v>
       </c>
@@ -16653,7 +16653,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>8</v>
       </c>
@@ -16667,7 +16667,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>8</v>
       </c>
@@ -16681,7 +16681,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>8</v>
       </c>
@@ -16695,7 +16695,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>8</v>
       </c>
@@ -16709,7 +16709,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>8</v>
       </c>
@@ -16723,7 +16723,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>8</v>
       </c>
@@ -16737,7 +16737,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>8</v>
       </c>
@@ -16751,7 +16751,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>8</v>
       </c>
@@ -16765,7 +16765,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>8</v>
       </c>
@@ -16779,7 +16779,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>8</v>
       </c>
@@ -16793,7 +16793,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>8</v>
       </c>
@@ -16807,7 +16807,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>8</v>
       </c>
@@ -16821,7 +16821,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>8</v>
       </c>
@@ -16835,7 +16835,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>8</v>
       </c>
@@ -16849,7 +16849,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>9</v>
       </c>
@@ -16863,7 +16863,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>9</v>
       </c>
@@ -16877,7 +16877,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>9</v>
       </c>
@@ -16891,7 +16891,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>9</v>
       </c>
@@ -16905,7 +16905,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>9</v>
       </c>
@@ -16919,7 +16919,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>9</v>
       </c>
@@ -16933,7 +16933,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>9</v>
       </c>
@@ -16947,7 +16947,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>9</v>
       </c>
@@ -16961,7 +16961,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>9</v>
       </c>
@@ -16975,7 +16975,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>9</v>
       </c>
@@ -16989,7 +16989,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>9</v>
       </c>
@@ -17003,7 +17003,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>9</v>
       </c>
@@ -17017,7 +17017,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>9</v>
       </c>
@@ -17031,7 +17031,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>9</v>
       </c>
@@ -17045,7 +17045,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>9</v>
       </c>
@@ -17059,7 +17059,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>9</v>
       </c>
@@ -17073,7 +17073,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>9</v>
       </c>
@@ -17087,7 +17087,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>9</v>
       </c>
@@ -17101,7 +17101,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>9</v>
       </c>
@@ -17115,7 +17115,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>9</v>
       </c>
@@ -17129,7 +17129,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>9</v>
       </c>
@@ -17143,7 +17143,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>9</v>
       </c>
@@ -17157,7 +17157,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>9</v>
       </c>
@@ -17171,7 +17171,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>9</v>
       </c>
@@ -17185,7 +17185,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>9</v>
       </c>
@@ -17199,7 +17199,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>10</v>
       </c>
@@ -17210,7 +17210,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>10</v>
       </c>
@@ -17221,7 +17221,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>10</v>
       </c>
@@ -17232,7 +17232,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>10</v>
       </c>
@@ -17243,7 +17243,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>10</v>
       </c>
@@ -17254,7 +17254,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>10</v>
       </c>
@@ -17265,7 +17265,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>10</v>
       </c>
@@ -17276,7 +17276,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>10</v>
       </c>
@@ -17287,7 +17287,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>10</v>
       </c>
@@ -17298,7 +17298,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>10</v>
       </c>
@@ -17309,7 +17309,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>10</v>
       </c>
@@ -17320,7 +17320,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>10</v>
       </c>
@@ -17331,7 +17331,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>10</v>
       </c>
@@ -17342,7 +17342,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>10</v>
       </c>
@@ -17353,7 +17353,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>10</v>
       </c>
@@ -17364,7 +17364,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>10</v>
       </c>
@@ -17375,7 +17375,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>10</v>
       </c>
@@ -17386,7 +17386,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>10</v>
       </c>
@@ -17397,7 +17397,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>10</v>
       </c>
@@ -17408,7 +17408,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>10</v>
       </c>
@@ -17422,7 +17422,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>10</v>
       </c>
@@ -17436,7 +17436,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>10</v>
       </c>
@@ -17450,7 +17450,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>10</v>
       </c>
@@ -17464,7 +17464,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>10</v>
       </c>
@@ -17478,7 +17478,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>10</v>
       </c>
@@ -17492,7 +17492,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>11</v>
       </c>
@@ -17506,7 +17506,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>11</v>
       </c>
@@ -17520,7 +17520,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>11</v>
       </c>
@@ -17534,7 +17534,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>11</v>
       </c>
@@ -17548,7 +17548,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>11</v>
       </c>
@@ -17562,7 +17562,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>11</v>
       </c>
@@ -17576,7 +17576,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>11</v>
       </c>
@@ -17590,7 +17590,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>11</v>
       </c>
@@ -17604,7 +17604,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>11</v>
       </c>
@@ -17618,7 +17618,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>11</v>
       </c>
@@ -17632,7 +17632,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>11</v>
       </c>
@@ -17646,7 +17646,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>11</v>
       </c>
@@ -17660,7 +17660,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>11</v>
       </c>
@@ -17674,7 +17674,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>11</v>
       </c>
@@ -17688,7 +17688,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>11</v>
       </c>
@@ -17702,7 +17702,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>11</v>
       </c>
@@ -17716,7 +17716,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>11</v>
       </c>
@@ -17730,7 +17730,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>11</v>
       </c>
@@ -17744,7 +17744,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>11</v>
       </c>
@@ -17758,7 +17758,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>11</v>
       </c>
@@ -17772,7 +17772,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>11</v>
       </c>
@@ -17786,7 +17786,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>11</v>
       </c>
@@ -17800,7 +17800,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>11</v>
       </c>
@@ -17814,7 +17814,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>11</v>
       </c>
@@ -17828,7 +17828,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>11</v>
       </c>
@@ -17842,7 +17842,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>12</v>
       </c>
@@ -17856,7 +17856,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>12</v>
       </c>
@@ -17870,7 +17870,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>12</v>
       </c>
@@ -17884,7 +17884,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>12</v>
       </c>
@@ -17898,7 +17898,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>12</v>
       </c>
@@ -17912,7 +17912,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>12</v>
       </c>
@@ -17926,7 +17926,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>12</v>
       </c>
@@ -17940,7 +17940,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>12</v>
       </c>
@@ -17954,7 +17954,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>12</v>
       </c>
@@ -17968,7 +17968,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>12</v>
       </c>
@@ -17982,7 +17982,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>12</v>
       </c>
@@ -17996,7 +17996,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>12</v>
       </c>
@@ -18010,7 +18010,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>12</v>
       </c>
@@ -18024,7 +18024,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>12</v>
       </c>
@@ -18038,7 +18038,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>12</v>
       </c>
@@ -18052,7 +18052,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>12</v>
       </c>
@@ -18066,7 +18066,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>12</v>
       </c>
@@ -18080,7 +18080,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>12</v>
       </c>
@@ -18094,7 +18094,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>12</v>
       </c>
@@ -18108,7 +18108,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>12</v>
       </c>
@@ -18122,7 +18122,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>12</v>
       </c>
@@ -18136,7 +18136,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>12</v>
       </c>
@@ -18150,7 +18150,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>12</v>
       </c>
@@ -18164,7 +18164,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>12</v>
       </c>
@@ -18178,7 +18178,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>12</v>
       </c>
@@ -18192,7 +18192,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>13</v>
       </c>
@@ -18206,7 +18206,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>13</v>
       </c>
@@ -18220,7 +18220,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>13</v>
       </c>
@@ -18234,7 +18234,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>13</v>
       </c>
@@ -18248,7 +18248,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>13</v>
       </c>
@@ -18262,7 +18262,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>13</v>
       </c>
@@ -18276,7 +18276,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>13</v>
       </c>
@@ -18290,7 +18290,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>13</v>
       </c>
@@ -18304,7 +18304,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>13</v>
       </c>
@@ -18318,7 +18318,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>13</v>
       </c>
@@ -18332,7 +18332,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>13</v>
       </c>
@@ -18346,7 +18346,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>13</v>
       </c>
@@ -18360,7 +18360,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>13</v>
       </c>
@@ -18374,7 +18374,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>13</v>
       </c>
@@ -18388,7 +18388,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>13</v>
       </c>
@@ -18402,7 +18402,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>13</v>
       </c>
@@ -18416,7 +18416,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>13</v>
       </c>
@@ -18430,7 +18430,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="219" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>13</v>
       </c>
@@ -18444,7 +18444,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>13</v>
       </c>
@@ -18458,7 +18458,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>13</v>
       </c>
@@ -18472,7 +18472,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>13</v>
       </c>
@@ -18486,7 +18486,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>13</v>
       </c>
@@ -18500,7 +18500,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>13</v>
       </c>
@@ -18514,7 +18514,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>13</v>
       </c>
@@ -18528,7 +18528,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>13</v>
       </c>
@@ -18542,7 +18542,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>14</v>
       </c>
@@ -18556,7 +18556,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>14</v>
       </c>
@@ -18570,7 +18570,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>14</v>
       </c>
@@ -18584,7 +18584,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="230" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>14</v>
       </c>
@@ -18598,7 +18598,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>14</v>
       </c>
@@ -18612,7 +18612,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>14</v>
       </c>
@@ -18626,7 +18626,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>14</v>
       </c>
@@ -18640,7 +18640,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>14</v>
       </c>
@@ -18654,7 +18654,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="235" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>14</v>
       </c>
@@ -18668,7 +18668,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="236" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>14</v>
       </c>
@@ -18682,7 +18682,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="237" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>14</v>
       </c>
@@ -18696,7 +18696,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="238" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>14</v>
       </c>
@@ -18710,7 +18710,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="239" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>14</v>
       </c>
@@ -18724,7 +18724,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="240" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>14</v>
       </c>
@@ -18738,7 +18738,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="241" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>14</v>
       </c>
@@ -18752,7 +18752,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="242" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>14</v>
       </c>
@@ -18766,7 +18766,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="243" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>14</v>
       </c>
@@ -18780,7 +18780,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="244" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>14</v>
       </c>
@@ -18794,7 +18794,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="245" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>14</v>
       </c>
@@ -18808,7 +18808,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>14</v>
       </c>
@@ -18822,7 +18822,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="247" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>14</v>
       </c>
@@ -18836,7 +18836,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="248" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>14</v>
       </c>
@@ -18850,7 +18850,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="249" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>14</v>
       </c>
@@ -18864,7 +18864,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="250" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>14</v>
       </c>
@@ -18878,7 +18878,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="251" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>14</v>
       </c>
@@ -18892,7 +18892,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>15</v>
       </c>
@@ -18903,7 +18903,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>15</v>
       </c>
@@ -18914,7 +18914,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>15</v>
       </c>
@@ -18925,7 +18925,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>15</v>
       </c>
@@ -18936,7 +18936,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>15</v>
       </c>
@@ -18947,7 +18947,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>15</v>
       </c>
@@ -18958,7 +18958,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>15</v>
       </c>
@@ -18972,7 +18972,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="259" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>15</v>
       </c>
@@ -18986,7 +18986,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="260" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>15</v>
       </c>
@@ -19000,7 +19000,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="261" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>15</v>
       </c>
@@ -19014,7 +19014,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="262" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>15</v>
       </c>
@@ -19028,7 +19028,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="263" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>15</v>
       </c>
@@ -19042,7 +19042,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="264" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>15</v>
       </c>
@@ -19056,7 +19056,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="265" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>15</v>
       </c>
@@ -19070,7 +19070,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="266" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>15</v>
       </c>
@@ -19084,7 +19084,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="267" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>15</v>
       </c>
@@ -19098,7 +19098,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="268" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>15</v>
       </c>
@@ -19112,7 +19112,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="269" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>15</v>
       </c>
@@ -19126,7 +19126,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="270" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>15</v>
       </c>
@@ -19140,7 +19140,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="271" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>15</v>
       </c>
@@ -19154,7 +19154,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="272" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>15</v>
       </c>
@@ -19168,7 +19168,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="273" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>15</v>
       </c>
@@ -19182,7 +19182,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="274" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>15</v>
       </c>
@@ -19196,7 +19196,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="275" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>15</v>
       </c>
@@ -19210,7 +19210,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="276" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>15</v>
       </c>
@@ -19224,7 +19224,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="277" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>16</v>
       </c>
@@ -19235,7 +19235,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="278" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>16</v>
       </c>
@@ -19246,7 +19246,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="279" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>16</v>
       </c>
@@ -19257,7 +19257,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="280" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>16</v>
       </c>
@@ -19268,7 +19268,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="281" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>16</v>
       </c>
@@ -19282,7 +19282,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="282" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>16</v>
       </c>
@@ -19296,7 +19296,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="283" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>16</v>
       </c>
@@ -19310,7 +19310,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="284" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>16</v>
       </c>
@@ -19324,7 +19324,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="285" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>16</v>
       </c>
@@ -19338,7 +19338,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="286" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>16</v>
       </c>
@@ -19352,7 +19352,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="287" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>16</v>
       </c>
@@ -19366,7 +19366,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="288" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>16</v>
       </c>
@@ -19380,7 +19380,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="289" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>16</v>
       </c>
@@ -19394,7 +19394,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="290" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>16</v>
       </c>
@@ -19408,7 +19408,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="291" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>16</v>
       </c>
@@ -19419,7 +19419,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="292" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>16</v>
       </c>
@@ -19433,7 +19433,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="293" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>16</v>
       </c>
@@ -19447,7 +19447,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="294" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>16</v>
       </c>
@@ -19461,7 +19461,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="295" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>16</v>
       </c>
@@ -19475,7 +19475,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="296" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>16</v>
       </c>
@@ -19489,7 +19489,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="297" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>16</v>
       </c>
@@ -19503,7 +19503,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="298" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>16</v>
       </c>
@@ -19517,7 +19517,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="299" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>16</v>
       </c>
@@ -19531,7 +19531,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="300" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>16</v>
       </c>
@@ -19545,7 +19545,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="301" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>16</v>
       </c>
@@ -19571,12 +19571,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DCCDE7F-90D3-4824-8130-ABEE2C3BAACE}">
   <dimension ref="A1:AB51"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.6640625" customWidth="1"/>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>19</v>
       </c>
@@ -19590,7 +19590,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>20</v>
       </c>
@@ -19661,7 +19661,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -19754,7 +19754,7 @@
         <v>51.674399999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -19847,7 +19847,7 @@
         <v>-88.491599999999991</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -19940,7 +19940,7 @@
         <v>-36.817199999999993</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -19954,7 +19954,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -19968,7 +19968,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -19982,7 +19982,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>20</v>
       </c>
@@ -19996,7 +19996,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>20</v>
       </c>
@@ -20010,7 +20010,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -20024,7 +20024,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -20038,7 +20038,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -20052,7 +20052,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>20</v>
       </c>
@@ -20066,7 +20066,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>20</v>
       </c>
@@ -20080,7 +20080,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>20</v>
       </c>
@@ -20094,7 +20094,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -20108,7 +20108,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -20122,7 +20122,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -20136,7 +20136,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>20</v>
       </c>
@@ -20150,7 +20150,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -20164,7 +20164,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>20</v>
       </c>
@@ -20178,7 +20178,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>20</v>
       </c>
@@ -20192,7 +20192,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>20</v>
       </c>
@@ -20206,7 +20206,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>20</v>
       </c>
@@ -20220,7 +20220,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>20</v>
       </c>
@@ -20234,7 +20234,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>21</v>
       </c>
@@ -20248,7 +20248,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>21</v>
       </c>
@@ -20262,7 +20262,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>21</v>
       </c>
@@ -20276,7 +20276,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>21</v>
       </c>
@@ -20290,7 +20290,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>21</v>
       </c>
@@ -20304,7 +20304,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>21</v>
       </c>
@@ -20318,7 +20318,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>21</v>
       </c>
@@ -20332,7 +20332,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>21</v>
       </c>
@@ -20346,7 +20346,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>21</v>
       </c>
@@ -20360,7 +20360,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>21</v>
       </c>
@@ -20374,7 +20374,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>21</v>
       </c>
@@ -20388,7 +20388,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>21</v>
       </c>
@@ -20402,7 +20402,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>21</v>
       </c>
@@ -20416,7 +20416,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>21</v>
       </c>
@@ -20430,7 +20430,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>21</v>
       </c>
@@ -20444,7 +20444,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>21</v>
       </c>
@@ -20458,7 +20458,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>21</v>
       </c>
@@ -20472,7 +20472,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>21</v>
       </c>
@@ -20486,7 +20486,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>21</v>
       </c>
@@ -20500,7 +20500,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>21</v>
       </c>
@@ -20514,7 +20514,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>21</v>
       </c>
@@ -20528,7 +20528,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>21</v>
       </c>
@@ -20542,7 +20542,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>21</v>
       </c>
@@ -20556,7 +20556,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>21</v>
       </c>
@@ -20570,7 +20570,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>21</v>
       </c>
@@ -20593,14 +20593,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F31AC804-BBB6-49B0-9019-74125F94880C}">
   <dimension ref="A1:AA97"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="42.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.33203125" customWidth="1"/>
-    <col min="9" max="9" width="11.44140625" customWidth="1"/>
+    <col min="1" max="1" width="42.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.28515625" customWidth="1"/>
+    <col min="9" max="9" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>24</v>
       </c>
@@ -20614,7 +20614,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -20682,7 +20682,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -20771,7 +20771,7 @@
         <v>5.43</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -20860,7 +20860,7 @@
         <v>6.24</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -20949,7 +20949,7 @@
         <v>24.222999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -21038,7 +21038,7 @@
         <v>1.22</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -21052,7 +21052,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -21066,7 +21066,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -21080,7 +21080,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -21094,7 +21094,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -21108,7 +21108,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -21122,7 +21122,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>4</v>
       </c>
@@ -21136,7 +21136,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -21150,7 +21150,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -21164,7 +21164,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>4</v>
       </c>
@@ -21178,7 +21178,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>4</v>
       </c>
@@ -21192,7 +21192,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -21206,7 +21206,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>4</v>
       </c>
@@ -21220,7 +21220,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>4</v>
       </c>
@@ -21234,7 +21234,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>4</v>
       </c>
@@ -21248,7 +21248,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>4</v>
       </c>
@@ -21262,7 +21262,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>4</v>
       </c>
@@ -21276,7 +21276,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>4</v>
       </c>
@@ -21290,7 +21290,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>4</v>
       </c>
@@ -21304,7 +21304,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>6</v>
       </c>
@@ -21318,7 +21318,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>6</v>
       </c>
@@ -21332,7 +21332,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>6</v>
       </c>
@@ -21346,7 +21346,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>6</v>
       </c>
@@ -21360,7 +21360,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>6</v>
       </c>
@@ -21374,7 +21374,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>6</v>
       </c>
@@ -21388,7 +21388,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>6</v>
       </c>
@@ -21402,7 +21402,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>6</v>
       </c>
@@ -21416,7 +21416,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>6</v>
       </c>
@@ -21430,7 +21430,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>6</v>
       </c>
@@ -21444,7 +21444,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>6</v>
       </c>
@@ -21458,7 +21458,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>6</v>
       </c>
@@ -21472,7 +21472,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>6</v>
       </c>
@@ -21486,7 +21486,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>6</v>
       </c>
@@ -21500,7 +21500,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>6</v>
       </c>
@@ -21514,7 +21514,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>6</v>
       </c>
@@ -21528,7 +21528,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>6</v>
       </c>
@@ -21542,7 +21542,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>6</v>
       </c>
@@ -21556,7 +21556,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>6</v>
       </c>
@@ -21570,7 +21570,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>6</v>
       </c>
@@ -21584,7 +21584,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>6</v>
       </c>
@@ -21598,7 +21598,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>6</v>
       </c>
@@ -21612,7 +21612,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>6</v>
       </c>
@@ -21626,7 +21626,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>6</v>
       </c>
@@ -21640,7 +21640,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>7</v>
       </c>
@@ -21654,7 +21654,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>7</v>
       </c>
@@ -21668,7 +21668,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>7</v>
       </c>
@@ -21682,7 +21682,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>7</v>
       </c>
@@ -21696,7 +21696,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>7</v>
       </c>
@@ -21710,7 +21710,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>7</v>
       </c>
@@ -21724,7 +21724,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>7</v>
       </c>
@@ -21738,7 +21738,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>7</v>
       </c>
@@ -21752,7 +21752,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>7</v>
       </c>
@@ -21766,7 +21766,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>7</v>
       </c>
@@ -21780,7 +21780,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>7</v>
       </c>
@@ -21794,7 +21794,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>7</v>
       </c>
@@ -21808,7 +21808,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>7</v>
       </c>
@@ -21822,7 +21822,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>7</v>
       </c>
@@ -21836,7 +21836,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>7</v>
       </c>
@@ -21850,7 +21850,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>7</v>
       </c>
@@ -21864,7 +21864,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>7</v>
       </c>
@@ -21878,7 +21878,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>7</v>
       </c>
@@ -21892,7 +21892,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>7</v>
       </c>
@@ -21906,7 +21906,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>7</v>
       </c>
@@ -21920,7 +21920,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>7</v>
       </c>
@@ -21934,7 +21934,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>7</v>
       </c>
@@ -21948,7 +21948,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>7</v>
       </c>
@@ -21962,7 +21962,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>7</v>
       </c>
@@ -21976,7 +21976,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>25</v>
       </c>
@@ -21990,7 +21990,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>25</v>
       </c>
@@ -22004,7 +22004,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>25</v>
       </c>
@@ -22018,7 +22018,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>25</v>
       </c>
@@ -22032,7 +22032,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>25</v>
       </c>
@@ -22046,7 +22046,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>25</v>
       </c>
@@ -22060,7 +22060,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>25</v>
       </c>
@@ -22074,7 +22074,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>25</v>
       </c>
@@ -22088,7 +22088,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>25</v>
       </c>
@@ -22102,7 +22102,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>25</v>
       </c>
@@ -22116,7 +22116,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>25</v>
       </c>
@@ -22130,7 +22130,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>25</v>
       </c>
@@ -22144,7 +22144,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>25</v>
       </c>
@@ -22158,7 +22158,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>25</v>
       </c>
@@ -22172,7 +22172,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>25</v>
       </c>
@@ -22186,7 +22186,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>25</v>
       </c>
@@ -22200,7 +22200,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>25</v>
       </c>
@@ -22214,7 +22214,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>25</v>
       </c>
@@ -22228,7 +22228,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>25</v>
       </c>
@@ -22242,7 +22242,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>25</v>
       </c>
@@ -22256,7 +22256,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>25</v>
       </c>
@@ -22270,7 +22270,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>25</v>
       </c>
@@ -22284,7 +22284,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>25</v>
       </c>
@@ -22298,7 +22298,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>25</v>
       </c>
@@ -22321,24 +22321,24 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2DE3364-19EF-4DBB-9C60-BFBDC0F3AE34}">
   <dimension ref="A1:AD39"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.88671875" customWidth="1"/>
-    <col min="2" max="2" width="12.6640625" customWidth="1"/>
-    <col min="3" max="3" width="13.6640625" customWidth="1"/>
+    <col min="1" max="1" width="10.85546875" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" customWidth="1"/>
+    <col min="3" max="3" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>29</v>
       </c>
@@ -22421,7 +22421,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1990</v>
       </c>
@@ -22532,7 +22532,7 @@
         <v>253.74799999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>1991</v>
       </c>
@@ -22543,7 +22543,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>1992</v>
       </c>
@@ -22561,7 +22561,7 @@
         <v>754.71479999999997</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>1993</v>
       </c>
@@ -22579,7 +22579,7 @@
         <v>797.41800000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>1994</v>
       </c>
@@ -22597,7 +22597,7 @@
         <v>831.71879999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>1995</v>
       </c>
@@ -22615,7 +22615,7 @@
         <v>861.99119999999994</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>1996</v>
       </c>
@@ -22633,7 +22633,7 @@
         <v>910.35719999999992</v>
       </c>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>1997</v>
       </c>
@@ -22651,7 +22651,7 @@
         <v>960.41160000000002</v>
       </c>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>1998</v>
       </c>
@@ -22669,7 +22669,7 @@
         <v>975.79799999999989</v>
       </c>
     </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>1999</v>
       </c>
@@ -22687,7 +22687,7 @@
         <v>985.77719999999999</v>
       </c>
     </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2000</v>
       </c>
@@ -22705,7 +22705,7 @@
         <v>996.87239999999997</v>
       </c>
     </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2001</v>
       </c>
@@ -22723,7 +22723,7 @@
         <v>943.4556</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2002</v>
       </c>
@@ -22741,7 +22741,7 @@
         <v>956.85839999999985</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2003</v>
       </c>
@@ -22759,7 +22759,7 @@
         <v>942.22439999999995</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2004</v>
       </c>
@@ -22777,7 +22777,7 @@
         <v>938.46600000000001</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2005</v>
       </c>
@@ -22795,7 +22795,7 @@
         <v>907.8696000000001</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2006</v>
       </c>
@@ -22813,7 +22813,7 @@
         <v>896.21999999999991</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>2007</v>
       </c>
@@ -22831,7 +22831,7 @@
         <v>915.36839999999995</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>2008</v>
       </c>
@@ -22849,7 +22849,7 @@
         <v>920.58839999999998</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>2009</v>
       </c>
@@ -22867,7 +22867,7 @@
         <v>939.85919999999999</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2010</v>
       </c>
@@ -22885,7 +22885,7 @@
         <v>935.84879999999998</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>2011</v>
       </c>
@@ -22903,7 +22903,7 @@
         <v>919.18439999999998</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>2012</v>
       </c>
@@ -22921,7 +22921,7 @@
         <v>867.67920000000004</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>2013</v>
       </c>
@@ -22939,7 +22939,7 @@
         <v>894.36959999999999</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>2014</v>
       </c>
@@ -22957,7 +22957,7 @@
         <v>891.07560000000001</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>2015</v>
       </c>
@@ -22975,7 +22975,7 @@
         <v>890.85599999999999</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>2016</v>
       </c>
@@ -22993,7 +22993,7 @@
         <v>913.49279999999999</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>2017</v>
       </c>
@@ -23004,7 +23004,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>2018</v>
       </c>
@@ -23015,7 +23015,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>2019</v>
       </c>
@@ -23026,7 +23026,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>2020</v>
       </c>
@@ -23037,7 +23037,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>2021</v>
       </c>
@@ -23048,7 +23048,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>2022</v>
       </c>
@@ -23059,7 +23059,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>2023</v>
       </c>
@@ -23070,7 +23070,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>2024</v>
       </c>
@@ -23090,23 +23090,23 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB763C44-0720-4A5D-A285-14210CC2296D}">
   <dimension ref="A2:D7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.33203125" customWidth="1"/>
+    <col min="1" max="1" width="13.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
       <c r="D2">
         <f>0.0036</f>
         <v>3.5999999999999999E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>31</v>
       </c>
@@ -23114,7 +23114,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>15.5</v>
       </c>
@@ -23123,7 +23123,7 @@
         <v>4305.5555555555557</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -23131,7 +23131,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>3971</v>
       </c>
@@ -23152,14 +23152,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDEB2676-8085-4D3C-98E7-5BF41F1AF8D5}">
   <dimension ref="A1:W49"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.88671875" customWidth="1"/>
-    <col min="2" max="11" width="7.77734375" customWidth="1"/>
-    <col min="14" max="14" width="18.44140625" customWidth="1"/>
+    <col min="1" max="1" width="11.85546875" customWidth="1"/>
+    <col min="2" max="11" width="7.7109375" customWidth="1"/>
+    <col min="14" max="14" width="18.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>34</v>
       </c>
@@ -23194,7 +23194,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>35</v>
       </c>
@@ -23256,7 +23256,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>35</v>
       </c>
@@ -23330,7 +23330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>67</v>
       </c>
@@ -23404,7 +23404,7 @@
         <v>1193.4002561548721</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>67</v>
       </c>
@@ -23478,7 +23478,7 @@
         <v>366.57755802738978</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>36</v>
       </c>
@@ -23552,7 +23552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>36</v>
       </c>
@@ -23626,7 +23626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -23700,7 +23700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>37</v>
       </c>
@@ -23774,7 +23774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>37</v>
       </c>
@@ -23848,7 +23848,7 @@
         <v>2417.2778962392399</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>37</v>
       </c>
@@ -23922,7 +23922,7 @@
         <v>3622.2536445412229</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>38</v>
       </c>
@@ -23996,7 +23996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>38</v>
       </c>
@@ -24070,7 +24070,7 @@
         <v>343.51136363636368</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>38</v>
       </c>
@@ -24144,7 +24144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>39</v>
       </c>
@@ -24218,7 +24218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>39</v>
       </c>
@@ -24261,7 +24261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>39</v>
       </c>
@@ -24296,7 +24296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -24331,7 +24331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>40</v>
       </c>
@@ -24369,7 +24369,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>40</v>
       </c>
@@ -24404,7 +24404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>41</v>
       </c>
@@ -24466,7 +24466,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>41</v>
       </c>
@@ -24540,7 +24540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>41</v>
       </c>
@@ -24614,7 +24614,7 @@
         <v>0.3435113636363637</v>
       </c>
     </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>42</v>
       </c>
@@ -24688,7 +24688,7 @@
         <v>7.5995093549627253</v>
       </c>
     </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>42</v>
       </c>
@@ -24723,7 +24723,7 @@
         <v>2417.2778962392399</v>
       </c>
     </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>42</v>
       </c>
@@ -24758,7 +24758,7 @@
         <v>23.26791557877343</v>
       </c>
     </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>43</v>
       </c>
@@ -24793,7 +24793,7 @@
         <v>8.3938141495607681</v>
       </c>
     </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>43</v>
       </c>
@@ -24828,7 +24828,7 @@
         <v>3622.2536445412229</v>
       </c>
     </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>43</v>
       </c>
@@ -24863,7 +24863,7 @@
         <v>34.866612621252422</v>
       </c>
     </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>44</v>
       </c>
@@ -24898,7 +24898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>44</v>
       </c>
@@ -24933,7 +24933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>44</v>
       </c>
@@ -24968,7 +24968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>45</v>
       </c>
@@ -25003,7 +25003,7 @@
         <v>3.497727272727273</v>
       </c>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>45</v>
       </c>
@@ -25038,7 +25038,7 @@
         <v>343.51136363636368</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>45</v>
       </c>
@@ -25073,7 +25073,7 @@
         <v>13.731818181818181</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>46</v>
       </c>
@@ -25108,7 +25108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>46</v>
       </c>
@@ -25143,7 +25143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>46</v>
       </c>
@@ -25178,7 +25178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>47</v>
       </c>
@@ -25213,7 +25213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>47</v>
       </c>
@@ -25248,7 +25248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>47</v>
       </c>
@@ -25283,7 +25283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
       <c r="N45">
         <v>2007</v>
       </c>
@@ -25303,7 +25303,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
       <c r="M46" t="s">
         <v>4</v>
       </c>
@@ -25326,7 +25326,7 @@
         <v>5.43</v>
       </c>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
       <c r="M47" t="s">
         <v>6</v>
       </c>
@@ -25349,7 +25349,7 @@
         <v>6.24</v>
       </c>
     </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
       <c r="M48" t="s">
         <v>7</v>
       </c>
@@ -25372,7 +25372,7 @@
         <v>24.222999999999999</v>
       </c>
     </row>
-    <row r="49" spans="13:19" x14ac:dyDescent="0.3">
+    <row r="49" spans="13:19" x14ac:dyDescent="0.25">
       <c r="M49" t="s">
         <v>25</v>
       </c>
@@ -25404,21 +25404,21 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95A32E31-20CB-4056-864B-0FCE4F4387EC}">
   <dimension ref="A1:AB26"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="8.21875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="9.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>34</v>
       </c>
@@ -25453,7 +25453,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>35</v>
       </c>
@@ -25527,7 +25527,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>67</v>
       </c>
@@ -25591,32 +25591,32 @@
       <c r="V3" t="s">
         <v>4</v>
       </c>
-      <c r="W3" s="6">
+      <c r="W3" s="5">
         <f>(O3-O15)/O15</f>
         <v>-4.9985752101565036E-2</v>
       </c>
-      <c r="X3" s="6">
+      <c r="X3" s="5">
         <f t="shared" ref="X3:AB11" si="1">(P3-P15)/P15</f>
         <v>-5.0028070086574131E-2</v>
       </c>
-      <c r="Y3" s="6">
+      <c r="Y3" s="5">
         <f t="shared" si="1"/>
         <v>-2.0065987170524043E-2</v>
       </c>
-      <c r="Z3" s="6">
+      <c r="Z3" s="5">
         <f t="shared" si="1"/>
         <v>-5.0256282214645759E-2</v>
       </c>
-      <c r="AA3" s="6">
+      <c r="AA3" s="5">
         <f t="shared" si="1"/>
         <v>-5.0169937646938195E-2</v>
       </c>
-      <c r="AB3" s="6">
+      <c r="AB3" s="5">
         <f t="shared" si="1"/>
         <v>-4.9817272552413853E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>36</v>
       </c>
@@ -25680,32 +25680,32 @@
       <c r="V4" t="s">
         <v>6</v>
       </c>
-      <c r="W4" s="6">
+      <c r="W4" s="5">
         <f t="shared" ref="W4:W11" si="3">(O4-O16)/O16</f>
         <v>-5.0000000000000225E-2</v>
       </c>
-      <c r="X4" s="6">
+      <c r="X4" s="5">
         <f t="shared" si="1"/>
         <v>-5.0000000000000169E-2</v>
       </c>
-      <c r="Y4" s="6">
+      <c r="Y4" s="5">
         <f t="shared" si="1"/>
         <v>-5.0000000000000058E-2</v>
       </c>
-      <c r="Z4" s="6">
+      <c r="Z4" s="5">
         <f t="shared" si="1"/>
         <v>-4.9999999999999843E-2</v>
       </c>
-      <c r="AA4" s="6">
+      <c r="AA4" s="5">
         <f t="shared" si="1"/>
         <v>-5.0000000000000142E-2</v>
       </c>
-      <c r="AB4" s="6">
+      <c r="AB4" s="5">
         <f t="shared" si="1"/>
         <v>-7.0907474393169814E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>37</v>
       </c>
@@ -25769,32 +25769,32 @@
       <c r="V5" t="s">
         <v>7</v>
       </c>
-      <c r="W5" s="6">
+      <c r="W5" s="5">
         <f t="shared" si="3"/>
         <v>-4.9999999999999899E-2</v>
       </c>
-      <c r="X5" s="6">
+      <c r="X5" s="5">
         <f t="shared" si="1"/>
         <v>2.7094534503137584E-2</v>
       </c>
-      <c r="Y5" s="6">
+      <c r="Y5" s="5">
         <f>(Q5-Q17)/Q17</f>
         <v>7.1097821921179666E-2</v>
       </c>
-      <c r="Z5" s="6">
+      <c r="Z5" s="5">
         <f t="shared" si="1"/>
         <v>-3.032271906213559E-2</v>
       </c>
-      <c r="AA5" s="6">
+      <c r="AA5" s="5">
         <f t="shared" si="1"/>
         <v>5.9084192447603483E-2</v>
       </c>
-      <c r="AB5" s="6">
+      <c r="AB5" s="5">
         <f t="shared" si="1"/>
         <v>5.9718156892095392E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>75</v>
       </c>
@@ -25858,32 +25858,32 @@
       <c r="V6" t="s">
         <v>8</v>
       </c>
-      <c r="W6" s="6">
+      <c r="W6" s="5">
         <f t="shared" si="3"/>
         <v>9.391631084557403E-2</v>
       </c>
-      <c r="X6" s="6">
+      <c r="X6" s="5">
         <f t="shared" si="1"/>
         <v>-1.8960585838748101E-2</v>
       </c>
-      <c r="Y6" s="6">
+      <c r="Y6" s="5">
         <f t="shared" si="1"/>
         <v>-2.9633854757698051E-2</v>
       </c>
-      <c r="Z6" s="6">
+      <c r="Z6" s="5">
         <f t="shared" si="1"/>
         <v>9.053246214281109E-2</v>
       </c>
-      <c r="AA6" s="6">
+      <c r="AA6" s="5">
         <f t="shared" si="1"/>
         <v>3.7969504759447006E-2</v>
       </c>
-      <c r="AB6" s="6">
+      <c r="AB6" s="5">
         <f t="shared" si="1"/>
         <v>9.9970863183288905E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>38</v>
       </c>
@@ -25947,32 +25947,32 @@
       <c r="V7" t="s">
         <v>9</v>
       </c>
-      <c r="W7" s="6">
+      <c r="W7" s="5">
         <f t="shared" si="3"/>
         <v>3.8799485385410537E-16</v>
       </c>
-      <c r="X7" s="6">
+      <c r="X7" s="5">
         <f t="shared" si="1"/>
         <v>-3.4694554223037667E-16</v>
       </c>
-      <c r="Y7" s="6">
+      <c r="Y7" s="5">
         <f t="shared" si="1"/>
         <v>-7.3494093753388118E-16</v>
       </c>
-      <c r="Z7" s="6">
+      <c r="Z7" s="5">
         <f t="shared" si="1"/>
         <v>3.4915631877832434E-3</v>
       </c>
-      <c r="AA7" s="6">
+      <c r="AA7" s="5">
         <f t="shared" si="1"/>
         <v>0.10000000000000041</v>
       </c>
-      <c r="AB7" s="6">
+      <c r="AB7" s="5">
         <f t="shared" si="1"/>
         <v>9.9999999999999811E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>39</v>
       </c>
@@ -26036,32 +26036,32 @@
       <c r="V8" t="s">
         <v>11</v>
       </c>
-      <c r="W8" s="6">
+      <c r="W8" s="5">
         <f t="shared" si="3"/>
         <v>-5.0000000000000017E-2</v>
       </c>
-      <c r="X8" s="6">
+      <c r="X8" s="5">
         <f t="shared" si="1"/>
         <v>-5.0000000000000863E-2</v>
       </c>
-      <c r="Y8" s="6">
+      <c r="Y8" s="5">
         <f t="shared" si="1"/>
         <v>-5.0000000000000065E-2</v>
       </c>
-      <c r="Z8" s="6">
+      <c r="Z8" s="5">
         <f t="shared" si="1"/>
         <v>-0.11522498060512071</v>
       </c>
-      <c r="AA8" s="6">
+      <c r="AA8" s="5">
         <f t="shared" si="1"/>
         <v>-8.7055602358887541E-2</v>
       </c>
-      <c r="AB8" s="6">
+      <c r="AB8" s="5">
         <f t="shared" si="1"/>
         <v>-4.9999999999999954E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>58</v>
       </c>
@@ -26125,32 +26125,32 @@
       <c r="V9" t="s">
         <v>13</v>
       </c>
-      <c r="W9" s="6">
+      <c r="W9" s="5">
         <f t="shared" si="3"/>
         <v>-5.0045946991681099E-2</v>
       </c>
-      <c r="X9" s="6">
+      <c r="X9" s="5">
         <f t="shared" si="1"/>
         <v>-4.9973772647757819E-2</v>
       </c>
-      <c r="Y9" s="6">
+      <c r="Y9" s="5">
         <f t="shared" si="1"/>
         <v>-4.9983764742574835E-2</v>
       </c>
-      <c r="Z9" s="6">
+      <c r="Z9" s="5">
         <f t="shared" si="1"/>
         <v>-4.6047763451031724E-2</v>
       </c>
-      <c r="AA9" s="6">
+      <c r="AA9" s="5">
         <f t="shared" si="1"/>
         <v>3.837495752633352E-2</v>
       </c>
-      <c r="AB9" s="6">
+      <c r="AB9" s="5">
         <f t="shared" si="1"/>
         <v>4.9998120976877163E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>69</v>
       </c>
@@ -26214,32 +26214,32 @@
       <c r="V10" t="s">
         <v>66</v>
       </c>
-      <c r="W10" s="6">
+      <c r="W10" s="5">
         <f t="shared" si="3"/>
         <v>-4.9999999999999885E-2</v>
       </c>
-      <c r="X10" s="6">
+      <c r="X10" s="5">
         <f t="shared" si="1"/>
         <v>-5.0000000000000509E-2</v>
       </c>
-      <c r="Y10" s="6">
+      <c r="Y10" s="5">
         <f t="shared" si="1"/>
         <v>-3.6935849608660622E-2</v>
       </c>
-      <c r="Z10" s="6">
+      <c r="Z10" s="5">
         <f t="shared" si="1"/>
         <v>0.12585138104205884</v>
       </c>
-      <c r="AA10" s="6">
+      <c r="AA10" s="5">
         <f t="shared" si="1"/>
         <v>-4.9999999999999954E-2</v>
       </c>
-      <c r="AB10" s="6">
+      <c r="AB10" s="5">
         <f t="shared" si="1"/>
         <v>-5.006518904823945E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>59</v>
       </c>
@@ -26303,32 +26303,32 @@
       <c r="V11" t="s">
         <v>68</v>
       </c>
-      <c r="W11" s="6">
+      <c r="W11" s="5">
         <f t="shared" si="3"/>
         <v>-0.9142661179698216</v>
       </c>
-      <c r="X11" s="6">
+      <c r="X11" s="5">
         <f t="shared" si="1"/>
         <v>0.22292103424178883</v>
       </c>
-      <c r="Y11" s="6" t="e">
+      <c r="Y11" s="5" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z11" s="6">
+      <c r="Z11" s="5">
         <f t="shared" si="1"/>
         <v>-1</v>
       </c>
-      <c r="AA11" s="6">
+      <c r="AA11" s="5">
         <f t="shared" si="1"/>
         <v>-0.60845153664302598</v>
       </c>
-      <c r="AB11" s="6">
+      <c r="AB11" s="5">
         <f t="shared" si="1"/>
         <v>-0.57166438979963574</v>
       </c>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>60</v>
       </c>
@@ -26363,7 +26363,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>33</v>
       </c>
@@ -26398,7 +26398,7 @@
         <v>29.61999999999999</v>
       </c>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>41</v>
       </c>
@@ -26451,7 +26451,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>70</v>
       </c>
@@ -26507,7 +26507,7 @@
         <v>12.477599999999999</v>
       </c>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>44</v>
       </c>
@@ -26563,7 +26563,7 @@
         <v>32.842799999999997</v>
       </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>46</v>
       </c>
@@ -26619,7 +26619,7 @@
         <v>188.3844</v>
       </c>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>47</v>
       </c>
@@ -26675,7 +26675,7 @@
         <v>196.3152</v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>61</v>
       </c>
@@ -26731,7 +26731,7 @@
         <v>146.9556</v>
       </c>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>71</v>
       </c>
@@ -26787,7 +26787,7 @@
         <v>19.148399999999999</v>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>72</v>
       </c>
@@ -26843,7 +26843,7 @@
         <v>223.5204</v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>62</v>
       </c>
@@ -26881,31 +26881,31 @@
         <v>66</v>
       </c>
       <c r="O22">
-        <f>SUM(P25+P26)</f>
+        <f t="shared" ref="O22:T22" si="10">SUM(P25+P26)</f>
         <v>1.8539999999999999</v>
       </c>
       <c r="P22">
-        <f>SUM(Q25+Q26)</f>
+        <f t="shared" si="10"/>
         <v>25.869599999999998</v>
       </c>
       <c r="Q22">
-        <f>SUM(R25+R26)</f>
+        <f t="shared" si="10"/>
         <v>49.215599999999995</v>
       </c>
       <c r="R22">
-        <f>SUM(S25+S26)</f>
+        <f t="shared" si="10"/>
         <v>45.878399999999999</v>
       </c>
       <c r="S22">
-        <f>SUM(T25+T26)</f>
+        <f t="shared" si="10"/>
         <v>128.6028</v>
       </c>
       <c r="T22">
-        <f>SUM(U25+U26)</f>
+        <f t="shared" si="10"/>
         <v>209.85119999999998</v>
       </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>63</v>
       </c>
@@ -26961,7 +26961,7 @@
         <v>0.87839999999999996</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>64</v>
       </c>
@@ -26996,7 +26996,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>65</v>
       </c>
@@ -27055,7 +27055,7 @@
         <v>193.50719999999998</v>
       </c>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="N26" t="s">
         <v>15</v>
       </c>

--- a/ELC_data_Spain.xlsx
+++ b/ELC_data_Spain.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Riccardo\PoliTo\anno4\Models and scenarios\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Documents\TEMOA\PROJECT\Models-and-scenarios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{393074A5-B2D7-41DE-BD95-587F9BD4F59F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5059C8F-F8E4-4E8B-A6B8-968FAA586DFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="1" activeTab="6" xr2:uid="{8BBF5E45-81C8-439F-BD27-48A9AF2DFBEB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="6" xr2:uid="{8BBF5E45-81C8-439F-BD27-48A9AF2DFBEB}"/>
   </bookViews>
   <sheets>
     <sheet name="ELC_Generation" sheetId="1" r:id="rId1"/>
@@ -38,30 +38,8 @@
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1153" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1156" uniqueCount="79">
   <si>
     <t>electricity generation sources in Spain</t>
   </si>
@@ -240,9 +218,6 @@
     <t>ELC_DERGAS_CC_E</t>
   </si>
   <si>
-    <t>ELC_GEO_E</t>
-  </si>
-  <si>
     <t>ELC_HYD_E</t>
   </si>
   <si>
@@ -270,9 +245,6 @@
     <t>Others</t>
   </si>
   <si>
-    <t>ELC_DST_TURB_E</t>
-  </si>
-  <si>
     <t>ELC_NGA_E</t>
   </si>
   <si>
@@ -289,6 +261,21 @@
   </si>
   <si>
     <t>ELC_CHP_NGA_TAP_N</t>
+  </si>
+  <si>
+    <t>ELC_CHP_NGA_CC_P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NET </t>
+  </si>
+  <si>
+    <t>DATI STORICI</t>
+  </si>
+  <si>
+    <t>STG_ELC_HYD_PUM_E</t>
+  </si>
+  <si>
+    <t>ELC_CHP_NGA_TURB_N</t>
   </si>
 </sst>
 </file>
@@ -803,7 +790,7 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -817,6 +804,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="43" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="20% - Colore 1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -7018,7 +7006,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Cal_Generation!$N$15</c:f>
+              <c:f>Cal_Generation!$B$42</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -7039,7 +7027,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>Cal_Generation!$O$14:$T$14</c:f>
+              <c:f>Cal_Generation!$C$41:$H$41</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -7066,7 +7054,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Cal_Generation!$O$15:$T$15</c:f>
+              <c:f>Cal_Generation!$C$42:$H$42</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -7102,7 +7090,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Cal_Generation!$N$16</c:f>
+              <c:f>Cal_Generation!$B$43</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -7123,7 +7111,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>Cal_Generation!$O$14:$T$14</c:f>
+              <c:f>Cal_Generation!$C$41:$H$41</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -7150,7 +7138,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Cal_Generation!$O$16:$T$16</c:f>
+              <c:f>Cal_Generation!$C$43:$H$43</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -7186,7 +7174,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Cal_Generation!$N$17</c:f>
+              <c:f>Cal_Generation!$B$44</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -7207,7 +7195,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>Cal_Generation!$O$14:$T$14</c:f>
+              <c:f>Cal_Generation!$C$41:$H$41</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -7234,7 +7222,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Cal_Generation!$O$17:$T$17</c:f>
+              <c:f>Cal_Generation!$C$44:$H$44</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -7270,7 +7258,7 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>Cal_Generation!$N$18</c:f>
+              <c:f>Cal_Generation!$B$45</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -7291,7 +7279,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>Cal_Generation!$O$14:$T$14</c:f>
+              <c:f>Cal_Generation!$C$41:$H$41</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -7318,7 +7306,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Cal_Generation!$O$18:$T$18</c:f>
+              <c:f>Cal_Generation!$C$45:$H$45</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -7354,7 +7342,7 @@
           <c:order val="4"/>
           <c:tx>
             <c:strRef>
-              <c:f>Cal_Generation!$N$19</c:f>
+              <c:f>Cal_Generation!$B$46</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -7375,7 +7363,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>Cal_Generation!$O$14:$T$14</c:f>
+              <c:f>Cal_Generation!$C$41:$H$41</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -7402,7 +7390,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Cal_Generation!$O$19:$T$19</c:f>
+              <c:f>Cal_Generation!$C$46:$H$46</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -7438,7 +7426,7 @@
           <c:order val="5"/>
           <c:tx>
             <c:strRef>
-              <c:f>Cal_Generation!$N$20</c:f>
+              <c:f>Cal_Generation!$B$47</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -7459,7 +7447,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>Cal_Generation!$O$14:$T$14</c:f>
+              <c:f>Cal_Generation!$C$41:$H$41</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -7486,7 +7474,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Cal_Generation!$O$20:$T$20</c:f>
+              <c:f>Cal_Generation!$C$47:$H$47</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -7522,7 +7510,7 @@
           <c:order val="6"/>
           <c:tx>
             <c:strRef>
-              <c:f>Cal_Generation!$N$21</c:f>
+              <c:f>Cal_Generation!$B$48</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -7545,7 +7533,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>Cal_Generation!$O$14:$T$14</c:f>
+              <c:f>Cal_Generation!$C$41:$H$41</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -7572,7 +7560,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Cal_Generation!$O$21:$T$21</c:f>
+              <c:f>Cal_Generation!$C$48:$H$48</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -7608,7 +7596,7 @@
           <c:order val="7"/>
           <c:tx>
             <c:strRef>
-              <c:f>Cal_Generation!$N$22</c:f>
+              <c:f>Cal_Generation!$B$49</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -7631,7 +7619,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>Cal_Generation!$O$14:$T$14</c:f>
+              <c:f>Cal_Generation!$C$41:$H$41</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -7658,7 +7646,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Cal_Generation!$O$22:$T$22</c:f>
+              <c:f>Cal_Generation!$C$49:$H$49</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -7694,7 +7682,7 @@
           <c:order val="8"/>
           <c:tx>
             <c:strRef>
-              <c:f>Cal_Generation!$N$23</c:f>
+              <c:f>Cal_Generation!$B$50</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -7717,7 +7705,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>Cal_Generation!$O$14:$T$14</c:f>
+              <c:f>Cal_Generation!$C$41:$H$41</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -7744,7 +7732,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Cal_Generation!$O$23:$T$23</c:f>
+              <c:f>Cal_Generation!$C$50:$H$50</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -8175,7 +8163,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Cal_Generation!$N$3</c:f>
+              <c:f>Cal_Generation!$B$30</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -8196,7 +8184,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>Cal_Generation!$O$2:$T$2</c:f>
+              <c:f>Cal_Generation!$C$29:$H$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -8223,27 +8211,27 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Cal_Generation!$O$3:$T$3</c:f>
+              <c:f>Cal_Generation!$C$30:$H$30</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>253.37450000000001</c:v>
+                  <c:v>266.70999999999998</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>90.021999999999991</c:v>
+                  <c:v>94.568830910453428</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>159.79</c:v>
+                  <c:v>159.79000000000011</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>132.37299999999999</c:v>
+                  <c:v>132.3730000000001</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>29.73500000000001</c:v>
+                  <c:v>29.734999999999989</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>11.856</c:v>
+                  <c:v>11.856000000000005</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8259,7 +8247,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Cal_Generation!$N$4</c:f>
+              <c:f>Cal_Generation!$B$31</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -8280,7 +8268,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>Cal_Generation!$O$2:$T$2</c:f>
+              <c:f>Cal_Generation!$C$29:$H$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -8307,27 +8295,27 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Cal_Generation!$O$4:$T$4</c:f>
+              <c:f>Cal_Generation!$C$31:$H$31</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>63.297359999999983</c:v>
+                  <c:v>66.628799999999998</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>56.642039999999987</c:v>
+                  <c:v>65.585520000000002</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>48.293819999999997</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>49.583160000000007</c:v>
+                  <c:v>49.583159999999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>36.217799999999997</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>30.513999999999999</c:v>
+                  <c:v>30.513999999999989</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8343,7 +8331,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Cal_Generation!$N$5</c:f>
+              <c:f>Cal_Generation!$B$32</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -8364,7 +8352,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>Cal_Generation!$O$2:$T$2</c:f>
+              <c:f>Cal_Generation!$C$29:$H$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -8391,27 +8379,27 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Cal_Generation!$O$5:$T$5</c:f>
+              <c:f>Cal_Generation!$C$32:$H$32</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>324.21258</c:v>
+                  <c:v>341.27640000000008</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>350.71539729176556</c:v>
+                  <c:v>341.46359999999999</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>182.28242640844772</c:v>
+                  <c:v>179.5431599999998</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>202.4825796126716</c:v>
+                  <c:v>198.37367999999961</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>327.79714840445774</c:v>
+                  <c:v>294.03450000000055</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>199.63436915522325</c:v>
+                  <c:v>182.13954350934227</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8427,7 +8415,7 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>Cal_Generation!$N$6</c:f>
+              <c:f>Cal_Generation!$B$33</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -8448,7 +8436,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>Cal_Generation!$O$2:$T$2</c:f>
+              <c:f>Cal_Generation!$C$29:$H$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -8475,27 +8463,27 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Cal_Generation!$O$6:$T$6</c:f>
+              <c:f>Cal_Generation!$C$33:$H$33</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>217.0010537154852</c:v>
+                  <c:v>198.37</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>218.93267982188161</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>200.18459503119641</c:v>
+                  <c:v>211.76298686064999</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>218.93267982188161</c:v>
+                  <c:v>196.4373620758995</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>218.93267982188161</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>215.941</c:v>
+                  <c:v>215.94100000000009</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8511,7 +8499,7 @@
           <c:order val="4"/>
           <c:tx>
             <c:strRef>
-              <c:f>Cal_Generation!$N$7</c:f>
+              <c:f>Cal_Generation!$B$34</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -8532,7 +8520,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>Cal_Generation!$O$2:$T$2</c:f>
+              <c:f>Cal_Generation!$C$29:$H$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -8559,27 +8547,27 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Cal_Generation!$O$7:$T$7</c:f>
+              <c:f>Cal_Generation!$C$34:$H$34</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>109.87920000000004</c:v>
+                  <c:v>109.87919999999998</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>163.83959999999993</c:v>
+                  <c:v>163.83959999999996</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>154.68839999999989</c:v>
+                  <c:v>154.68839999999997</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>132.95339999999996</c:v>
+                  <c:v>132.95339999999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>87.523920000000032</c:v>
+                  <c:v>87.523920000000004</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>161.65115999999998</c:v>
+                  <c:v>146.95559999999995</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8595,7 +8583,7 @@
           <c:order val="5"/>
           <c:tx>
             <c:strRef>
-              <c:f>Cal_Generation!$N$8</c:f>
+              <c:f>Cal_Generation!$B$35</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -8616,7 +8604,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>Cal_Generation!$O$2:$T$2</c:f>
+              <c:f>Cal_Generation!$C$29:$H$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -8643,21 +8631,21 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Cal_Generation!$O$8:$T$8</c:f>
+              <c:f>Cal_Generation!$C$35:$H$35</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>7.3906199999999993</c:v>
+                  <c:v>7.390620000000002</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>11.47751999999999</c:v>
+                  <c:v>11.47752</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>16.16976</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>16.42283999999999</c:v>
+                  <c:v>16.422840000000001</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>19.505970000000008</c:v>
@@ -8679,7 +8667,7 @@
           <c:order val="6"/>
           <c:tx>
             <c:strRef>
-              <c:f>Cal_Generation!$N$9</c:f>
+              <c:f>Cal_Generation!$B$36</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -8702,7 +8690,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>Cal_Generation!$O$2:$T$2</c:f>
+              <c:f>Cal_Generation!$C$29:$H$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -8729,27 +8717,27 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Cal_Generation!$O$9:$T$9</c:f>
+              <c:f>Cal_Generation!$C$36:$H$36</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>94.278000000000006</c:v>
+                  <c:v>94.277999999999992</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>151.411</c:v>
+                  <c:v>169.19500000000005</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>177.88750000000005</c:v>
+                  <c:v>177.88750000000007</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>174.78847091302663</c:v>
+                  <c:v>174.06850000000003</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>234.69599999999997</c:v>
+                  <c:v>218.00362155117051</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>234.69599999999997</c:v>
+                  <c:v>222.89844034123342</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8765,7 +8753,7 @@
           <c:order val="7"/>
           <c:tx>
             <c:strRef>
-              <c:f>Cal_Generation!$N$10</c:f>
+              <c:f>Cal_Generation!$B$37</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -8788,7 +8776,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>Cal_Generation!$O$2:$T$2</c:f>
+              <c:f>Cal_Generation!$C$29:$H$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -8815,7 +8803,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Cal_Generation!$O$10:$T$10</c:f>
+              <c:f>Cal_Generation!$C$37:$H$37</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -8829,13 +8817,13 @@
                   <c:v>47.397779999999997</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>51.652259999999991</c:v>
+                  <c:v>51.652259999999998</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>122.17266000000001</c:v>
+                  <c:v>122.17265999999989</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>199.34496000000007</c:v>
+                  <c:v>199.34496000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8851,7 +8839,7 @@
           <c:order val="8"/>
           <c:tx>
             <c:strRef>
-              <c:f>Cal_Generation!$N$11</c:f>
+              <c:f>Cal_Generation!$B$38</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -8874,7 +8862,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>Cal_Generation!$O$2:$T$2</c:f>
+              <c:f>Cal_Generation!$C$29:$H$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -8901,15 +8889,15 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Cal_Generation!$O$11:$T$11</c:f>
+              <c:f>Cal_Generation!$C$38:$H$38</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0.1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.7</c:v>
+                  <c:v>0.6</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -8918,10 +8906,10 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.39749999999999996</c:v>
+                  <c:v>0.29749999999999999</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.37624999999999997</c:v>
+                  <c:v>0.27625</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13872,16 +13860,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>50799</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>127000</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>211666</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>93132</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>258232</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>120649</xdr:rowOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>419099</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>86782</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -13908,16 +13896,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>239606</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>143933</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>222671</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>169332</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>118533</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>11430</xdr:rowOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>448732</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>36829</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -14263,13 +14251,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29F0DB51-B7D9-4ADC-AB31-B7E4C1F96502}">
   <dimension ref="A1:AD301"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="34.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="34.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -14283,7 +14271,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -14360,7 +14348,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -14453,7 +14441,7 @@
         <v>12.477599999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -14546,7 +14534,7 @@
         <v>32.842799999999997</v>
       </c>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -14639,7 +14627,7 @@
         <v>188.3844</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -14732,7 +14720,7 @@
         <v>196.3152</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -14825,7 +14813,7 @@
         <v>146.9556</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -14918,7 +14906,7 @@
         <v>2.8799999999999999E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -15011,7 +14999,7 @@
         <v>19.148399999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -15104,7 +15092,7 @@
         <v>6.0695999999999994</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -15197,7 +15185,7 @@
         <v>223.5204</v>
       </c>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -15290,7 +15278,7 @@
         <v>193.50719999999998</v>
       </c>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>4</v>
       </c>
@@ -15383,7 +15371,7 @@
         <v>16.344000000000001</v>
       </c>
     </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -15476,7 +15464,7 @@
         <v>0.87839999999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -15566,7 +15554,7 @@
         <v>1036.4724000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>4</v>
       </c>
@@ -15580,7 +15568,7 @@
         <v>5</v>
       </c>
       <c r="K16" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L16">
         <f>L15/3.6</f>
@@ -15659,7 +15647,7 @@
         <v>287.90900000000005</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>4</v>
       </c>
@@ -15673,7 +15661,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -15687,7 +15675,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>4</v>
       </c>
@@ -15701,7 +15689,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>4</v>
       </c>
@@ -15715,7 +15703,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>4</v>
       </c>
@@ -15729,7 +15717,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>4</v>
       </c>
@@ -15743,7 +15731,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>4</v>
       </c>
@@ -15757,7 +15745,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>4</v>
       </c>
@@ -15771,7 +15759,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>4</v>
       </c>
@@ -15785,7 +15773,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>4</v>
       </c>
@@ -15799,7 +15787,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>6</v>
       </c>
@@ -15813,7 +15801,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>6</v>
       </c>
@@ -15827,7 +15815,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>6</v>
       </c>
@@ -15841,7 +15829,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>6</v>
       </c>
@@ -15855,7 +15843,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>6</v>
       </c>
@@ -15869,7 +15857,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>6</v>
       </c>
@@ -15883,7 +15871,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>6</v>
       </c>
@@ -15897,7 +15885,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>6</v>
       </c>
@@ -15911,7 +15899,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>6</v>
       </c>
@@ -15925,7 +15913,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>6</v>
       </c>
@@ -15939,7 +15927,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>6</v>
       </c>
@@ -15953,7 +15941,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>6</v>
       </c>
@@ -15967,7 +15955,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>6</v>
       </c>
@@ -15981,7 +15969,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>6</v>
       </c>
@@ -15995,7 +15983,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>6</v>
       </c>
@@ -16009,7 +15997,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>6</v>
       </c>
@@ -16023,7 +16011,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>6</v>
       </c>
@@ -16037,7 +16025,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>6</v>
       </c>
@@ -16051,7 +16039,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>6</v>
       </c>
@@ -16065,7 +16053,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>6</v>
       </c>
@@ -16079,7 +16067,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>6</v>
       </c>
@@ -16093,7 +16081,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>6</v>
       </c>
@@ -16107,7 +16095,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>6</v>
       </c>
@@ -16121,7 +16109,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>6</v>
       </c>
@@ -16135,7 +16123,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>6</v>
       </c>
@@ -16149,7 +16137,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>7</v>
       </c>
@@ -16163,7 +16151,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>7</v>
       </c>
@@ -16177,7 +16165,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>7</v>
       </c>
@@ -16191,7 +16179,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>7</v>
       </c>
@@ -16205,7 +16193,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>7</v>
       </c>
@@ -16219,7 +16207,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>7</v>
       </c>
@@ -16233,7 +16221,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>7</v>
       </c>
@@ -16247,7 +16235,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>7</v>
       </c>
@@ -16261,7 +16249,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>7</v>
       </c>
@@ -16275,7 +16263,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>7</v>
       </c>
@@ -16289,7 +16277,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>7</v>
       </c>
@@ -16303,7 +16291,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>7</v>
       </c>
@@ -16317,7 +16305,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>7</v>
       </c>
@@ -16331,7 +16319,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>7</v>
       </c>
@@ -16345,7 +16333,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>7</v>
       </c>
@@ -16359,7 +16347,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>7</v>
       </c>
@@ -16373,7 +16361,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>7</v>
       </c>
@@ -16387,7 +16375,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>7</v>
       </c>
@@ -16401,7 +16389,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>7</v>
       </c>
@@ -16415,7 +16403,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>7</v>
       </c>
@@ -16429,7 +16417,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>7</v>
       </c>
@@ -16443,7 +16431,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>7</v>
       </c>
@@ -16457,7 +16445,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>7</v>
       </c>
@@ -16471,7 +16459,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>7</v>
       </c>
@@ -16485,7 +16473,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>7</v>
       </c>
@@ -16499,7 +16487,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>8</v>
       </c>
@@ -16513,7 +16501,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>8</v>
       </c>
@@ -16527,7 +16515,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>8</v>
       </c>
@@ -16541,7 +16529,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>8</v>
       </c>
@@ -16555,7 +16543,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>8</v>
       </c>
@@ -16569,7 +16557,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>8</v>
       </c>
@@ -16583,7 +16571,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>8</v>
       </c>
@@ -16597,7 +16585,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>8</v>
       </c>
@@ -16611,7 +16599,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>8</v>
       </c>
@@ -16625,7 +16613,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>8</v>
       </c>
@@ -16639,7 +16627,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>8</v>
       </c>
@@ -16653,7 +16641,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>8</v>
       </c>
@@ -16667,7 +16655,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>8</v>
       </c>
@@ -16681,7 +16669,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>8</v>
       </c>
@@ -16695,7 +16683,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>8</v>
       </c>
@@ -16709,7 +16697,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>8</v>
       </c>
@@ -16723,7 +16711,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>8</v>
       </c>
@@ -16737,7 +16725,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>8</v>
       </c>
@@ -16751,7 +16739,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>8</v>
       </c>
@@ -16765,7 +16753,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>8</v>
       </c>
@@ -16779,7 +16767,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>8</v>
       </c>
@@ -16793,7 +16781,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>8</v>
       </c>
@@ -16807,7 +16795,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>8</v>
       </c>
@@ -16821,7 +16809,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>8</v>
       </c>
@@ -16835,7 +16823,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>8</v>
       </c>
@@ -16849,7 +16837,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>9</v>
       </c>
@@ -16863,7 +16851,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>9</v>
       </c>
@@ -16877,7 +16865,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>9</v>
       </c>
@@ -16891,7 +16879,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>9</v>
       </c>
@@ -16905,7 +16893,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>9</v>
       </c>
@@ -16919,7 +16907,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>9</v>
       </c>
@@ -16933,7 +16921,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>9</v>
       </c>
@@ -16947,7 +16935,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>9</v>
       </c>
@@ -16961,7 +16949,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>9</v>
       </c>
@@ -16975,7 +16963,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>9</v>
       </c>
@@ -16989,7 +16977,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>9</v>
       </c>
@@ -17003,7 +16991,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>9</v>
       </c>
@@ -17017,7 +17005,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>9</v>
       </c>
@@ -17031,7 +17019,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>9</v>
       </c>
@@ -17045,7 +17033,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>9</v>
       </c>
@@ -17059,7 +17047,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>9</v>
       </c>
@@ -17073,7 +17061,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>9</v>
       </c>
@@ -17087,7 +17075,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>9</v>
       </c>
@@ -17101,7 +17089,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>9</v>
       </c>
@@ -17115,7 +17103,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>9</v>
       </c>
@@ -17129,7 +17117,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>9</v>
       </c>
@@ -17143,7 +17131,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>9</v>
       </c>
@@ -17157,7 +17145,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>9</v>
       </c>
@@ -17171,7 +17159,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>9</v>
       </c>
@@ -17185,7 +17173,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>9</v>
       </c>
@@ -17199,7 +17187,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>10</v>
       </c>
@@ -17210,7 +17198,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>10</v>
       </c>
@@ -17221,7 +17209,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>10</v>
       </c>
@@ -17232,7 +17220,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>10</v>
       </c>
@@ -17243,7 +17231,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>10</v>
       </c>
@@ -17254,7 +17242,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>10</v>
       </c>
@@ -17265,7 +17253,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>10</v>
       </c>
@@ -17276,7 +17264,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>10</v>
       </c>
@@ -17287,7 +17275,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>10</v>
       </c>
@@ -17298,7 +17286,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>10</v>
       </c>
@@ -17309,7 +17297,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>10</v>
       </c>
@@ -17320,7 +17308,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>10</v>
       </c>
@@ -17331,7 +17319,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>10</v>
       </c>
@@ -17342,7 +17330,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>10</v>
       </c>
@@ -17353,7 +17341,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>10</v>
       </c>
@@ -17364,7 +17352,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>10</v>
       </c>
@@ -17375,7 +17363,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>10</v>
       </c>
@@ -17386,7 +17374,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>10</v>
       </c>
@@ -17397,7 +17385,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>10</v>
       </c>
@@ -17408,7 +17396,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>10</v>
       </c>
@@ -17422,7 +17410,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>10</v>
       </c>
@@ -17436,7 +17424,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>10</v>
       </c>
@@ -17450,7 +17438,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>10</v>
       </c>
@@ -17464,7 +17452,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>10</v>
       </c>
@@ -17478,7 +17466,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>10</v>
       </c>
@@ -17492,7 +17480,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>11</v>
       </c>
@@ -17506,7 +17494,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>11</v>
       </c>
@@ -17520,7 +17508,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>11</v>
       </c>
@@ -17534,7 +17522,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>11</v>
       </c>
@@ -17548,7 +17536,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>11</v>
       </c>
@@ -17562,7 +17550,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>11</v>
       </c>
@@ -17576,7 +17564,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>11</v>
       </c>
@@ -17590,7 +17578,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>11</v>
       </c>
@@ -17604,7 +17592,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>11</v>
       </c>
@@ -17618,7 +17606,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>11</v>
       </c>
@@ -17632,7 +17620,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>11</v>
       </c>
@@ -17646,7 +17634,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>11</v>
       </c>
@@ -17660,7 +17648,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>11</v>
       </c>
@@ -17674,7 +17662,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>11</v>
       </c>
@@ -17688,7 +17676,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>11</v>
       </c>
@@ -17702,7 +17690,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>11</v>
       </c>
@@ -17716,7 +17704,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>11</v>
       </c>
@@ -17730,7 +17718,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>11</v>
       </c>
@@ -17744,7 +17732,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>11</v>
       </c>
@@ -17758,7 +17746,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>11</v>
       </c>
@@ -17772,7 +17760,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>11</v>
       </c>
@@ -17786,7 +17774,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>11</v>
       </c>
@@ -17800,7 +17788,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>11</v>
       </c>
@@ -17814,7 +17802,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>11</v>
       </c>
@@ -17828,7 +17816,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>11</v>
       </c>
@@ -17842,7 +17830,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>12</v>
       </c>
@@ -17856,7 +17844,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>12</v>
       </c>
@@ -17870,7 +17858,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>12</v>
       </c>
@@ -17884,7 +17872,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>12</v>
       </c>
@@ -17898,7 +17886,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>12</v>
       </c>
@@ -17912,7 +17900,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>12</v>
       </c>
@@ -17926,7 +17914,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>12</v>
       </c>
@@ -17940,7 +17928,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>12</v>
       </c>
@@ -17954,7 +17942,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>12</v>
       </c>
@@ -17968,7 +17956,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>12</v>
       </c>
@@ -17982,7 +17970,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>12</v>
       </c>
@@ -17996,7 +17984,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>12</v>
       </c>
@@ -18010,7 +17998,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>12</v>
       </c>
@@ -18024,7 +18012,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>12</v>
       </c>
@@ -18038,7 +18026,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>12</v>
       </c>
@@ -18052,7 +18040,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>12</v>
       </c>
@@ -18066,7 +18054,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>12</v>
       </c>
@@ -18080,7 +18068,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>12</v>
       </c>
@@ -18094,7 +18082,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>12</v>
       </c>
@@ -18108,7 +18096,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>12</v>
       </c>
@@ -18122,7 +18110,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>12</v>
       </c>
@@ -18136,7 +18124,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>12</v>
       </c>
@@ -18150,7 +18138,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>12</v>
       </c>
@@ -18164,7 +18152,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>12</v>
       </c>
@@ -18178,7 +18166,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>12</v>
       </c>
@@ -18192,7 +18180,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>13</v>
       </c>
@@ -18206,7 +18194,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>13</v>
       </c>
@@ -18220,7 +18208,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>13</v>
       </c>
@@ -18234,7 +18222,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>13</v>
       </c>
@@ -18248,7 +18236,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>13</v>
       </c>
@@ -18262,7 +18250,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>13</v>
       </c>
@@ -18276,7 +18264,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>13</v>
       </c>
@@ -18290,7 +18278,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>13</v>
       </c>
@@ -18304,7 +18292,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>13</v>
       </c>
@@ -18318,7 +18306,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>13</v>
       </c>
@@ -18332,7 +18320,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>13</v>
       </c>
@@ -18346,7 +18334,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>13</v>
       </c>
@@ -18360,7 +18348,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>13</v>
       </c>
@@ -18374,7 +18362,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>13</v>
       </c>
@@ -18388,7 +18376,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>13</v>
       </c>
@@ -18402,7 +18390,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>13</v>
       </c>
@@ -18416,7 +18404,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>13</v>
       </c>
@@ -18430,7 +18418,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="219" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>13</v>
       </c>
@@ -18444,7 +18432,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>13</v>
       </c>
@@ -18458,7 +18446,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>13</v>
       </c>
@@ -18472,7 +18460,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>13</v>
       </c>
@@ -18486,7 +18474,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>13</v>
       </c>
@@ -18500,7 +18488,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>13</v>
       </c>
@@ -18514,7 +18502,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>13</v>
       </c>
@@ -18528,7 +18516,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>13</v>
       </c>
@@ -18542,7 +18530,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>14</v>
       </c>
@@ -18556,7 +18544,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>14</v>
       </c>
@@ -18570,7 +18558,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>14</v>
       </c>
@@ -18584,7 +18572,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="230" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>14</v>
       </c>
@@ -18598,7 +18586,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>14</v>
       </c>
@@ -18612,7 +18600,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>14</v>
       </c>
@@ -18626,7 +18614,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>14</v>
       </c>
@@ -18640,7 +18628,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>14</v>
       </c>
@@ -18654,7 +18642,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="235" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>14</v>
       </c>
@@ -18668,7 +18656,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="236" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>14</v>
       </c>
@@ -18682,7 +18670,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="237" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>14</v>
       </c>
@@ -18696,7 +18684,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="238" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>14</v>
       </c>
@@ -18710,7 +18698,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="239" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>14</v>
       </c>
@@ -18724,7 +18712,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="240" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>14</v>
       </c>
@@ -18738,7 +18726,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="241" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>14</v>
       </c>
@@ -18752,7 +18740,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="242" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>14</v>
       </c>
@@ -18766,7 +18754,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="243" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>14</v>
       </c>
@@ -18780,7 +18768,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="244" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>14</v>
       </c>
@@ -18794,7 +18782,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="245" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>14</v>
       </c>
@@ -18808,7 +18796,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>14</v>
       </c>
@@ -18822,7 +18810,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="247" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>14</v>
       </c>
@@ -18836,7 +18824,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="248" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>14</v>
       </c>
@@ -18850,7 +18838,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="249" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>14</v>
       </c>
@@ -18864,7 +18852,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="250" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>14</v>
       </c>
@@ -18878,7 +18866,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="251" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>14</v>
       </c>
@@ -18892,7 +18880,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>15</v>
       </c>
@@ -18903,7 +18891,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>15</v>
       </c>
@@ -18914,7 +18902,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>15</v>
       </c>
@@ -18925,7 +18913,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>15</v>
       </c>
@@ -18936,7 +18924,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>15</v>
       </c>
@@ -18947,7 +18935,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>15</v>
       </c>
@@ -18958,7 +18946,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>15</v>
       </c>
@@ -18972,7 +18960,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="259" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>15</v>
       </c>
@@ -18986,7 +18974,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="260" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>15</v>
       </c>
@@ -19000,7 +18988,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="261" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>15</v>
       </c>
@@ -19014,7 +19002,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="262" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>15</v>
       </c>
@@ -19028,7 +19016,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="263" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>15</v>
       </c>
@@ -19042,7 +19030,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="264" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>15</v>
       </c>
@@ -19056,7 +19044,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="265" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>15</v>
       </c>
@@ -19070,7 +19058,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="266" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>15</v>
       </c>
@@ -19084,7 +19072,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="267" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>15</v>
       </c>
@@ -19098,7 +19086,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="268" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>15</v>
       </c>
@@ -19112,7 +19100,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="269" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>15</v>
       </c>
@@ -19126,7 +19114,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="270" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>15</v>
       </c>
@@ -19140,7 +19128,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="271" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>15</v>
       </c>
@@ -19154,7 +19142,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="272" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>15</v>
       </c>
@@ -19168,7 +19156,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="273" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>15</v>
       </c>
@@ -19182,7 +19170,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="274" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>15</v>
       </c>
@@ -19196,7 +19184,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="275" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>15</v>
       </c>
@@ -19210,7 +19198,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="276" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>15</v>
       </c>
@@ -19224,7 +19212,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="277" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>16</v>
       </c>
@@ -19235,7 +19223,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="278" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>16</v>
       </c>
@@ -19246,7 +19234,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="279" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>16</v>
       </c>
@@ -19257,7 +19245,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="280" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>16</v>
       </c>
@@ -19268,7 +19256,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="281" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>16</v>
       </c>
@@ -19282,7 +19270,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="282" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>16</v>
       </c>
@@ -19296,7 +19284,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="283" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>16</v>
       </c>
@@ -19310,7 +19298,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="284" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>16</v>
       </c>
@@ -19324,7 +19312,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="285" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>16</v>
       </c>
@@ -19338,7 +19326,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="286" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>16</v>
       </c>
@@ -19352,7 +19340,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="287" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>16</v>
       </c>
@@ -19366,7 +19354,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="288" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>16</v>
       </c>
@@ -19380,7 +19368,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="289" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>16</v>
       </c>
@@ -19394,7 +19382,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="290" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>16</v>
       </c>
@@ -19408,7 +19396,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="291" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>16</v>
       </c>
@@ -19419,7 +19407,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="292" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>16</v>
       </c>
@@ -19433,7 +19421,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="293" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>16</v>
       </c>
@@ -19447,7 +19435,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="294" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>16</v>
       </c>
@@ -19461,7 +19449,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="295" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>16</v>
       </c>
@@ -19475,7 +19463,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="296" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>16</v>
       </c>
@@ -19489,7 +19477,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="297" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>16</v>
       </c>
@@ -19503,7 +19491,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="298" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>16</v>
       </c>
@@ -19517,7 +19505,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="299" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>16</v>
       </c>
@@ -19531,7 +19519,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="300" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>16</v>
       </c>
@@ -19545,7 +19533,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="301" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>16</v>
       </c>
@@ -19571,12 +19559,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DCCDE7F-90D3-4824-8130-ABEE2C3BAACE}">
   <dimension ref="A1:AB51"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="1" max="1" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>19</v>
       </c>
@@ -19590,7 +19578,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>20</v>
       </c>
@@ -19661,7 +19649,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -19754,7 +19742,7 @@
         <v>51.674399999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -19847,7 +19835,7 @@
         <v>-88.491599999999991</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -19940,7 +19928,7 @@
         <v>-36.817199999999993</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -19954,7 +19942,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -19968,7 +19956,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -19982,7 +19970,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>20</v>
       </c>
@@ -19996,7 +19984,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>20</v>
       </c>
@@ -20010,7 +19998,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -20024,7 +20012,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -20038,7 +20026,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -20052,7 +20040,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>20</v>
       </c>
@@ -20066,7 +20054,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>20</v>
       </c>
@@ -20080,7 +20068,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>20</v>
       </c>
@@ -20094,7 +20082,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -20108,7 +20096,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -20122,7 +20110,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -20136,7 +20124,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>20</v>
       </c>
@@ -20150,7 +20138,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -20164,7 +20152,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>20</v>
       </c>
@@ -20178,7 +20166,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>20</v>
       </c>
@@ -20192,7 +20180,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>20</v>
       </c>
@@ -20206,7 +20194,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>20</v>
       </c>
@@ -20220,7 +20208,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>20</v>
       </c>
@@ -20234,7 +20222,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>21</v>
       </c>
@@ -20248,7 +20236,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>21</v>
       </c>
@@ -20262,7 +20250,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>21</v>
       </c>
@@ -20276,7 +20264,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>21</v>
       </c>
@@ -20290,7 +20278,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>21</v>
       </c>
@@ -20304,7 +20292,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>21</v>
       </c>
@@ -20318,7 +20306,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>21</v>
       </c>
@@ -20332,7 +20320,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>21</v>
       </c>
@@ -20346,7 +20334,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>21</v>
       </c>
@@ -20360,7 +20348,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>21</v>
       </c>
@@ -20374,7 +20362,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>21</v>
       </c>
@@ -20388,7 +20376,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>21</v>
       </c>
@@ -20402,7 +20390,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>21</v>
       </c>
@@ -20416,7 +20404,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>21</v>
       </c>
@@ -20430,7 +20418,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>21</v>
       </c>
@@ -20444,7 +20432,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>21</v>
       </c>
@@ -20458,7 +20446,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>21</v>
       </c>
@@ -20472,7 +20460,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>21</v>
       </c>
@@ -20486,7 +20474,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>21</v>
       </c>
@@ -20500,7 +20488,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>21</v>
       </c>
@@ -20514,7 +20502,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>21</v>
       </c>
@@ -20528,7 +20516,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>21</v>
       </c>
@@ -20542,7 +20530,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>21</v>
       </c>
@@ -20556,7 +20544,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>21</v>
       </c>
@@ -20570,7 +20558,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>21</v>
       </c>
@@ -20593,14 +20581,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F31AC804-BBB6-49B0-9019-74125F94880C}">
   <dimension ref="A1:AA97"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="42.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.28515625" customWidth="1"/>
-    <col min="9" max="9" width="11.42578125" customWidth="1"/>
+    <col min="1" max="1" width="42.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.33203125" customWidth="1"/>
+    <col min="9" max="9" width="11.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>24</v>
       </c>
@@ -20614,7 +20602,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -20682,7 +20670,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -20771,7 +20759,7 @@
         <v>5.43</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -20860,7 +20848,7 @@
         <v>6.24</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -20949,7 +20937,7 @@
         <v>24.222999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -21038,7 +21026,7 @@
         <v>1.22</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -21052,7 +21040,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -21066,7 +21054,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -21080,7 +21068,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -21094,7 +21082,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -21108,7 +21096,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -21122,7 +21110,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>4</v>
       </c>
@@ -21136,7 +21124,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -21150,7 +21138,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -21164,7 +21152,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>4</v>
       </c>
@@ -21178,7 +21166,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>4</v>
       </c>
@@ -21192,7 +21180,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -21206,7 +21194,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>4</v>
       </c>
@@ -21220,7 +21208,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>4</v>
       </c>
@@ -21234,7 +21222,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>4</v>
       </c>
@@ -21248,7 +21236,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>4</v>
       </c>
@@ -21262,7 +21250,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>4</v>
       </c>
@@ -21276,7 +21264,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>4</v>
       </c>
@@ -21290,7 +21278,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>4</v>
       </c>
@@ -21304,7 +21292,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>6</v>
       </c>
@@ -21318,7 +21306,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>6</v>
       </c>
@@ -21332,7 +21320,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>6</v>
       </c>
@@ -21346,7 +21334,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>6</v>
       </c>
@@ -21360,7 +21348,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>6</v>
       </c>
@@ -21374,7 +21362,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>6</v>
       </c>
@@ -21388,7 +21376,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>6</v>
       </c>
@@ -21402,7 +21390,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>6</v>
       </c>
@@ -21416,7 +21404,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>6</v>
       </c>
@@ -21430,7 +21418,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>6</v>
       </c>
@@ -21444,7 +21432,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>6</v>
       </c>
@@ -21458,7 +21446,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>6</v>
       </c>
@@ -21472,7 +21460,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>6</v>
       </c>
@@ -21486,7 +21474,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>6</v>
       </c>
@@ -21500,7 +21488,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>6</v>
       </c>
@@ -21514,7 +21502,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>6</v>
       </c>
@@ -21528,7 +21516,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>6</v>
       </c>
@@ -21542,7 +21530,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>6</v>
       </c>
@@ -21556,7 +21544,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>6</v>
       </c>
@@ -21570,7 +21558,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>6</v>
       </c>
@@ -21584,7 +21572,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>6</v>
       </c>
@@ -21598,7 +21586,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>6</v>
       </c>
@@ -21612,7 +21600,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>6</v>
       </c>
@@ -21626,7 +21614,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>6</v>
       </c>
@@ -21640,7 +21628,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>7</v>
       </c>
@@ -21654,7 +21642,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>7</v>
       </c>
@@ -21668,7 +21656,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>7</v>
       </c>
@@ -21682,7 +21670,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>7</v>
       </c>
@@ -21696,7 +21684,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>7</v>
       </c>
@@ -21710,7 +21698,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>7</v>
       </c>
@@ -21724,7 +21712,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>7</v>
       </c>
@@ -21738,7 +21726,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>7</v>
       </c>
@@ -21752,7 +21740,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>7</v>
       </c>
@@ -21766,7 +21754,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>7</v>
       </c>
@@ -21780,7 +21768,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>7</v>
       </c>
@@ -21794,7 +21782,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>7</v>
       </c>
@@ -21808,7 +21796,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>7</v>
       </c>
@@ -21822,7 +21810,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>7</v>
       </c>
@@ -21836,7 +21824,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>7</v>
       </c>
@@ -21850,7 +21838,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>7</v>
       </c>
@@ -21864,7 +21852,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>7</v>
       </c>
@@ -21878,7 +21866,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>7</v>
       </c>
@@ -21892,7 +21880,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>7</v>
       </c>
@@ -21906,7 +21894,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>7</v>
       </c>
@@ -21920,7 +21908,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>7</v>
       </c>
@@ -21934,7 +21922,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>7</v>
       </c>
@@ -21948,7 +21936,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>7</v>
       </c>
@@ -21962,7 +21950,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>7</v>
       </c>
@@ -21976,7 +21964,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>25</v>
       </c>
@@ -21990,7 +21978,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>25</v>
       </c>
@@ -22004,7 +21992,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>25</v>
       </c>
@@ -22018,7 +22006,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>25</v>
       </c>
@@ -22032,7 +22020,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>25</v>
       </c>
@@ -22046,7 +22034,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>25</v>
       </c>
@@ -22060,7 +22048,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>25</v>
       </c>
@@ -22074,7 +22062,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>25</v>
       </c>
@@ -22088,7 +22076,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>25</v>
       </c>
@@ -22102,7 +22090,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>25</v>
       </c>
@@ -22116,7 +22104,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>25</v>
       </c>
@@ -22130,7 +22118,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>25</v>
       </c>
@@ -22144,7 +22132,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>25</v>
       </c>
@@ -22158,7 +22146,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>25</v>
       </c>
@@ -22172,7 +22160,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>25</v>
       </c>
@@ -22186,7 +22174,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>25</v>
       </c>
@@ -22200,7 +22188,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>25</v>
       </c>
@@ -22214,7 +22202,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>25</v>
       </c>
@@ -22228,7 +22216,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>25</v>
       </c>
@@ -22242,7 +22230,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>25</v>
       </c>
@@ -22256,7 +22244,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>25</v>
       </c>
@@ -22270,7 +22258,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>25</v>
       </c>
@@ -22284,7 +22272,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>25</v>
       </c>
@@ -22298,7 +22286,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>25</v>
       </c>
@@ -22321,24 +22309,24 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2DE3364-19EF-4DBB-9C60-BFBDC0F3AE34}">
   <dimension ref="A1:AD39"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" customWidth="1"/>
-    <col min="3" max="3" width="13.7109375" customWidth="1"/>
+    <col min="1" max="1" width="10.88671875" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" customWidth="1"/>
+    <col min="3" max="3" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>29</v>
       </c>
@@ -22421,7 +22409,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1990</v>
       </c>
@@ -22532,7 +22520,7 @@
         <v>253.74799999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1991</v>
       </c>
@@ -22543,7 +22531,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1992</v>
       </c>
@@ -22561,7 +22549,7 @@
         <v>754.71479999999997</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1993</v>
       </c>
@@ -22579,7 +22567,7 @@
         <v>797.41800000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>1994</v>
       </c>
@@ -22597,7 +22585,7 @@
         <v>831.71879999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>1995</v>
       </c>
@@ -22615,7 +22603,7 @@
         <v>861.99119999999994</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>1996</v>
       </c>
@@ -22633,7 +22621,7 @@
         <v>910.35719999999992</v>
       </c>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>1997</v>
       </c>
@@ -22651,7 +22639,7 @@
         <v>960.41160000000002</v>
       </c>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>1998</v>
       </c>
@@ -22669,7 +22657,7 @@
         <v>975.79799999999989</v>
       </c>
     </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>1999</v>
       </c>
@@ -22687,7 +22675,7 @@
         <v>985.77719999999999</v>
       </c>
     </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2000</v>
       </c>
@@ -22705,7 +22693,7 @@
         <v>996.87239999999997</v>
       </c>
     </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>2001</v>
       </c>
@@ -22723,7 +22711,7 @@
         <v>943.4556</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>2002</v>
       </c>
@@ -22741,7 +22729,7 @@
         <v>956.85839999999985</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>2003</v>
       </c>
@@ -22759,7 +22747,7 @@
         <v>942.22439999999995</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>2004</v>
       </c>
@@ -22777,7 +22765,7 @@
         <v>938.46600000000001</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>2005</v>
       </c>
@@ -22795,7 +22783,7 @@
         <v>907.8696000000001</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>2006</v>
       </c>
@@ -22813,7 +22801,7 @@
         <v>896.21999999999991</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>2007</v>
       </c>
@@ -22831,7 +22819,7 @@
         <v>915.36839999999995</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>2008</v>
       </c>
@@ -22849,7 +22837,7 @@
         <v>920.58839999999998</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>2009</v>
       </c>
@@ -22867,7 +22855,7 @@
         <v>939.85919999999999</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>2010</v>
       </c>
@@ -22885,7 +22873,7 @@
         <v>935.84879999999998</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>2011</v>
       </c>
@@ -22903,7 +22891,7 @@
         <v>919.18439999999998</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>2012</v>
       </c>
@@ -22921,7 +22909,7 @@
         <v>867.67920000000004</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>2013</v>
       </c>
@@ -22939,7 +22927,7 @@
         <v>894.36959999999999</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>2014</v>
       </c>
@@ -22957,7 +22945,7 @@
         <v>891.07560000000001</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>2015</v>
       </c>
@@ -22975,7 +22963,7 @@
         <v>890.85599999999999</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>2016</v>
       </c>
@@ -22993,7 +22981,7 @@
         <v>913.49279999999999</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>2017</v>
       </c>
@@ -23004,7 +22992,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>2018</v>
       </c>
@@ -23015,7 +23003,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>2019</v>
       </c>
@@ -23026,7 +23014,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>2020</v>
       </c>
@@ -23037,7 +23025,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>2021</v>
       </c>
@@ -23048,7 +23036,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>2022</v>
       </c>
@@ -23059,7 +23047,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>2023</v>
       </c>
@@ -23070,7 +23058,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>2024</v>
       </c>
@@ -23090,12 +23078,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB763C44-0720-4A5D-A285-14210CC2296D}">
   <dimension ref="A2:D7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.28515625" customWidth="1"/>
+    <col min="1" max="1" width="13.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>32</v>
       </c>
@@ -23106,7 +23094,7 @@
         <v>3.5999999999999999E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>31</v>
       </c>
@@ -23114,7 +23102,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>15.5</v>
       </c>
@@ -23123,7 +23111,7 @@
         <v>4305.5555555555557</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -23131,7 +23119,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>3971</v>
       </c>
@@ -23152,14 +23140,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDEB2676-8085-4D3C-98E7-5BF41F1AF8D5}">
   <dimension ref="A1:W49"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.85546875" customWidth="1"/>
-    <col min="2" max="11" width="7.7109375" customWidth="1"/>
-    <col min="14" max="14" width="18.42578125" customWidth="1"/>
+    <col min="1" max="1" width="11.88671875" customWidth="1"/>
+    <col min="2" max="11" width="7.6640625" customWidth="1"/>
+    <col min="14" max="14" width="18.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>34</v>
       </c>
@@ -23194,7 +23182,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>35</v>
       </c>
@@ -23256,7 +23244,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>35</v>
       </c>
@@ -23330,9 +23318,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B4" t="s">
         <v>49</v>
@@ -23404,9 +23392,9 @@
         <v>1193.4002561548721</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B5" t="s">
         <v>50</v>
@@ -23478,7 +23466,7 @@
         <v>366.57755802738978</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>36</v>
       </c>
@@ -23552,7 +23540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>36</v>
       </c>
@@ -23626,7 +23614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -23700,7 +23688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>37</v>
       </c>
@@ -23774,7 +23762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>37</v>
       </c>
@@ -23848,7 +23836,7 @@
         <v>2417.2778962392399</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>37</v>
       </c>
@@ -23922,7 +23910,7 @@
         <v>3622.2536445412229</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>38</v>
       </c>
@@ -23996,7 +23984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>38</v>
       </c>
@@ -24070,7 +24058,7 @@
         <v>343.51136363636368</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>38</v>
       </c>
@@ -24144,7 +24132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>39</v>
       </c>
@@ -24218,7 +24206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>39</v>
       </c>
@@ -24261,7 +24249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>39</v>
       </c>
@@ -24296,7 +24284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -24331,7 +24319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>40</v>
       </c>
@@ -24369,7 +24357,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>40</v>
       </c>
@@ -24404,7 +24392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>41</v>
       </c>
@@ -24466,7 +24454,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>41</v>
       </c>
@@ -24540,7 +24528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>41</v>
       </c>
@@ -24614,7 +24602,7 @@
         <v>0.3435113636363637</v>
       </c>
     </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>42</v>
       </c>
@@ -24688,7 +24676,7 @@
         <v>7.5995093549627253</v>
       </c>
     </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>42</v>
       </c>
@@ -24723,7 +24711,7 @@
         <v>2417.2778962392399</v>
       </c>
     </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>42</v>
       </c>
@@ -24758,7 +24746,7 @@
         <v>23.26791557877343</v>
       </c>
     </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>43</v>
       </c>
@@ -24793,7 +24781,7 @@
         <v>8.3938141495607681</v>
       </c>
     </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>43</v>
       </c>
@@ -24828,7 +24816,7 @@
         <v>3622.2536445412229</v>
       </c>
     </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>43</v>
       </c>
@@ -24863,7 +24851,7 @@
         <v>34.866612621252422</v>
       </c>
     </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>44</v>
       </c>
@@ -24898,7 +24886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>44</v>
       </c>
@@ -24933,7 +24921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>44</v>
       </c>
@@ -24968,7 +24956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>45</v>
       </c>
@@ -25003,7 +24991,7 @@
         <v>3.497727272727273</v>
       </c>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>45</v>
       </c>
@@ -25038,7 +25026,7 @@
         <v>343.51136363636368</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>45</v>
       </c>
@@ -25073,7 +25061,7 @@
         <v>13.731818181818181</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>46</v>
       </c>
@@ -25108,7 +25096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>46</v>
       </c>
@@ -25143,7 +25131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>46</v>
       </c>
@@ -25178,7 +25166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>47</v>
       </c>
@@ -25213,7 +25201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>47</v>
       </c>
@@ -25248,7 +25236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>47</v>
       </c>
@@ -25283,7 +25271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.3">
       <c r="N45">
         <v>2007</v>
       </c>
@@ -25303,7 +25291,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.3">
       <c r="M46" t="s">
         <v>4</v>
       </c>
@@ -25326,7 +25314,7 @@
         <v>5.43</v>
       </c>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.3">
       <c r="M47" t="s">
         <v>6</v>
       </c>
@@ -25349,7 +25337,7 @@
         <v>6.24</v>
       </c>
     </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.3">
       <c r="M48" t="s">
         <v>7</v>
       </c>
@@ -25372,7 +25360,7 @@
         <v>24.222999999999999</v>
       </c>
     </row>
-    <row r="49" spans="13:19" x14ac:dyDescent="0.25">
+    <row r="49" spans="13:19" x14ac:dyDescent="0.3">
       <c r="M49" t="s">
         <v>25</v>
       </c>
@@ -25403,22 +25391,23 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95A32E31-20CB-4056-864B-0FCE4F4387EC}">
-  <dimension ref="A1:AB26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:K68"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="9.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>34</v>
       </c>
@@ -25453,7 +25442,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>35</v>
       </c>
@@ -25461,16 +25450,16 @@
         <v>56</v>
       </c>
       <c r="C2">
-        <v>7.3906199999999993</v>
+        <v>7.390620000000002</v>
       </c>
       <c r="D2">
-        <v>11.47751999999999</v>
+        <v>11.47752</v>
       </c>
       <c r="E2">
         <v>16.16976</v>
       </c>
       <c r="F2">
-        <v>16.42283999999999</v>
+        <v>16.422840000000001</v>
       </c>
       <c r="G2">
         <v>19.505970000000008</v>
@@ -25479,60 +25468,21 @@
         <v>18.19098</v>
       </c>
       <c r="I2">
-        <v>21.374999999999989</v>
+        <v>21.375</v>
       </c>
       <c r="J2">
-        <v>22.562499999999989</v>
+        <v>22.5625</v>
       </c>
       <c r="K2">
-        <v>5.7933717951093033</v>
-      </c>
-      <c r="O2">
-        <v>2007</v>
-      </c>
-      <c r="P2">
-        <v>2010</v>
-      </c>
-      <c r="Q2">
-        <v>2014</v>
-      </c>
-      <c r="R2">
-        <v>2018</v>
-      </c>
-      <c r="S2">
-        <v>2022</v>
-      </c>
-      <c r="T2">
-        <v>2024</v>
-      </c>
-      <c r="V2" t="s">
-        <v>73</v>
-      </c>
-      <c r="W2">
-        <v>2007</v>
-      </c>
-      <c r="X2">
-        <v>2010</v>
-      </c>
-      <c r="Y2">
-        <v>2014</v>
-      </c>
-      <c r="Z2">
-        <v>2018</v>
-      </c>
-      <c r="AA2">
-        <v>2022</v>
-      </c>
-      <c r="AB2">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+        <v>55.000000000000043</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="B3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -25541,84 +25491,30 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>2.739266408448001</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>5.4785328168960046</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>7.502977506816003</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>8.7534737579519977</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>5.8046240131200006</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>6.4181787496703997</v>
       </c>
       <c r="K3">
-        <v>49.206628204890713</v>
-      </c>
-      <c r="N3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O3">
-        <f>SUM(C8,C7)</f>
-        <v>253.37450000000001</v>
-      </c>
-      <c r="P3">
-        <f t="shared" ref="P3:T3" si="0">SUM(D8,D7)</f>
-        <v>90.021999999999991</v>
-      </c>
-      <c r="Q3">
-        <f t="shared" si="0"/>
-        <v>159.79</v>
-      </c>
-      <c r="R3">
-        <f t="shared" si="0"/>
-        <v>132.37299999999999</v>
-      </c>
-      <c r="S3">
-        <f t="shared" si="0"/>
-        <v>29.73500000000001</v>
-      </c>
-      <c r="T3">
-        <f t="shared" si="0"/>
-        <v>11.856</v>
-      </c>
-      <c r="V3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W3" s="5">
-        <f>(O3-O15)/O15</f>
-        <v>-4.9985752101565036E-2</v>
-      </c>
-      <c r="X3" s="5">
-        <f t="shared" ref="X3:AB11" si="1">(P3-P15)/P15</f>
-        <v>-5.0028070086574131E-2</v>
-      </c>
-      <c r="Y3" s="5">
-        <f t="shared" si="1"/>
-        <v>-2.0065987170524043E-2</v>
-      </c>
-      <c r="Z3" s="5">
-        <f t="shared" si="1"/>
-        <v>-5.0256282214645759E-2</v>
-      </c>
-      <c r="AA3" s="5">
-        <f t="shared" si="1"/>
-        <v>-5.0169937646938195E-2</v>
-      </c>
-      <c r="AB3" s="5">
-        <f t="shared" si="1"/>
-        <v>-4.9817272552413853E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+        <v>6.1329941142336013</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="B4" t="s">
         <v>57</v>
@@ -25630,82 +25526,28 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>2.7392664084480001</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>4.1088996126720003</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>3.9301941830400011</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>3.5727833237760018</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>8.9319583094400006</v>
+        <v>30.61675114629714</v>
       </c>
       <c r="J4">
-        <v>9.8254854576000028</v>
+        <v>32.152990487039993</v>
       </c>
       <c r="K4">
-        <v>6.5082742297919998</v>
-      </c>
-      <c r="N4" t="s">
-        <v>6</v>
-      </c>
-      <c r="O4">
-        <f>SUM(C16)</f>
-        <v>63.297359999999983</v>
-      </c>
-      <c r="P4">
-        <f t="shared" ref="P4:T4" si="2">SUM(D16)</f>
-        <v>56.642039999999987</v>
-      </c>
-      <c r="Q4">
-        <f t="shared" si="2"/>
-        <v>48.293819999999997</v>
-      </c>
-      <c r="R4">
-        <f t="shared" si="2"/>
-        <v>49.583160000000007</v>
-      </c>
-      <c r="S4">
-        <f t="shared" si="2"/>
-        <v>36.217799999999997</v>
-      </c>
-      <c r="T4">
-        <f t="shared" si="2"/>
-        <v>30.513999999999999</v>
-      </c>
-      <c r="V4" t="s">
-        <v>6</v>
-      </c>
-      <c r="W4" s="5">
-        <f t="shared" ref="W4:W11" si="3">(O4-O16)/O16</f>
-        <v>-5.0000000000000225E-2</v>
-      </c>
-      <c r="X4" s="5">
-        <f t="shared" si="1"/>
-        <v>-5.0000000000000169E-2</v>
-      </c>
-      <c r="Y4" s="5">
-        <f t="shared" si="1"/>
-        <v>-5.0000000000000058E-2</v>
-      </c>
-      <c r="Z4" s="5">
-        <f t="shared" si="1"/>
-        <v>-4.9999999999999843E-2</v>
-      </c>
-      <c r="AA4" s="5">
-        <f t="shared" si="1"/>
-        <v>-5.0000000000000142E-2</v>
-      </c>
-      <c r="AB4" s="5">
-        <f t="shared" si="1"/>
-        <v>-7.0907474393169814E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+        <v>17.732142812159999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>37</v>
       </c>
@@ -25725,78 +25567,24 @@
         <v>11.923865542655999</v>
       </c>
       <c r="G5">
-        <v>16.332731711133619</v>
+        <v>16.14149032265469</v>
       </c>
       <c r="H5">
-        <v>16.092006761079251</v>
+        <v>14.967744398208</v>
       </c>
       <c r="I5">
-        <v>18.532732622619921</v>
+        <v>12.63359344032</v>
       </c>
       <c r="J5">
-        <v>18.138458556928249</v>
+        <v>12.63359344032</v>
       </c>
       <c r="K5">
-        <v>7.1341377993215982</v>
-      </c>
-      <c r="N5" t="s">
-        <v>7</v>
-      </c>
-      <c r="O5" cm="1">
-        <f t="array" ref="O5">SUM(C4+C5:C6,C14:C15,C17:C18)</f>
-        <v>324.21258</v>
-      </c>
-      <c r="P5" cm="1">
-        <f t="array" ref="P5">SUM(D4+D5:D6,D14:D15,D17:D18)</f>
-        <v>350.71539729176556</v>
-      </c>
-      <c r="Q5" cm="1">
-        <f t="array" ref="Q5">SUM(E4+E5:E6,E14:E15,E17:E18)</f>
-        <v>182.28242640844772</v>
-      </c>
-      <c r="R5" cm="1">
-        <f t="array" ref="R5">SUM(F4+F5:F6,F14:F15,F17:F18)</f>
-        <v>202.4825796126716</v>
-      </c>
-      <c r="S5" cm="1">
-        <f t="array" ref="S5">SUM(G4+G5:G6,G14:G15,G17:G18)</f>
-        <v>327.79714840445774</v>
-      </c>
-      <c r="T5" cm="1">
-        <f t="array" ref="T5">SUM(H4+H5:H6,H14:H15,H17:H18)</f>
-        <v>199.63436915522325</v>
-      </c>
-      <c r="V5" t="s">
-        <v>7</v>
-      </c>
-      <c r="W5" s="5">
-        <f t="shared" si="3"/>
-        <v>-4.9999999999999899E-2</v>
-      </c>
-      <c r="X5" s="5">
-        <f t="shared" si="1"/>
-        <v>2.7094534503137584E-2</v>
-      </c>
-      <c r="Y5" s="5">
-        <f>(Q5-Q17)/Q17</f>
-        <v>7.1097821921179666E-2</v>
-      </c>
-      <c r="Z5" s="5">
-        <f t="shared" si="1"/>
-        <v>-3.032271906213559E-2</v>
-      </c>
-      <c r="AA5" s="5">
-        <f t="shared" si="1"/>
-        <v>5.9084192447603483E-2</v>
-      </c>
-      <c r="AB5" s="5">
-        <f t="shared" si="1"/>
-        <v>5.9718156892095392E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+        <v>12.58002944752533</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B6" t="s">
         <v>57</v>
@@ -25811,81 +25599,27 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>61.425515860127703</v>
+        <v>50.354424989857208</v>
       </c>
       <c r="G6">
-        <v>174.0375236699584</v>
+        <v>75.670864088298316</v>
       </c>
       <c r="H6">
-        <v>176.39679574659201</v>
+        <v>56.089964446146993</v>
       </c>
       <c r="I6">
-        <v>240.4566559356511</v>
+        <v>46.878242739044538</v>
       </c>
       <c r="J6">
-        <v>323.21809405585572</v>
+        <v>49.090852591489373</v>
       </c>
       <c r="K6">
-        <v>281.14070738208392</v>
-      </c>
-      <c r="N6" t="s">
-        <v>8</v>
-      </c>
-      <c r="O6">
-        <f>SUM(C19)</f>
-        <v>217.0010537154852</v>
-      </c>
-      <c r="P6">
-        <f t="shared" ref="P6:T6" si="4">SUM(D19)</f>
-        <v>218.93267982188161</v>
-      </c>
-      <c r="Q6">
-        <f t="shared" si="4"/>
-        <v>200.18459503119641</v>
-      </c>
-      <c r="R6">
-        <f t="shared" si="4"/>
-        <v>218.93267982188161</v>
-      </c>
-      <c r="S6">
-        <f t="shared" si="4"/>
-        <v>218.93267982188161</v>
-      </c>
-      <c r="T6">
-        <f t="shared" si="4"/>
-        <v>215.941</v>
-      </c>
-      <c r="V6" t="s">
-        <v>8</v>
-      </c>
-      <c r="W6" s="5">
-        <f t="shared" si="3"/>
-        <v>9.391631084557403E-2</v>
-      </c>
-      <c r="X6" s="5">
-        <f t="shared" si="1"/>
-        <v>-1.8960585838748101E-2</v>
-      </c>
-      <c r="Y6" s="5">
-        <f t="shared" si="1"/>
-        <v>-2.9633854757698051E-2</v>
-      </c>
-      <c r="Z6" s="5">
-        <f t="shared" si="1"/>
-        <v>9.053246214281109E-2</v>
-      </c>
-      <c r="AA6" s="5">
-        <f t="shared" si="1"/>
-        <v>3.7969504759447006E-2</v>
-      </c>
-      <c r="AB6" s="5">
-        <f t="shared" si="1"/>
-        <v>9.9970863183288905E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+        <v>45.753419384678352</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="B7" t="s">
         <v>57</v>
@@ -25909,161 +25643,53 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>38.248920465489348</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>55.644490493355789</v>
       </c>
       <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="N7" t="s">
-        <v>9</v>
-      </c>
-      <c r="O7">
-        <f>SUM(C13,C12)</f>
-        <v>109.87920000000004</v>
-      </c>
-      <c r="P7">
-        <f t="shared" ref="P7:T7" si="5">SUM(D13,D12)</f>
-        <v>163.83959999999993</v>
-      </c>
-      <c r="Q7">
-        <f t="shared" si="5"/>
-        <v>154.68839999999989</v>
-      </c>
-      <c r="R7">
-        <f t="shared" si="5"/>
-        <v>132.95339999999996</v>
-      </c>
-      <c r="S7">
-        <f t="shared" si="5"/>
-        <v>87.523920000000032</v>
-      </c>
-      <c r="T7">
-        <f t="shared" si="5"/>
-        <v>161.65115999999998</v>
-      </c>
-      <c r="V7" t="s">
-        <v>9</v>
-      </c>
-      <c r="W7" s="5">
-        <f t="shared" si="3"/>
-        <v>3.8799485385410537E-16</v>
-      </c>
-      <c r="X7" s="5">
-        <f t="shared" si="1"/>
-        <v>-3.4694554223037667E-16</v>
-      </c>
-      <c r="Y7" s="5">
-        <f t="shared" si="1"/>
-        <v>-7.3494093753388118E-16</v>
-      </c>
-      <c r="Z7" s="5">
-        <f t="shared" si="1"/>
-        <v>3.4915631877832434E-3</v>
-      </c>
-      <c r="AA7" s="5">
-        <f t="shared" si="1"/>
-        <v>0.10000000000000041</v>
-      </c>
-      <c r="AB7" s="5">
-        <f t="shared" si="1"/>
-        <v>9.9999999999999811E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+        <v>38.876842042369248</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B8" t="s">
         <v>57</v>
       </c>
       <c r="C8">
-        <v>253.37450000000001</v>
+        <v>266.70999999999998</v>
       </c>
       <c r="D8">
-        <v>90.021999999999991</v>
+        <v>92.193830910453428</v>
       </c>
       <c r="E8">
-        <v>159.79</v>
+        <v>155.04000000000011</v>
       </c>
       <c r="F8">
-        <v>132.37299999999999</v>
+        <v>125.2480000000001</v>
       </c>
       <c r="G8">
-        <v>29.73500000000001</v>
+        <v>22.609999999999989</v>
       </c>
       <c r="H8">
-        <v>11.856</v>
+        <v>4.7310000000000052</v>
       </c>
       <c r="I8">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="J8">
-        <v>0.95000000000000007</v>
+        <v>0</v>
       </c>
       <c r="K8">
         <v>0</v>
       </c>
-      <c r="N8" t="s">
-        <v>11</v>
-      </c>
-      <c r="O8">
-        <f>SUM(C2,C3)</f>
-        <v>7.3906199999999993</v>
-      </c>
-      <c r="P8">
-        <f t="shared" ref="P8:T8" si="6">SUM(D2,D3)</f>
-        <v>11.47751999999999</v>
-      </c>
-      <c r="Q8">
-        <f t="shared" si="6"/>
-        <v>16.16976</v>
-      </c>
-      <c r="R8">
-        <f t="shared" si="6"/>
-        <v>16.42283999999999</v>
-      </c>
-      <c r="S8">
-        <f t="shared" si="6"/>
-        <v>19.505970000000008</v>
-      </c>
-      <c r="T8">
-        <f t="shared" si="6"/>
-        <v>18.19098</v>
-      </c>
-      <c r="V8" t="s">
-        <v>11</v>
-      </c>
-      <c r="W8" s="5">
-        <f t="shared" si="3"/>
-        <v>-5.0000000000000017E-2</v>
-      </c>
-      <c r="X8" s="5">
-        <f t="shared" si="1"/>
-        <v>-5.0000000000000863E-2</v>
-      </c>
-      <c r="Y8" s="5">
-        <f t="shared" si="1"/>
-        <v>-5.0000000000000065E-2</v>
-      </c>
-      <c r="Z8" s="5">
-        <f t="shared" si="1"/>
-        <v>-0.11522498060512071</v>
-      </c>
-      <c r="AA8" s="5">
-        <f t="shared" si="1"/>
-        <v>-8.7055602358887541E-2</v>
-      </c>
-      <c r="AB8" s="5">
-        <f t="shared" si="1"/>
-        <v>-4.9999999999999954E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="B9" t="s">
         <v>57</v>
@@ -26072,87 +25698,33 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>0.6</v>
+        <v>2.375</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>7.1250000000000009</v>
       </c>
       <c r="G9">
-        <v>0.29749999999999999</v>
+        <v>7.125</v>
       </c>
       <c r="H9">
-        <v>0.27625</v>
+        <v>7.1249999999999991</v>
       </c>
       <c r="I9">
-        <v>0.21249999999999999</v>
+        <v>1.9</v>
       </c>
       <c r="J9">
-        <v>0.10625</v>
+        <v>0.95</v>
       </c>
       <c r="K9">
         <v>0</v>
       </c>
-      <c r="N9" t="s">
-        <v>13</v>
-      </c>
-      <c r="O9">
-        <f>SUM(C25,C24)</f>
-        <v>94.278000000000006</v>
-      </c>
-      <c r="P9">
-        <f t="shared" ref="P9:T9" si="7">SUM(D25,D24)</f>
-        <v>151.411</v>
-      </c>
-      <c r="Q9">
-        <f t="shared" si="7"/>
-        <v>177.88750000000005</v>
-      </c>
-      <c r="R9">
-        <f t="shared" si="7"/>
-        <v>174.78847091302663</v>
-      </c>
-      <c r="S9">
-        <f t="shared" si="7"/>
-        <v>234.69599999999997</v>
-      </c>
-      <c r="T9">
-        <f t="shared" si="7"/>
-        <v>234.69599999999997</v>
-      </c>
-      <c r="V9" t="s">
-        <v>13</v>
-      </c>
-      <c r="W9" s="5">
-        <f t="shared" si="3"/>
-        <v>-5.0045946991681099E-2</v>
-      </c>
-      <c r="X9" s="5">
-        <f t="shared" si="1"/>
-        <v>-4.9973772647757819E-2</v>
-      </c>
-      <c r="Y9" s="5">
-        <f t="shared" si="1"/>
-        <v>-4.9983764742574835E-2</v>
-      </c>
-      <c r="Z9" s="5">
-        <f t="shared" si="1"/>
-        <v>-4.6047763451031724E-2</v>
-      </c>
-      <c r="AA9" s="5">
-        <f t="shared" si="1"/>
-        <v>3.837495752633352E-2</v>
-      </c>
-      <c r="AB9" s="5">
-        <f t="shared" si="1"/>
-        <v>4.9998120976877163E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="B10" t="s">
         <v>57</v>
@@ -26161,7 +25733,7 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -26170,76 +25742,22 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>0.29749999999999999</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>0.27625</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>0.21249999999999999</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>0.10625</v>
       </c>
       <c r="K10">
-        <v>0.52999999999999992</v>
-      </c>
-      <c r="N10" t="s">
-        <v>66</v>
-      </c>
-      <c r="O10">
-        <f>SUM(C22:C23,C20:C21)</f>
-        <v>1.7613000000000001</v>
-      </c>
-      <c r="P10">
-        <f t="shared" ref="P10:T10" si="8">SUM(D22:D23,D20:D21)</f>
-        <v>24.576119999999985</v>
-      </c>
-      <c r="Q10">
-        <f t="shared" si="8"/>
-        <v>47.397779999999997</v>
-      </c>
-      <c r="R10">
-        <f t="shared" si="8"/>
-        <v>51.652259999999991</v>
-      </c>
-      <c r="S10">
-        <f t="shared" si="8"/>
-        <v>122.17266000000001</v>
-      </c>
-      <c r="T10">
-        <f t="shared" si="8"/>
-        <v>199.34496000000007</v>
-      </c>
-      <c r="V10" t="s">
-        <v>66</v>
-      </c>
-      <c r="W10" s="5">
-        <f t="shared" si="3"/>
-        <v>-4.9999999999999885E-2</v>
-      </c>
-      <c r="X10" s="5">
-        <f t="shared" si="1"/>
-        <v>-5.0000000000000509E-2</v>
-      </c>
-      <c r="Y10" s="5">
-        <f t="shared" si="1"/>
-        <v>-3.6935849608660622E-2</v>
-      </c>
-      <c r="Z10" s="5">
-        <f t="shared" si="1"/>
-        <v>0.12585138104205884</v>
-      </c>
-      <c r="AA10" s="5">
-        <f t="shared" si="1"/>
-        <v>-4.9999999999999954E-2</v>
-      </c>
-      <c r="AB10" s="5">
-        <f t="shared" si="1"/>
-        <v>-5.006518904823945E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>59</v>
       </c>
@@ -26247,213 +25765,141 @@
         <v>57</v>
       </c>
       <c r="C11">
-        <v>0.1</v>
+        <v>64.115802975979975</v>
       </c>
       <c r="D11">
-        <v>0.1</v>
+        <v>105.03380906816631</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>105.03380906816631</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>105.03380906816631</v>
       </c>
       <c r="G11">
-        <v>0.1</v>
+        <v>76.117619087266618</v>
       </c>
       <c r="H11">
-        <v>0.1</v>
+        <v>112.57276229505921</v>
       </c>
       <c r="I11">
-        <v>1</v>
+        <v>180.53430674053351</v>
       </c>
       <c r="J11">
-        <v>3</v>
+        <v>197.9987056287091</v>
       </c>
       <c r="K11">
-        <v>5</v>
-      </c>
-      <c r="N11" t="s">
-        <v>68</v>
-      </c>
-      <c r="O11">
-        <f>SUM(C10:C11,C9)</f>
-        <v>0.1</v>
-      </c>
-      <c r="P11">
-        <f t="shared" ref="P11:T11" si="9">SUM(D10:D11,D9)</f>
-        <v>0.7</v>
-      </c>
-      <c r="Q11">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="R11">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="S11">
-        <f t="shared" si="9"/>
-        <v>0.39749999999999996</v>
-      </c>
-      <c r="T11">
-        <f t="shared" si="9"/>
-        <v>0.37624999999999997</v>
-      </c>
-      <c r="V11" t="s">
-        <v>68</v>
-      </c>
-      <c r="W11" s="5">
-        <f t="shared" si="3"/>
-        <v>-0.9142661179698216</v>
-      </c>
-      <c r="X11" s="5">
-        <f t="shared" si="1"/>
-        <v>0.22292103424178883</v>
-      </c>
-      <c r="Y11" s="5" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z11" s="5">
-        <f t="shared" si="1"/>
-        <v>-1</v>
-      </c>
-      <c r="AA11" s="5">
-        <f t="shared" si="1"/>
-        <v>-0.60845153664302598</v>
-      </c>
-      <c r="AB11" s="5">
-        <f t="shared" si="1"/>
-        <v>-0.57166438979963574</v>
-      </c>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
+        <v>152.19624955171309</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="B12" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12">
+        <v>1.1361729792628801</v>
+      </c>
+      <c r="D12">
+        <v>11.406300912733389</v>
+      </c>
+      <c r="E12">
+        <v>11.406300912733389</v>
+      </c>
+      <c r="F12">
+        <v>11.406300912733389</v>
+      </c>
+      <c r="G12">
+        <v>11.406300912733389</v>
+      </c>
+      <c r="H12">
+        <v>30.592145155550579</v>
+      </c>
+      <c r="I12">
+        <v>56.764800000000001</v>
+      </c>
+      <c r="J12">
+        <v>52.842813034977247</v>
+      </c>
+      <c r="K12">
+        <v>56.76479999999998</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" t="s">
         <v>57</v>
       </c>
-      <c r="C12">
-        <v>104.21285483422299</v>
-      </c>
-      <c r="D12">
-        <v>134.91126666666659</v>
-      </c>
-      <c r="E12">
-        <v>132.79641078009391</v>
-      </c>
-      <c r="F12">
-        <v>117.045387491673</v>
-      </c>
-      <c r="G12">
-        <v>64.263559361638556</v>
-      </c>
-      <c r="H12">
-        <v>132.75049333333331</v>
-      </c>
-      <c r="I12">
-        <v>200</v>
-      </c>
-      <c r="J12">
-        <v>200</v>
-      </c>
-      <c r="K12">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>33</v>
-      </c>
-      <c r="B13" t="s">
-        <v>56</v>
-      </c>
       <c r="C13">
-        <v>5.6663451657770407</v>
+        <v>341.27640000000008</v>
       </c>
       <c r="D13">
-        <v>28.928333333333331</v>
+        <v>341.46359999999999</v>
       </c>
       <c r="E13">
-        <v>21.89198921990598</v>
+        <v>176.8038935915518</v>
       </c>
       <c r="F13">
-        <v>15.908012508326969</v>
+        <v>130.61685665059039</v>
       </c>
       <c r="G13">
-        <v>23.26036063836148</v>
+        <v>194.7191680822315</v>
       </c>
       <c r="H13">
-        <v>28.900666666666659</v>
+        <v>102.3283609070353</v>
       </c>
       <c r="I13">
-        <v>29.06666666666667</v>
+        <v>81.364290365245665</v>
       </c>
       <c r="J13">
-        <v>29.34333333333333</v>
+        <v>27.2</v>
       </c>
       <c r="K13">
-        <v>29.61999999999999</v>
-      </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B14" t="s">
         <v>57</v>
       </c>
       <c r="C14">
-        <v>218.50257999999999</v>
+        <v>0</v>
       </c>
       <c r="D14">
-        <v>250.01994274631099</v>
+        <v>0</v>
       </c>
       <c r="E14">
-        <v>176.80389359155171</v>
+        <v>0</v>
       </c>
       <c r="F14">
-        <v>120.9153989845439</v>
+        <v>0</v>
       </c>
       <c r="G14">
-        <v>129.56650465728569</v>
+        <v>0</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="I14">
-        <v>11.906861628833861</v>
+        <v>3.769322158815291</v>
       </c>
       <c r="J14">
-        <v>27.2</v>
+        <v>51.216483529647519</v>
       </c>
       <c r="K14">
-        <v>0</v>
-      </c>
-      <c r="O14">
-        <v>2007</v>
-      </c>
-      <c r="P14">
-        <v>2010</v>
-      </c>
-      <c r="Q14">
-        <v>2014</v>
-      </c>
-      <c r="R14">
-        <v>2018</v>
-      </c>
-      <c r="S14">
-        <v>2022</v>
-      </c>
-      <c r="T14">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
+        <v>2.5362030710475478</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="B15" t="s">
         <v>57</v>
@@ -26480,260 +25926,155 @@
         <v>0</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>3.9975629399039132</v>
       </c>
       <c r="K15">
-        <v>0</v>
-      </c>
-      <c r="N15" t="s">
-        <v>4</v>
-      </c>
-      <c r="O15">
-        <v>266.70600000000002</v>
-      </c>
-      <c r="P15">
-        <v>94.762799999999999</v>
-      </c>
-      <c r="Q15">
-        <v>163.06199999999998</v>
-      </c>
-      <c r="R15">
-        <v>139.3776</v>
-      </c>
-      <c r="S15">
-        <v>31.305599999999998</v>
-      </c>
-      <c r="T15">
-        <v>12.477599999999999</v>
-      </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
+        <v>66.695244215084998</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="B16" t="s">
         <v>57</v>
       </c>
       <c r="C16">
-        <v>63.297359999999983</v>
+        <v>0</v>
       </c>
       <c r="D16">
-        <v>56.642039999999987</v>
+        <v>0</v>
       </c>
       <c r="E16">
-        <v>48.293819999999997</v>
+        <v>0</v>
       </c>
       <c r="F16">
-        <v>49.583160000000007</v>
+        <v>0</v>
       </c>
       <c r="G16">
-        <v>36.217799999999997</v>
+        <v>0</v>
       </c>
       <c r="H16">
-        <v>30.513999999999999</v>
+        <v>0</v>
       </c>
       <c r="I16">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="J16">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="K16">
         <v>0</v>
       </c>
-      <c r="N16" t="s">
-        <v>6</v>
-      </c>
-      <c r="O16">
-        <v>66.628799999999998</v>
-      </c>
-      <c r="P16">
-        <v>59.623199999999997</v>
-      </c>
-      <c r="Q16">
-        <v>50.835599999999999</v>
-      </c>
-      <c r="R16">
-        <v>52.192799999999998</v>
-      </c>
-      <c r="S16">
-        <v>38.124000000000002</v>
-      </c>
-      <c r="T16">
-        <v>32.842799999999997</v>
-      </c>
-    </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B17" t="s">
         <v>57</v>
       </c>
       <c r="C17">
-        <v>100.29</v>
+        <v>66.628799999999998</v>
       </c>
       <c r="D17">
-        <v>94.835454545454553</v>
+        <v>65.585520000000002</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>48.293819999999997</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>49.583159999999999</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>36.217799999999997</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>30.513999999999989</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>9.5000000000000018</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="K17">
         <v>0</v>
       </c>
-      <c r="N17" t="s">
-        <v>7</v>
-      </c>
-      <c r="O17">
-        <v>341.27639999999997</v>
-      </c>
-      <c r="P17">
-        <v>341.46359999999999</v>
-      </c>
-      <c r="Q17">
-        <v>170.18279999999999</v>
-      </c>
-      <c r="R17">
-        <v>208.81440000000001</v>
-      </c>
-      <c r="S17">
-        <v>309.51</v>
-      </c>
-      <c r="T17">
-        <v>188.3844</v>
-      </c>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="B18" t="s">
         <v>57</v>
       </c>
       <c r="C18">
-        <v>5.42</v>
+        <v>198.37</v>
       </c>
       <c r="D18">
-        <v>5.86</v>
+        <v>218.93267982188161</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>211.76298686064999</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>196.4373620758995</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>218.93267982188161</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>215.94100000000009</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>136.5</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>134.75</v>
       </c>
       <c r="K18">
-        <v>0</v>
-      </c>
-      <c r="N18" t="s">
-        <v>8</v>
-      </c>
-      <c r="O18">
-        <v>198.3708</v>
-      </c>
-      <c r="P18">
-        <v>223.16399999999999</v>
-      </c>
-      <c r="Q18">
-        <v>206.298</v>
-      </c>
-      <c r="R18">
-        <v>200.7576</v>
-      </c>
-      <c r="S18">
-        <v>210.92400000000001</v>
-      </c>
-      <c r="T18">
-        <v>196.3152</v>
-      </c>
-    </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="B19" t="s">
         <v>57</v>
       </c>
       <c r="C19">
-        <v>217.0010537154852</v>
+        <v>0</v>
       </c>
       <c r="D19">
-        <v>218.93267982188161</v>
+        <v>0</v>
       </c>
       <c r="E19">
-        <v>200.18459503119641</v>
+        <v>0</v>
       </c>
       <c r="F19">
-        <v>218.93267982188161</v>
+        <v>0</v>
       </c>
       <c r="G19">
-        <v>218.93267982188161</v>
+        <v>0</v>
       </c>
       <c r="H19">
-        <v>215.941</v>
+        <v>49.628895730560011</v>
       </c>
       <c r="I19">
-        <v>136.5</v>
+        <v>49.084556838181598</v>
       </c>
       <c r="J19">
-        <v>68.25</v>
+        <v>46.347652021864597</v>
       </c>
       <c r="K19">
-        <v>0</v>
-      </c>
-      <c r="N19" t="s">
-        <v>9</v>
-      </c>
-      <c r="O19">
-        <v>109.8792</v>
-      </c>
-      <c r="P19">
-        <v>163.83959999999999</v>
-      </c>
-      <c r="Q19">
-        <v>154.6884</v>
-      </c>
-      <c r="R19">
-        <v>132.49080000000001</v>
-      </c>
-      <c r="S19">
-        <v>79.5672</v>
-      </c>
-      <c r="T19">
-        <v>146.9556</v>
-      </c>
-    </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
+        <v>49.628895730560011</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B20" t="s">
         <v>57</v>
@@ -26754,42 +26095,21 @@
         <v>0</v>
       </c>
       <c r="H20">
-        <v>49.481560908852892</v>
+        <v>16.203395098367999</v>
       </c>
       <c r="I20">
-        <v>49.628895730560011</v>
+        <v>12.160229912994311</v>
       </c>
       <c r="J20">
-        <v>48.19925229350401</v>
+        <v>13.48791353468928</v>
       </c>
       <c r="K20">
-        <v>43.910321982336008</v>
-      </c>
-      <c r="N20" t="s">
-        <v>11</v>
-      </c>
-      <c r="O20">
-        <v>7.7795999999999994</v>
-      </c>
-      <c r="P20">
-        <v>12.0816</v>
-      </c>
-      <c r="Q20">
-        <v>17.020800000000001</v>
-      </c>
-      <c r="R20">
-        <v>18.561599999999999</v>
-      </c>
-      <c r="S20">
-        <v>21.366</v>
-      </c>
-      <c r="T20">
-        <v>19.148399999999999</v>
-      </c>
-    </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
+        <v>13.11200140741632</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="B21" t="s">
         <v>57</v>
@@ -26798,170 +26118,101 @@
         <v>0</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>4.4761199999999954</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>27.327780000000001</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>31.572260000000011</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>102.1326599999999</v>
       </c>
       <c r="H21">
-        <v>15.112139945502481</v>
+        <v>113.492669171072</v>
       </c>
       <c r="I21">
-        <v>13.606246993833469</v>
+        <v>176.25521324882411</v>
       </c>
       <c r="J21">
-        <v>15.736658564505611</v>
+        <v>196.4144344434462</v>
       </c>
       <c r="K21">
-        <v>14.97894754286593</v>
-      </c>
-      <c r="N21" t="s">
-        <v>13</v>
-      </c>
-      <c r="O21">
-        <v>99.244799999999998</v>
-      </c>
-      <c r="P21">
-        <v>159.37559999999999</v>
-      </c>
-      <c r="Q21">
-        <v>187.24680000000001</v>
-      </c>
-      <c r="R21">
-        <v>183.22559999999999</v>
-      </c>
-      <c r="S21">
-        <v>226.0224</v>
-      </c>
-      <c r="T21">
-        <v>223.5204</v>
-      </c>
-    </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
+        <v>222.25910286202361</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>62</v>
       </c>
       <c r="B22" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>1.7613000000000001</v>
       </c>
       <c r="D22">
-        <v>4.4761199999999937</v>
+        <v>20.099999999999991</v>
       </c>
       <c r="E22">
-        <v>27.327780000000001</v>
+        <v>20.07</v>
       </c>
       <c r="F22">
-        <v>31.57226</v>
+        <v>20.079999999999991</v>
       </c>
       <c r="G22">
-        <v>102.13266</v>
+        <v>20.039999999999988</v>
       </c>
       <c r="H22">
-        <v>114.7312591456447</v>
+        <v>20.02</v>
       </c>
       <c r="I22">
-        <v>174.2648572756066</v>
+        <v>0</v>
       </c>
       <c r="J22">
-        <v>201.4853547067687</v>
+        <v>5</v>
       </c>
       <c r="K22">
-        <v>226.1107304747982</v>
-      </c>
-      <c r="N22" t="s">
-        <v>66</v>
-      </c>
-      <c r="O22">
-        <f t="shared" ref="O22:T22" si="10">SUM(P25+P26)</f>
-        <v>1.8539999999999999</v>
-      </c>
-      <c r="P22">
-        <f t="shared" si="10"/>
-        <v>25.869599999999998</v>
-      </c>
-      <c r="Q22">
-        <f t="shared" si="10"/>
-        <v>49.215599999999995</v>
-      </c>
-      <c r="R22">
-        <f t="shared" si="10"/>
-        <v>45.878399999999999</v>
-      </c>
-      <c r="S22">
-        <f t="shared" si="10"/>
-        <v>128.6028</v>
-      </c>
-      <c r="T22">
-        <f t="shared" si="10"/>
-        <v>209.85119999999998</v>
-      </c>
-    </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>63</v>
       </c>
       <c r="B23" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C23">
-        <v>1.7613000000000001</v>
+        <v>75.369028573276267</v>
       </c>
       <c r="D23">
-        <v>20.099999999999991</v>
+        <v>94.326291108638628</v>
       </c>
       <c r="E23">
-        <v>20.07</v>
+        <v>94.326291108638628</v>
       </c>
       <c r="F23">
-        <v>20.079999999999991</v>
+        <v>94.091457579524757</v>
       </c>
       <c r="G23">
-        <v>20.04</v>
+        <v>94.3262911086386</v>
       </c>
       <c r="H23">
-        <v>20.019999999999989</v>
+        <v>94.326291108638642</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K23">
-        <v>0</v>
-      </c>
-      <c r="N23" t="s">
-        <v>68</v>
-      </c>
-      <c r="O23">
-        <v>1.1663999999999999</v>
-      </c>
-      <c r="P23">
-        <v>0.57240000000000002</v>
-      </c>
-      <c r="Q23">
-        <v>0</v>
-      </c>
-      <c r="R23">
-        <v>0.33839999999999998</v>
-      </c>
-      <c r="S23">
-        <v>1.0151999999999999</v>
-      </c>
-      <c r="T23">
-        <v>0.87839999999999996</v>
-      </c>
-    </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>64</v>
       </c>
@@ -26969,116 +26220,977 @@
         <v>57</v>
       </c>
       <c r="C24">
-        <v>75.369028573276282</v>
+        <v>18.908971426723721</v>
       </c>
       <c r="D24">
-        <v>79.673704630580659</v>
+        <v>74.868708891361408</v>
       </c>
       <c r="E24">
-        <v>79.673704630580673</v>
+        <v>83.561208891361446</v>
       </c>
       <c r="F24">
-        <v>78.814124698542045</v>
+        <v>79.977042420475271</v>
       </c>
       <c r="G24">
-        <v>79.673704630580659</v>
+        <v>123.6773304425319</v>
       </c>
       <c r="H24">
-        <v>79.673704630580659</v>
+        <v>128.5721492325948</v>
       </c>
       <c r="I24">
-        <v>12</v>
+        <v>319.28615384615398</v>
       </c>
       <c r="J24">
-        <v>12</v>
+        <v>461.64307692307699</v>
       </c>
       <c r="K24">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="B25" t="s">
         <v>57</v>
       </c>
       <c r="C25">
-        <v>18.908971426723721</v>
+        <v>44.627224044757128</v>
       </c>
       <c r="D25">
-        <v>71.737295369419343</v>
+        <v>47.399490019100263</v>
       </c>
       <c r="E25">
-        <v>98.213795369419358</v>
+        <v>38.248290019100288</v>
       </c>
       <c r="F25">
-        <v>95.974346214484584</v>
+        <v>16.513290019100289</v>
       </c>
       <c r="G25">
-        <v>155.02229536941931</v>
+        <v>0</v>
       </c>
       <c r="H25">
-        <v>155.02229536941931</v>
+        <v>3.79069254939018</v>
       </c>
       <c r="I25">
-        <v>319.28615384615392</v>
+        <v>4.7008932594665396</v>
       </c>
       <c r="J25">
-        <v>461.64307692307727</v>
+        <v>18.65848133631355</v>
       </c>
       <c r="K25">
-        <v>603.99999999999989</v>
-      </c>
-      <c r="N25" t="s">
+        <v>88.038950448286769</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C29">
+        <v>2007</v>
+      </c>
+      <c r="D29">
+        <v>2010</v>
+      </c>
+      <c r="E29">
+        <v>2014</v>
+      </c>
+      <c r="F29">
+        <v>2018</v>
+      </c>
+      <c r="G29">
+        <v>2022</v>
+      </c>
+      <c r="H29">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B30" t="s">
+        <v>4</v>
+      </c>
+      <c r="C30">
+        <f>SUM(C8:C9)</f>
+        <v>266.70999999999998</v>
+      </c>
+      <c r="D30">
+        <f t="shared" ref="D30:H30" si="0">SUM(D8:D9)</f>
+        <v>94.568830910453428</v>
+      </c>
+      <c r="E30">
+        <f t="shared" si="0"/>
+        <v>159.79000000000011</v>
+      </c>
+      <c r="F30">
+        <f t="shared" si="0"/>
+        <v>132.3730000000001</v>
+      </c>
+      <c r="G30">
+        <f t="shared" si="0"/>
+        <v>29.734999999999989</v>
+      </c>
+      <c r="H30">
+        <f t="shared" si="0"/>
+        <v>11.856000000000005</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31">
+        <f>SUM(C17)</f>
+        <v>66.628799999999998</v>
+      </c>
+      <c r="D31">
+        <f t="shared" ref="D31:H31" si="1">SUM(D17)</f>
+        <v>65.585520000000002</v>
+      </c>
+      <c r="E31">
+        <f t="shared" si="1"/>
+        <v>48.293819999999997</v>
+      </c>
+      <c r="F31">
+        <f t="shared" si="1"/>
+        <v>49.583159999999999</v>
+      </c>
+      <c r="G31">
+        <f t="shared" si="1"/>
+        <v>36.217799999999997</v>
+      </c>
+      <c r="H31">
+        <f t="shared" si="1"/>
+        <v>30.513999999999989</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B32" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32">
+        <f>SUM(C3:C7,C13:C16)</f>
+        <v>341.27640000000008</v>
+      </c>
+      <c r="D32">
+        <f t="shared" ref="D32:H32" si="2">SUM(D3:D7,D13:D16)</f>
+        <v>341.46359999999999</v>
+      </c>
+      <c r="E32">
+        <f t="shared" si="2"/>
+        <v>179.5431599999998</v>
+      </c>
+      <c r="F32">
+        <f t="shared" si="2"/>
+        <v>198.37367999999961</v>
+      </c>
+      <c r="G32">
+        <f t="shared" si="2"/>
+        <v>294.03450000000055</v>
+      </c>
+      <c r="H32">
+        <f t="shared" si="2"/>
+        <v>182.13954350934227</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B33" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33">
+        <f>SUM(C18)</f>
+        <v>198.37</v>
+      </c>
+      <c r="D33">
+        <f t="shared" ref="D33:H33" si="3">SUM(D18)</f>
+        <v>218.93267982188161</v>
+      </c>
+      <c r="E33">
+        <f t="shared" si="3"/>
+        <v>211.76298686064999</v>
+      </c>
+      <c r="F33">
+        <f t="shared" si="3"/>
+        <v>196.4373620758995</v>
+      </c>
+      <c r="G33">
+        <f t="shared" si="3"/>
+        <v>218.93267982188161</v>
+      </c>
+      <c r="H33">
+        <f t="shared" si="3"/>
+        <v>215.94100000000009</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C34">
+        <f>SUM(C11:C12,C25)</f>
+        <v>109.87919999999998</v>
+      </c>
+      <c r="D34">
+        <f t="shared" ref="D34:H34" si="4">SUM(D11:D12,D25)</f>
+        <v>163.83959999999996</v>
+      </c>
+      <c r="E34">
+        <f t="shared" si="4"/>
+        <v>154.68839999999997</v>
+      </c>
+      <c r="F34">
+        <f t="shared" si="4"/>
+        <v>132.95339999999999</v>
+      </c>
+      <c r="G34">
+        <f t="shared" si="4"/>
+        <v>87.523920000000004</v>
+      </c>
+      <c r="H34">
+        <f t="shared" si="4"/>
+        <v>146.95559999999995</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B35" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35">
+        <f>SUM(C2)</f>
+        <v>7.390620000000002</v>
+      </c>
+      <c r="D35">
+        <f t="shared" ref="D35:H35" si="5">SUM(D2)</f>
+        <v>11.47752</v>
+      </c>
+      <c r="E35">
+        <f t="shared" si="5"/>
+        <v>16.16976</v>
+      </c>
+      <c r="F35">
+        <f t="shared" si="5"/>
+        <v>16.422840000000001</v>
+      </c>
+      <c r="G35">
+        <f t="shared" si="5"/>
+        <v>19.505970000000008</v>
+      </c>
+      <c r="H35">
+        <f t="shared" si="5"/>
+        <v>18.19098</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B36" t="s">
+        <v>13</v>
+      </c>
+      <c r="C36">
+        <f>SUM(C23:C24)</f>
+        <v>94.277999999999992</v>
+      </c>
+      <c r="D36">
+        <f t="shared" ref="D36:H36" si="6">SUM(D23:D24)</f>
+        <v>169.19500000000005</v>
+      </c>
+      <c r="E36">
+        <f t="shared" si="6"/>
+        <v>177.88750000000007</v>
+      </c>
+      <c r="F36">
+        <f t="shared" si="6"/>
+        <v>174.06850000000003</v>
+      </c>
+      <c r="G36">
+        <f t="shared" si="6"/>
+        <v>218.00362155117051</v>
+      </c>
+      <c r="H36">
+        <f t="shared" si="6"/>
+        <v>222.89844034123342</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B37" t="s">
+        <v>65</v>
+      </c>
+      <c r="C37">
+        <f>SUM(C19:C22)</f>
+        <v>1.7613000000000001</v>
+      </c>
+      <c r="D37">
+        <f t="shared" ref="D37:H37" si="7">SUM(D19:D22)</f>
+        <v>24.576119999999985</v>
+      </c>
+      <c r="E37">
+        <f t="shared" si="7"/>
+        <v>47.397779999999997</v>
+      </c>
+      <c r="F37">
+        <f t="shared" si="7"/>
+        <v>51.652259999999998</v>
+      </c>
+      <c r="G37">
+        <f t="shared" si="7"/>
+        <v>122.17265999999989</v>
+      </c>
+      <c r="H37">
+        <f t="shared" si="7"/>
+        <v>199.34496000000001</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B38" t="s">
+        <v>67</v>
+      </c>
+      <c r="C38">
+        <f>SUM(C10)</f>
+        <v>0</v>
+      </c>
+      <c r="D38">
+        <f t="shared" ref="D38:H38" si="8">SUM(D10)</f>
+        <v>0.6</v>
+      </c>
+      <c r="E38">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F38">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="G38">
+        <f t="shared" si="8"/>
+        <v>0.29749999999999999</v>
+      </c>
+      <c r="H38">
+        <f t="shared" si="8"/>
+        <v>0.27625</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>76</v>
+      </c>
+      <c r="C41">
+        <v>2007</v>
+      </c>
+      <c r="D41">
+        <v>2010</v>
+      </c>
+      <c r="E41">
+        <v>2014</v>
+      </c>
+      <c r="F41">
+        <v>2018</v>
+      </c>
+      <c r="G41">
+        <v>2022</v>
+      </c>
+      <c r="H41">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B42" t="s">
+        <v>4</v>
+      </c>
+      <c r="C42">
+        <v>266.70600000000002</v>
+      </c>
+      <c r="D42">
+        <v>94.762799999999999</v>
+      </c>
+      <c r="E42">
+        <v>163.06199999999998</v>
+      </c>
+      <c r="F42">
+        <v>139.3776</v>
+      </c>
+      <c r="G42">
+        <v>31.305599999999998</v>
+      </c>
+      <c r="H42">
+        <v>12.477599999999999</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B43" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43">
+        <v>66.628799999999998</v>
+      </c>
+      <c r="D43">
+        <v>59.623199999999997</v>
+      </c>
+      <c r="E43">
+        <v>50.835599999999999</v>
+      </c>
+      <c r="F43">
+        <v>52.192799999999998</v>
+      </c>
+      <c r="G43">
+        <v>38.124000000000002</v>
+      </c>
+      <c r="H43">
+        <v>32.842799999999997</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B44" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44">
+        <v>341.27639999999997</v>
+      </c>
+      <c r="D44">
+        <v>341.46359999999999</v>
+      </c>
+      <c r="E44">
+        <v>170.18279999999999</v>
+      </c>
+      <c r="F44">
+        <v>208.81440000000001</v>
+      </c>
+      <c r="G44">
+        <v>309.51</v>
+      </c>
+      <c r="H44">
+        <v>188.3844</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B45" t="s">
+        <v>8</v>
+      </c>
+      <c r="C45">
+        <v>198.3708</v>
+      </c>
+      <c r="D45">
+        <v>223.16399999999999</v>
+      </c>
+      <c r="E45">
+        <v>206.298</v>
+      </c>
+      <c r="F45">
+        <v>200.7576</v>
+      </c>
+      <c r="G45">
+        <v>210.92400000000001</v>
+      </c>
+      <c r="H45">
+        <v>196.3152</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B46" t="s">
+        <v>9</v>
+      </c>
+      <c r="C46">
+        <v>109.8792</v>
+      </c>
+      <c r="D46">
+        <v>163.83959999999999</v>
+      </c>
+      <c r="E46">
+        <v>154.6884</v>
+      </c>
+      <c r="F46">
+        <v>132.49080000000001</v>
+      </c>
+      <c r="G46">
+        <v>79.5672</v>
+      </c>
+      <c r="H46">
+        <v>146.9556</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B47" t="s">
+        <v>11</v>
+      </c>
+      <c r="C47">
+        <v>7.7795999999999994</v>
+      </c>
+      <c r="D47">
+        <v>12.0816</v>
+      </c>
+      <c r="E47">
+        <v>17.020800000000001</v>
+      </c>
+      <c r="F47">
+        <v>18.561599999999999</v>
+      </c>
+      <c r="G47">
+        <v>21.366</v>
+      </c>
+      <c r="H47">
+        <v>19.148399999999999</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B48" t="s">
+        <v>13</v>
+      </c>
+      <c r="C48">
+        <v>99.244799999999998</v>
+      </c>
+      <c r="D48">
+        <v>159.37559999999999</v>
+      </c>
+      <c r="E48">
+        <v>187.24680000000001</v>
+      </c>
+      <c r="F48">
+        <v>183.22559999999999</v>
+      </c>
+      <c r="G48">
+        <v>226.0224</v>
+      </c>
+      <c r="H48">
+        <v>223.5204</v>
+      </c>
+    </row>
+    <row r="49" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B49" t="s">
+        <v>65</v>
+      </c>
+      <c r="C49">
+        <f t="shared" ref="C49:H49" si="9">SUM(D52+D53)</f>
+        <v>1.8539999999999999</v>
+      </c>
+      <c r="D49">
+        <f t="shared" si="9"/>
+        <v>25.869599999999998</v>
+      </c>
+      <c r="E49">
+        <f t="shared" si="9"/>
+        <v>49.215599999999995</v>
+      </c>
+      <c r="F49">
+        <f t="shared" si="9"/>
+        <v>45.878399999999999</v>
+      </c>
+      <c r="G49">
+        <f t="shared" si="9"/>
+        <v>128.6028</v>
+      </c>
+      <c r="H49">
+        <f t="shared" si="9"/>
+        <v>209.85119999999998</v>
+      </c>
+    </row>
+    <row r="50" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B50" t="s">
+        <v>67</v>
+      </c>
+      <c r="C50">
+        <v>1.1663999999999999</v>
+      </c>
+      <c r="D50">
+        <v>0.57240000000000002</v>
+      </c>
+      <c r="E50">
+        <v>0</v>
+      </c>
+      <c r="F50">
+        <v>0.33839999999999998</v>
+      </c>
+      <c r="G50">
+        <v>1.0151999999999999</v>
+      </c>
+      <c r="H50">
+        <v>0.87839999999999996</v>
+      </c>
+    </row>
+    <row r="52" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B52" t="s">
         <v>14</v>
       </c>
-      <c r="O25">
+      <c r="C52">
         <v>0.44639999999999996</v>
       </c>
-      <c r="P25">
+      <c r="D52">
         <v>1.8251999999999999</v>
       </c>
-      <c r="Q25">
+      <c r="E52">
         <v>23.13</v>
       </c>
-      <c r="R25">
+      <c r="F52">
         <v>29.581199999999999</v>
       </c>
-      <c r="S25">
+      <c r="G52">
         <v>28.357199999999999</v>
       </c>
-      <c r="T25">
+      <c r="H52">
         <v>112.2732</v>
       </c>
-      <c r="U25">
+      <c r="I52">
         <v>193.50719999999998</v>
       </c>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="N26" t="s">
+    <row r="53" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B53" t="s">
         <v>15</v>
       </c>
-      <c r="O26">
-        <v>0</v>
-      </c>
-      <c r="P26">
+      <c r="C53">
+        <v>0</v>
+      </c>
+      <c r="D53">
         <v>2.8799999999999999E-2</v>
       </c>
-      <c r="Q26">
+      <c r="E53">
         <v>2.7395999999999998</v>
       </c>
-      <c r="R26">
+      <c r="F53">
         <v>19.634399999999999</v>
       </c>
-      <c r="S26">
+      <c r="G53">
         <v>17.5212</v>
       </c>
-      <c r="T26">
+      <c r="H53">
         <v>16.329599999999999</v>
       </c>
-      <c r="U26">
+      <c r="I53">
         <v>16.344000000000001</v>
+      </c>
+    </row>
+    <row r="56" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B56" t="s">
+        <v>71</v>
+      </c>
+      <c r="C56">
+        <v>2007</v>
+      </c>
+      <c r="D56">
+        <v>2010</v>
+      </c>
+      <c r="E56">
+        <v>2014</v>
+      </c>
+      <c r="F56">
+        <v>2018</v>
+      </c>
+      <c r="G56">
+        <v>2022</v>
+      </c>
+      <c r="H56">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="57" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B57" t="s">
+        <v>4</v>
+      </c>
+      <c r="C57" s="5">
+        <f>(C30-C42)/C42</f>
+        <v>1.4997787826154102E-5</v>
+      </c>
+      <c r="D57" s="5">
+        <f>(D30-D42)/D42</f>
+        <v>-2.0468906527305042E-3</v>
+      </c>
+      <c r="E57" s="5">
+        <f>(E30-E42)/E42</f>
+        <v>-2.0065987170523346E-2</v>
+      </c>
+      <c r="F57" s="5">
+        <f>(F30-F42)/F42</f>
+        <v>-5.025628221464494E-2</v>
+      </c>
+      <c r="G57" s="5">
+        <f>(G30-G42)/G42</f>
+        <v>-5.0169937646938875E-2</v>
+      </c>
+      <c r="H57" s="5">
+        <f>(H30-H42)/H42</f>
+        <v>-4.9817272552413423E-2</v>
+      </c>
+    </row>
+    <row r="58" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B58" t="s">
+        <v>6</v>
+      </c>
+      <c r="C58" s="5">
+        <f>(C31-C43)/C43</f>
+        <v>0</v>
+      </c>
+      <c r="D58" s="5">
+        <f>(D31-D43)/D43</f>
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="E58" s="5">
+        <f>(E31-E43)/E43</f>
+        <v>-5.0000000000000058E-2</v>
+      </c>
+      <c r="F58" s="5">
+        <f>(F31-F43)/F43</f>
+        <v>-4.9999999999999982E-2</v>
+      </c>
+      <c r="G58" s="5">
+        <f>(G31-G43)/G43</f>
+        <v>-5.0000000000000142E-2</v>
+      </c>
+      <c r="H58" s="5">
+        <f>(H31-H43)/H43</f>
+        <v>-7.0907474393170147E-2</v>
+      </c>
+    </row>
+    <row r="59" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B59" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59" s="5">
+        <f>(C32-C44)/C44</f>
+        <v>3.3312247117473121E-16</v>
+      </c>
+      <c r="D59" s="5">
+        <f>(D32-D44)/D44</f>
+        <v>0</v>
+      </c>
+      <c r="E59" s="5">
+        <f>(E32-E44)/E44</f>
+        <v>5.5001798066548535E-2</v>
+      </c>
+      <c r="F59" s="5">
+        <f>(F32-F44)/F44</f>
+        <v>-5.0000000000001897E-2</v>
+      </c>
+      <c r="G59" s="5">
+        <f>(G32-G44)/G44</f>
+        <v>-4.9999999999998199E-2</v>
+      </c>
+      <c r="H59" s="5">
+        <f>(H32-H44)/H44</f>
+        <v>-3.314954152603785E-2</v>
+      </c>
+    </row>
+    <row r="60" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B60" t="s">
+        <v>8</v>
+      </c>
+      <c r="C60" s="5">
+        <f>(C33-C45)/C45</f>
+        <v>-4.0328516091992146E-6</v>
+      </c>
+      <c r="D60" s="5">
+        <f>(D33-D45)/D45</f>
+        <v>-1.8960585838748101E-2</v>
+      </c>
+      <c r="E60" s="5">
+        <f>(E33-E45)/E45</f>
+        <v>2.6490740873154305E-2</v>
+      </c>
+      <c r="F60" s="5">
+        <f>(F33-F45)/F45</f>
+        <v>-2.1519673098804211E-2</v>
+      </c>
+      <c r="G60" s="5">
+        <f>(G33-G45)/G45</f>
+        <v>3.7969504759447006E-2</v>
+      </c>
+      <c r="H60" s="5">
+        <f>(H33-H45)/H45</f>
+        <v>9.9970863183289335E-2</v>
+      </c>
+    </row>
+    <row r="61" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B61" t="s">
+        <v>9</v>
+      </c>
+      <c r="C61" s="5">
+        <f>(C34-C46)/C46</f>
+        <v>-1.2933161795136844E-16</v>
+      </c>
+      <c r="D61" s="5">
+        <f>(D34-D46)/D46</f>
+        <v>-1.7347277111518834E-16</v>
+      </c>
+      <c r="E61" s="5">
+        <f>(E34-E46)/E46</f>
+        <v>-1.8373523438347029E-16</v>
+      </c>
+      <c r="F61" s="5">
+        <f>(F34-F46)/F46</f>
+        <v>3.4915631877834577E-3</v>
+      </c>
+      <c r="G61" s="5">
+        <f>(G34-G46)/G46</f>
+        <v>0.10000000000000005</v>
+      </c>
+      <c r="H61" s="5">
+        <f>(H34-H46)/H46</f>
+        <v>-3.8680675565142133E-16</v>
+      </c>
+    </row>
+    <row r="62" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B62" t="s">
+        <v>11</v>
+      </c>
+      <c r="C62" s="5">
+        <f>(C35-C47)/C47</f>
+        <v>-4.9999999999999677E-2</v>
+      </c>
+      <c r="D62" s="5">
+        <f>(D35-D47)/D47</f>
+        <v>-4.9999999999999975E-2</v>
+      </c>
+      <c r="E62" s="5">
+        <f>(E35-E47)/E47</f>
+        <v>-5.0000000000000065E-2</v>
+      </c>
+      <c r="F62" s="5">
+        <f>(F35-F47)/F47</f>
+        <v>-0.11522498060512014</v>
+      </c>
+      <c r="G62" s="5">
+        <f>(G35-G47)/G47</f>
+        <v>-8.7055602358887541E-2</v>
+      </c>
+      <c r="H62" s="5">
+        <f>(H35-H47)/H47</f>
+        <v>-4.9999999999999954E-2</v>
+      </c>
+    </row>
+    <row r="63" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B63" t="s">
+        <v>13</v>
+      </c>
+      <c r="C63" s="5">
+        <f>(C36-C48)/C48</f>
+        <v>-5.0045946991681238E-2</v>
+      </c>
+      <c r="D63" s="5">
+        <f>(D36-D48)/D48</f>
+        <v>6.1611689618737489E-2</v>
+      </c>
+      <c r="E63" s="5">
+        <f>(E36-E48)/E48</f>
+        <v>-4.9983764742574682E-2</v>
+      </c>
+      <c r="F63" s="5">
+        <f>(F36-F48)/F48</f>
+        <v>-4.9977186594012832E-2</v>
+      </c>
+      <c r="G63" s="5">
+        <f>(G36-G48)/G48</f>
+        <v>-3.547780418591031E-2</v>
+      </c>
+      <c r="H63" s="5">
+        <f>(H36-H48)/H48</f>
+        <v>-2.7825632862439873E-3</v>
+      </c>
+    </row>
+    <row r="64" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B64" t="s">
+        <v>65</v>
+      </c>
+      <c r="C64" s="5">
+        <f>(C37-C49)/C49</f>
+        <v>-4.9999999999999885E-2</v>
+      </c>
+      <c r="D64" s="5">
+        <f>(D37-D49)/D49</f>
+        <v>-5.0000000000000509E-2</v>
+      </c>
+      <c r="E64" s="5">
+        <f>(E37-E49)/E49</f>
+        <v>-3.6935849608660622E-2</v>
+      </c>
+      <c r="F64" s="5">
+        <f>(F37-F49)/F49</f>
+        <v>0.12585138104205898</v>
+      </c>
+      <c r="G64" s="5">
+        <f>(G37-G49)/G49</f>
+        <v>-5.0000000000000842E-2</v>
+      </c>
+      <c r="H64" s="5">
+        <f>(H37-H49)/H49</f>
+        <v>-5.0065189048239721E-2</v>
+      </c>
+    </row>
+    <row r="65" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B65" t="s">
+        <v>67</v>
+      </c>
+      <c r="C65" s="5">
+        <f>(C38-C50)/C50</f>
+        <v>-1</v>
+      </c>
+      <c r="D65" s="5">
+        <f>(D38-D50)/D50</f>
+        <v>4.8218029350104746E-2</v>
+      </c>
+      <c r="E65" s="5" t="e">
+        <f>(E38-E50)/E50</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F65" s="5">
+        <f>(F38-F50)/F50</f>
+        <v>-1</v>
+      </c>
+      <c r="G65" s="5">
+        <f>(G38-G50)/G50</f>
+        <v>-0.70695429472025217</v>
+      </c>
+      <c r="H65" s="5">
+        <f>(H38-H50)/H50</f>
+        <v>-0.68550774134790526</v>
+      </c>
+    </row>
+    <row r="67" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B67" t="s">
+        <v>75</v>
+      </c>
+      <c r="C67" s="7">
+        <f>SUM(C30:C38)-SUM(C42:C50)</f>
+        <v>-6.6116800000002058</v>
+      </c>
+      <c r="D67" s="7">
+        <f>SUM(D30:D38)-SUM(D42:D50)</f>
+        <v>9.4864707323349649</v>
+      </c>
+      <c r="E67" s="7">
+        <f>SUM(E30:E38)-SUM(E42:E50)</f>
+        <v>-3.0165931393499932</v>
+      </c>
+      <c r="F67" s="7">
+        <f>SUM(F30:F38)-SUM(F42:F50)</f>
+        <v>-29.772997924100991</v>
+      </c>
+      <c r="G67" s="7">
+        <f>SUM(G30:G38)-SUM(G42:G50)</f>
+        <v>-20.013548626947568</v>
+      </c>
+      <c r="H67" s="7">
+        <f>SUM(H30:H38)-SUM(H42:H50)</f>
+        <v>-2.2572261494244685</v>
+      </c>
+      <c r="I67" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="68" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C68" s="5">
+        <f>C67/SUM(C42:C50)</f>
+        <v>-6.0496328138011915E-3</v>
+      </c>
+      <c r="D68" s="5">
+        <f t="shared" ref="D68:H68" si="10">D67/SUM(D42:D50)</f>
+        <v>8.7776540975851303E-3</v>
+      </c>
+      <c r="E68" s="5">
+        <f t="shared" si="10"/>
+        <v>-3.0209735509989419E-3</v>
+      </c>
+      <c r="F68" s="5">
+        <f t="shared" si="10"/>
+        <v>-3.0329940556552859E-2</v>
+      </c>
+      <c r="G68" s="5">
+        <f t="shared" si="10"/>
+        <v>-1.9125417776573277E-2</v>
+      </c>
+      <c r="H68" s="5">
+        <f t="shared" si="10"/>
+        <v>-2.1906862454064919E-3</v>
       </c>
     </row>
   </sheetData>

--- a/ELC_data_Spain.xlsx
+++ b/ELC_data_Spain.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Documents\TEMOA\PROJECT\Models-and-scenarios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5059C8F-F8E4-4E8B-A6B8-968FAA586DFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93D7079C-FB3F-46AB-B919-DC34978FEFFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="6" xr2:uid="{8BBF5E45-81C8-439F-BD27-48A9AF2DFBEB}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1156" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1165" uniqueCount="82">
   <si>
     <t>electricity generation sources in Spain</t>
   </si>
@@ -260,9 +260,6 @@
     <t>Production (GWh)</t>
   </si>
   <si>
-    <t>ELC_CHP_NGA_TAP_N</t>
-  </si>
-  <si>
     <t>ELC_CHP_NGA_CC_P</t>
   </si>
   <si>
@@ -276,6 +273,18 @@
   </si>
   <si>
     <t>ELC_CHP_NGA_TURB_N</t>
+  </si>
+  <si>
+    <t>ELC_CHP_NGA_TURB_P</t>
+  </si>
+  <si>
+    <t>ELC_BIO_CEN_E</t>
+  </si>
+  <si>
+    <t>ELC_BGS_LAN_N</t>
+  </si>
+  <si>
+    <t>ELC_NGA_CC_P</t>
   </si>
 </sst>
 </file>
@@ -790,7 +799,7 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -801,10 +810,11 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="43" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="43" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="43" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="20% - Colore 1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -7006,7 +7016,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Cal_Generation!$B$42</c:f>
+              <c:f>Cal_Generation!$B$46</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -7027,26 +7037,38 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>Cal_Generation!$C$41:$H$41</c:f>
+              <c:f>Cal_Generation!$C$45:$L$45</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>2007</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>2010</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>2014</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>2018</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="7">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>2022</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="9">
                   <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
@@ -7054,26 +7076,38 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Cal_Generation!$C$42:$H$42</c:f>
+              <c:f>Cal_Generation!$C$46:$L$46</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>266.70600000000002</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>179.90280000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>94.762799999999999</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
+                  <c:v>201.5676</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>163.06199999999998</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
+                  <c:v>134.83079999999998</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>139.3776</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="7">
+                  <c:v>22.136399999999998</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>31.305599999999998</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="9">
                   <c:v>12.477599999999999</c:v>
                 </c:pt>
               </c:numCache>
@@ -7090,7 +7124,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Cal_Generation!$B$43</c:f>
+              <c:f>Cal_Generation!$B$47</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -7111,26 +7145,38 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>Cal_Generation!$C$41:$H$41</c:f>
+              <c:f>Cal_Generation!$C$45:$L$45</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>2007</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>2010</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>2014</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>2018</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="7">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>2022</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="9">
                   <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
@@ -7138,26 +7184,38 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Cal_Generation!$C$43:$H$43</c:f>
+              <c:f>Cal_Generation!$C$47:$L$47</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>66.628799999999998</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>64.807199999999995</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>59.623199999999997</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
+                  <c:v>55.1556</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>50.835599999999999</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
+                  <c:v>60.915599999999998</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>52.192799999999998</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="7">
+                  <c:v>38.534399999999998</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>38.124000000000002</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="9">
                   <c:v>32.842799999999997</c:v>
                 </c:pt>
               </c:numCache>
@@ -7174,7 +7232,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Cal_Generation!$B$44</c:f>
+              <c:f>Cal_Generation!$B$48</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -7195,26 +7253,38 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>Cal_Generation!$C$41:$H$41</c:f>
+              <c:f>Cal_Generation!$C$45:$L$45</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>2007</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>2010</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>2014</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>2018</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="7">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>2022</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="9">
                   <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
@@ -7222,26 +7292,38 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Cal_Generation!$C$44:$H$44</c:f>
+              <c:f>Cal_Generation!$C$48:$L$48</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>341.27639999999997</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>434.87279999999998</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>341.46359999999999</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
+                  <c:v>263.90879999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>170.18279999999999</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
+                  <c:v>190.15199999999999</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>208.81440000000001</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="7">
+                  <c:v>251.06039999999999</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>309.51</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="9">
                   <c:v>188.3844</c:v>
                 </c:pt>
               </c:numCache>
@@ -7258,7 +7340,7 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>Cal_Generation!$B$45</c:f>
+              <c:f>Cal_Generation!$B$49</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -7279,26 +7361,38 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>Cal_Generation!$C$41:$H$41</c:f>
+              <c:f>Cal_Generation!$C$45:$L$45</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>2007</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>2010</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>2014</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>2018</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="7">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>2022</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="9">
                   <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
@@ -7306,26 +7400,38 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Cal_Generation!$C$45:$H$45</c:f>
+              <c:f>Cal_Generation!$C$49:$L$49</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>198.3708</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>212.30279999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>223.16399999999999</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
+                  <c:v>221.292</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>206.298</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
+                  <c:v>211.0788</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>200.7576</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="7">
+                  <c:v>209.87639999999999</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>210.92400000000001</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="9">
                   <c:v>196.3152</c:v>
                 </c:pt>
               </c:numCache>
@@ -7342,7 +7448,7 @@
           <c:order val="4"/>
           <c:tx>
             <c:strRef>
-              <c:f>Cal_Generation!$B$46</c:f>
+              <c:f>Cal_Generation!$B$50</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -7363,26 +7469,38 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>Cal_Generation!$C$41:$H$41</c:f>
+              <c:f>Cal_Generation!$C$45:$L$45</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>2007</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>2010</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>2014</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>2018</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="7">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>2022</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="9">
                   <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
@@ -7390,26 +7508,38 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Cal_Generation!$C$46:$H$46</c:f>
+              <c:f>Cal_Generation!$C$50:$L$50</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>109.8792</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>94.118399999999994</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>163.83959999999999</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
+                  <c:v>86.983199999999997</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>154.6884</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
+                  <c:v>143.51400000000001</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>132.49080000000001</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="7">
+                  <c:v>122.39279999999999</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>79.5672</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="9">
                   <c:v>146.9556</c:v>
                 </c:pt>
               </c:numCache>
@@ -7426,7 +7556,7 @@
           <c:order val="5"/>
           <c:tx>
             <c:strRef>
-              <c:f>Cal_Generation!$B$47</c:f>
+              <c:f>Cal_Generation!$B$51</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -7447,26 +7577,38 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>Cal_Generation!$C$41:$H$41</c:f>
+              <c:f>Cal_Generation!$C$45:$L$45</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>2007</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>2010</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>2014</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>2018</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="7">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>2022</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="9">
                   <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
@@ -7474,26 +7616,38 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Cal_Generation!$C$47:$H$47</c:f>
+              <c:f>Cal_Generation!$C$51:$L$51</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>7.7795999999999994</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>8.9027999999999992</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>12.0816</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
+                  <c:v>15.3432</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>17.020800000000001</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
+                  <c:v>17.834399999999999</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>18.561599999999999</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="7">
+                  <c:v>19.565999999999999</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>21.366</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="9">
                   <c:v>19.148399999999999</c:v>
                 </c:pt>
               </c:numCache>
@@ -7510,7 +7664,7 @@
           <c:order val="6"/>
           <c:tx>
             <c:strRef>
-              <c:f>Cal_Generation!$B$48</c:f>
+              <c:f>Cal_Generation!$B$52</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -7533,26 +7687,38 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>Cal_Generation!$C$41:$H$41</c:f>
+              <c:f>Cal_Generation!$C$45:$L$45</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>2007</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>2010</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>2014</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>2018</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="7">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>2022</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="9">
                   <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
@@ -7560,26 +7726,38 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Cal_Generation!$C$48:$H$48</c:f>
+              <c:f>Cal_Generation!$C$52:$L$52</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>99.244799999999998</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>118.6056</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>159.37559999999999</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
+                  <c:v>178.0992</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>187.24680000000001</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
+                  <c:v>176.05799999999999</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>183.22559999999999</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="7">
+                  <c:v>203.19839999999999</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>226.0224</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="9">
                   <c:v>223.5204</c:v>
                 </c:pt>
               </c:numCache>
@@ -7596,7 +7774,7 @@
           <c:order val="7"/>
           <c:tx>
             <c:strRef>
-              <c:f>Cal_Generation!$B$49</c:f>
+              <c:f>Cal_Generation!$B$53</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -7619,26 +7797,38 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>Cal_Generation!$C$41:$H$41</c:f>
+              <c:f>Cal_Generation!$C$45:$L$45</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>2007</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>2010</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>2014</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>2018</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="7">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>2022</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="9">
                   <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
@@ -7646,26 +7836,38 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Cal_Generation!$C$49:$H$49</c:f>
+              <c:f>Cal_Generation!$C$53:$L$53</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>1.8539999999999999</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>9.280800000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>25.869599999999998</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
+                  <c:v>43.081199999999995</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>49.215599999999995</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
+                  <c:v>49.111199999999997</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>45.878399999999999</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="7">
+                  <c:v>74.401200000000003</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>128.6028</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="9">
                   <c:v>209.85119999999998</c:v>
                 </c:pt>
               </c:numCache>
@@ -7682,7 +7884,7 @@
           <c:order val="8"/>
           <c:tx>
             <c:strRef>
-              <c:f>Cal_Generation!$B$50</c:f>
+              <c:f>Cal_Generation!$B$54</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -7705,26 +7907,38 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>Cal_Generation!$C$41:$H$41</c:f>
+              <c:f>Cal_Generation!$C$45:$L$45</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>2007</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>2010</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>2014</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>2018</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="7">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>2022</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="9">
                   <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
@@ -7732,26 +7946,38 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Cal_Generation!$C$50:$H$50</c:f>
+              <c:f>Cal_Generation!$C$54:$L$54</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>1.1663999999999999</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>1.1052</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>0.57240000000000002</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
+                  <c:v>0.63</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>0</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
+                  <c:v>0.38879999999999998</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>0.33839999999999998</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="7">
+                  <c:v>0.57599999999999996</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>1.0151999999999999</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="9">
                   <c:v>0.87839999999999996</c:v>
                 </c:pt>
               </c:numCache>
@@ -8163,7 +8389,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Cal_Generation!$B$30</c:f>
+              <c:f>Cal_Generation!$B$34</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -8184,26 +8410,38 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>Cal_Generation!$C$29:$H$29</c:f>
+              <c:f>Cal_Generation!$C$33:$L$33</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>2007</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>2010</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>2014</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>2018</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="7">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>2022</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="9">
                   <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
@@ -8211,27 +8449,39 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Cal_Generation!$C$30:$H$30</c:f>
+              <c:f>Cal_Generation!$C$34:$L$34</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>266.70999999999998</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>94.568830910453428</c:v>
+                  <c:v>179.90280000000001</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>159.79000000000011</c:v>
+                  <c:v>94.760000000000076</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>132.3730000000001</c:v>
+                  <c:v>191.49150000000009</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>29.734999999999989</c:v>
+                  <c:v>159.78999999999991</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>11.856000000000005</c:v>
+                  <c:v>128.0885000000001</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>132.37299999999991</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>21.03299999999998</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>29.734999999999982</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>11.855999999999995</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8247,7 +8497,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Cal_Generation!$B$31</c:f>
+              <c:f>Cal_Generation!$B$35</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -8268,26 +8518,38 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>Cal_Generation!$C$29:$H$29</c:f>
+              <c:f>Cal_Generation!$C$33:$L$33</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>2007</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>2010</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>2014</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>2018</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="7">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>2022</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="9">
                   <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
@@ -8295,27 +8557,39 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Cal_Generation!$C$31:$H$31</c:f>
+              <c:f>Cal_Generation!$C$35:$L$35</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>66.628799999999998</c:v>
+                  <c:v>66.628800000000012</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>65.585520000000002</c:v>
+                  <c:v>63.299879999999987</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>59.623199999999997</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>52.397820000000003</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>48.293819999999997</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>49.583159999999999</c:v>
-                </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
+                  <c:v>57.86981999999999</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>49.583160000000007</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>36.607679999999981</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>36.217799999999997</c:v>
                 </c:pt>
-                <c:pt idx="5">
-                  <c:v>30.513999999999989</c:v>
+                <c:pt idx="9">
+                  <c:v>30.513999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8331,7 +8605,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Cal_Generation!$B$32</c:f>
+              <c:f>Cal_Generation!$B$36</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -8352,26 +8626,38 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>Cal_Generation!$C$29:$H$29</c:f>
+              <c:f>Cal_Generation!$C$33:$L$33</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>2007</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>2010</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>2014</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>2018</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="7">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>2022</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="9">
                   <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
@@ -8379,27 +8665,39 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Cal_Generation!$C$32:$H$32</c:f>
+              <c:f>Cal_Generation!$C$36:$L$36</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>341.27640000000008</c:v>
+                  <c:v>341.27640000000002</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>341.46359999999999</c:v>
+                  <c:v>434.87279999999998</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>355.24043883151421</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>263.90879999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>179.5431599999998</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>198.37367999999961</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>294.03450000000055</c:v>
-                </c:pt>
                 <c:pt idx="5">
-                  <c:v>182.13954350934227</c:v>
+                  <c:v>192.3917570382846</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>198.37367999999981</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>238.50737999999996</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>294.03450000000061</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>185.05699019229564</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8415,7 +8713,7 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>Cal_Generation!$B$33</c:f>
+              <c:f>Cal_Generation!$B$37</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -8436,26 +8734,38 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>Cal_Generation!$C$29:$H$29</c:f>
+              <c:f>Cal_Generation!$C$33:$L$33</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>2007</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>2010</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>2014</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>2018</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="7">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>2022</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="9">
                   <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
@@ -8463,27 +8773,39 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Cal_Generation!$C$33:$H$33</c:f>
+              <c:f>Cal_Generation!$C$37:$L$37</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>198.37</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>218.93267982188161</c:v>
+                  <c:v>212.30279999999999</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>211.76298686064999</c:v>
+                  <c:v>221.29</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>196.4373620758995</c:v>
+                  <c:v>221.28999999999991</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>218.93267982188161</c:v>
+                  <c:v>221.29000000000011</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>215.94100000000009</c:v>
+                  <c:v>221.29000000000019</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>205.41152724581971</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>212.50564951457699</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>221.28999999999971</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>215.941</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8499,7 +8821,7 @@
           <c:order val="4"/>
           <c:tx>
             <c:strRef>
-              <c:f>Cal_Generation!$B$34</c:f>
+              <c:f>Cal_Generation!$B$38</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -8520,26 +8842,38 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>Cal_Generation!$C$29:$H$29</c:f>
+              <c:f>Cal_Generation!$C$33:$L$33</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>2007</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>2010</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>2014</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>2018</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="7">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>2022</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="9">
                   <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
@@ -8547,27 +8881,39 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Cal_Generation!$C$34:$H$34</c:f>
+              <c:f>Cal_Generation!$C$38:$L$38</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>109.87919999999998</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>163.83959999999996</c:v>
+                  <c:v>94.11839999999998</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>154.68839999999997</c:v>
+                  <c:v>163.83960000000008</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>132.95339999999999</c:v>
+                  <c:v>86.983199999999997</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>87.523920000000004</c:v>
+                  <c:v>154.68840000000012</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>146.95559999999995</c:v>
+                  <c:v>143.5140000000001</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>132.95339999999993</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>122.39280000000005</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>87.523920000000018</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>146.95560000000003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8583,7 +8929,7 @@
           <c:order val="5"/>
           <c:tx>
             <c:strRef>
-              <c:f>Cal_Generation!$B$35</c:f>
+              <c:f>Cal_Generation!$B$39</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -8604,26 +8950,38 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>Cal_Generation!$C$29:$H$29</c:f>
+              <c:f>Cal_Generation!$C$33:$L$33</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>2007</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>2010</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>2014</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>2018</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="7">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>2022</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="9">
                   <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
@@ -8631,27 +8989,39 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Cal_Generation!$C$35:$H$35</c:f>
+              <c:f>Cal_Generation!$C$39:$L$39</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>7.390620000000002</c:v>
+                  <c:v>7.3906199999999993</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>11.47752</c:v>
+                  <c:v>8.7529199999999996</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>16.16976</c:v>
+                  <c:v>11.477520000000002</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>16.422840000000001</c:v>
+                  <c:v>14.576040000000003</c:v>
                 </c:pt>
                 <c:pt idx="4">
+                  <c:v>16.169760000000004</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>16.901640000000004</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>17.633519999999997</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>20.820959999999999</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>19.505970000000008</c:v>
                 </c:pt>
-                <c:pt idx="5">
-                  <c:v>18.19098</c:v>
+                <c:pt idx="9">
+                  <c:v>18.190980000000007</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8667,7 +9037,7 @@
           <c:order val="6"/>
           <c:tx>
             <c:strRef>
-              <c:f>Cal_Generation!$B$36</c:f>
+              <c:f>Cal_Generation!$B$40</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -8690,26 +9060,38 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>Cal_Generation!$C$29:$H$29</c:f>
+              <c:f>Cal_Generation!$C$33:$L$33</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>2007</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>2010</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>2014</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>2018</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="7">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>2022</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="9">
                   <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
@@ -8717,27 +9099,39 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Cal_Generation!$C$36:$H$36</c:f>
+              <c:f>Cal_Generation!$C$40:$L$40</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>94.277999999999992</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>169.19500000000005</c:v>
+                  <c:v>113.32233333333335</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>177.88750000000007</c:v>
+                  <c:v>169.19499999999999</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>174.06850000000003</c:v>
+                  <c:v>169.19499999999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>218.00362155117051</c:v>
+                  <c:v>177.88749999999999</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>222.89844034123342</c:v>
+                  <c:v>177.88749999999996</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>174.06849999999997</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>193.04000000000002</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>225.6897101157445</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>228.11640739433489</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8753,7 +9147,7 @@
           <c:order val="7"/>
           <c:tx>
             <c:strRef>
-              <c:f>Cal_Generation!$B$37</c:f>
+              <c:f>Cal_Generation!$B$41</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -8776,26 +9170,38 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>Cal_Generation!$C$29:$H$29</c:f>
+              <c:f>Cal_Generation!$C$33:$L$33</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>2007</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>2010</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>2014</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>2018</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="7">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>2022</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="9">
                   <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
@@ -8803,27 +9209,39 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Cal_Generation!$C$37:$H$37</c:f>
+              <c:f>Cal_Generation!$C$41:$L$41</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>1.7613000000000001</c:v>
+                  <c:v>1.761299999999999</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>24.576119999999985</c:v>
+                  <c:v>9.3662400000000012</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>47.397779999999997</c:v>
+                  <c:v>24.57612</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>51.652259999999998</c:v>
+                  <c:v>40.927140000000001</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>122.17265999999989</c:v>
+                  <c:v>47.397779999999976</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>199.34496000000001</c:v>
+                  <c:v>49.237739999999974</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>51.652260000000012</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>70.681139999999985</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>122.17265999999999</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>199.34496000000004</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8839,7 +9257,7 @@
           <c:order val="8"/>
           <c:tx>
             <c:strRef>
-              <c:f>Cal_Generation!$B$38</c:f>
+              <c:f>Cal_Generation!$B$42</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -8862,26 +9280,38 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>Cal_Generation!$C$29:$H$29</c:f>
+              <c:f>Cal_Generation!$C$33:$L$33</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>2007</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>2010</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>2014</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>2018</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="7">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>2022</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="9">
                   <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
@@ -8889,26 +9319,38 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Cal_Generation!$C$38:$H$38</c:f>
+              <c:f>Cal_Generation!$C$42:$L$42</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.6</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>0.60000000000000009</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.29749999999999999</c:v>
+                  <c:v>0.12942089052995509</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>0.40500000000000003</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.2975000000000001</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>0.27625</c:v>
                 </c:pt>
               </c:numCache>
@@ -23084,11 +23526,11 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
       <c r="D2">
         <f>0.0036</f>
         <v>3.5999999999999999E-3</v>
@@ -25391,13 +25833,14 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95A32E31-20CB-4056-864B-0FCE4F4387EC}">
-  <dimension ref="A1:K68"/>
+  <dimension ref="A1:M72"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="10" width="13.33203125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="10.44140625" bestFit="1" customWidth="1"/>
@@ -25407,7 +25850,7 @@
     <col min="28" max="28" width="9.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>34</v>
       </c>
@@ -25418,31 +25861,34 @@
         <v>2007</v>
       </c>
       <c r="D1" s="4">
+        <v>2008</v>
+      </c>
+      <c r="E1" s="4">
         <v>2010</v>
       </c>
-      <c r="E1" s="4">
+      <c r="F1" s="4">
+        <v>2012</v>
+      </c>
+      <c r="G1" s="4">
         <v>2014</v>
       </c>
-      <c r="F1" s="4">
+      <c r="H1" s="4">
+        <v>2016</v>
+      </c>
+      <c r="I1" s="4">
         <v>2018</v>
       </c>
-      <c r="G1" s="4">
+      <c r="J1" s="4">
+        <v>2020</v>
+      </c>
+      <c r="K1" s="4">
         <v>2022</v>
       </c>
-      <c r="H1" s="4">
+      <c r="L1" s="4">
         <v>2024</v>
       </c>
-      <c r="I1" s="4">
-        <v>2030</v>
-      </c>
-      <c r="J1" s="4">
-        <v>2040</v>
-      </c>
-      <c r="K1" s="4">
-        <v>2050</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>35</v>
       </c>
@@ -25450,39 +25896,42 @@
         <v>56</v>
       </c>
       <c r="C2">
-        <v>7.390620000000002</v>
+        <v>4.6937302325581394</v>
       </c>
       <c r="D2">
-        <v>11.47752</v>
+        <v>4.6937302325581403</v>
       </c>
       <c r="E2">
-        <v>16.16976</v>
+        <v>4.6937302325581403</v>
       </c>
       <c r="F2">
-        <v>16.422840000000001</v>
+        <v>4.4590437209302323</v>
       </c>
       <c r="G2">
-        <v>19.505970000000008</v>
+        <v>4.2243572093023261</v>
       </c>
       <c r="H2">
-        <v>18.19098</v>
+        <v>3.9896706976744181</v>
       </c>
       <c r="I2">
-        <v>21.375</v>
+        <v>3.754984186046511</v>
       </c>
       <c r="J2">
-        <v>22.5625</v>
+        <v>3.5202976744186039</v>
       </c>
       <c r="K2">
-        <v>55.000000000000043</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+        <v>3.285611162790699</v>
+      </c>
+      <c r="L2">
+        <v>3.050924651162791</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -25491,65 +25940,71 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>2.739266408448001</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>5.4785328168960046</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>7.502977506816003</v>
+        <v>1.8284065116279069</v>
       </c>
       <c r="H3">
-        <v>8.7534737579519977</v>
+        <v>2.9377925581395372</v>
       </c>
       <c r="I3">
-        <v>5.8046240131200006</v>
+        <v>4.4910753488372066</v>
       </c>
       <c r="J3">
-        <v>6.4181787496703997</v>
+        <v>8.499918139534886</v>
       </c>
       <c r="K3">
-        <v>6.1329941142336013</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+        <v>8.0063309302325631</v>
+      </c>
+      <c r="L3">
+        <v>7.5127437209302377</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="B4" t="s">
         <v>57</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>2.6968897674418599</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>4.0591897674418584</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>6.7837897674418617</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>10.11699627906977</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>10.11699627906977</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>9.9741767441860478</v>
       </c>
       <c r="I4">
-        <v>30.61675114629714</v>
+        <v>9.3874604651162805</v>
       </c>
       <c r="J4">
-        <v>32.152990487039993</v>
+        <v>8.8007441860465114</v>
       </c>
       <c r="K4">
-        <v>17.732142812159999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+        <v>8.2140279069767459</v>
+      </c>
+      <c r="L4">
+        <v>7.6273116279069786</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B5" t="s">
         <v>57</v>
@@ -25564,25 +26019,28 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>11.923865542655999</v>
+        <v>1.3695602929920001</v>
       </c>
       <c r="G5">
-        <v>16.14149032265469</v>
+        <v>2.7391205859840002</v>
       </c>
       <c r="H5">
-        <v>14.967744398208</v>
+        <v>4.1086808789760001</v>
       </c>
       <c r="I5">
-        <v>12.63359344032</v>
+        <v>5.4782411719680004</v>
       </c>
       <c r="J5">
-        <v>12.63359344032</v>
+        <v>6.1672331697024054</v>
       </c>
       <c r="K5">
-        <v>12.58002944752533</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+        <v>7.5025400394240016</v>
+      </c>
+      <c r="L5">
+        <v>8.7529633793280048</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>73</v>
       </c>
@@ -25599,27 +26057,30 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>50.354424989857208</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>75.670864088298316</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>56.089964446146993</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>46.878242739044538</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>49.090852591489373</v>
+        <v>0</v>
       </c>
       <c r="K6">
-        <v>45.753419384678352</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>78</v>
+        <v>37</v>
       </c>
       <c r="B7" t="s">
         <v>57</v>
@@ -25640,56 +26101,59 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>5.9616153930240001</v>
       </c>
       <c r="I7">
-        <v>38.248920465489348</v>
+        <v>11.923230786048</v>
       </c>
       <c r="J7">
-        <v>55.644490493355789</v>
+        <v>12.95930292479999</v>
       </c>
       <c r="K7">
-        <v>38.876842042369248</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>38</v>
-      </c>
+        <v>16.124226565919621</v>
+      </c>
+      <c r="L7">
+        <v>14.966633574144</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>57</v>
       </c>
       <c r="C8">
-        <v>266.70999999999998</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>92.193830910453428</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>155.04000000000011</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>125.2480000000001</v>
+        <v>0</v>
       </c>
       <c r="G8">
-        <v>22.609999999999989</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>4.7310000000000052</v>
+        <v>69.915502274376507</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>68.498922397292418</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>69.642529862269853</v>
       </c>
       <c r="K8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+        <v>76.445952871109085</v>
+      </c>
+      <c r="L8">
+        <v>55.271587015626423</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>40</v>
+        <v>77</v>
       </c>
       <c r="B9" t="s">
         <v>57</v>
@@ -25698,33 +26162,36 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>2.375</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="F9">
-        <v>7.1250000000000009</v>
+        <v>0</v>
       </c>
       <c r="G9">
-        <v>7.125</v>
+        <v>0</v>
       </c>
       <c r="H9">
-        <v>7.1249999999999991</v>
+        <v>0</v>
       </c>
       <c r="I9">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="J9">
-        <v>0.95</v>
+        <v>0</v>
       </c>
       <c r="K9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="B10" t="s">
         <v>57</v>
@@ -25733,7 +26200,7 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -25742,167 +26209,182 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>0.29749999999999999</v>
+        <v>0</v>
       </c>
       <c r="H10">
-        <v>0.27625</v>
+        <v>0</v>
       </c>
       <c r="I10">
-        <v>0.21249999999999999</v>
+        <v>0</v>
       </c>
       <c r="J10">
-        <v>0.10625</v>
+        <v>0</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="B11" t="s">
         <v>57</v>
       </c>
       <c r="C11">
-        <v>64.115802975979975</v>
+        <v>266.70999999999998</v>
       </c>
       <c r="D11">
-        <v>105.03380906816631</v>
+        <v>177.52780000000001</v>
       </c>
       <c r="E11">
-        <v>105.03380906816631</v>
+        <v>92.385000000000076</v>
       </c>
       <c r="F11">
-        <v>105.03380906816631</v>
+        <v>186.74150000000009</v>
       </c>
       <c r="G11">
-        <v>76.117619087266618</v>
+        <v>155.03999999999991</v>
       </c>
       <c r="H11">
-        <v>112.57276229505921</v>
+        <v>120.9635000000001</v>
       </c>
       <c r="I11">
-        <v>180.53430674053351</v>
+        <v>125.24799999999991</v>
       </c>
       <c r="J11">
-        <v>197.9987056287091</v>
+        <v>13.90799999999998</v>
       </c>
       <c r="K11">
-        <v>152.19624955171309</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+        <v>22.609999999999982</v>
+      </c>
+      <c r="L11">
+        <v>4.7309999999999972</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="B12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C12">
-        <v>1.1361729792628801</v>
+        <v>0</v>
       </c>
       <c r="D12">
-        <v>11.406300912733389</v>
+        <v>2.375</v>
       </c>
       <c r="E12">
-        <v>11.406300912733389</v>
+        <v>2.375</v>
       </c>
       <c r="F12">
-        <v>11.406300912733389</v>
+        <v>4.7499999999999991</v>
       </c>
       <c r="G12">
-        <v>11.406300912733389</v>
+        <v>4.75</v>
       </c>
       <c r="H12">
-        <v>30.592145155550579</v>
+        <v>7.125</v>
       </c>
       <c r="I12">
-        <v>56.764800000000001</v>
+        <v>7.1249999999999991</v>
       </c>
       <c r="J12">
-        <v>52.842813034977247</v>
+        <v>7.1249999999999991</v>
       </c>
       <c r="K12">
-        <v>56.76479999999998</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+        <v>7.1249999999999991</v>
+      </c>
+      <c r="L12">
+        <v>7.1249999999999973</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="B13" t="s">
         <v>57</v>
       </c>
       <c r="C13">
-        <v>341.27640000000008</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>341.46359999999999</v>
+        <v>0</v>
       </c>
       <c r="E13">
-        <v>176.8038935915518</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="F13">
-        <v>130.61685665059039</v>
+        <v>0</v>
       </c>
       <c r="G13">
-        <v>194.7191680822315</v>
+        <v>0.12942089052995509</v>
       </c>
       <c r="H13">
-        <v>102.3283609070353</v>
+        <v>0.40500000000000003</v>
       </c>
       <c r="I13">
-        <v>81.364290365245665</v>
+        <v>0</v>
       </c>
       <c r="J13">
-        <v>27.2</v>
+        <v>0</v>
       </c>
       <c r="K13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0.2975000000000001</v>
+      </c>
+      <c r="L13">
+        <v>0.27625</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="B14" t="s">
         <v>57</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>72.328026287897885</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>56.029209792794298</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>105.02826477030121</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>65.586215722042567</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>105.02826477030121</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>105.02826477030121</v>
       </c>
       <c r="I14">
-        <v>3.769322158815291</v>
+        <v>105.02826477030111</v>
       </c>
       <c r="J14">
-        <v>51.216483529647519</v>
+        <v>105.02826477030121</v>
       </c>
       <c r="K14">
-        <v>2.5362030710475478</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+        <v>76.118221178444315</v>
+      </c>
+      <c r="L14">
+        <v>132.9758336700601</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="B15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -25911,135 +26393,147 @@
         <v>0</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>11.405698821555699</v>
       </c>
       <c r="F15">
         <v>0</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>11.405698821555699</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>11.405698821555699</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>11.40569882155569</v>
       </c>
       <c r="J15">
-        <v>3.9975629399039132</v>
+        <v>11.405698821555699</v>
       </c>
       <c r="K15">
-        <v>66.695244215084998</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+        <v>11.405698821555699</v>
+      </c>
+      <c r="L15">
+        <v>11.405698821555699</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>68</v>
+        <v>41</v>
       </c>
       <c r="B16" t="s">
         <v>57</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>341.27640000000002</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>434.87279999999998</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>341.46359999999999</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>262.53923970700799</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>176.80403941401579</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>112.40595849190809</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>112.4732856446914</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>149.73831404322769</v>
       </c>
       <c r="K16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+        <v>193.9617805235479</v>
+      </c>
+      <c r="L16">
+        <v>106.0658062231972</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B17" t="s">
         <v>57</v>
       </c>
       <c r="C17">
-        <v>66.628799999999998</v>
+        <v>0</v>
       </c>
       <c r="D17">
-        <v>65.585520000000002</v>
+        <v>0</v>
       </c>
       <c r="E17">
-        <v>48.293819999999997</v>
+        <v>0</v>
       </c>
       <c r="F17">
-        <v>49.583159999999999</v>
+        <v>0</v>
       </c>
       <c r="G17">
-        <v>36.217799999999997</v>
+        <v>0</v>
       </c>
       <c r="H17">
-        <v>30.513999999999989</v>
+        <v>0</v>
       </c>
       <c r="I17">
-        <v>9.5000000000000018</v>
+        <v>0</v>
       </c>
       <c r="J17">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="K17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="B18" t="s">
         <v>57</v>
       </c>
       <c r="C18">
-        <v>198.37</v>
+        <v>0</v>
       </c>
       <c r="D18">
-        <v>218.93267982188161</v>
+        <v>0</v>
       </c>
       <c r="E18">
-        <v>211.76298686064999</v>
+        <v>13.77683883151423</v>
       </c>
       <c r="F18">
-        <v>196.4373620758995</v>
+        <v>0</v>
       </c>
       <c r="G18">
-        <v>218.93267982188161</v>
+        <v>0</v>
       </c>
       <c r="H18">
-        <v>215.94100000000009</v>
+        <v>0</v>
       </c>
       <c r="I18">
-        <v>136.5</v>
+        <v>0</v>
       </c>
       <c r="J18">
-        <v>134.75</v>
+        <v>0</v>
       </c>
       <c r="K18">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="B19" t="s">
         <v>57</v>
@@ -26060,21 +26554,24 @@
         <v>0</v>
       </c>
       <c r="H19">
-        <v>49.628895730560011</v>
+        <v>0</v>
       </c>
       <c r="I19">
-        <v>49.084556838181598</v>
+        <v>0</v>
       </c>
       <c r="J19">
-        <v>46.347652021864597</v>
+        <v>0</v>
       </c>
       <c r="K19">
-        <v>49.628895730560011</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B20" t="s">
         <v>57</v>
@@ -26095,1102 +26592,1796 @@
         <v>0</v>
       </c>
       <c r="H20">
-        <v>16.203395098367999</v>
+        <v>0</v>
       </c>
       <c r="I20">
-        <v>12.160229912994311</v>
+        <v>0</v>
       </c>
       <c r="J20">
-        <v>13.48791353468928</v>
+        <v>0</v>
       </c>
       <c r="K20">
-        <v>13.11200140741632</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="B21" t="s">
         <v>57</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>66.628800000000012</v>
       </c>
       <c r="D21">
-        <v>4.4761199999999954</v>
+        <v>63.299879999999987</v>
       </c>
       <c r="E21">
-        <v>27.327780000000001</v>
+        <v>59.623199999999997</v>
       </c>
       <c r="F21">
-        <v>31.572260000000011</v>
+        <v>52.397820000000003</v>
       </c>
       <c r="G21">
-        <v>102.1326599999999</v>
+        <v>48.293819999999997</v>
       </c>
       <c r="H21">
-        <v>113.492669171072</v>
+        <v>57.86981999999999</v>
       </c>
       <c r="I21">
-        <v>176.25521324882411</v>
+        <v>49.583160000000007</v>
       </c>
       <c r="J21">
-        <v>196.4144344434462</v>
+        <v>36.607679999999981</v>
       </c>
       <c r="K21">
-        <v>222.25910286202361</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+        <v>36.217799999999997</v>
+      </c>
+      <c r="L21">
+        <v>30.513999999999999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="B22" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C22">
-        <v>1.7613000000000001</v>
+        <v>0</v>
       </c>
       <c r="D22">
-        <v>20.099999999999991</v>
+        <v>0</v>
       </c>
       <c r="E22">
-        <v>20.07</v>
+        <v>0</v>
       </c>
       <c r="F22">
-        <v>20.079999999999991</v>
+        <v>0</v>
       </c>
       <c r="G22">
-        <v>20.039999999999988</v>
+        <v>0</v>
       </c>
       <c r="H22">
-        <v>20.02</v>
+        <v>0</v>
       </c>
       <c r="I22">
         <v>0</v>
       </c>
       <c r="J22">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B23" t="s">
         <v>57</v>
       </c>
       <c r="C23">
-        <v>75.369028573276267</v>
+        <v>198.37</v>
       </c>
       <c r="D23">
-        <v>94.326291108638628</v>
+        <v>212.30279999999999</v>
       </c>
       <c r="E23">
-        <v>94.326291108638628</v>
+        <v>221.29</v>
       </c>
       <c r="F23">
-        <v>94.091457579524757</v>
+        <v>221.28999999999991</v>
       </c>
       <c r="G23">
-        <v>94.3262911086386</v>
+        <v>221.29000000000011</v>
       </c>
       <c r="H23">
-        <v>94.326291108638642</v>
+        <v>221.29000000000019</v>
       </c>
       <c r="I23">
-        <v>12</v>
+        <v>205.41152724581971</v>
       </c>
       <c r="J23">
-        <v>12</v>
+        <v>212.50564951457699</v>
       </c>
       <c r="K23">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+        <v>221.28999999999971</v>
+      </c>
+      <c r="L23">
+        <v>215.941</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B24" t="s">
         <v>57</v>
       </c>
       <c r="C24">
-        <v>18.908971426723721</v>
+        <v>0</v>
       </c>
       <c r="D24">
-        <v>74.868708891361408</v>
+        <v>0</v>
       </c>
       <c r="E24">
-        <v>83.561208891361446</v>
+        <v>0</v>
       </c>
       <c r="F24">
-        <v>79.977042420475271</v>
+        <v>0</v>
       </c>
       <c r="G24">
-        <v>123.6773304425319</v>
+        <v>0</v>
       </c>
       <c r="H24">
-        <v>128.5721492325948</v>
+        <v>0</v>
       </c>
       <c r="I24">
-        <v>319.28615384615398</v>
+        <v>0</v>
       </c>
       <c r="J24">
-        <v>461.64307692307699</v>
+        <v>0</v>
       </c>
       <c r="K24">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>49.620175176794461</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B25" t="s">
         <v>57</v>
       </c>
       <c r="C25">
-        <v>44.627224044757128</v>
+        <v>0</v>
       </c>
       <c r="D25">
-        <v>47.399490019100263</v>
+        <v>0</v>
       </c>
       <c r="E25">
-        <v>38.248290019100288</v>
+        <v>0</v>
       </c>
       <c r="F25">
-        <v>16.513290019100289</v>
+        <v>0</v>
       </c>
       <c r="G25">
         <v>0</v>
       </c>
       <c r="H25">
-        <v>3.79069254939018</v>
+        <v>0</v>
       </c>
       <c r="I25">
-        <v>4.7008932594665396</v>
+        <v>0</v>
       </c>
       <c r="J25">
-        <v>18.65848133631355</v>
+        <v>0</v>
       </c>
       <c r="K25">
-        <v>88.038950448286769</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>15.587237066209751</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>61</v>
+      </c>
+      <c r="B26" t="s">
+        <v>57</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <v>4.9806336000000018</v>
+      </c>
+      <c r="E26">
+        <v>20.249380800000001</v>
+      </c>
+      <c r="F26">
+        <v>36.659267999999997</v>
+      </c>
+      <c r="G26">
+        <v>43.188775199999981</v>
+      </c>
+      <c r="H26">
+        <v>45.087602399999973</v>
+      </c>
+      <c r="I26">
+        <v>47.560989600000013</v>
+      </c>
+      <c r="J26">
+        <v>66.64873679999998</v>
+      </c>
+      <c r="K26">
+        <v>118.199124</v>
+      </c>
+      <c r="L26">
+        <v>130.45834775699581</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>62</v>
+      </c>
+      <c r="B27" t="s">
+        <v>56</v>
+      </c>
+      <c r="C27">
+        <v>1.761299999999999</v>
+      </c>
+      <c r="D27">
+        <v>4.3856063999999986</v>
+      </c>
+      <c r="E27">
+        <v>4.3267391999999996</v>
+      </c>
+      <c r="F27">
+        <v>4.2678720000000014</v>
+      </c>
+      <c r="G27">
+        <v>4.209004799999998</v>
+      </c>
+      <c r="H27">
+        <v>4.1501375999999999</v>
+      </c>
+      <c r="I27">
+        <v>4.0912703999999991</v>
+      </c>
+      <c r="J27">
+        <v>4.0324032000000001</v>
+      </c>
+      <c r="K27">
+        <v>3.9735359999999988</v>
+      </c>
+      <c r="L27">
+        <v>3.6791999999999989</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>63</v>
+      </c>
+      <c r="B28" t="s">
+        <v>57</v>
+      </c>
+      <c r="C28">
+        <v>75.367565957311342</v>
+      </c>
+      <c r="D28">
+        <v>75.367565957311342</v>
+      </c>
+      <c r="E28">
+        <v>79.14678398091911</v>
+      </c>
+      <c r="F28">
+        <v>79.146783980919096</v>
+      </c>
+      <c r="G28">
+        <v>79.146783980919096</v>
+      </c>
+      <c r="H28">
+        <v>79.146783980919096</v>
+      </c>
+      <c r="I28">
+        <v>78.436252035127012</v>
+      </c>
+      <c r="J28">
+        <v>94.299283980919114</v>
+      </c>
+      <c r="K28">
+        <v>94.2992839809191</v>
+      </c>
+      <c r="L28">
+        <v>94.299283980919085</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>64</v>
+      </c>
+      <c r="B29" t="s">
+        <v>57</v>
+      </c>
       <c r="C29">
+        <v>18.910434042688649</v>
+      </c>
+      <c r="D29">
+        <v>37.954767376021998</v>
+      </c>
+      <c r="E29">
+        <v>90.048216019080897</v>
+      </c>
+      <c r="F29">
+        <v>90.048216019080897</v>
+      </c>
+      <c r="G29">
+        <v>98.740716019080907</v>
+      </c>
+      <c r="H29">
+        <v>98.740716019080864</v>
+      </c>
+      <c r="I29">
+        <v>95.632247964872974</v>
+      </c>
+      <c r="J29">
+        <v>98.740716019080892</v>
+      </c>
+      <c r="K29">
+        <v>131.39042613482539</v>
+      </c>
+      <c r="L29">
+        <v>133.8171234134158</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>76</v>
+      </c>
+      <c r="B30" t="s">
+        <v>57</v>
+      </c>
+      <c r="C30">
+        <v>37.551173712102099</v>
+      </c>
+      <c r="D30">
+        <v>38.089190207205689</v>
+      </c>
+      <c r="E30">
+        <v>47.405636408143167</v>
+      </c>
+      <c r="F30">
+        <v>21.396984277957429</v>
+      </c>
+      <c r="G30">
+        <v>38.254436408143206</v>
+      </c>
+      <c r="H30">
+        <v>27.08003640814319</v>
+      </c>
+      <c r="I30">
+        <v>16.51943640814314</v>
+      </c>
+      <c r="J30">
+        <v>5.9588364081431404</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+      <c r="L30">
+        <v>2.5740675083842381</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C33" s="8">
         <v>2007</v>
       </c>
-      <c r="D29">
+      <c r="D33" s="8">
+        <v>2008</v>
+      </c>
+      <c r="E33" s="8">
         <v>2010</v>
       </c>
-      <c r="E29">
+      <c r="F33" s="8">
+        <v>2012</v>
+      </c>
+      <c r="G33" s="8">
         <v>2014</v>
       </c>
-      <c r="F29">
+      <c r="H33" s="8">
+        <v>2016</v>
+      </c>
+      <c r="I33" s="8">
         <v>2018</v>
       </c>
-      <c r="G29">
+      <c r="J33" s="8">
+        <v>2020</v>
+      </c>
+      <c r="K33" s="8">
         <v>2022</v>
       </c>
-      <c r="H29">
+      <c r="L33" s="8">
         <v>2024</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B30" t="s">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B34" t="s">
         <v>4</v>
       </c>
-      <c r="C30">
-        <f>SUM(C8:C9)</f>
+      <c r="C34">
+        <f>SUM(C11:C12)</f>
         <v>266.70999999999998</v>
       </c>
-      <c r="D30">
-        <f t="shared" ref="D30:H30" si="0">SUM(D8:D9)</f>
-        <v>94.568830910453428</v>
-      </c>
-      <c r="E30">
+      <c r="D34">
+        <f t="shared" ref="D34:L34" si="0">SUM(D11:D12)</f>
+        <v>179.90280000000001</v>
+      </c>
+      <c r="E34">
         <f t="shared" si="0"/>
-        <v>159.79000000000011</v>
-      </c>
-      <c r="F30">
+        <v>94.760000000000076</v>
+      </c>
+      <c r="F34">
         <f t="shared" si="0"/>
-        <v>132.3730000000001</v>
-      </c>
-      <c r="G30">
+        <v>191.49150000000009</v>
+      </c>
+      <c r="G34">
         <f t="shared" si="0"/>
-        <v>29.734999999999989</v>
-      </c>
-      <c r="H30">
+        <v>159.78999999999991</v>
+      </c>
+      <c r="H34">
         <f t="shared" si="0"/>
-        <v>11.856000000000005</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B31" t="s">
+        <v>128.0885000000001</v>
+      </c>
+      <c r="I34">
+        <f t="shared" si="0"/>
+        <v>132.37299999999991</v>
+      </c>
+      <c r="J34">
+        <f t="shared" si="0"/>
+        <v>21.03299999999998</v>
+      </c>
+      <c r="K34">
+        <f t="shared" si="0"/>
+        <v>29.734999999999982</v>
+      </c>
+      <c r="L34">
+        <f t="shared" si="0"/>
+        <v>11.855999999999995</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B35" t="s">
         <v>6</v>
       </c>
-      <c r="C31">
-        <f>SUM(C17)</f>
-        <v>66.628799999999998</v>
-      </c>
-      <c r="D31">
-        <f t="shared" ref="D31:H31" si="1">SUM(D17)</f>
-        <v>65.585520000000002</v>
-      </c>
-      <c r="E31">
+      <c r="C35">
+        <f>SUM(C21:C22)</f>
+        <v>66.628800000000012</v>
+      </c>
+      <c r="D35">
+        <f t="shared" ref="D35:L35" si="1">SUM(D21:D22)</f>
+        <v>63.299879999999987</v>
+      </c>
+      <c r="E35">
+        <f t="shared" si="1"/>
+        <v>59.623199999999997</v>
+      </c>
+      <c r="F35">
+        <f t="shared" si="1"/>
+        <v>52.397820000000003</v>
+      </c>
+      <c r="G35">
         <f t="shared" si="1"/>
         <v>48.293819999999997</v>
       </c>
-      <c r="F31">
+      <c r="H35">
         <f t="shared" si="1"/>
-        <v>49.583159999999999</v>
-      </c>
-      <c r="G31">
+        <v>57.86981999999999</v>
+      </c>
+      <c r="I35">
+        <f t="shared" si="1"/>
+        <v>49.583160000000007</v>
+      </c>
+      <c r="J35">
+        <f t="shared" si="1"/>
+        <v>36.607679999999981</v>
+      </c>
+      <c r="K35">
         <f t="shared" si="1"/>
         <v>36.217799999999997</v>
       </c>
-      <c r="H31">
+      <c r="L35">
         <f t="shared" si="1"/>
-        <v>30.513999999999989</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B32" t="s">
+        <v>30.513999999999999</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B36" t="s">
         <v>7</v>
       </c>
-      <c r="C32">
-        <f>SUM(C3:C7,C13:C16)</f>
-        <v>341.27640000000008</v>
-      </c>
-      <c r="D32">
-        <f t="shared" ref="D32:H32" si="2">SUM(D3:D7,D13:D16)</f>
-        <v>341.46359999999999</v>
-      </c>
-      <c r="E32">
+      <c r="C36">
+        <f>SUM(C5:C10,C16:C20)</f>
+        <v>341.27640000000002</v>
+      </c>
+      <c r="D36">
+        <f t="shared" ref="D36:L36" si="2">SUM(D5:D10,D16:D20)</f>
+        <v>434.87279999999998</v>
+      </c>
+      <c r="E36">
+        <f t="shared" si="2"/>
+        <v>355.24043883151421</v>
+      </c>
+      <c r="F36">
+        <f t="shared" si="2"/>
+        <v>263.90879999999999</v>
+      </c>
+      <c r="G36">
         <f t="shared" si="2"/>
         <v>179.5431599999998</v>
       </c>
-      <c r="F32">
+      <c r="H36">
         <f t="shared" si="2"/>
-        <v>198.37367999999961</v>
-      </c>
-      <c r="G32">
+        <v>192.3917570382846</v>
+      </c>
+      <c r="I36">
         <f t="shared" si="2"/>
-        <v>294.03450000000055</v>
-      </c>
-      <c r="H32">
+        <v>198.37367999999981</v>
+      </c>
+      <c r="J36">
         <f t="shared" si="2"/>
-        <v>182.13954350934227</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B33" t="s">
+        <v>238.50737999999996</v>
+      </c>
+      <c r="K36">
+        <f t="shared" si="2"/>
+        <v>294.03450000000061</v>
+      </c>
+      <c r="L36">
+        <f t="shared" si="2"/>
+        <v>185.05699019229564</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B37" t="s">
         <v>8</v>
       </c>
-      <c r="C33">
-        <f>SUM(C18)</f>
+      <c r="C37">
+        <f>SUM(C23)</f>
         <v>198.37</v>
       </c>
-      <c r="D33">
-        <f t="shared" ref="D33:H33" si="3">SUM(D18)</f>
-        <v>218.93267982188161</v>
-      </c>
-      <c r="E33">
+      <c r="D37">
+        <f t="shared" ref="D37:L37" si="3">SUM(D23)</f>
+        <v>212.30279999999999</v>
+      </c>
+      <c r="E37">
         <f t="shared" si="3"/>
-        <v>211.76298686064999</v>
-      </c>
-      <c r="F33">
+        <v>221.29</v>
+      </c>
+      <c r="F37">
         <f t="shared" si="3"/>
-        <v>196.4373620758995</v>
-      </c>
-      <c r="G33">
+        <v>221.28999999999991</v>
+      </c>
+      <c r="G37">
         <f t="shared" si="3"/>
-        <v>218.93267982188161</v>
-      </c>
-      <c r="H33">
+        <v>221.29000000000011</v>
+      </c>
+      <c r="H37">
         <f t="shared" si="3"/>
-        <v>215.94100000000009</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B34" t="s">
+        <v>221.29000000000019</v>
+      </c>
+      <c r="I37">
+        <f t="shared" si="3"/>
+        <v>205.41152724581971</v>
+      </c>
+      <c r="J37">
+        <f t="shared" si="3"/>
+        <v>212.50564951457699</v>
+      </c>
+      <c r="K37">
+        <f t="shared" si="3"/>
+        <v>221.28999999999971</v>
+      </c>
+      <c r="L37">
+        <f t="shared" si="3"/>
+        <v>215.941</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B38" t="s">
         <v>9</v>
       </c>
-      <c r="C34">
-        <f>SUM(C11:C12,C25)</f>
+      <c r="C38">
+        <f>SUM(C14:C15,C30)</f>
         <v>109.87919999999998</v>
       </c>
-      <c r="D34">
-        <f t="shared" ref="D34:H34" si="4">SUM(D11:D12,D25)</f>
-        <v>163.83959999999996</v>
-      </c>
-      <c r="E34">
+      <c r="D38">
+        <f t="shared" ref="D38:L38" si="4">SUM(D14:D15,D30)</f>
+        <v>94.11839999999998</v>
+      </c>
+      <c r="E38">
         <f t="shared" si="4"/>
-        <v>154.68839999999997</v>
-      </c>
-      <c r="F34">
+        <v>163.83960000000008</v>
+      </c>
+      <c r="F38">
         <f t="shared" si="4"/>
-        <v>132.95339999999999</v>
-      </c>
-      <c r="G34">
+        <v>86.983199999999997</v>
+      </c>
+      <c r="G38">
         <f t="shared" si="4"/>
-        <v>87.523920000000004</v>
-      </c>
-      <c r="H34">
+        <v>154.68840000000012</v>
+      </c>
+      <c r="H38">
         <f t="shared" si="4"/>
-        <v>146.95559999999995</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B35" t="s">
+        <v>143.5140000000001</v>
+      </c>
+      <c r="I38">
+        <f t="shared" si="4"/>
+        <v>132.95339999999993</v>
+      </c>
+      <c r="J38">
+        <f t="shared" si="4"/>
+        <v>122.39280000000005</v>
+      </c>
+      <c r="K38">
+        <f t="shared" si="4"/>
+        <v>87.523920000000018</v>
+      </c>
+      <c r="L38">
+        <f t="shared" si="4"/>
+        <v>146.95560000000003</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B39" t="s">
         <v>11</v>
       </c>
-      <c r="C35">
-        <f>SUM(C2)</f>
-        <v>7.390620000000002</v>
-      </c>
-      <c r="D35">
-        <f t="shared" ref="D35:H35" si="5">SUM(D2)</f>
-        <v>11.47752</v>
-      </c>
-      <c r="E35">
+      <c r="C39">
+        <f>SUM(C2:C4)</f>
+        <v>7.3906199999999993</v>
+      </c>
+      <c r="D39">
+        <f t="shared" ref="D39:L39" si="5">SUM(D2:D4)</f>
+        <v>8.7529199999999996</v>
+      </c>
+      <c r="E39">
         <f t="shared" si="5"/>
-        <v>16.16976</v>
-      </c>
-      <c r="F35">
+        <v>11.477520000000002</v>
+      </c>
+      <c r="F39">
         <f t="shared" si="5"/>
-        <v>16.422840000000001</v>
-      </c>
-      <c r="G35">
+        <v>14.576040000000003</v>
+      </c>
+      <c r="G39">
+        <f t="shared" si="5"/>
+        <v>16.169760000000004</v>
+      </c>
+      <c r="H39">
+        <f t="shared" si="5"/>
+        <v>16.901640000000004</v>
+      </c>
+      <c r="I39">
+        <f t="shared" si="5"/>
+        <v>17.633519999999997</v>
+      </c>
+      <c r="J39">
+        <f t="shared" si="5"/>
+        <v>20.820959999999999</v>
+      </c>
+      <c r="K39">
         <f t="shared" si="5"/>
         <v>19.505970000000008</v>
       </c>
-      <c r="H35">
+      <c r="L39">
         <f t="shared" si="5"/>
-        <v>18.19098</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B36" t="s">
+        <v>18.190980000000007</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B40" t="s">
         <v>13</v>
       </c>
-      <c r="C36">
-        <f>SUM(C23:C24)</f>
+      <c r="C40">
+        <f>SUM(C28:C29)</f>
         <v>94.277999999999992</v>
       </c>
-      <c r="D36">
-        <f t="shared" ref="D36:H36" si="6">SUM(D23:D24)</f>
-        <v>169.19500000000005</v>
-      </c>
-      <c r="E36">
+      <c r="D40">
+        <f t="shared" ref="D40:L40" si="6">SUM(D28:D29)</f>
+        <v>113.32233333333335</v>
+      </c>
+      <c r="E40">
         <f t="shared" si="6"/>
-        <v>177.88750000000007</v>
-      </c>
-      <c r="F36">
+        <v>169.19499999999999</v>
+      </c>
+      <c r="F40">
         <f t="shared" si="6"/>
-        <v>174.06850000000003</v>
-      </c>
-      <c r="G36">
+        <v>169.19499999999999</v>
+      </c>
+      <c r="G40">
         <f t="shared" si="6"/>
-        <v>218.00362155117051</v>
-      </c>
-      <c r="H36">
+        <v>177.88749999999999</v>
+      </c>
+      <c r="H40">
         <f t="shared" si="6"/>
-        <v>222.89844034123342</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B37" t="s">
+        <v>177.88749999999996</v>
+      </c>
+      <c r="I40">
+        <f t="shared" si="6"/>
+        <v>174.06849999999997</v>
+      </c>
+      <c r="J40">
+        <f t="shared" si="6"/>
+        <v>193.04000000000002</v>
+      </c>
+      <c r="K40">
+        <f t="shared" si="6"/>
+        <v>225.6897101157445</v>
+      </c>
+      <c r="L40">
+        <f t="shared" si="6"/>
+        <v>228.11640739433489</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B41" t="s">
         <v>65</v>
       </c>
-      <c r="C37">
-        <f>SUM(C19:C22)</f>
-        <v>1.7613000000000001</v>
-      </c>
-      <c r="D37">
-        <f t="shared" ref="D37:H37" si="7">SUM(D19:D22)</f>
-        <v>24.576119999999985</v>
-      </c>
-      <c r="E37">
+      <c r="C41">
+        <f>SUM(C24:C27)</f>
+        <v>1.761299999999999</v>
+      </c>
+      <c r="D41">
+        <f t="shared" ref="D41:L41" si="7">SUM(D24:D27)</f>
+        <v>9.3662400000000012</v>
+      </c>
+      <c r="E41">
         <f t="shared" si="7"/>
-        <v>47.397779999999997</v>
-      </c>
-      <c r="F37">
+        <v>24.57612</v>
+      </c>
+      <c r="F41">
         <f t="shared" si="7"/>
-        <v>51.652259999999998</v>
-      </c>
-      <c r="G37">
+        <v>40.927140000000001</v>
+      </c>
+      <c r="G41">
         <f t="shared" si="7"/>
-        <v>122.17265999999989</v>
-      </c>
-      <c r="H37">
+        <v>47.397779999999976</v>
+      </c>
+      <c r="H41">
         <f t="shared" si="7"/>
-        <v>199.34496000000001</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B38" t="s">
+        <v>49.237739999999974</v>
+      </c>
+      <c r="I41">
+        <f t="shared" si="7"/>
+        <v>51.652260000000012</v>
+      </c>
+      <c r="J41">
+        <f t="shared" si="7"/>
+        <v>70.681139999999985</v>
+      </c>
+      <c r="K41">
+        <f t="shared" si="7"/>
+        <v>122.17265999999999</v>
+      </c>
+      <c r="L41">
+        <f t="shared" si="7"/>
+        <v>199.34496000000004</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B42" t="s">
         <v>67</v>
       </c>
-      <c r="C38">
-        <f>SUM(C10)</f>
-        <v>0</v>
-      </c>
-      <c r="D38">
-        <f t="shared" ref="D38:H38" si="8">SUM(D10)</f>
-        <v>0.6</v>
-      </c>
-      <c r="E38">
+      <c r="C42">
+        <f>SUM(C13)</f>
+        <v>0</v>
+      </c>
+      <c r="D42">
+        <f t="shared" ref="D42:L42" si="8">SUM(D13)</f>
+        <v>0</v>
+      </c>
+      <c r="E42">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F38">
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="F42">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="G38">
+      <c r="G42">
         <f t="shared" si="8"/>
-        <v>0.29749999999999999</v>
-      </c>
-      <c r="H38">
+        <v>0.12942089052995509</v>
+      </c>
+      <c r="H42">
+        <f t="shared" si="8"/>
+        <v>0.40500000000000003</v>
+      </c>
+      <c r="I42">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <f t="shared" si="8"/>
+        <v>0.2975000000000001</v>
+      </c>
+      <c r="L42">
         <f t="shared" si="8"/>
         <v>0.27625</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>76</v>
-      </c>
-      <c r="C41">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>75</v>
+      </c>
+      <c r="C45" s="8">
         <v>2007</v>
       </c>
-      <c r="D41">
+      <c r="D45" s="8">
+        <v>2008</v>
+      </c>
+      <c r="E45" s="8">
         <v>2010</v>
       </c>
-      <c r="E41">
+      <c r="F45" s="8">
+        <v>2012</v>
+      </c>
+      <c r="G45" s="8">
         <v>2014</v>
       </c>
-      <c r="F41">
+      <c r="H45" s="8">
+        <v>2016</v>
+      </c>
+      <c r="I45" s="8">
         <v>2018</v>
       </c>
-      <c r="G41">
+      <c r="J45" s="8">
+        <v>2020</v>
+      </c>
+      <c r="K45" s="8">
         <v>2022</v>
       </c>
-      <c r="H41">
+      <c r="L45" s="8">
         <v>2024</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B42" t="s">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B46" t="s">
         <v>4</v>
       </c>
-      <c r="C42">
+      <c r="C46">
         <v>266.70600000000002</v>
       </c>
-      <c r="D42">
+      <c r="D46">
+        <v>179.90280000000001</v>
+      </c>
+      <c r="E46">
         <v>94.762799999999999</v>
       </c>
-      <c r="E42">
+      <c r="F46">
+        <v>201.5676</v>
+      </c>
+      <c r="G46">
         <v>163.06199999999998</v>
       </c>
-      <c r="F42">
+      <c r="H46">
+        <v>134.83079999999998</v>
+      </c>
+      <c r="I46">
         <v>139.3776</v>
       </c>
-      <c r="G42">
+      <c r="J46">
+        <v>22.136399999999998</v>
+      </c>
+      <c r="K46">
         <v>31.305599999999998</v>
       </c>
-      <c r="H42">
+      <c r="L46">
         <v>12.477599999999999</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B43" t="s">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B47" t="s">
         <v>6</v>
       </c>
-      <c r="C43">
+      <c r="C47">
         <v>66.628799999999998</v>
       </c>
-      <c r="D43">
+      <c r="D47">
+        <v>64.807199999999995</v>
+      </c>
+      <c r="E47">
         <v>59.623199999999997</v>
       </c>
-      <c r="E43">
+      <c r="F47">
+        <v>55.1556</v>
+      </c>
+      <c r="G47">
         <v>50.835599999999999</v>
       </c>
-      <c r="F43">
+      <c r="H47">
+        <v>60.915599999999998</v>
+      </c>
+      <c r="I47">
         <v>52.192799999999998</v>
       </c>
-      <c r="G43">
+      <c r="J47">
+        <v>38.534399999999998</v>
+      </c>
+      <c r="K47">
         <v>38.124000000000002</v>
       </c>
-      <c r="H43">
+      <c r="L47">
         <v>32.842799999999997</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B44" t="s">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B48" t="s">
         <v>7</v>
       </c>
-      <c r="C44">
+      <c r="C48">
         <v>341.27639999999997</v>
       </c>
-      <c r="D44">
+      <c r="D48">
+        <v>434.87279999999998</v>
+      </c>
+      <c r="E48">
         <v>341.46359999999999</v>
       </c>
-      <c r="E44">
+      <c r="F48">
+        <v>263.90879999999999</v>
+      </c>
+      <c r="G48">
         <v>170.18279999999999</v>
       </c>
-      <c r="F44">
+      <c r="H48">
+        <v>190.15199999999999</v>
+      </c>
+      <c r="I48">
         <v>208.81440000000001</v>
       </c>
-      <c r="G44">
+      <c r="J48">
+        <v>251.06039999999999</v>
+      </c>
+      <c r="K48">
         <v>309.51</v>
       </c>
-      <c r="H44">
+      <c r="L48">
         <v>188.3844</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B45" t="s">
+    <row r="49" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B49" t="s">
         <v>8</v>
       </c>
-      <c r="C45">
+      <c r="C49">
         <v>198.3708</v>
       </c>
-      <c r="D45">
+      <c r="D49">
+        <v>212.30279999999999</v>
+      </c>
+      <c r="E49">
         <v>223.16399999999999</v>
       </c>
-      <c r="E45">
+      <c r="F49">
+        <v>221.292</v>
+      </c>
+      <c r="G49">
         <v>206.298</v>
       </c>
-      <c r="F45">
+      <c r="H49">
+        <v>211.0788</v>
+      </c>
+      <c r="I49">
         <v>200.7576</v>
       </c>
-      <c r="G45">
+      <c r="J49">
+        <v>209.87639999999999</v>
+      </c>
+      <c r="K49">
         <v>210.92400000000001</v>
       </c>
-      <c r="H45">
+      <c r="L49">
         <v>196.3152</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B46" t="s">
+    <row r="50" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B50" t="s">
         <v>9</v>
       </c>
-      <c r="C46">
+      <c r="C50">
         <v>109.8792</v>
       </c>
-      <c r="D46">
+      <c r="D50">
+        <v>94.118399999999994</v>
+      </c>
+      <c r="E50">
         <v>163.83959999999999</v>
       </c>
-      <c r="E46">
+      <c r="F50">
+        <v>86.983199999999997</v>
+      </c>
+      <c r="G50">
         <v>154.6884</v>
       </c>
-      <c r="F46">
+      <c r="H50">
+        <v>143.51400000000001</v>
+      </c>
+      <c r="I50">
         <v>132.49080000000001</v>
       </c>
-      <c r="G46">
+      <c r="J50">
+        <v>122.39279999999999</v>
+      </c>
+      <c r="K50">
         <v>79.5672</v>
       </c>
-      <c r="H46">
+      <c r="L50">
         <v>146.9556</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B47" t="s">
+    <row r="51" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B51" t="s">
         <v>11</v>
       </c>
-      <c r="C47">
+      <c r="C51">
         <v>7.7795999999999994</v>
       </c>
-      <c r="D47">
+      <c r="D51">
+        <v>8.9027999999999992</v>
+      </c>
+      <c r="E51">
         <v>12.0816</v>
       </c>
-      <c r="E47">
+      <c r="F51">
+        <v>15.3432</v>
+      </c>
+      <c r="G51">
         <v>17.020800000000001</v>
       </c>
-      <c r="F47">
+      <c r="H51">
+        <v>17.834399999999999</v>
+      </c>
+      <c r="I51">
         <v>18.561599999999999</v>
       </c>
-      <c r="G47">
+      <c r="J51">
+        <v>19.565999999999999</v>
+      </c>
+      <c r="K51">
         <v>21.366</v>
       </c>
-      <c r="H47">
+      <c r="L51">
         <v>19.148399999999999</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B48" t="s">
+    <row r="52" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B52" t="s">
         <v>13</v>
       </c>
-      <c r="C48">
+      <c r="C52">
         <v>99.244799999999998</v>
       </c>
-      <c r="D48">
+      <c r="D52">
+        <v>118.6056</v>
+      </c>
+      <c r="E52">
         <v>159.37559999999999</v>
       </c>
-      <c r="E48">
+      <c r="F52">
+        <v>178.0992</v>
+      </c>
+      <c r="G52">
         <v>187.24680000000001</v>
       </c>
-      <c r="F48">
+      <c r="H52">
+        <v>176.05799999999999</v>
+      </c>
+      <c r="I52">
         <v>183.22559999999999</v>
       </c>
-      <c r="G48">
+      <c r="J52">
+        <v>203.19839999999999</v>
+      </c>
+      <c r="K52">
         <v>226.0224</v>
       </c>
-      <c r="H48">
+      <c r="L52">
         <v>223.5204</v>
       </c>
     </row>
-    <row r="49" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B49" t="s">
+    <row r="53" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B53" t="s">
         <v>65</v>
       </c>
-      <c r="C49">
-        <f t="shared" ref="C49:H49" si="9">SUM(D52+D53)</f>
+      <c r="C53">
+        <f>SUM(C56+C57)</f>
         <v>1.8539999999999999</v>
       </c>
-      <c r="D49">
+      <c r="D53">
+        <f t="shared" ref="D53:L53" si="9">SUM(D56+D57)</f>
+        <v>9.280800000000001</v>
+      </c>
+      <c r="E53">
         <f t="shared" si="9"/>
         <v>25.869599999999998</v>
       </c>
-      <c r="E49">
+      <c r="F53">
+        <f t="shared" si="9"/>
+        <v>43.081199999999995</v>
+      </c>
+      <c r="G53">
         <f t="shared" si="9"/>
         <v>49.215599999999995</v>
       </c>
-      <c r="F49">
+      <c r="H53">
+        <f t="shared" si="9"/>
+        <v>49.111199999999997</v>
+      </c>
+      <c r="I53">
         <f t="shared" si="9"/>
         <v>45.878399999999999</v>
       </c>
-      <c r="G49">
+      <c r="J53">
+        <f t="shared" si="9"/>
+        <v>74.401200000000003</v>
+      </c>
+      <c r="K53">
         <f t="shared" si="9"/>
         <v>128.6028</v>
       </c>
-      <c r="H49">
+      <c r="L53">
         <f t="shared" si="9"/>
         <v>209.85119999999998</v>
       </c>
     </row>
-    <row r="50" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B50" t="s">
+    <row r="54" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B54" t="s">
         <v>67</v>
       </c>
-      <c r="C50">
+      <c r="C54">
         <v>1.1663999999999999</v>
       </c>
-      <c r="D50">
+      <c r="D54">
+        <v>1.1052</v>
+      </c>
+      <c r="E54">
         <v>0.57240000000000002</v>
       </c>
-      <c r="E50">
-        <v>0</v>
-      </c>
-      <c r="F50">
+      <c r="F54">
+        <v>0.63</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
+        <v>0.38879999999999998</v>
+      </c>
+      <c r="I54">
         <v>0.33839999999999998</v>
       </c>
-      <c r="G50">
+      <c r="J54">
+        <v>0.57599999999999996</v>
+      </c>
+      <c r="K54">
         <v>1.0151999999999999</v>
       </c>
-      <c r="H50">
+      <c r="L54">
         <v>0.87839999999999996</v>
       </c>
     </row>
-    <row r="52" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B52" t="s">
+    <row r="56" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B56" t="s">
         <v>14</v>
       </c>
-      <c r="C52">
-        <v>0.44639999999999996</v>
-      </c>
-      <c r="D52">
+      <c r="C56">
         <v>1.8251999999999999</v>
       </c>
-      <c r="E52">
+      <c r="D56">
+        <v>9.2232000000000003</v>
+      </c>
+      <c r="E56">
         <v>23.13</v>
       </c>
-      <c r="F52">
+      <c r="F56">
+        <v>29.491199999999999</v>
+      </c>
+      <c r="G56">
         <v>29.581199999999999</v>
       </c>
-      <c r="G52">
+      <c r="H56">
+        <v>29.026799999999998</v>
+      </c>
+      <c r="I56">
         <v>28.357199999999999</v>
       </c>
-      <c r="H52">
+      <c r="J56">
+        <v>56.43</v>
+      </c>
+      <c r="K56">
         <v>112.2732</v>
       </c>
-      <c r="I52">
+      <c r="L56">
         <v>193.50719999999998</v>
       </c>
     </row>
-    <row r="53" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B53" t="s">
+    <row r="57" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B57" t="s">
         <v>15</v>
       </c>
-      <c r="C53">
-        <v>0</v>
-      </c>
-      <c r="D53">
+      <c r="C57">
         <v>2.8799999999999999E-2</v>
       </c>
-      <c r="E53">
+      <c r="D57">
+        <v>5.7599999999999998E-2</v>
+      </c>
+      <c r="E57">
         <v>2.7395999999999998</v>
       </c>
-      <c r="F53">
+      <c r="F57">
+        <v>13.59</v>
+      </c>
+      <c r="G57">
         <v>19.634399999999999</v>
       </c>
-      <c r="G53">
+      <c r="H57">
+        <v>20.084399999999999</v>
+      </c>
+      <c r="I57">
         <v>17.5212</v>
       </c>
-      <c r="H53">
+      <c r="J57">
+        <v>17.9712</v>
+      </c>
+      <c r="K57">
         <v>16.329599999999999</v>
       </c>
-      <c r="I53">
+      <c r="L57">
         <v>16.344000000000001</v>
       </c>
     </row>
-    <row r="56" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B56" t="s">
+    <row r="60" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B60" t="s">
         <v>71</v>
       </c>
-      <c r="C56">
+      <c r="C60" s="8">
         <v>2007</v>
       </c>
-      <c r="D56">
+      <c r="D60" s="8">
+        <v>2008</v>
+      </c>
+      <c r="E60" s="8">
         <v>2010</v>
       </c>
-      <c r="E56">
+      <c r="F60" s="8">
+        <v>2012</v>
+      </c>
+      <c r="G60" s="8">
         <v>2014</v>
       </c>
-      <c r="F56">
+      <c r="H60" s="8">
+        <v>2016</v>
+      </c>
+      <c r="I60" s="8">
         <v>2018</v>
       </c>
-      <c r="G56">
+      <c r="J60" s="8">
+        <v>2020</v>
+      </c>
+      <c r="K60" s="8">
         <v>2022</v>
       </c>
-      <c r="H56">
+      <c r="L60" s="8">
         <v>2024</v>
       </c>
     </row>
-    <row r="57" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B57" t="s">
+    <row r="61" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B61" t="s">
         <v>4</v>
       </c>
-      <c r="C57" s="5">
-        <f>(C30-C42)/C42</f>
+      <c r="C61" s="5">
+        <f t="shared" ref="C61:H69" si="10">(C34-C46)/C46</f>
         <v>1.4997787826154102E-5</v>
       </c>
-      <c r="D57" s="5">
-        <f>(D30-D42)/D42</f>
-        <v>-2.0468906527305042E-3</v>
-      </c>
-      <c r="E57" s="5">
-        <f>(E30-E42)/E42</f>
-        <v>-2.0065987170523346E-2</v>
-      </c>
-      <c r="F57" s="5">
-        <f>(F30-F42)/F42</f>
-        <v>-5.025628221464494E-2</v>
-      </c>
-      <c r="G57" s="5">
-        <f>(G30-G42)/G42</f>
-        <v>-5.0169937646938875E-2</v>
-      </c>
-      <c r="H57" s="5">
-        <f>(H30-H42)/H42</f>
-        <v>-4.9817272552413423E-2</v>
-      </c>
-    </row>
-    <row r="58" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B58" t="s">
+      <c r="D61" s="5">
+        <f t="shared" ref="D61:L61" si="11">(D34-D46)/D46</f>
+        <v>0</v>
+      </c>
+      <c r="E61" s="5">
+        <f t="shared" si="11"/>
+        <v>-2.9547459550819731E-5</v>
+      </c>
+      <c r="F61" s="5">
+        <f t="shared" si="11"/>
+        <v>-4.9988688658295838E-2</v>
+      </c>
+      <c r="G61" s="5">
+        <f t="shared" si="11"/>
+        <v>-2.0065987170524567E-2</v>
+      </c>
+      <c r="H61" s="5">
+        <f t="shared" si="11"/>
+        <v>-5.0005636694285635E-2</v>
+      </c>
+      <c r="I61" s="5">
+        <f t="shared" si="11"/>
+        <v>-5.0256282214646369E-2</v>
+      </c>
+      <c r="J61" s="5">
+        <f t="shared" si="11"/>
+        <v>-4.9845503333876259E-2</v>
+      </c>
+      <c r="K61" s="5">
+        <f t="shared" si="11"/>
+        <v>-5.0169937646939104E-2</v>
+      </c>
+      <c r="L61" s="5">
+        <f t="shared" si="11"/>
+        <v>-4.9817272552414284E-2</v>
+      </c>
+    </row>
+    <row r="62" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B62" t="s">
         <v>6</v>
       </c>
-      <c r="C58" s="5">
-        <f>(C31-C43)/C43</f>
-        <v>0</v>
-      </c>
-      <c r="D58" s="5">
-        <f>(D31-D43)/D43</f>
-        <v>0.10000000000000009</v>
-      </c>
-      <c r="E58" s="5">
-        <f>(E31-E43)/E43</f>
+      <c r="C62" s="5">
+        <f t="shared" si="10"/>
+        <v>2.1328396602072984E-16</v>
+      </c>
+      <c r="D62" s="5">
+        <f t="shared" ref="D62:L62" si="12">(D35-D47)/D47</f>
+        <v>-2.3258526830352295E-2</v>
+      </c>
+      <c r="E62" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="F62" s="5">
+        <f t="shared" si="12"/>
+        <v>-4.999999999999994E-2</v>
+      </c>
+      <c r="G62" s="5">
+        <f t="shared" si="12"/>
         <v>-5.0000000000000058E-2</v>
       </c>
-      <c r="F58" s="5">
-        <f>(F31-F43)/F43</f>
-        <v>-4.9999999999999982E-2</v>
-      </c>
-      <c r="G58" s="5">
-        <f>(G31-G43)/G43</f>
+      <c r="H62" s="5">
+        <f t="shared" si="12"/>
+        <v>-5.0000000000000128E-2</v>
+      </c>
+      <c r="I62" s="5">
+        <f t="shared" si="12"/>
+        <v>-4.9999999999999843E-2</v>
+      </c>
+      <c r="J62" s="5">
+        <f t="shared" si="12"/>
+        <v>-5.0000000000000454E-2</v>
+      </c>
+      <c r="K62" s="5">
+        <f t="shared" si="12"/>
         <v>-5.0000000000000142E-2</v>
       </c>
-      <c r="H58" s="5">
-        <f>(H31-H43)/H43</f>
-        <v>-7.0907474393170147E-2</v>
-      </c>
-    </row>
-    <row r="59" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B59" t="s">
+      <c r="L62" s="5">
+        <f t="shared" si="12"/>
+        <v>-7.0907474393169814E-2</v>
+      </c>
+    </row>
+    <row r="63" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B63" t="s">
         <v>7</v>
       </c>
-      <c r="C59" s="5">
-        <f>(C32-C44)/C44</f>
-        <v>3.3312247117473121E-16</v>
-      </c>
-      <c r="D59" s="5">
-        <f>(D32-D44)/D44</f>
-        <v>0</v>
-      </c>
-      <c r="E59" s="5">
-        <f>(E32-E44)/E44</f>
+      <c r="C63" s="5">
+        <f t="shared" si="10"/>
+        <v>1.665612355873656E-16</v>
+      </c>
+      <c r="D63" s="5">
+        <f t="shared" ref="D63:L63" si="13">(D36-D48)/D48</f>
+        <v>0</v>
+      </c>
+      <c r="E63" s="5">
+        <f t="shared" si="13"/>
+        <v>4.0346434675655699E-2</v>
+      </c>
+      <c r="F63" s="5">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="G63" s="5">
+        <f t="shared" si="13"/>
         <v>5.5001798066548535E-2</v>
       </c>
-      <c r="F59" s="5">
-        <f>(F32-F44)/F44</f>
-        <v>-5.0000000000001897E-2</v>
-      </c>
-      <c r="G59" s="5">
-        <f>(G32-G44)/G44</f>
-        <v>-4.9999999999998199E-2</v>
-      </c>
-      <c r="H59" s="5">
-        <f>(H32-H44)/H44</f>
-        <v>-3.314954152603785E-2</v>
-      </c>
-    </row>
-    <row r="60" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B60" t="s">
+      <c r="H63" s="5">
+        <f t="shared" si="13"/>
+        <v>1.1778771920803403E-2</v>
+      </c>
+      <c r="I63" s="5">
+        <f t="shared" si="13"/>
+        <v>-5.0000000000000946E-2</v>
+      </c>
+      <c r="J63" s="5">
+        <f t="shared" si="13"/>
+        <v>-5.0000000000000128E-2</v>
+      </c>
+      <c r="K63" s="5">
+        <f t="shared" si="13"/>
+        <v>-4.9999999999998018E-2</v>
+      </c>
+      <c r="L63" s="5">
+        <f t="shared" si="13"/>
+        <v>-1.7662873399837544E-2</v>
+      </c>
+    </row>
+    <row r="64" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B64" t="s">
         <v>8</v>
-      </c>
-      <c r="C60" s="5">
-        <f>(C33-C45)/C45</f>
-        <v>-4.0328516091992146E-6</v>
-      </c>
-      <c r="D60" s="5">
-        <f>(D33-D45)/D45</f>
-        <v>-1.8960585838748101E-2</v>
-      </c>
-      <c r="E60" s="5">
-        <f>(E33-E45)/E45</f>
-        <v>2.6490740873154305E-2</v>
-      </c>
-      <c r="F60" s="5">
-        <f>(F33-F45)/F45</f>
-        <v>-2.1519673098804211E-2</v>
-      </c>
-      <c r="G60" s="5">
-        <f>(G33-G45)/G45</f>
-        <v>3.7969504759447006E-2</v>
-      </c>
-      <c r="H60" s="5">
-        <f>(H33-H45)/H45</f>
-        <v>9.9970863183289335E-2</v>
-      </c>
-    </row>
-    <row r="61" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B61" t="s">
-        <v>9</v>
-      </c>
-      <c r="C61" s="5">
-        <f>(C34-C46)/C46</f>
-        <v>-1.2933161795136844E-16</v>
-      </c>
-      <c r="D61" s="5">
-        <f>(D34-D46)/D46</f>
-        <v>-1.7347277111518834E-16</v>
-      </c>
-      <c r="E61" s="5">
-        <f>(E34-E46)/E46</f>
-        <v>-1.8373523438347029E-16</v>
-      </c>
-      <c r="F61" s="5">
-        <f>(F34-F46)/F46</f>
-        <v>3.4915631877834577E-3</v>
-      </c>
-      <c r="G61" s="5">
-        <f>(G34-G46)/G46</f>
-        <v>0.10000000000000005</v>
-      </c>
-      <c r="H61" s="5">
-        <f>(H34-H46)/H46</f>
-        <v>-3.8680675565142133E-16</v>
-      </c>
-    </row>
-    <row r="62" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B62" t="s">
-        <v>11</v>
-      </c>
-      <c r="C62" s="5">
-        <f>(C35-C47)/C47</f>
-        <v>-4.9999999999999677E-2</v>
-      </c>
-      <c r="D62" s="5">
-        <f>(D35-D47)/D47</f>
-        <v>-4.9999999999999975E-2</v>
-      </c>
-      <c r="E62" s="5">
-        <f>(E35-E47)/E47</f>
-        <v>-5.0000000000000065E-2</v>
-      </c>
-      <c r="F62" s="5">
-        <f>(F35-F47)/F47</f>
-        <v>-0.11522498060512014</v>
-      </c>
-      <c r="G62" s="5">
-        <f>(G35-G47)/G47</f>
-        <v>-8.7055602358887541E-2</v>
-      </c>
-      <c r="H62" s="5">
-        <f>(H35-H47)/H47</f>
-        <v>-4.9999999999999954E-2</v>
-      </c>
-    </row>
-    <row r="63" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B63" t="s">
-        <v>13</v>
-      </c>
-      <c r="C63" s="5">
-        <f>(C36-C48)/C48</f>
-        <v>-5.0045946991681238E-2</v>
-      </c>
-      <c r="D63" s="5">
-        <f>(D36-D48)/D48</f>
-        <v>6.1611689618737489E-2</v>
-      </c>
-      <c r="E63" s="5">
-        <f>(E36-E48)/E48</f>
-        <v>-4.9983764742574682E-2</v>
-      </c>
-      <c r="F63" s="5">
-        <f>(F36-F48)/F48</f>
-        <v>-4.9977186594012832E-2</v>
-      </c>
-      <c r="G63" s="5">
-        <f>(G36-G48)/G48</f>
-        <v>-3.547780418591031E-2</v>
-      </c>
-      <c r="H63" s="5">
-        <f>(H36-H48)/H48</f>
-        <v>-2.7825632862439873E-3</v>
-      </c>
-    </row>
-    <row r="64" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B64" t="s">
-        <v>65</v>
       </c>
       <c r="C64" s="5">
         <f>(C37-C49)/C49</f>
-        <v>-4.9999999999999885E-2</v>
+        <v>-4.0328516091992146E-6</v>
       </c>
       <c r="D64" s="5">
-        <f>(D37-D49)/D49</f>
-        <v>-5.0000000000000509E-2</v>
+        <f t="shared" ref="D64:L64" si="14">(D37-D49)/D49</f>
+        <v>0</v>
       </c>
       <c r="E64" s="5">
-        <f>(E37-E49)/E49</f>
-        <v>-3.6935849608660622E-2</v>
+        <f t="shared" si="14"/>
+        <v>-8.3974117689232814E-3</v>
       </c>
       <c r="F64" s="5">
-        <f>(F37-F49)/F49</f>
-        <v>0.12585138104205898</v>
+        <f t="shared" si="14"/>
+        <v>-9.0378323667137303E-6</v>
       </c>
       <c r="G64" s="5">
-        <f>(G37-G49)/G49</f>
-        <v>-5.0000000000000842E-2</v>
+        <f t="shared" si="14"/>
+        <v>7.267157219168438E-2</v>
       </c>
       <c r="H64" s="5">
-        <f>(H37-H49)/H49</f>
-        <v>-5.0065189048239721E-2</v>
-      </c>
-    </row>
-    <row r="65" spans="2:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="14"/>
+        <v>4.8376246217053491E-2</v>
+      </c>
+      <c r="I64" s="5">
+        <f t="shared" si="14"/>
+        <v>2.3181823481749714E-2</v>
+      </c>
+      <c r="J64" s="5">
+        <f t="shared" si="14"/>
+        <v>1.2527609176529604E-2</v>
+      </c>
+      <c r="K64" s="5">
+        <f t="shared" si="14"/>
+        <v>4.9145663841002926E-2</v>
+      </c>
+      <c r="L64" s="5">
+        <f t="shared" si="14"/>
+        <v>9.9970863183288905E-2</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B65" t="s">
+        <v>9</v>
+      </c>
+      <c r="C65" s="5">
+        <f t="shared" si="10"/>
+        <v>-1.2933161795136844E-16</v>
+      </c>
+      <c r="D65" s="5">
+        <f t="shared" ref="D65:L65" si="15">(D38-D50)/D50</f>
+        <v>-1.509891234360338E-16</v>
+      </c>
+      <c r="E65" s="5">
+        <f t="shared" si="15"/>
+        <v>5.2041831334556501E-16</v>
+      </c>
+      <c r="F65" s="5">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="G65" s="5">
+        <f t="shared" si="15"/>
+        <v>7.3494093753388118E-16</v>
+      </c>
+      <c r="H65" s="5">
+        <f t="shared" si="15"/>
+        <v>5.9412411535607685E-16</v>
+      </c>
+      <c r="I65" s="5">
+        <f t="shared" si="15"/>
+        <v>3.4915631877830288E-3</v>
+      </c>
+      <c r="J65" s="5">
+        <f t="shared" si="15"/>
+        <v>4.6443433650351992E-16</v>
+      </c>
+      <c r="K65" s="5">
+        <f t="shared" si="15"/>
+        <v>0.10000000000000023</v>
+      </c>
+      <c r="L65" s="5">
+        <f t="shared" si="15"/>
+        <v>1.9340337782571066E-16</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B66" t="s">
+        <v>11</v>
+      </c>
+      <c r="C66" s="5">
+        <f t="shared" si="10"/>
+        <v>-5.0000000000000017E-2</v>
+      </c>
+      <c r="D66" s="5">
+        <f t="shared" ref="D66:L66" si="16">(D39-D51)/D51</f>
+        <v>-1.6835152985577525E-2</v>
+      </c>
+      <c r="E66" s="5">
+        <f t="shared" si="16"/>
+        <v>-4.9999999999999829E-2</v>
+      </c>
+      <c r="F66" s="5">
+        <f t="shared" si="16"/>
+        <v>-4.9999999999999802E-2</v>
+      </c>
+      <c r="G66" s="5">
+        <f t="shared" si="16"/>
+        <v>-4.9999999999999857E-2</v>
+      </c>
+      <c r="H66" s="5">
+        <f t="shared" si="16"/>
+        <v>-5.2301170771093773E-2</v>
+      </c>
+      <c r="I66" s="5">
+        <f t="shared" si="16"/>
+        <v>-5.0000000000000079E-2</v>
+      </c>
+      <c r="J66" s="5">
+        <f t="shared" si="16"/>
+        <v>6.4139834406623769E-2</v>
+      </c>
+      <c r="K66" s="5">
+        <f t="shared" si="16"/>
+        <v>-8.7055602358887541E-2</v>
+      </c>
+      <c r="L66" s="5">
+        <f t="shared" si="16"/>
+        <v>-4.999999999999958E-2</v>
+      </c>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B67" t="s">
+        <v>13</v>
+      </c>
+      <c r="C67" s="5">
+        <f t="shared" si="10"/>
+        <v>-5.0045946991681238E-2</v>
+      </c>
+      <c r="D67" s="5">
+        <f t="shared" ref="D67:L67" si="17">(D40-D52)/D52</f>
+        <v>-4.4544833183818036E-2</v>
+      </c>
+      <c r="E67" s="5">
+        <f t="shared" si="17"/>
+        <v>6.1611689618737135E-2</v>
+      </c>
+      <c r="F67" s="5">
+        <f t="shared" si="17"/>
+        <v>-4.9995732715250846E-2</v>
+      </c>
+      <c r="G67" s="5">
+        <f t="shared" si="17"/>
+        <v>-4.998376474257514E-2</v>
+      </c>
+      <c r="H67" s="5">
+        <f t="shared" si="17"/>
+        <v>1.0391461904599436E-2</v>
+      </c>
+      <c r="I67" s="5">
+        <f t="shared" si="17"/>
+        <v>-4.9977186594013144E-2</v>
+      </c>
+      <c r="J67" s="5">
+        <f t="shared" si="17"/>
+        <v>-4.9992519626138654E-2</v>
+      </c>
+      <c r="K67" s="5">
+        <f t="shared" si="17"/>
+        <v>-1.4719332431453742E-3</v>
+      </c>
+      <c r="L67" s="5">
+        <f t="shared" si="17"/>
+        <v>2.0561914681321663E-2</v>
+      </c>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B68" t="s">
+        <v>65</v>
+      </c>
+      <c r="C68" s="5">
+        <f t="shared" si="10"/>
+        <v>-5.0000000000000488E-2</v>
+      </c>
+      <c r="D68" s="5">
+        <f t="shared" ref="D68:L68" si="18">(D41-D53)/D53</f>
+        <v>9.2061029221619014E-3</v>
+      </c>
+      <c r="E68" s="5">
+        <f t="shared" si="18"/>
+        <v>-4.9999999999999961E-2</v>
+      </c>
+      <c r="F68" s="5">
+        <f t="shared" si="18"/>
+        <v>-4.9999999999999871E-2</v>
+      </c>
+      <c r="G68" s="5">
+        <f t="shared" si="18"/>
+        <v>-3.6935849608661059E-2</v>
+      </c>
+      <c r="H68" s="5">
+        <f t="shared" si="18"/>
+        <v>2.5766016713087286E-3</v>
+      </c>
+      <c r="I68" s="5">
+        <f t="shared" si="18"/>
+        <v>0.12585138104205931</v>
+      </c>
+      <c r="J68" s="5">
+        <f t="shared" si="18"/>
+        <v>-5.0000000000000239E-2</v>
+      </c>
+      <c r="K68" s="5">
+        <f t="shared" si="18"/>
+        <v>-5.0000000000000065E-2</v>
+      </c>
+      <c r="L68" s="5">
+        <f t="shared" si="18"/>
+        <v>-5.0065189048239589E-2</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B69" t="s">
         <v>67</v>
       </c>
-      <c r="C65" s="5">
-        <f>(C38-C50)/C50</f>
+      <c r="C69" s="5">
+        <f t="shared" si="10"/>
         <v>-1</v>
       </c>
-      <c r="D65" s="5">
-        <f>(D38-D50)/D50</f>
-        <v>4.8218029350104746E-2</v>
-      </c>
-      <c r="E65" s="5" t="e">
-        <f>(E38-E50)/E50</f>
+      <c r="D69" s="5">
+        <f t="shared" ref="D69:L69" si="19">(D42-D54)/D54</f>
+        <v>-1</v>
+      </c>
+      <c r="E69" s="5">
+        <f t="shared" si="19"/>
+        <v>4.8218029350104941E-2</v>
+      </c>
+      <c r="F69" s="5">
+        <f t="shared" si="19"/>
+        <v>-1</v>
+      </c>
+      <c r="G69" s="5" t="e">
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F65" s="5">
-        <f>(F38-F50)/F50</f>
+      <c r="H69" s="5">
+        <f t="shared" si="19"/>
+        <v>4.1666666666666789E-2</v>
+      </c>
+      <c r="I69" s="5">
+        <f t="shared" si="19"/>
         <v>-1</v>
       </c>
-      <c r="G65" s="5">
-        <f>(G38-G50)/G50</f>
-        <v>-0.70695429472025217</v>
-      </c>
-      <c r="H65" s="5">
-        <f>(H38-H50)/H50</f>
+      <c r="J69" s="5">
+        <f t="shared" si="19"/>
+        <v>-1</v>
+      </c>
+      <c r="K69" s="5">
+        <f t="shared" si="19"/>
+        <v>-0.70695429472025206</v>
+      </c>
+      <c r="L69" s="5">
+        <f t="shared" si="19"/>
         <v>-0.68550774134790526</v>
       </c>
     </row>
-    <row r="67" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B67" t="s">
-        <v>75</v>
-      </c>
-      <c r="C67" s="7">
-        <f>SUM(C30:C38)-SUM(C42:C50)</f>
-        <v>-6.6116800000002058</v>
-      </c>
-      <c r="D67" s="7">
-        <f>SUM(D30:D38)-SUM(D42:D50)</f>
-        <v>9.4864707323349649</v>
-      </c>
-      <c r="E67" s="7">
-        <f>SUM(E30:E38)-SUM(E42:E50)</f>
-        <v>-3.0165931393499932</v>
-      </c>
-      <c r="F67" s="7">
-        <f>SUM(F30:F38)-SUM(F42:F50)</f>
-        <v>-29.772997924100991</v>
-      </c>
-      <c r="G67" s="7">
-        <f>SUM(G30:G38)-SUM(G42:G50)</f>
-        <v>-20.013548626947568</v>
-      </c>
-      <c r="H67" s="7">
-        <f>SUM(H30:H38)-SUM(H42:H50)</f>
-        <v>-2.2572261494244685</v>
-      </c>
-      <c r="I67" t="s">
+    <row r="71" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B71" t="s">
+        <v>74</v>
+      </c>
+      <c r="C71" s="6">
+        <f>SUM(C34:C42)-SUM(C46:C54)</f>
+        <v>-6.6116800000004332</v>
+      </c>
+      <c r="D71" s="6">
+        <f t="shared" ref="D71:L71" si="20">SUM(D34:D42)-SUM(D46:D54)</f>
+        <v>-7.9602266666668129</v>
+      </c>
+      <c r="E71" s="6">
+        <f t="shared" si="20"/>
+        <v>19.849478831514261</v>
+      </c>
+      <c r="F71" s="6">
+        <f t="shared" si="20"/>
+        <v>-25.291300000000319</v>
+      </c>
+      <c r="G71" s="6">
+        <f t="shared" si="20"/>
+        <v>6.6398408905297401</v>
+      </c>
+      <c r="H71" s="6">
+        <f t="shared" si="20"/>
+        <v>3.7023570382850721</v>
+      </c>
+      <c r="I71" s="6">
+        <f t="shared" si="20"/>
+        <v>-19.588152754180669</v>
+      </c>
+      <c r="J71" s="6">
+        <f t="shared" si="20"/>
+        <v>-26.15339048542296</v>
+      </c>
+      <c r="K71" s="6">
+        <f t="shared" si="20"/>
+        <v>-9.9701398842553317</v>
+      </c>
+      <c r="L71" s="6">
+        <f t="shared" si="20"/>
+        <v>5.8781875866304745</v>
+      </c>
+      <c r="M71" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="68" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C68" s="5">
-        <f>C67/SUM(C42:C50)</f>
-        <v>-6.0496328138011915E-3</v>
-      </c>
-      <c r="D68" s="5">
-        <f t="shared" ref="D68:H68" si="10">D67/SUM(D42:D50)</f>
-        <v>8.7776540975851303E-3</v>
-      </c>
-      <c r="E68" s="5">
-        <f t="shared" si="10"/>
-        <v>-3.0209735509989419E-3</v>
-      </c>
-      <c r="F68" s="5">
-        <f t="shared" si="10"/>
-        <v>-3.0329940556552859E-2</v>
-      </c>
-      <c r="G68" s="5">
-        <f t="shared" si="10"/>
-        <v>-1.9125417776573277E-2</v>
-      </c>
-      <c r="H68" s="5">
-        <f t="shared" si="10"/>
-        <v>-2.1906862454064919E-3</v>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="C72" s="5">
+        <f>C71/SUM(C46:C54)</f>
+        <v>-6.0496328138013996E-3</v>
+      </c>
+      <c r="D72" s="5">
+        <f t="shared" ref="D72:L72" si="21">D71/SUM(D46:D54)</f>
+        <v>-7.0826924094444946E-3</v>
+      </c>
+      <c r="E72" s="5">
+        <f t="shared" si="21"/>
+        <v>1.8366351841100942E-2</v>
+      </c>
+      <c r="F72" s="5">
+        <f t="shared" si="21"/>
+        <v>-2.3724069021204341E-2</v>
+      </c>
+      <c r="G72" s="5">
+        <f t="shared" si="21"/>
+        <v>6.6494826403582603E-3</v>
+      </c>
+      <c r="H72" s="5">
+        <f t="shared" si="21"/>
+        <v>3.7630031014695971E-3</v>
+      </c>
+      <c r="I72" s="5">
+        <f t="shared" si="21"/>
+        <v>-1.9954574616956926E-2</v>
+      </c>
+      <c r="J72" s="5">
+        <f t="shared" si="21"/>
+        <v>-2.777129031669285E-2</v>
+      </c>
+      <c r="K72" s="5">
+        <f t="shared" si="21"/>
+        <v>-9.5277001661020176E-3</v>
+      </c>
+      <c r="L72" s="5">
+        <f t="shared" si="21"/>
+        <v>5.7049067490352766E-3</v>
       </c>
     </row>
   </sheetData>

--- a/ELC_data_Spain.xlsx
+++ b/ELC_data_Spain.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Documents\TEMOA\PROJECT\Models-and-scenarios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93D7079C-FB3F-46AB-B919-DC34978FEFFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43FE3A73-BAF8-4037-94D3-722989BA3FC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="6" xr2:uid="{8BBF5E45-81C8-439F-BD27-48A9AF2DFBEB}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1165" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1164" uniqueCount="82">
   <si>
     <t>electricity generation sources in Spain</t>
   </si>
@@ -284,7 +284,7 @@
     <t>ELC_BGS_LAN_N</t>
   </si>
   <si>
-    <t>ELC_NGA_CC_P</t>
+    <t>ELC_CHP_NGA_TAP_N</t>
   </si>
 </sst>
 </file>
@@ -811,10 +811,10 @@
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="43" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="43" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="20% - Colore 1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -8460,28 +8460,28 @@
                   <c:v>179.90280000000001</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>94.760000000000076</c:v>
+                  <c:v>94.760000000000062</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>191.49150000000009</c:v>
+                  <c:v>191.4915</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>159.78999999999991</c:v>
+                  <c:v>159.78999999999979</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>128.0885000000001</c:v>
+                  <c:v>128.08850000000018</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>132.37299999999991</c:v>
+                  <c:v>132.37299999999999</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>21.03299999999998</c:v>
+                  <c:v>21.032999999999959</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>29.734999999999982</c:v>
+                  <c:v>29.734999999999957</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>11.855999999999995</c:v>
+                  <c:v>11.856000000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8562,7 +8562,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>66.628800000000012</c:v>
+                  <c:v>66.628799999999998</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>63.299879999999987</c:v>
@@ -8571,7 +8571,7 @@
                   <c:v>59.623199999999997</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>52.397820000000003</c:v>
+                  <c:v>52.397819999999967</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>48.293819999999997</c:v>
@@ -8580,13 +8580,13 @@
                   <c:v>57.86981999999999</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>49.583160000000007</c:v>
+                  <c:v>49.583159999999999</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>36.607679999999981</c:v>
+                  <c:v>36.607680000000002</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>36.217799999999997</c:v>
+                  <c:v>36.217800000000011</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>30.513999999999999</c:v>
@@ -8670,34 +8670,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>341.27640000000002</c:v>
+                  <c:v>341.27640000000008</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>434.87279999999998</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>355.24043883151421</c:v>
+                  <c:v>341.46359999999999</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>263.90879999999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>179.5431599999998</c:v>
+                  <c:v>179.54315999999992</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>192.3917570382846</c:v>
+                  <c:v>180.64439999999988</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>198.37367999999981</c:v>
+                  <c:v>208.81440000000009</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>238.50737999999996</c:v>
+                  <c:v>251.06040000000019</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>294.03450000000061</c:v>
+                  <c:v>294.03450000000021</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>185.05699019229564</c:v>
+                  <c:v>184.15325839555859</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8784,28 +8784,28 @@
                   <c:v>212.30279999999999</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>223.40450000000021</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>221.29</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>221.28999999999991</c:v>
-                </c:pt>
                 <c:pt idx="4">
-                  <c:v>221.29000000000011</c:v>
+                  <c:v>208.50232205901611</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>221.29000000000019</c:v>
+                  <c:v>223.29959885294511</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>205.41152724581971</c:v>
+                  <c:v>200.76</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>212.50564951457699</c:v>
+                  <c:v>209.88000000000011</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>221.28999999999971</c:v>
+                  <c:v>223.40450000000001</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>215.941</c:v>
+                  <c:v>215.94100000000009</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8889,31 +8889,31 @@
                   <c:v>109.87919999999998</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>94.11839999999998</c:v>
+                  <c:v>94.118399999999994</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>163.83960000000008</c:v>
+                  <c:v>163.83960000000005</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>86.983199999999997</c:v>
+                  <c:v>86.983200000000011</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>154.68840000000012</c:v>
+                  <c:v>154.68840000000006</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>143.5140000000001</c:v>
+                  <c:v>143.51400000000007</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>132.95339999999993</c:v>
+                  <c:v>132.95340000000002</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>122.39280000000005</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>87.523920000000018</c:v>
+                  <c:v>87.523920000000004</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>146.95560000000003</c:v>
+                  <c:v>146.95560000000006</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8994,16 +8994,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>7.3906199999999993</c:v>
+                  <c:v>7.3906200000000011</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>8.7529199999999996</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>11.477520000000002</c:v>
+                  <c:v>13.289760000000005</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>14.576040000000003</c:v>
+                  <c:v>14.576040000000011</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>16.169760000000004</c:v>
@@ -9015,13 +9015,13 @@
                   <c:v>17.633519999999997</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>20.820959999999999</c:v>
+                  <c:v>20.820960000000007</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>19.505970000000008</c:v>
+                  <c:v>19.505970000000005</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>18.190980000000007</c:v>
+                  <c:v>18.190980000000003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9104,34 +9104,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>94.277999999999992</c:v>
+                  <c:v>94.278000000000006</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>113.32233333333335</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>169.19499999999999</c:v>
+                  <c:v>159.37999999999997</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>169.19499999999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>177.88749999999999</c:v>
+                  <c:v>177.88750000000002</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>177.88749999999996</c:v>
+                  <c:v>175.11315935382538</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>174.06849999999997</c:v>
+                  <c:v>174.06849999999994</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>193.04000000000002</c:v>
+                  <c:v>193.04</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>225.6897101157445</c:v>
+                  <c:v>223.57521011574451</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>228.11640739433489</c:v>
+                  <c:v>228.28940093056423</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9214,34 +9214,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>1.761299999999999</c:v>
+                  <c:v>1.7613000000000001</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>9.3662400000000012</c:v>
+                  <c:v>9.3662399999999995</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>24.57612</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>40.927140000000001</c:v>
+                  <c:v>43.081199999999995</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>47.397779999999976</c:v>
+                  <c:v>47.397780000000004</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>49.237739999999974</c:v>
+                  <c:v>49.237739999999988</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>51.652260000000012</c:v>
+                  <c:v>45.878399999999985</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>70.681139999999985</c:v>
+                  <c:v>74.401199999999989</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>122.17265999999999</c:v>
+                  <c:v>122.17265999999989</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>199.34496000000004</c:v>
+                  <c:v>199.34496000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9330,16 +9330,16 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.60000000000000009</c:v>
+                  <c:v>0.6</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.12942089052995509</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.40500000000000003</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0</c:v>
@@ -14062,15 +14062,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>20955</xdr:colOff>
+      <xdr:colOff>173355</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>148590</xdr:rowOff>
+      <xdr:rowOff>129540</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>28</xdr:col>
-      <xdr:colOff>152400</xdr:colOff>
+      <xdr:colOff>304800</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -23526,11 +23526,11 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
       <c r="D2">
         <f>0.0036</f>
         <v>3.5999999999999999E-3</v>
@@ -25896,7 +25896,7 @@
         <v>56</v>
       </c>
       <c r="C2">
-        <v>4.6937302325581394</v>
+        <v>4.6937302325581411</v>
       </c>
       <c r="D2">
         <v>4.6937302325581403</v>
@@ -25908,10 +25908,10 @@
         <v>4.4590437209302323</v>
       </c>
       <c r="G2">
-        <v>4.2243572093023261</v>
+        <v>4.2243572093023243</v>
       </c>
       <c r="H2">
-        <v>3.9896706976744181</v>
+        <v>3.989670697674419</v>
       </c>
       <c r="I2">
         <v>3.754984186046511</v>
@@ -25946,22 +25946,22 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>1.8284065116279069</v>
+        <v>1.828406511627908</v>
       </c>
       <c r="H3">
         <v>2.9377925581395372</v>
       </c>
       <c r="I3">
-        <v>4.4910753488372066</v>
+        <v>4.4910753488372048</v>
       </c>
       <c r="J3">
-        <v>8.499918139534886</v>
+        <v>8.4999181395348877</v>
       </c>
       <c r="K3">
-        <v>8.0063309302325631</v>
+        <v>8.0063309302325596</v>
       </c>
       <c r="L3">
-        <v>7.5127437209302377</v>
+        <v>7.5127437209302332</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
@@ -25978,10 +25978,10 @@
         <v>4.0591897674418584</v>
       </c>
       <c r="E4">
-        <v>6.7837897674418617</v>
+        <v>8.5960297674418644</v>
       </c>
       <c r="F4">
-        <v>10.11699627906977</v>
+        <v>10.116996279069779</v>
       </c>
       <c r="G4">
         <v>10.11699627906977</v>
@@ -25993,7 +25993,7 @@
         <v>9.3874604651162805</v>
       </c>
       <c r="J4">
-        <v>8.8007441860465114</v>
+        <v>8.800744186046515</v>
       </c>
       <c r="K4">
         <v>8.2140279069767459</v>
@@ -26019,25 +26019,25 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>1.3695602929920001</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>2.7391205859840002</v>
+        <v>2.7391205859840011</v>
       </c>
       <c r="H5">
         <v>4.1086808789760001</v>
       </c>
       <c r="I5">
-        <v>5.4782411719680004</v>
+        <v>4.1086808789760001</v>
       </c>
       <c r="J5">
-        <v>6.1672331697024054</v>
+        <v>5.9542743167999994</v>
       </c>
       <c r="K5">
         <v>7.5025400394240016</v>
       </c>
       <c r="L5">
-        <v>8.7529633793280048</v>
+        <v>8.7529633793280031</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
@@ -26101,22 +26101,25 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>5.9616153930240001</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>11.923230786048</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>12.95930292479999</v>
+        <v>12.959302924799999</v>
       </c>
       <c r="K7">
-        <v>16.124226565919621</v>
+        <v>16.124226565919631</v>
       </c>
       <c r="L7">
         <v>14.966633574144</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>81</v>
+      </c>
       <c r="B8" t="s">
         <v>57</v>
       </c>
@@ -26136,19 +26139,19 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>69.915502274376507</v>
+        <v>19.3351582628177</v>
       </c>
       <c r="I8">
-        <v>68.498922397292418</v>
+        <v>19.3351582628177</v>
       </c>
       <c r="J8">
-        <v>69.642529862269853</v>
+        <v>19.339609281951461</v>
       </c>
       <c r="K8">
-        <v>76.445952871109085</v>
+        <v>19.438954387199999</v>
       </c>
       <c r="L8">
-        <v>55.271587015626423</v>
+        <v>16.035678829439998</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
@@ -26241,28 +26244,28 @@
         <v>177.52780000000001</v>
       </c>
       <c r="E11">
-        <v>92.385000000000076</v>
+        <v>92.385000000000062</v>
       </c>
       <c r="F11">
-        <v>186.74150000000009</v>
+        <v>186.7415</v>
       </c>
       <c r="G11">
-        <v>155.03999999999991</v>
+        <v>155.03999999999979</v>
       </c>
       <c r="H11">
-        <v>120.9635000000001</v>
+        <v>120.9635000000002</v>
       </c>
       <c r="I11">
-        <v>125.24799999999991</v>
+        <v>125.248</v>
       </c>
       <c r="J11">
-        <v>13.90799999999998</v>
+        <v>13.90799999999996</v>
       </c>
       <c r="K11">
-        <v>22.609999999999982</v>
+        <v>22.60999999999996</v>
       </c>
       <c r="L11">
-        <v>4.7309999999999972</v>
+        <v>4.7310000000000034</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
@@ -26282,25 +26285,25 @@
         <v>2.375</v>
       </c>
       <c r="F12">
-        <v>4.7499999999999991</v>
+        <v>4.7499999999999938</v>
       </c>
       <c r="G12">
         <v>4.75</v>
       </c>
       <c r="H12">
-        <v>7.125</v>
+        <v>7.1249999999999991</v>
       </c>
       <c r="I12">
-        <v>7.1249999999999991</v>
+        <v>7.1249999999999982</v>
       </c>
       <c r="J12">
         <v>7.1249999999999991</v>
       </c>
       <c r="K12">
+        <v>7.1249999999999982</v>
+      </c>
+      <c r="L12">
         <v>7.1249999999999991</v>
-      </c>
-      <c r="L12">
-        <v>7.1249999999999973</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -26317,16 +26320,16 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <v>0.60000000000000009</v>
+        <v>0.6</v>
       </c>
       <c r="F13">
         <v>0</v>
       </c>
       <c r="G13">
-        <v>0.12942089052995509</v>
+        <v>0</v>
       </c>
       <c r="H13">
-        <v>0.40500000000000003</v>
+        <v>0</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -26349,34 +26352,34 @@
         <v>57</v>
       </c>
       <c r="C14">
-        <v>72.328026287897885</v>
+        <v>72.328026287897856</v>
       </c>
       <c r="D14">
-        <v>56.029209792794298</v>
+        <v>56.029209792794383</v>
       </c>
       <c r="E14">
-        <v>105.02826477030121</v>
+        <v>110.0203463944904</v>
       </c>
       <c r="F14">
-        <v>65.586215722042567</v>
+        <v>62.403703486473162</v>
       </c>
       <c r="G14">
-        <v>105.02826477030121</v>
+        <v>110.0203463944904</v>
       </c>
       <c r="H14">
-        <v>105.02826477030121</v>
+        <v>110.0203463944904</v>
       </c>
       <c r="I14">
-        <v>105.02826477030111</v>
+        <v>108.21106015775931</v>
       </c>
       <c r="J14">
-        <v>105.02826477030121</v>
+        <v>95.506508573393035</v>
       </c>
       <c r="K14">
-        <v>76.118221178444315</v>
+        <v>75.740880433912992</v>
       </c>
       <c r="L14">
-        <v>132.9758336700601</v>
+        <v>110.0203463944904</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
@@ -26393,28 +26396,28 @@
         <v>0</v>
       </c>
       <c r="E15">
-        <v>11.405698821555699</v>
+        <v>15.19416370025009</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>1.739292035569433</v>
       </c>
       <c r="G15">
-        <v>11.405698821555699</v>
+        <v>15.19416370025009</v>
       </c>
       <c r="H15">
-        <v>11.405698821555699</v>
+        <v>15.19416370025009</v>
       </c>
       <c r="I15">
-        <v>11.40569882155569</v>
+        <v>8.2507060724705514</v>
       </c>
       <c r="J15">
-        <v>11.405698821555699</v>
+        <v>11.81783815455584</v>
       </c>
       <c r="K15">
-        <v>11.405698821555699</v>
+        <v>11.78303956608702</v>
       </c>
       <c r="L15">
-        <v>11.405698821555699</v>
+        <v>34.890279572218027</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
@@ -26425,7 +26428,7 @@
         <v>57</v>
       </c>
       <c r="C16">
-        <v>341.27640000000002</v>
+        <v>341.27640000000008</v>
       </c>
       <c r="D16">
         <v>434.87279999999998</v>
@@ -26434,25 +26437,25 @@
         <v>341.46359999999999</v>
       </c>
       <c r="F16">
-        <v>262.53923970700799</v>
+        <v>263.90879999999999</v>
       </c>
       <c r="G16">
-        <v>176.80403941401579</v>
+        <v>176.8040394140159</v>
       </c>
       <c r="H16">
-        <v>112.40595849190809</v>
+        <v>157.20056085820619</v>
       </c>
       <c r="I16">
-        <v>112.4732856446914</v>
+        <v>185.3705608582064</v>
       </c>
       <c r="J16">
-        <v>149.73831404322769</v>
+        <v>212.80721347644871</v>
       </c>
       <c r="K16">
-        <v>193.9617805235479</v>
+        <v>250.96877900745659</v>
       </c>
       <c r="L16">
-        <v>106.0658062231972</v>
+        <v>144.39798261264659</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
@@ -26495,7 +26498,7 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>81</v>
+        <v>43</v>
       </c>
       <c r="B18" t="s">
         <v>57</v>
@@ -26507,7 +26510,7 @@
         <v>0</v>
       </c>
       <c r="E18">
-        <v>13.77683883151423</v>
+        <v>0</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -26533,7 +26536,7 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="B19" t="s">
         <v>57</v>
@@ -26571,159 +26574,159 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="B20" t="s">
         <v>57</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>66.628799999999998</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>63.299879999999987</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>59.623199999999997</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>52.397819999999967</v>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>48.293819999999997</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>57.86981999999999</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>49.583159999999999</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>36.607680000000002</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>36.217800000000011</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>30.513999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B21" t="s">
         <v>57</v>
       </c>
       <c r="C21">
-        <v>66.628800000000012</v>
+        <v>0</v>
       </c>
       <c r="D21">
-        <v>63.299879999999987</v>
+        <v>0</v>
       </c>
       <c r="E21">
-        <v>59.623199999999997</v>
+        <v>0</v>
       </c>
       <c r="F21">
-        <v>52.397820000000003</v>
+        <v>0</v>
       </c>
       <c r="G21">
-        <v>48.293819999999997</v>
+        <v>0</v>
       </c>
       <c r="H21">
-        <v>57.86981999999999</v>
+        <v>0</v>
       </c>
       <c r="I21">
-        <v>49.583160000000007</v>
+        <v>0</v>
       </c>
       <c r="J21">
-        <v>36.607679999999981</v>
+        <v>0</v>
       </c>
       <c r="K21">
-        <v>36.217799999999997</v>
+        <v>0</v>
       </c>
       <c r="L21">
-        <v>30.513999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="B22" t="s">
         <v>57</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>198.37</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>212.30279999999999</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>223.40450000000021</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>221.29</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>208.50232205901611</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>223.29959885294511</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>200.76</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>209.88000000000011</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>223.40450000000001</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>215.94100000000009</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="B23" t="s">
         <v>57</v>
       </c>
       <c r="C23">
-        <v>198.37</v>
+        <v>0</v>
       </c>
       <c r="D23">
-        <v>212.30279999999999</v>
+        <v>0</v>
       </c>
       <c r="E23">
-        <v>221.29</v>
+        <v>0</v>
       </c>
       <c r="F23">
-        <v>221.28999999999991</v>
+        <v>0</v>
       </c>
       <c r="G23">
-        <v>221.29000000000011</v>
+        <v>0</v>
       </c>
       <c r="H23">
-        <v>221.29000000000019</v>
+        <v>0</v>
       </c>
       <c r="I23">
-        <v>205.41152724581971</v>
+        <v>0</v>
       </c>
       <c r="J23">
-        <v>212.50564951457699</v>
+        <v>0</v>
       </c>
       <c r="K23">
-        <v>221.28999999999971</v>
+        <v>0</v>
       </c>
       <c r="L23">
-        <v>215.941</v>
+        <v>49.625829926784</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B24" t="s">
         <v>57</v>
@@ -26756,12 +26759,12 @@
         <v>0</v>
       </c>
       <c r="L24">
-        <v>49.620175176794461</v>
+        <v>16.2023932122624</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="B25" t="s">
         <v>57</v>
@@ -26770,252 +26773,214 @@
         <v>0</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>4.9806336000000009</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>20.249380800000001</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>38.813327999999998</v>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>43.188775200000002</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>45.087602399999987</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>45.087602399999987</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>70.368796799999984</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>118.1991239999999</v>
       </c>
       <c r="L25">
-        <v>15.587237066209751</v>
+        <v>129.83753686095361</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B26" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>1.7613000000000001</v>
       </c>
       <c r="D26">
-        <v>4.9806336000000018</v>
+        <v>4.3856063999999986</v>
       </c>
       <c r="E26">
-        <v>20.249380800000001</v>
+        <v>4.3267391999999996</v>
       </c>
       <c r="F26">
-        <v>36.659267999999997</v>
+        <v>4.2678719999999997</v>
       </c>
       <c r="G26">
-        <v>43.188775199999981</v>
+        <v>4.2090048000000007</v>
       </c>
       <c r="H26">
-        <v>45.087602399999973</v>
+        <v>4.1501375999999999</v>
       </c>
       <c r="I26">
-        <v>47.560989600000013</v>
+        <v>0.79079759999999866</v>
       </c>
       <c r="J26">
-        <v>66.64873679999998</v>
+        <v>4.0324031999999983</v>
       </c>
       <c r="K26">
-        <v>118.199124</v>
+        <v>3.9735360000000011</v>
       </c>
       <c r="L26">
-        <v>130.45834775699581</v>
+        <v>3.6792000000000011</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B27" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C27">
-        <v>1.761299999999999</v>
+        <v>75.367565957311356</v>
       </c>
       <c r="D27">
-        <v>4.3856063999999986</v>
+        <v>75.367565957311342</v>
       </c>
       <c r="E27">
-        <v>4.3267391999999996</v>
+        <v>76.222035654133109</v>
       </c>
       <c r="F27">
-        <v>4.2678720000000014</v>
+        <v>76.222035654133109</v>
       </c>
       <c r="G27">
-        <v>4.209004799999998</v>
+        <v>76.222035654133123</v>
       </c>
       <c r="H27">
-        <v>4.1501375999999999</v>
+        <v>76.134869187615635</v>
       </c>
       <c r="I27">
-        <v>4.0912703999999991</v>
+        <v>76.077209510667771</v>
       </c>
       <c r="J27">
-        <v>4.0324032000000001</v>
+        <v>91.374535654133098</v>
       </c>
       <c r="K27">
-        <v>3.9735359999999988</v>
+        <v>91.374535654133098</v>
       </c>
       <c r="L27">
-        <v>3.6791999999999989</v>
+        <v>91.374535654133126</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B28" t="s">
         <v>57</v>
       </c>
       <c r="C28">
-        <v>75.367565957311342</v>
+        <v>18.910434042688649</v>
       </c>
       <c r="D28">
-        <v>75.367565957311342</v>
+        <v>37.954767376022012</v>
       </c>
       <c r="E28">
-        <v>79.14678398091911</v>
+        <v>83.157964345866858</v>
       </c>
       <c r="F28">
-        <v>79.146783980919096</v>
+        <v>92.97296434586687</v>
       </c>
       <c r="G28">
-        <v>79.146783980919096</v>
+        <v>101.66546434586689</v>
       </c>
       <c r="H28">
-        <v>79.146783980919096</v>
+        <v>98.97829016620976</v>
       </c>
       <c r="I28">
-        <v>78.436252035127012</v>
+        <v>97.991290489332172</v>
       </c>
       <c r="J28">
-        <v>94.299283980919114</v>
+        <v>101.66546434586689</v>
       </c>
       <c r="K28">
-        <v>94.2992839809191</v>
+        <v>132.20067446161141</v>
       </c>
       <c r="L28">
-        <v>94.299283980919085</v>
+        <v>136.9148652764311</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="B29" t="s">
         <v>57</v>
       </c>
       <c r="C29">
-        <v>18.910434042688649</v>
+        <v>37.551173712102127</v>
       </c>
       <c r="D29">
-        <v>37.954767376021998</v>
+        <v>38.089190207205611</v>
       </c>
       <c r="E29">
-        <v>90.048216019080897</v>
+        <v>38.625089905259557</v>
       </c>
       <c r="F29">
-        <v>90.048216019080897</v>
+        <v>22.84020447795741</v>
       </c>
       <c r="G29">
-        <v>98.740716019080907</v>
+        <v>29.473889905259579</v>
       </c>
       <c r="H29">
-        <v>98.740716019080864</v>
+        <v>18.299489905259591</v>
       </c>
       <c r="I29">
-        <v>95.632247964872974</v>
+        <v>16.49163376977015</v>
       </c>
       <c r="J29">
-        <v>98.740716019080892</v>
+        <v>15.068453272051171</v>
       </c>
       <c r="K29">
-        <v>131.39042613482539</v>
+        <v>0</v>
       </c>
       <c r="L29">
-        <v>133.8171234134158</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>76</v>
-      </c>
-      <c r="B30" t="s">
-        <v>57</v>
-      </c>
-      <c r="C30">
-        <v>37.551173712102099</v>
-      </c>
-      <c r="D30">
-        <v>38.089190207205689</v>
-      </c>
-      <c r="E30">
-        <v>47.405636408143167</v>
-      </c>
-      <c r="F30">
-        <v>21.396984277957429</v>
-      </c>
-      <c r="G30">
-        <v>38.254436408143206</v>
-      </c>
-      <c r="H30">
-        <v>27.08003640814319</v>
-      </c>
-      <c r="I30">
-        <v>16.51943640814314</v>
-      </c>
-      <c r="J30">
-        <v>5.9588364081431404</v>
-      </c>
-      <c r="K30">
-        <v>0</v>
-      </c>
-      <c r="L30">
-        <v>2.5740675083842381</v>
+        <v>2.04497403329162</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C33" s="8">
+      <c r="C33" s="7">
         <v>2007</v>
       </c>
-      <c r="D33" s="8">
+      <c r="D33" s="7">
         <v>2008</v>
       </c>
-      <c r="E33" s="8">
+      <c r="E33" s="7">
         <v>2010</v>
       </c>
-      <c r="F33" s="8">
+      <c r="F33" s="7">
         <v>2012</v>
       </c>
-      <c r="G33" s="8">
+      <c r="G33" s="7">
         <v>2014</v>
       </c>
-      <c r="H33" s="8">
+      <c r="H33" s="7">
         <v>2016</v>
       </c>
-      <c r="I33" s="8">
+      <c r="I33" s="7">
         <v>2018</v>
       </c>
-      <c r="J33" s="8">
+      <c r="J33" s="7">
         <v>2020</v>
       </c>
-      <c r="K33" s="8">
+      <c r="K33" s="7">
         <v>2022</v>
       </c>
-      <c r="L33" s="8">
+      <c r="L33" s="7">
         <v>2024</v>
       </c>
     </row>
@@ -27033,35 +26998,35 @@
       </c>
       <c r="E34">
         <f t="shared" si="0"/>
-        <v>94.760000000000076</v>
+        <v>94.760000000000062</v>
       </c>
       <c r="F34">
         <f t="shared" si="0"/>
-        <v>191.49150000000009</v>
+        <v>191.4915</v>
       </c>
       <c r="G34">
         <f t="shared" si="0"/>
-        <v>159.78999999999991</v>
+        <v>159.78999999999979</v>
       </c>
       <c r="H34">
         <f t="shared" si="0"/>
-        <v>128.0885000000001</v>
+        <v>128.08850000000018</v>
       </c>
       <c r="I34">
         <f t="shared" si="0"/>
-        <v>132.37299999999991</v>
+        <v>132.37299999999999</v>
       </c>
       <c r="J34">
         <f t="shared" si="0"/>
-        <v>21.03299999999998</v>
+        <v>21.032999999999959</v>
       </c>
       <c r="K34">
         <f t="shared" si="0"/>
-        <v>29.734999999999982</v>
+        <v>29.734999999999957</v>
       </c>
       <c r="L34">
         <f t="shared" si="0"/>
-        <v>11.855999999999995</v>
+        <v>11.856000000000002</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
@@ -27069,11 +27034,11 @@
         <v>6</v>
       </c>
       <c r="C35">
-        <f>SUM(C21:C22)</f>
-        <v>66.628800000000012</v>
+        <f>SUM(C20:C21)</f>
+        <v>66.628799999999998</v>
       </c>
       <c r="D35">
-        <f t="shared" ref="D35:L35" si="1">SUM(D21:D22)</f>
+        <f t="shared" ref="D35:L35" si="1">SUM(D20:D21)</f>
         <v>63.299879999999987</v>
       </c>
       <c r="E35">
@@ -27082,7 +27047,7 @@
       </c>
       <c r="F35">
         <f t="shared" si="1"/>
-        <v>52.397820000000003</v>
+        <v>52.397819999999967</v>
       </c>
       <c r="G35">
         <f t="shared" si="1"/>
@@ -27094,15 +27059,15 @@
       </c>
       <c r="I35">
         <f t="shared" si="1"/>
-        <v>49.583160000000007</v>
+        <v>49.583159999999999</v>
       </c>
       <c r="J35">
         <f t="shared" si="1"/>
-        <v>36.607679999999981</v>
+        <v>36.607680000000002</v>
       </c>
       <c r="K35">
         <f t="shared" si="1"/>
-        <v>36.217799999999997</v>
+        <v>36.217800000000011</v>
       </c>
       <c r="L35">
         <f t="shared" si="1"/>
@@ -27114,16 +27079,16 @@
         <v>7</v>
       </c>
       <c r="C36">
-        <f>SUM(C5:C10,C16:C20)</f>
-        <v>341.27640000000002</v>
+        <f>SUM(C5:C10,C16:C19)</f>
+        <v>341.27640000000008</v>
       </c>
       <c r="D36">
-        <f t="shared" ref="D36:L36" si="2">SUM(D5:D10,D16:D20)</f>
+        <f t="shared" ref="D36:L36" si="2">SUM(D5:D10,D16:D19)</f>
         <v>434.87279999999998</v>
       </c>
       <c r="E36">
         <f t="shared" si="2"/>
-        <v>355.24043883151421</v>
+        <v>341.46359999999999</v>
       </c>
       <c r="F36">
         <f t="shared" si="2"/>
@@ -27131,27 +27096,27 @@
       </c>
       <c r="G36">
         <f t="shared" si="2"/>
-        <v>179.5431599999998</v>
+        <v>179.54315999999992</v>
       </c>
       <c r="H36">
         <f t="shared" si="2"/>
-        <v>192.3917570382846</v>
+        <v>180.64439999999988</v>
       </c>
       <c r="I36">
         <f t="shared" si="2"/>
-        <v>198.37367999999981</v>
+        <v>208.81440000000009</v>
       </c>
       <c r="J36">
         <f t="shared" si="2"/>
-        <v>238.50737999999996</v>
+        <v>251.06040000000019</v>
       </c>
       <c r="K36">
         <f t="shared" si="2"/>
-        <v>294.03450000000061</v>
+        <v>294.03450000000021</v>
       </c>
       <c r="L36">
         <f t="shared" si="2"/>
-        <v>185.05699019229564</v>
+        <v>184.15325839555859</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
@@ -27159,44 +27124,44 @@
         <v>8</v>
       </c>
       <c r="C37">
-        <f>SUM(C23)</f>
+        <f>SUM(C22)</f>
         <v>198.37</v>
       </c>
       <c r="D37">
-        <f t="shared" ref="D37:L37" si="3">SUM(D23)</f>
+        <f t="shared" ref="D37:L37" si="3">SUM(D22)</f>
         <v>212.30279999999999</v>
       </c>
       <c r="E37">
         <f t="shared" si="3"/>
-        <v>221.29</v>
+        <v>223.40450000000021</v>
       </c>
       <c r="F37">
         <f t="shared" si="3"/>
-        <v>221.28999999999991</v>
+        <v>221.29</v>
       </c>
       <c r="G37">
         <f t="shared" si="3"/>
-        <v>221.29000000000011</v>
+        <v>208.50232205901611</v>
       </c>
       <c r="H37">
         <f t="shared" si="3"/>
-        <v>221.29000000000019</v>
+        <v>223.29959885294511</v>
       </c>
       <c r="I37">
         <f t="shared" si="3"/>
-        <v>205.41152724581971</v>
+        <v>200.76</v>
       </c>
       <c r="J37">
         <f t="shared" si="3"/>
-        <v>212.50564951457699</v>
+        <v>209.88000000000011</v>
       </c>
       <c r="K37">
         <f t="shared" si="3"/>
-        <v>221.28999999999971</v>
+        <v>223.40450000000001</v>
       </c>
       <c r="L37">
         <f t="shared" si="3"/>
-        <v>215.941</v>
+        <v>215.94100000000009</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
@@ -27204,32 +27169,32 @@
         <v>9</v>
       </c>
       <c r="C38">
-        <f>SUM(C14:C15,C30)</f>
+        <f>SUM(C14:C15,C29)</f>
         <v>109.87919999999998</v>
       </c>
       <c r="D38">
-        <f t="shared" ref="D38:L38" si="4">SUM(D14:D15,D30)</f>
-        <v>94.11839999999998</v>
+        <f t="shared" ref="D38:L38" si="4">SUM(D14:D15,D29)</f>
+        <v>94.118399999999994</v>
       </c>
       <c r="E38">
         <f t="shared" si="4"/>
-        <v>163.83960000000008</v>
+        <v>163.83960000000005</v>
       </c>
       <c r="F38">
         <f t="shared" si="4"/>
-        <v>86.983199999999997</v>
+        <v>86.983200000000011</v>
       </c>
       <c r="G38">
         <f t="shared" si="4"/>
-        <v>154.68840000000012</v>
+        <v>154.68840000000006</v>
       </c>
       <c r="H38">
         <f t="shared" si="4"/>
-        <v>143.5140000000001</v>
+        <v>143.51400000000007</v>
       </c>
       <c r="I38">
         <f t="shared" si="4"/>
-        <v>132.95339999999993</v>
+        <v>132.95340000000002</v>
       </c>
       <c r="J38">
         <f t="shared" si="4"/>
@@ -27237,11 +27202,11 @@
       </c>
       <c r="K38">
         <f t="shared" si="4"/>
-        <v>87.523920000000018</v>
+        <v>87.523920000000004</v>
       </c>
       <c r="L38">
         <f t="shared" si="4"/>
-        <v>146.95560000000003</v>
+        <v>146.95560000000006</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
@@ -27250,7 +27215,7 @@
       </c>
       <c r="C39">
         <f>SUM(C2:C4)</f>
-        <v>7.3906199999999993</v>
+        <v>7.3906200000000011</v>
       </c>
       <c r="D39">
         <f t="shared" ref="D39:L39" si="5">SUM(D2:D4)</f>
@@ -27258,11 +27223,11 @@
       </c>
       <c r="E39">
         <f t="shared" si="5"/>
-        <v>11.477520000000002</v>
+        <v>13.289760000000005</v>
       </c>
       <c r="F39">
         <f t="shared" si="5"/>
-        <v>14.576040000000003</v>
+        <v>14.576040000000011</v>
       </c>
       <c r="G39">
         <f t="shared" si="5"/>
@@ -27278,15 +27243,15 @@
       </c>
       <c r="J39">
         <f t="shared" si="5"/>
-        <v>20.820959999999999</v>
+        <v>20.820960000000007</v>
       </c>
       <c r="K39">
         <f t="shared" si="5"/>
-        <v>19.505970000000008</v>
+        <v>19.505970000000005</v>
       </c>
       <c r="L39">
         <f t="shared" si="5"/>
-        <v>18.190980000000007</v>
+        <v>18.190980000000003</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
@@ -27294,16 +27259,16 @@
         <v>13</v>
       </c>
       <c r="C40">
-        <f>SUM(C28:C29)</f>
-        <v>94.277999999999992</v>
+        <f>SUM(C27:C28)</f>
+        <v>94.278000000000006</v>
       </c>
       <c r="D40">
-        <f t="shared" ref="D40:L40" si="6">SUM(D28:D29)</f>
+        <f t="shared" ref="D40:L40" si="6">SUM(D27:D28)</f>
         <v>113.32233333333335</v>
       </c>
       <c r="E40">
         <f t="shared" si="6"/>
-        <v>169.19499999999999</v>
+        <v>159.37999999999997</v>
       </c>
       <c r="F40">
         <f t="shared" si="6"/>
@@ -27311,27 +27276,27 @@
       </c>
       <c r="G40">
         <f t="shared" si="6"/>
-        <v>177.88749999999999</v>
+        <v>177.88750000000002</v>
       </c>
       <c r="H40">
         <f t="shared" si="6"/>
-        <v>177.88749999999996</v>
+        <v>175.11315935382538</v>
       </c>
       <c r="I40">
         <f t="shared" si="6"/>
-        <v>174.06849999999997</v>
+        <v>174.06849999999994</v>
       </c>
       <c r="J40">
         <f t="shared" si="6"/>
-        <v>193.04000000000002</v>
+        <v>193.04</v>
       </c>
       <c r="K40">
         <f t="shared" si="6"/>
-        <v>225.6897101157445</v>
+        <v>223.57521011574451</v>
       </c>
       <c r="L40">
         <f t="shared" si="6"/>
-        <v>228.11640739433489</v>
+        <v>228.28940093056423</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
@@ -27339,12 +27304,12 @@
         <v>65</v>
       </c>
       <c r="C41">
-        <f>SUM(C24:C27)</f>
-        <v>1.761299999999999</v>
+        <f>SUM(C23:C26)</f>
+        <v>1.7613000000000001</v>
       </c>
       <c r="D41">
-        <f t="shared" ref="D41:L41" si="7">SUM(D24:D27)</f>
-        <v>9.3662400000000012</v>
+        <f t="shared" ref="D41:L41" si="7">SUM(D23:D26)</f>
+        <v>9.3662399999999995</v>
       </c>
       <c r="E41">
         <f t="shared" si="7"/>
@@ -27352,31 +27317,31 @@
       </c>
       <c r="F41">
         <f t="shared" si="7"/>
-        <v>40.927140000000001</v>
+        <v>43.081199999999995</v>
       </c>
       <c r="G41">
         <f t="shared" si="7"/>
-        <v>47.397779999999976</v>
+        <v>47.397780000000004</v>
       </c>
       <c r="H41">
         <f t="shared" si="7"/>
-        <v>49.237739999999974</v>
+        <v>49.237739999999988</v>
       </c>
       <c r="I41">
         <f t="shared" si="7"/>
-        <v>51.652260000000012</v>
+        <v>45.878399999999985</v>
       </c>
       <c r="J41">
         <f t="shared" si="7"/>
-        <v>70.681139999999985</v>
+        <v>74.401199999999989</v>
       </c>
       <c r="K41">
         <f t="shared" si="7"/>
-        <v>122.17265999999999</v>
+        <v>122.17265999999989</v>
       </c>
       <c r="L41">
         <f t="shared" si="7"/>
-        <v>199.34496000000004</v>
+        <v>199.34496000000001</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
@@ -27393,7 +27358,7 @@
       </c>
       <c r="E42">
         <f t="shared" si="8"/>
-        <v>0.60000000000000009</v>
+        <v>0.6</v>
       </c>
       <c r="F42">
         <f t="shared" si="8"/>
@@ -27401,11 +27366,11 @@
       </c>
       <c r="G42">
         <f t="shared" si="8"/>
-        <v>0.12942089052995509</v>
+        <v>0</v>
       </c>
       <c r="H42">
         <f t="shared" si="8"/>
-        <v>0.40500000000000003</v>
+        <v>0</v>
       </c>
       <c r="I42">
         <f t="shared" si="8"/>
@@ -27428,34 +27393,34 @@
       <c r="A45" t="s">
         <v>75</v>
       </c>
-      <c r="C45" s="8">
+      <c r="C45" s="7">
         <v>2007</v>
       </c>
-      <c r="D45" s="8">
+      <c r="D45" s="7">
         <v>2008</v>
       </c>
-      <c r="E45" s="8">
+      <c r="E45" s="7">
         <v>2010</v>
       </c>
-      <c r="F45" s="8">
+      <c r="F45" s="7">
         <v>2012</v>
       </c>
-      <c r="G45" s="8">
+      <c r="G45" s="7">
         <v>2014</v>
       </c>
-      <c r="H45" s="8">
+      <c r="H45" s="7">
         <v>2016</v>
       </c>
-      <c r="I45" s="8">
+      <c r="I45" s="7">
         <v>2018</v>
       </c>
-      <c r="J45" s="8">
+      <c r="J45" s="7">
         <v>2020</v>
       </c>
-      <c r="K45" s="8">
+      <c r="K45" s="7">
         <v>2022</v>
       </c>
-      <c r="L45" s="8">
+      <c r="L45" s="7">
         <v>2024</v>
       </c>
     </row>
@@ -27733,7 +27698,7 @@
         <v>49.111199999999997</v>
       </c>
       <c r="I53">
-        <f t="shared" si="9"/>
+        <f>SUM(I56+I57)</f>
         <v>45.878399999999999</v>
       </c>
       <c r="J53">
@@ -27858,34 +27823,34 @@
       <c r="B60" t="s">
         <v>71</v>
       </c>
-      <c r="C60" s="8">
+      <c r="C60" s="7">
         <v>2007</v>
       </c>
-      <c r="D60" s="8">
+      <c r="D60" s="7">
         <v>2008</v>
       </c>
-      <c r="E60" s="8">
+      <c r="E60" s="7">
         <v>2010</v>
       </c>
-      <c r="F60" s="8">
+      <c r="F60" s="7">
         <v>2012</v>
       </c>
-      <c r="G60" s="8">
+      <c r="G60" s="7">
         <v>2014</v>
       </c>
-      <c r="H60" s="8">
+      <c r="H60" s="7">
         <v>2016</v>
       </c>
-      <c r="I60" s="8">
+      <c r="I60" s="7">
         <v>2018</v>
       </c>
-      <c r="J60" s="8">
+      <c r="J60" s="7">
         <v>2020</v>
       </c>
-      <c r="K60" s="8">
+      <c r="K60" s="7">
         <v>2022</v>
       </c>
-      <c r="L60" s="8">
+      <c r="L60" s="7">
         <v>2024</v>
       </c>
     </row>
@@ -27894,7 +27859,7 @@
         <v>4</v>
       </c>
       <c r="C61" s="5">
-        <f t="shared" ref="C61:H69" si="10">(C34-C46)/C46</f>
+        <f t="shared" ref="C61:C69" si="10">(C34-C46)/C46</f>
         <v>1.4997787826154102E-5</v>
       </c>
       <c r="D61" s="5">
@@ -27903,35 +27868,35 @@
       </c>
       <c r="E61" s="5">
         <f t="shared" si="11"/>
-        <v>-2.9547459550819731E-5</v>
+        <v>-2.9547459550969696E-5</v>
       </c>
       <c r="F61" s="5">
         <f t="shared" si="11"/>
-        <v>-4.9988688658295838E-2</v>
+        <v>-4.9988688658296261E-2</v>
       </c>
       <c r="G61" s="5">
         <f t="shared" si="11"/>
-        <v>-2.0065987170524567E-2</v>
+        <v>-2.0065987170525264E-2</v>
       </c>
       <c r="H61" s="5">
         <f t="shared" si="11"/>
-        <v>-5.0005636694285635E-2</v>
+        <v>-5.0005636694285004E-2</v>
       </c>
       <c r="I61" s="5">
         <f t="shared" si="11"/>
-        <v>-5.0256282214646369E-2</v>
+        <v>-5.0256282214645759E-2</v>
       </c>
       <c r="J61" s="5">
         <f t="shared" si="11"/>
-        <v>-4.9845503333876259E-2</v>
+        <v>-4.9845503333877224E-2</v>
       </c>
       <c r="K61" s="5">
         <f t="shared" si="11"/>
-        <v>-5.0169937646939104E-2</v>
+        <v>-5.0169937646939895E-2</v>
       </c>
       <c r="L61" s="5">
         <f t="shared" si="11"/>
-        <v>-4.9817272552414284E-2</v>
+        <v>-4.9817272552413708E-2</v>
       </c>
     </row>
     <row r="62" spans="2:12" x14ac:dyDescent="0.3">
@@ -27940,7 +27905,7 @@
       </c>
       <c r="C62" s="5">
         <f t="shared" si="10"/>
-        <v>2.1328396602072984E-16</v>
+        <v>0</v>
       </c>
       <c r="D62" s="5">
         <f t="shared" ref="D62:L62" si="12">(D35-D47)/D47</f>
@@ -27952,7 +27917,7 @@
       </c>
       <c r="F62" s="5">
         <f t="shared" si="12"/>
-        <v>-4.999999999999994E-2</v>
+        <v>-5.0000000000000586E-2</v>
       </c>
       <c r="G62" s="5">
         <f t="shared" si="12"/>
@@ -27964,15 +27929,15 @@
       </c>
       <c r="I62" s="5">
         <f t="shared" si="12"/>
-        <v>-4.9999999999999843E-2</v>
+        <v>-4.9999999999999982E-2</v>
       </c>
       <c r="J62" s="5">
         <f t="shared" si="12"/>
-        <v>-5.0000000000000454E-2</v>
+        <v>-4.9999999999999899E-2</v>
       </c>
       <c r="K62" s="5">
         <f t="shared" si="12"/>
-        <v>-5.0000000000000142E-2</v>
+        <v>-4.9999999999999767E-2</v>
       </c>
       <c r="L62" s="5">
         <f t="shared" si="12"/>
@@ -27985,7 +27950,7 @@
       </c>
       <c r="C63" s="5">
         <f t="shared" si="10"/>
-        <v>1.665612355873656E-16</v>
+        <v>3.3312247117473121E-16</v>
       </c>
       <c r="D63" s="5">
         <f t="shared" ref="D63:L63" si="13">(D36-D48)/D48</f>
@@ -27993,7 +27958,7 @@
       </c>
       <c r="E63" s="5">
         <f t="shared" si="13"/>
-        <v>4.0346434675655699E-2</v>
+        <v>0</v>
       </c>
       <c r="F63" s="5">
         <f t="shared" si="13"/>
@@ -28001,27 +27966,27 @@
       </c>
       <c r="G63" s="5">
         <f t="shared" si="13"/>
-        <v>5.5001798066548535E-2</v>
+        <v>5.5001798066549201E-2</v>
       </c>
       <c r="H63" s="5">
         <f t="shared" si="13"/>
-        <v>1.1778771920803403E-2</v>
+        <v>-5.0000000000000586E-2</v>
       </c>
       <c r="I63" s="5">
         <f t="shared" si="13"/>
-        <v>-5.0000000000000946E-2</v>
+        <v>4.0832973344372813E-16</v>
       </c>
       <c r="J63" s="5">
         <f t="shared" si="13"/>
-        <v>-5.0000000000000128E-2</v>
+        <v>7.9244662245749657E-16</v>
       </c>
       <c r="K63" s="5">
         <f t="shared" si="13"/>
-        <v>-4.9999999999998018E-2</v>
+        <v>-4.9999999999999302E-2</v>
       </c>
       <c r="L63" s="5">
         <f t="shared" si="13"/>
-        <v>-1.7662873399837544E-2</v>
+        <v>-2.2460148528441869E-2</v>
       </c>
     </row>
     <row r="64" spans="2:12" x14ac:dyDescent="0.3">
@@ -28038,35 +28003,35 @@
       </c>
       <c r="E64" s="5">
         <f t="shared" si="14"/>
-        <v>-8.3974117689232814E-3</v>
+        <v>1.0776827803777699E-3</v>
       </c>
       <c r="F64" s="5">
         <f t="shared" si="14"/>
-        <v>-9.0378323667137303E-6</v>
+        <v>-9.0378323663284252E-6</v>
       </c>
       <c r="G64" s="5">
         <f t="shared" si="14"/>
-        <v>7.267157219168438E-2</v>
+        <v>1.0685135381904366E-2</v>
       </c>
       <c r="H64" s="5">
         <f t="shared" si="14"/>
-        <v>4.8376246217053491E-2</v>
+        <v>5.789685583272744E-2</v>
       </c>
       <c r="I64" s="5">
         <f t="shared" si="14"/>
-        <v>2.3181823481749714E-2</v>
+        <v>1.1954715537515923E-5</v>
       </c>
       <c r="J64" s="5">
         <f t="shared" si="14"/>
-        <v>1.2527609176529604E-2</v>
+        <v>1.7152952881407857E-5</v>
       </c>
       <c r="K64" s="5">
         <f t="shared" si="14"/>
-        <v>4.9145663841002926E-2</v>
+        <v>5.9170601733325778E-2</v>
       </c>
       <c r="L64" s="5">
         <f t="shared" si="14"/>
-        <v>9.9970863183288905E-2</v>
+        <v>9.9970863183289335E-2</v>
       </c>
     </row>
     <row r="65" spans="2:13" x14ac:dyDescent="0.3">
@@ -28079,27 +28044,27 @@
       </c>
       <c r="D65" s="5">
         <f t="shared" ref="D65:L65" si="15">(D38-D50)/D50</f>
-        <v>-1.509891234360338E-16</v>
+        <v>0</v>
       </c>
       <c r="E65" s="5">
         <f t="shared" si="15"/>
-        <v>5.2041831334556501E-16</v>
+        <v>3.4694554223037667E-16</v>
       </c>
       <c r="F65" s="5">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>1.6337470586506366E-16</v>
       </c>
       <c r="G65" s="5">
         <f t="shared" si="15"/>
-        <v>7.3494093753388118E-16</v>
+        <v>3.6747046876694059E-16</v>
       </c>
       <c r="H65" s="5">
         <f t="shared" si="15"/>
-        <v>5.9412411535607685E-16</v>
+        <v>3.9608274357071792E-16</v>
       </c>
       <c r="I65" s="5">
         <f t="shared" si="15"/>
-        <v>3.4915631877830288E-3</v>
+        <v>3.4915631877836723E-3</v>
       </c>
       <c r="J65" s="5">
         <f t="shared" si="15"/>
@@ -28107,11 +28072,11 @@
       </c>
       <c r="K65" s="5">
         <f t="shared" si="15"/>
-        <v>0.10000000000000023</v>
+        <v>0.10000000000000005</v>
       </c>
       <c r="L65" s="5">
         <f t="shared" si="15"/>
-        <v>1.9340337782571066E-16</v>
+        <v>3.8680675565142133E-16</v>
       </c>
     </row>
     <row r="66" spans="2:13" x14ac:dyDescent="0.3">
@@ -28120,7 +28085,7 @@
       </c>
       <c r="C66" s="5">
         <f t="shared" si="10"/>
-        <v>-5.0000000000000017E-2</v>
+        <v>-4.9999999999999788E-2</v>
       </c>
       <c r="D66" s="5">
         <f t="shared" ref="D66:L66" si="16">(D39-D51)/D51</f>
@@ -28128,11 +28093,11 @@
       </c>
       <c r="E66" s="5">
         <f t="shared" si="16"/>
-        <v>-4.9999999999999829E-2</v>
+        <v>0.10000000000000039</v>
       </c>
       <c r="F66" s="5">
         <f t="shared" si="16"/>
-        <v>-4.9999999999999802E-2</v>
+        <v>-4.9999999999999226E-2</v>
       </c>
       <c r="G66" s="5">
         <f t="shared" si="16"/>
@@ -28148,15 +28113,15 @@
       </c>
       <c r="J66" s="5">
         <f t="shared" si="16"/>
-        <v>6.4139834406623769E-2</v>
+        <v>6.413983440662413E-2</v>
       </c>
       <c r="K66" s="5">
         <f t="shared" si="16"/>
-        <v>-8.7055602358887541E-2</v>
+        <v>-8.7055602358887707E-2</v>
       </c>
       <c r="L66" s="5">
         <f t="shared" si="16"/>
-        <v>-4.999999999999958E-2</v>
+        <v>-4.9999999999999767E-2</v>
       </c>
     </row>
     <row r="67" spans="2:13" x14ac:dyDescent="0.3">
@@ -28165,7 +28130,7 @@
       </c>
       <c r="C67" s="5">
         <f t="shared" si="10"/>
-        <v>-5.0045946991681238E-2</v>
+        <v>-5.0045946991681099E-2</v>
       </c>
       <c r="D67" s="5">
         <f t="shared" ref="D67:L67" si="17">(D40-D52)/D52</f>
@@ -28173,7 +28138,7 @@
       </c>
       <c r="E67" s="5">
         <f t="shared" si="17"/>
-        <v>6.1611689618737135E-2</v>
+        <v>2.7607739202083223E-5</v>
       </c>
       <c r="F67" s="5">
         <f t="shared" si="17"/>
@@ -28181,27 +28146,27 @@
       </c>
       <c r="G67" s="5">
         <f t="shared" si="17"/>
-        <v>-4.998376474257514E-2</v>
+        <v>-4.9983764742574988E-2</v>
       </c>
       <c r="H67" s="5">
         <f t="shared" si="17"/>
-        <v>1.0391461904599436E-2</v>
+        <v>-5.3666442091504602E-3</v>
       </c>
       <c r="I67" s="5">
         <f t="shared" si="17"/>
-        <v>-4.9977186594013144E-2</v>
+        <v>-4.9977186594013297E-2</v>
       </c>
       <c r="J67" s="5">
         <f t="shared" si="17"/>
-        <v>-4.9992519626138654E-2</v>
+        <v>-4.9992519626138793E-2</v>
       </c>
       <c r="K67" s="5">
         <f t="shared" si="17"/>
-        <v>-1.4719332431453742E-3</v>
+        <v>-1.0827200685664312E-2</v>
       </c>
       <c r="L67" s="5">
         <f t="shared" si="17"/>
-        <v>2.0561914681321663E-2</v>
+        <v>2.1335864335265291E-2</v>
       </c>
     </row>
     <row r="68" spans="2:13" x14ac:dyDescent="0.3">
@@ -28210,11 +28175,11 @@
       </c>
       <c r="C68" s="5">
         <f t="shared" si="10"/>
-        <v>-5.0000000000000488E-2</v>
+        <v>-4.9999999999999885E-2</v>
       </c>
       <c r="D68" s="5">
         <f t="shared" ref="D68:L68" si="18">(D41-D53)/D53</f>
-        <v>9.2061029221619014E-3</v>
+        <v>9.2061029221617106E-3</v>
       </c>
       <c r="E68" s="5">
         <f t="shared" si="18"/>
@@ -28222,31 +28187,31 @@
       </c>
       <c r="F68" s="5">
         <f t="shared" si="18"/>
-        <v>-4.9999999999999871E-2</v>
+        <v>0</v>
       </c>
       <c r="G68" s="5">
         <f t="shared" si="18"/>
-        <v>-3.6935849608661059E-2</v>
+        <v>-3.6935849608660476E-2</v>
       </c>
       <c r="H68" s="5">
         <f t="shared" si="18"/>
-        <v>2.5766016713087286E-3</v>
+        <v>2.5766016713090179E-3</v>
       </c>
       <c r="I68" s="5">
         <f t="shared" si="18"/>
-        <v>0.12585138104205931</v>
+        <v>-3.0975044280537257E-16</v>
       </c>
       <c r="J68" s="5">
         <f t="shared" si="18"/>
-        <v>-5.0000000000000239E-2</v>
+        <v>-1.9100303106941827E-16</v>
       </c>
       <c r="K68" s="5">
         <f t="shared" si="18"/>
-        <v>-5.0000000000000065E-2</v>
+        <v>-5.0000000000000842E-2</v>
       </c>
       <c r="L68" s="5">
         <f t="shared" si="18"/>
-        <v>-5.0065189048239589E-2</v>
+        <v>-5.0065189048239721E-2</v>
       </c>
     </row>
     <row r="69" spans="2:13" x14ac:dyDescent="0.3">
@@ -28263,7 +28228,7 @@
       </c>
       <c r="E69" s="5">
         <f t="shared" si="19"/>
-        <v>4.8218029350104941E-2</v>
+        <v>4.8218029350104746E-2</v>
       </c>
       <c r="F69" s="5">
         <f t="shared" si="19"/>
@@ -28275,7 +28240,7 @@
       </c>
       <c r="H69" s="5">
         <f t="shared" si="19"/>
-        <v>4.1666666666666789E-2</v>
+        <v>-1</v>
       </c>
       <c r="I69" s="5">
         <f t="shared" si="19"/>
@@ -28300,7 +28265,7 @@
       </c>
       <c r="C71" s="6">
         <f>SUM(C34:C42)-SUM(C46:C54)</f>
-        <v>-6.6116800000004332</v>
+        <v>-6.6116800000002058</v>
       </c>
       <c r="D71" s="6">
         <f t="shared" ref="D71:L71" si="20">SUM(D34:D42)-SUM(D46:D54)</f>
@@ -28308,35 +28273,35 @@
       </c>
       <c r="E71" s="6">
         <f t="shared" si="20"/>
-        <v>19.849478831514261</v>
+        <v>0.18437999999991916</v>
       </c>
       <c r="F71" s="6">
         <f t="shared" si="20"/>
-        <v>-25.291300000000319</v>
+        <v>-23.137240000000247</v>
       </c>
       <c r="G71" s="6">
         <f t="shared" si="20"/>
-        <v>6.6398408905297401</v>
+        <v>-6.2772579409841001</v>
       </c>
       <c r="H71" s="6">
         <f t="shared" si="20"/>
-        <v>3.7023570382850721</v>
+        <v>-9.2147417932291091</v>
       </c>
       <c r="I71" s="6">
         <f t="shared" si="20"/>
-        <v>-19.588152754180669</v>
+        <v>-19.572820000000092</v>
       </c>
       <c r="J71" s="6">
         <f t="shared" si="20"/>
-        <v>-26.15339048542296</v>
+        <v>-12.505959999999732</v>
       </c>
       <c r="K71" s="6">
         <f t="shared" si="20"/>
-        <v>-9.9701398842553317</v>
+        <v>-9.9701398842555591</v>
       </c>
       <c r="L71" s="6">
         <f t="shared" si="20"/>
-        <v>5.8781875866304745</v>
+        <v>5.1474493261227963</v>
       </c>
       <c r="M71" t="s">
         <v>31</v>
@@ -28345,7 +28310,7 @@
     <row r="72" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C72" s="5">
         <f>C71/SUM(C46:C54)</f>
-        <v>-6.0496328138013996E-3</v>
+        <v>-6.0496328138011915E-3</v>
       </c>
       <c r="D72" s="5">
         <f t="shared" ref="D72:L72" si="21">D71/SUM(D46:D54)</f>
@@ -28353,35 +28318,35 @@
       </c>
       <c r="E72" s="5">
         <f t="shared" si="21"/>
-        <v>1.8366351841100942E-2</v>
+        <v>1.7060336854206307E-4</v>
       </c>
       <c r="F72" s="5">
         <f t="shared" si="21"/>
-        <v>-2.3724069021204341E-2</v>
+        <v>-2.1703490082367011E-2</v>
       </c>
       <c r="G72" s="5">
         <f t="shared" si="21"/>
-        <v>6.6494826403582603E-3</v>
+        <v>-6.2863731820981426E-3</v>
       </c>
       <c r="H72" s="5">
         <f t="shared" si="21"/>
-        <v>3.7630031014695971E-3</v>
+        <v>-9.3656828848749079E-3</v>
       </c>
       <c r="I72" s="5">
         <f t="shared" si="21"/>
-        <v>-1.9954574616956926E-2</v>
+        <v>-1.9938955043676109E-2</v>
       </c>
       <c r="J72" s="5">
         <f t="shared" si="21"/>
-        <v>-2.777129031669285E-2</v>
+        <v>-1.32796031184759E-2</v>
       </c>
       <c r="K72" s="5">
         <f t="shared" si="21"/>
-        <v>-9.5277001661020176E-3</v>
+        <v>-9.5277001661022362E-3</v>
       </c>
       <c r="L72" s="5">
         <f t="shared" si="21"/>
-        <v>5.7049067490352766E-3</v>
+        <v>4.995709641472704E-3</v>
       </c>
     </row>
   </sheetData>

--- a/ELC_data_Spain.xlsx
+++ b/ELC_data_Spain.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Documents\TEMOA\PROJECT\Models-and-scenarios\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Riccardo\PoliTo\anno4\Models and scenarios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43FE3A73-BAF8-4037-94D3-722989BA3FC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{659E330A-431A-48C1-B25F-D29839B826BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="6" xr2:uid="{8BBF5E45-81C8-439F-BD27-48A9AF2DFBEB}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="6" xr2:uid="{8BBF5E45-81C8-439F-BD27-48A9AF2DFBEB}"/>
   </bookViews>
   <sheets>
     <sheet name="ELC_Generation" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1164" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1169" uniqueCount="87">
   <si>
     <t>electricity generation sources in Spain</t>
   </si>
@@ -263,9 +263,6 @@
     <t>ELC_CHP_NGA_CC_P</t>
   </si>
   <si>
-    <t xml:space="preserve">NET </t>
-  </si>
-  <si>
     <t>DATI STORICI</t>
   </si>
   <si>
@@ -285,6 +282,24 @@
   </si>
   <si>
     <t>ELC_CHP_NGA_TAP_N</t>
+  </si>
+  <si>
+    <t>Relative error to actual data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Difference from actual data </t>
+  </si>
+  <si>
+    <t>Average uincertainty</t>
+  </si>
+  <si>
+    <t>Stardand deviation</t>
+  </si>
+  <si>
+    <t>Upper bound error</t>
+  </si>
+  <si>
+    <t>Lower bound error</t>
   </si>
 </sst>
 </file>
@@ -799,7 +814,7 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -815,6 +830,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="20% - Colore 1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -6970,7 +6986,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="it-IT"/>
-              <a:t>DATI STORICI</a:t>
+              <a:t>Real data</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -8343,7 +8359,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="it-IT"/>
-              <a:t>DATI MODELLO</a:t>
+              <a:t>Model</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -9592,6 +9608,700 @@
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="it-IT"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="it-IT"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="it-IT"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Cal_Generation!$B$71</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Difference from actual data </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>Cal_Generation!$C$60:$L$60</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>2007</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2024</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Cal_Generation!$C$71:$L$71</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>-6.6116800000002058</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-7.9602266666668129</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.18437999999991916</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-23.137240000000247</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-6.2772579409841001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-9.2147417932291091</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-19.572820000000092</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-12.505959999999732</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-9.9701398842555591</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>5.1474493261227963</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-959E-4868-B142-B88A655700D9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:axId val="1363084703"/>
+        <c:axId val="1363067903"/>
+      </c:barChart>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Cal_Generation!$B$72</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Relative error to actual data</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Cal_Generation!$C$60:$L$60</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>2007</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2024</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Cal_Generation!$C$72:$L$72</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>-6.0496328138011915E-3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-7.0826924094444946E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.7060336854206307E-4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-2.1703490082367011E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-6.2863731820981426E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-9.3656828848749079E-3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-1.9938955043676109E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-1.32796031184759E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-9.5277001661022362E-3</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4.995709641472704E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-959E-4868-B142-B88A655700D9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1305396943"/>
+        <c:axId val="1305397903"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1305396943"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="it-IT"/>
+                  <a:t>Years</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="it-IT"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="low"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="it-IT"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1305397903"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1305397903"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="it-IT"/>
+                  <a:t>Relative error (-)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="it-IT"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.00%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="it-IT"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1305396943"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1363067903"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="r"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="it-IT"/>
+                  <a:t>Generation (PJ)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="it-IT"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="it-IT"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1363084703"/>
+        <c:crosses val="max"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:catAx>
+        <c:axId val="1363084703"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1363067903"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
       <c:spPr>
         <a:noFill/>
         <a:ln>
@@ -9956,6 +10666,46 @@
 </file>
 
 <file path=xl/charts/colors8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors9.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -14057,6 +14807,509 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style9.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -14367,6 +15620,42 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>550333</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>51856</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>518583</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>128056</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Grafico 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{676DD793-E96C-293C-6408-8B472DB5FEA6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -14693,13 +15982,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29F0DB51-B7D9-4ADC-AB31-B7E4C1F96502}">
   <dimension ref="A1:AD301"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34.109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="34.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -14713,7 +16002,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -14790,7 +16079,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -14883,7 +16172,7 @@
         <v>12.477599999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -14976,7 +16265,7 @@
         <v>32.842799999999997</v>
       </c>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -15069,7 +16358,7 @@
         <v>188.3844</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -15162,7 +16451,7 @@
         <v>196.3152</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -15255,7 +16544,7 @@
         <v>146.9556</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -15348,7 +16637,7 @@
         <v>2.8799999999999999E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -15441,7 +16730,7 @@
         <v>19.148399999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -15534,7 +16823,7 @@
         <v>6.0695999999999994</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -15627,7 +16916,7 @@
         <v>223.5204</v>
       </c>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -15720,7 +17009,7 @@
         <v>193.50719999999998</v>
       </c>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>4</v>
       </c>
@@ -15813,7 +17102,7 @@
         <v>16.344000000000001</v>
       </c>
     </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -15906,7 +17195,7 @@
         <v>0.87839999999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -15996,7 +17285,7 @@
         <v>1036.4724000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>4</v>
       </c>
@@ -16089,7 +17378,7 @@
         <v>287.90900000000005</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>4</v>
       </c>
@@ -16103,7 +17392,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -16117,7 +17406,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>4</v>
       </c>
@@ -16131,7 +17420,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>4</v>
       </c>
@@ -16145,7 +17434,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>4</v>
       </c>
@@ -16159,7 +17448,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>4</v>
       </c>
@@ -16173,7 +17462,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>4</v>
       </c>
@@ -16187,7 +17476,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>4</v>
       </c>
@@ -16201,7 +17490,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>4</v>
       </c>
@@ -16215,7 +17504,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>4</v>
       </c>
@@ -16229,7 +17518,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>6</v>
       </c>
@@ -16243,7 +17532,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>6</v>
       </c>
@@ -16257,7 +17546,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>6</v>
       </c>
@@ -16271,7 +17560,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>6</v>
       </c>
@@ -16285,7 +17574,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>6</v>
       </c>
@@ -16299,7 +17588,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>6</v>
       </c>
@@ -16313,7 +17602,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>6</v>
       </c>
@@ -16327,7 +17616,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>6</v>
       </c>
@@ -16341,7 +17630,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>6</v>
       </c>
@@ -16355,7 +17644,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>6</v>
       </c>
@@ -16369,7 +17658,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>6</v>
       </c>
@@ -16383,7 +17672,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>6</v>
       </c>
@@ -16397,7 +17686,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>6</v>
       </c>
@@ -16411,7 +17700,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>6</v>
       </c>
@@ -16425,7 +17714,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>6</v>
       </c>
@@ -16439,7 +17728,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>6</v>
       </c>
@@ -16453,7 +17742,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>6</v>
       </c>
@@ -16467,7 +17756,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>6</v>
       </c>
@@ -16481,7 +17770,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>6</v>
       </c>
@@ -16495,7 +17784,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>6</v>
       </c>
@@ -16509,7 +17798,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>6</v>
       </c>
@@ -16523,7 +17812,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>6</v>
       </c>
@@ -16537,7 +17826,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>6</v>
       </c>
@@ -16551,7 +17840,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>6</v>
       </c>
@@ -16565,7 +17854,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>6</v>
       </c>
@@ -16579,7 +17868,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>7</v>
       </c>
@@ -16593,7 +17882,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>7</v>
       </c>
@@ -16607,7 +17896,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>7</v>
       </c>
@@ -16621,7 +17910,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>7</v>
       </c>
@@ -16635,7 +17924,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>7</v>
       </c>
@@ -16649,7 +17938,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>7</v>
       </c>
@@ -16663,7 +17952,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>7</v>
       </c>
@@ -16677,7 +17966,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>7</v>
       </c>
@@ -16691,7 +17980,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>7</v>
       </c>
@@ -16705,7 +17994,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>7</v>
       </c>
@@ -16719,7 +18008,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>7</v>
       </c>
@@ -16733,7 +18022,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>7</v>
       </c>
@@ -16747,7 +18036,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>7</v>
       </c>
@@ -16761,7 +18050,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>7</v>
       </c>
@@ -16775,7 +18064,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>7</v>
       </c>
@@ -16789,7 +18078,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>7</v>
       </c>
@@ -16803,7 +18092,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>7</v>
       </c>
@@ -16817,7 +18106,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>7</v>
       </c>
@@ -16831,7 +18120,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>7</v>
       </c>
@@ -16845,7 +18134,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>7</v>
       </c>
@@ -16859,7 +18148,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>7</v>
       </c>
@@ -16873,7 +18162,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>7</v>
       </c>
@@ -16887,7 +18176,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>7</v>
       </c>
@@ -16901,7 +18190,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>7</v>
       </c>
@@ -16915,7 +18204,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>7</v>
       </c>
@@ -16929,7 +18218,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>8</v>
       </c>
@@ -16943,7 +18232,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>8</v>
       </c>
@@ -16957,7 +18246,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>8</v>
       </c>
@@ -16971,7 +18260,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>8</v>
       </c>
@@ -16985,7 +18274,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>8</v>
       </c>
@@ -16999,7 +18288,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>8</v>
       </c>
@@ -17013,7 +18302,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>8</v>
       </c>
@@ -17027,7 +18316,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>8</v>
       </c>
@@ -17041,7 +18330,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>8</v>
       </c>
@@ -17055,7 +18344,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>8</v>
       </c>
@@ -17069,7 +18358,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>8</v>
       </c>
@@ -17083,7 +18372,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>8</v>
       </c>
@@ -17097,7 +18386,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>8</v>
       </c>
@@ -17111,7 +18400,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>8</v>
       </c>
@@ -17125,7 +18414,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>8</v>
       </c>
@@ -17139,7 +18428,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>8</v>
       </c>
@@ -17153,7 +18442,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>8</v>
       </c>
@@ -17167,7 +18456,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>8</v>
       </c>
@@ -17181,7 +18470,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>8</v>
       </c>
@@ -17195,7 +18484,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>8</v>
       </c>
@@ -17209,7 +18498,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>8</v>
       </c>
@@ -17223,7 +18512,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>8</v>
       </c>
@@ -17237,7 +18526,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>8</v>
       </c>
@@ -17251,7 +18540,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>8</v>
       </c>
@@ -17265,7 +18554,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>8</v>
       </c>
@@ -17279,7 +18568,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>9</v>
       </c>
@@ -17293,7 +18582,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>9</v>
       </c>
@@ -17307,7 +18596,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>9</v>
       </c>
@@ -17321,7 +18610,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>9</v>
       </c>
@@ -17335,7 +18624,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>9</v>
       </c>
@@ -17349,7 +18638,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>9</v>
       </c>
@@ -17363,7 +18652,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>9</v>
       </c>
@@ -17377,7 +18666,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>9</v>
       </c>
@@ -17391,7 +18680,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>9</v>
       </c>
@@ -17405,7 +18694,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>9</v>
       </c>
@@ -17419,7 +18708,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>9</v>
       </c>
@@ -17433,7 +18722,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>9</v>
       </c>
@@ -17447,7 +18736,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>9</v>
       </c>
@@ -17461,7 +18750,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>9</v>
       </c>
@@ -17475,7 +18764,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>9</v>
       </c>
@@ -17489,7 +18778,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>9</v>
       </c>
@@ -17503,7 +18792,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>9</v>
       </c>
@@ -17517,7 +18806,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>9</v>
       </c>
@@ -17531,7 +18820,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>9</v>
       </c>
@@ -17545,7 +18834,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>9</v>
       </c>
@@ -17559,7 +18848,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>9</v>
       </c>
@@ -17573,7 +18862,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>9</v>
       </c>
@@ -17587,7 +18876,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>9</v>
       </c>
@@ -17601,7 +18890,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>9</v>
       </c>
@@ -17615,7 +18904,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>9</v>
       </c>
@@ -17629,7 +18918,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>10</v>
       </c>
@@ -17640,7 +18929,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>10</v>
       </c>
@@ -17651,7 +18940,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>10</v>
       </c>
@@ -17662,7 +18951,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>10</v>
       </c>
@@ -17673,7 +18962,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>10</v>
       </c>
@@ -17684,7 +18973,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>10</v>
       </c>
@@ -17695,7 +18984,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>10</v>
       </c>
@@ -17706,7 +18995,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>10</v>
       </c>
@@ -17717,7 +19006,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>10</v>
       </c>
@@ -17728,7 +19017,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>10</v>
       </c>
@@ -17739,7 +19028,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>10</v>
       </c>
@@ -17750,7 +19039,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>10</v>
       </c>
@@ -17761,7 +19050,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>10</v>
       </c>
@@ -17772,7 +19061,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>10</v>
       </c>
@@ -17783,7 +19072,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>10</v>
       </c>
@@ -17794,7 +19083,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>10</v>
       </c>
@@ -17805,7 +19094,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>10</v>
       </c>
@@ -17816,7 +19105,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>10</v>
       </c>
@@ -17827,7 +19116,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>10</v>
       </c>
@@ -17838,7 +19127,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>10</v>
       </c>
@@ -17852,7 +19141,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>10</v>
       </c>
@@ -17866,7 +19155,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>10</v>
       </c>
@@ -17880,7 +19169,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>10</v>
       </c>
@@ -17894,7 +19183,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>10</v>
       </c>
@@ -17908,7 +19197,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>10</v>
       </c>
@@ -17922,7 +19211,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>11</v>
       </c>
@@ -17936,7 +19225,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>11</v>
       </c>
@@ -17950,7 +19239,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>11</v>
       </c>
@@ -17964,7 +19253,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>11</v>
       </c>
@@ -17978,7 +19267,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>11</v>
       </c>
@@ -17992,7 +19281,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>11</v>
       </c>
@@ -18006,7 +19295,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>11</v>
       </c>
@@ -18020,7 +19309,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>11</v>
       </c>
@@ -18034,7 +19323,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>11</v>
       </c>
@@ -18048,7 +19337,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>11</v>
       </c>
@@ -18062,7 +19351,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>11</v>
       </c>
@@ -18076,7 +19365,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>11</v>
       </c>
@@ -18090,7 +19379,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>11</v>
       </c>
@@ -18104,7 +19393,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>11</v>
       </c>
@@ -18118,7 +19407,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>11</v>
       </c>
@@ -18132,7 +19421,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>11</v>
       </c>
@@ -18146,7 +19435,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>11</v>
       </c>
@@ -18160,7 +19449,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>11</v>
       </c>
@@ -18174,7 +19463,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>11</v>
       </c>
@@ -18188,7 +19477,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>11</v>
       </c>
@@ -18202,7 +19491,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>11</v>
       </c>
@@ -18216,7 +19505,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>11</v>
       </c>
@@ -18230,7 +19519,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>11</v>
       </c>
@@ -18244,7 +19533,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>11</v>
       </c>
@@ -18258,7 +19547,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>11</v>
       </c>
@@ -18272,7 +19561,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>12</v>
       </c>
@@ -18286,7 +19575,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>12</v>
       </c>
@@ -18300,7 +19589,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>12</v>
       </c>
@@ -18314,7 +19603,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>12</v>
       </c>
@@ -18328,7 +19617,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>12</v>
       </c>
@@ -18342,7 +19631,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>12</v>
       </c>
@@ -18356,7 +19645,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>12</v>
       </c>
@@ -18370,7 +19659,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>12</v>
       </c>
@@ -18384,7 +19673,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>12</v>
       </c>
@@ -18398,7 +19687,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>12</v>
       </c>
@@ -18412,7 +19701,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>12</v>
       </c>
@@ -18426,7 +19715,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>12</v>
       </c>
@@ -18440,7 +19729,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>12</v>
       </c>
@@ -18454,7 +19743,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>12</v>
       </c>
@@ -18468,7 +19757,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>12</v>
       </c>
@@ -18482,7 +19771,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>12</v>
       </c>
@@ -18496,7 +19785,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>12</v>
       </c>
@@ -18510,7 +19799,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>12</v>
       </c>
@@ -18524,7 +19813,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>12</v>
       </c>
@@ -18538,7 +19827,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>12</v>
       </c>
@@ -18552,7 +19841,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>12</v>
       </c>
@@ -18566,7 +19855,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>12</v>
       </c>
@@ -18580,7 +19869,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>12</v>
       </c>
@@ -18594,7 +19883,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>12</v>
       </c>
@@ -18608,7 +19897,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>12</v>
       </c>
@@ -18622,7 +19911,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>13</v>
       </c>
@@ -18636,7 +19925,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>13</v>
       </c>
@@ -18650,7 +19939,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>13</v>
       </c>
@@ -18664,7 +19953,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>13</v>
       </c>
@@ -18678,7 +19967,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>13</v>
       </c>
@@ -18692,7 +19981,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>13</v>
       </c>
@@ -18706,7 +19995,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>13</v>
       </c>
@@ -18720,7 +20009,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>13</v>
       </c>
@@ -18734,7 +20023,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>13</v>
       </c>
@@ -18748,7 +20037,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>13</v>
       </c>
@@ -18762,7 +20051,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>13</v>
       </c>
@@ -18776,7 +20065,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>13</v>
       </c>
@@ -18790,7 +20079,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>13</v>
       </c>
@@ -18804,7 +20093,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>13</v>
       </c>
@@ -18818,7 +20107,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>13</v>
       </c>
@@ -18832,7 +20121,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>13</v>
       </c>
@@ -18846,7 +20135,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>13</v>
       </c>
@@ -18860,7 +20149,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="219" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>13</v>
       </c>
@@ -18874,7 +20163,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>13</v>
       </c>
@@ -18888,7 +20177,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>13</v>
       </c>
@@ -18902,7 +20191,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>13</v>
       </c>
@@ -18916,7 +20205,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>13</v>
       </c>
@@ -18930,7 +20219,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>13</v>
       </c>
@@ -18944,7 +20233,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>13</v>
       </c>
@@ -18958,7 +20247,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>13</v>
       </c>
@@ -18972,7 +20261,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>14</v>
       </c>
@@ -18986,7 +20275,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>14</v>
       </c>
@@ -19000,7 +20289,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>14</v>
       </c>
@@ -19014,7 +20303,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="230" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>14</v>
       </c>
@@ -19028,7 +20317,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>14</v>
       </c>
@@ -19042,7 +20331,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>14</v>
       </c>
@@ -19056,7 +20345,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>14</v>
       </c>
@@ -19070,7 +20359,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>14</v>
       </c>
@@ -19084,7 +20373,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="235" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>14</v>
       </c>
@@ -19098,7 +20387,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="236" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>14</v>
       </c>
@@ -19112,7 +20401,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="237" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>14</v>
       </c>
@@ -19126,7 +20415,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="238" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>14</v>
       </c>
@@ -19140,7 +20429,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="239" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>14</v>
       </c>
@@ -19154,7 +20443,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="240" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>14</v>
       </c>
@@ -19168,7 +20457,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="241" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>14</v>
       </c>
@@ -19182,7 +20471,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="242" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>14</v>
       </c>
@@ -19196,7 +20485,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="243" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>14</v>
       </c>
@@ -19210,7 +20499,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="244" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>14</v>
       </c>
@@ -19224,7 +20513,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="245" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>14</v>
       </c>
@@ -19238,7 +20527,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>14</v>
       </c>
@@ -19252,7 +20541,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="247" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>14</v>
       </c>
@@ -19266,7 +20555,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="248" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>14</v>
       </c>
@@ -19280,7 +20569,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="249" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>14</v>
       </c>
@@ -19294,7 +20583,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="250" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>14</v>
       </c>
@@ -19308,7 +20597,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="251" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>14</v>
       </c>
@@ -19322,7 +20611,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>15</v>
       </c>
@@ -19333,7 +20622,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>15</v>
       </c>
@@ -19344,7 +20633,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>15</v>
       </c>
@@ -19355,7 +20644,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>15</v>
       </c>
@@ -19366,7 +20655,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>15</v>
       </c>
@@ -19377,7 +20666,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>15</v>
       </c>
@@ -19388,7 +20677,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>15</v>
       </c>
@@ -19402,7 +20691,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="259" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>15</v>
       </c>
@@ -19416,7 +20705,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="260" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>15</v>
       </c>
@@ -19430,7 +20719,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="261" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>15</v>
       </c>
@@ -19444,7 +20733,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="262" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>15</v>
       </c>
@@ -19458,7 +20747,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="263" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>15</v>
       </c>
@@ -19472,7 +20761,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="264" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>15</v>
       </c>
@@ -19486,7 +20775,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="265" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>15</v>
       </c>
@@ -19500,7 +20789,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="266" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>15</v>
       </c>
@@ -19514,7 +20803,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="267" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>15</v>
       </c>
@@ -19528,7 +20817,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="268" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>15</v>
       </c>
@@ -19542,7 +20831,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="269" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>15</v>
       </c>
@@ -19556,7 +20845,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="270" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>15</v>
       </c>
@@ -19570,7 +20859,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="271" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>15</v>
       </c>
@@ -19584,7 +20873,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="272" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>15</v>
       </c>
@@ -19598,7 +20887,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="273" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>15</v>
       </c>
@@ -19612,7 +20901,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="274" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>15</v>
       </c>
@@ -19626,7 +20915,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="275" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>15</v>
       </c>
@@ -19640,7 +20929,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="276" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>15</v>
       </c>
@@ -19654,7 +20943,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="277" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>16</v>
       </c>
@@ -19665,7 +20954,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="278" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>16</v>
       </c>
@@ -19676,7 +20965,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="279" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>16</v>
       </c>
@@ -19687,7 +20976,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="280" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>16</v>
       </c>
@@ -19698,7 +20987,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="281" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>16</v>
       </c>
@@ -19712,7 +21001,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="282" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>16</v>
       </c>
@@ -19726,7 +21015,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="283" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>16</v>
       </c>
@@ -19740,7 +21029,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="284" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>16</v>
       </c>
@@ -19754,7 +21043,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="285" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>16</v>
       </c>
@@ -19768,7 +21057,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="286" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>16</v>
       </c>
@@ -19782,7 +21071,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="287" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>16</v>
       </c>
@@ -19796,7 +21085,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="288" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>16</v>
       </c>
@@ -19810,7 +21099,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="289" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>16</v>
       </c>
@@ -19824,7 +21113,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="290" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>16</v>
       </c>
@@ -19838,7 +21127,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="291" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>16</v>
       </c>
@@ -19849,7 +21138,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="292" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>16</v>
       </c>
@@ -19863,7 +21152,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="293" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>16</v>
       </c>
@@ -19877,7 +21166,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="294" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>16</v>
       </c>
@@ -19891,7 +21180,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="295" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>16</v>
       </c>
@@ -19905,7 +21194,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="296" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>16</v>
       </c>
@@ -19919,7 +21208,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="297" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>16</v>
       </c>
@@ -19933,7 +21222,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="298" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>16</v>
       </c>
@@ -19947,7 +21236,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="299" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>16</v>
       </c>
@@ -19961,7 +21250,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="300" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>16</v>
       </c>
@@ -19975,7 +21264,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="301" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>16</v>
       </c>
@@ -20001,12 +21290,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DCCDE7F-90D3-4824-8130-ABEE2C3BAACE}">
   <dimension ref="A1:AB51"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.6640625" customWidth="1"/>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>19</v>
       </c>
@@ -20020,7 +21309,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>20</v>
       </c>
@@ -20091,7 +21380,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -20184,7 +21473,7 @@
         <v>51.674399999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -20277,7 +21566,7 @@
         <v>-88.491599999999991</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -20370,7 +21659,7 @@
         <v>-36.817199999999993</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -20384,7 +21673,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -20398,7 +21687,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -20412,7 +21701,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>20</v>
       </c>
@@ -20426,7 +21715,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>20</v>
       </c>
@@ -20440,7 +21729,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -20454,7 +21743,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -20468,7 +21757,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -20482,7 +21771,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>20</v>
       </c>
@@ -20496,7 +21785,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>20</v>
       </c>
@@ -20510,7 +21799,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>20</v>
       </c>
@@ -20524,7 +21813,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -20538,7 +21827,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -20552,7 +21841,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -20566,7 +21855,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>20</v>
       </c>
@@ -20580,7 +21869,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -20594,7 +21883,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>20</v>
       </c>
@@ -20608,7 +21897,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>20</v>
       </c>
@@ -20622,7 +21911,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>20</v>
       </c>
@@ -20636,7 +21925,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>20</v>
       </c>
@@ -20650,7 +21939,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>20</v>
       </c>
@@ -20664,7 +21953,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>21</v>
       </c>
@@ -20678,7 +21967,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>21</v>
       </c>
@@ -20692,7 +21981,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>21</v>
       </c>
@@ -20706,7 +21995,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>21</v>
       </c>
@@ -20720,7 +22009,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>21</v>
       </c>
@@ -20734,7 +22023,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>21</v>
       </c>
@@ -20748,7 +22037,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>21</v>
       </c>
@@ -20762,7 +22051,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>21</v>
       </c>
@@ -20776,7 +22065,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>21</v>
       </c>
@@ -20790,7 +22079,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>21</v>
       </c>
@@ -20804,7 +22093,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>21</v>
       </c>
@@ -20818,7 +22107,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>21</v>
       </c>
@@ -20832,7 +22121,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>21</v>
       </c>
@@ -20846,7 +22135,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>21</v>
       </c>
@@ -20860,7 +22149,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>21</v>
       </c>
@@ -20874,7 +22163,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>21</v>
       </c>
@@ -20888,7 +22177,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>21</v>
       </c>
@@ -20902,7 +22191,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>21</v>
       </c>
@@ -20916,7 +22205,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>21</v>
       </c>
@@ -20930,7 +22219,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>21</v>
       </c>
@@ -20944,7 +22233,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>21</v>
       </c>
@@ -20958,7 +22247,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>21</v>
       </c>
@@ -20972,7 +22261,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>21</v>
       </c>
@@ -20986,7 +22275,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>21</v>
       </c>
@@ -21000,7 +22289,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>21</v>
       </c>
@@ -21023,14 +22312,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F31AC804-BBB6-49B0-9019-74125F94880C}">
   <dimension ref="A1:AA97"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="42.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.33203125" customWidth="1"/>
-    <col min="9" max="9" width="11.44140625" customWidth="1"/>
+    <col min="1" max="1" width="42.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.28515625" customWidth="1"/>
+    <col min="9" max="9" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>24</v>
       </c>
@@ -21044,7 +22333,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -21112,7 +22401,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -21201,7 +22490,7 @@
         <v>5.43</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -21290,7 +22579,7 @@
         <v>6.24</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -21379,7 +22668,7 @@
         <v>24.222999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -21468,7 +22757,7 @@
         <v>1.22</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -21482,7 +22771,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -21496,7 +22785,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -21510,7 +22799,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -21524,7 +22813,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -21538,7 +22827,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -21552,7 +22841,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>4</v>
       </c>
@@ -21566,7 +22855,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -21580,7 +22869,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -21594,7 +22883,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>4</v>
       </c>
@@ -21608,7 +22897,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>4</v>
       </c>
@@ -21622,7 +22911,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -21636,7 +22925,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>4</v>
       </c>
@@ -21650,7 +22939,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>4</v>
       </c>
@@ -21664,7 +22953,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>4</v>
       </c>
@@ -21678,7 +22967,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>4</v>
       </c>
@@ -21692,7 +22981,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>4</v>
       </c>
@@ -21706,7 +22995,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>4</v>
       </c>
@@ -21720,7 +23009,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>4</v>
       </c>
@@ -21734,7 +23023,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>6</v>
       </c>
@@ -21748,7 +23037,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>6</v>
       </c>
@@ -21762,7 +23051,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>6</v>
       </c>
@@ -21776,7 +23065,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>6</v>
       </c>
@@ -21790,7 +23079,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>6</v>
       </c>
@@ -21804,7 +23093,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>6</v>
       </c>
@@ -21818,7 +23107,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>6</v>
       </c>
@@ -21832,7 +23121,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>6</v>
       </c>
@@ -21846,7 +23135,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>6</v>
       </c>
@@ -21860,7 +23149,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>6</v>
       </c>
@@ -21874,7 +23163,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>6</v>
       </c>
@@ -21888,7 +23177,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>6</v>
       </c>
@@ -21902,7 +23191,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>6</v>
       </c>
@@ -21916,7 +23205,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>6</v>
       </c>
@@ -21930,7 +23219,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>6</v>
       </c>
@@ -21944,7 +23233,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>6</v>
       </c>
@@ -21958,7 +23247,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>6</v>
       </c>
@@ -21972,7 +23261,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>6</v>
       </c>
@@ -21986,7 +23275,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>6</v>
       </c>
@@ -22000,7 +23289,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>6</v>
       </c>
@@ -22014,7 +23303,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>6</v>
       </c>
@@ -22028,7 +23317,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>6</v>
       </c>
@@ -22042,7 +23331,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>6</v>
       </c>
@@ -22056,7 +23345,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>6</v>
       </c>
@@ -22070,7 +23359,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>7</v>
       </c>
@@ -22084,7 +23373,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>7</v>
       </c>
@@ -22098,7 +23387,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>7</v>
       </c>
@@ -22112,7 +23401,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>7</v>
       </c>
@@ -22126,7 +23415,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>7</v>
       </c>
@@ -22140,7 +23429,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>7</v>
       </c>
@@ -22154,7 +23443,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>7</v>
       </c>
@@ -22168,7 +23457,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>7</v>
       </c>
@@ -22182,7 +23471,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>7</v>
       </c>
@@ -22196,7 +23485,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>7</v>
       </c>
@@ -22210,7 +23499,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>7</v>
       </c>
@@ -22224,7 +23513,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>7</v>
       </c>
@@ -22238,7 +23527,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>7</v>
       </c>
@@ -22252,7 +23541,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>7</v>
       </c>
@@ -22266,7 +23555,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>7</v>
       </c>
@@ -22280,7 +23569,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>7</v>
       </c>
@@ -22294,7 +23583,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>7</v>
       </c>
@@ -22308,7 +23597,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>7</v>
       </c>
@@ -22322,7 +23611,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>7</v>
       </c>
@@ -22336,7 +23625,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>7</v>
       </c>
@@ -22350,7 +23639,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>7</v>
       </c>
@@ -22364,7 +23653,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>7</v>
       </c>
@@ -22378,7 +23667,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>7</v>
       </c>
@@ -22392,7 +23681,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>7</v>
       </c>
@@ -22406,7 +23695,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>25</v>
       </c>
@@ -22420,7 +23709,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>25</v>
       </c>
@@ -22434,7 +23723,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>25</v>
       </c>
@@ -22448,7 +23737,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>25</v>
       </c>
@@ -22462,7 +23751,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>25</v>
       </c>
@@ -22476,7 +23765,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>25</v>
       </c>
@@ -22490,7 +23779,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>25</v>
       </c>
@@ -22504,7 +23793,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>25</v>
       </c>
@@ -22518,7 +23807,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>25</v>
       </c>
@@ -22532,7 +23821,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>25</v>
       </c>
@@ -22546,7 +23835,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>25</v>
       </c>
@@ -22560,7 +23849,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>25</v>
       </c>
@@ -22574,7 +23863,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>25</v>
       </c>
@@ -22588,7 +23877,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>25</v>
       </c>
@@ -22602,7 +23891,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>25</v>
       </c>
@@ -22616,7 +23905,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>25</v>
       </c>
@@ -22630,7 +23919,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>25</v>
       </c>
@@ -22644,7 +23933,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>25</v>
       </c>
@@ -22658,7 +23947,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>25</v>
       </c>
@@ -22672,7 +23961,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>25</v>
       </c>
@@ -22686,7 +23975,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>25</v>
       </c>
@@ -22700,7 +23989,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>25</v>
       </c>
@@ -22714,7 +24003,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>25</v>
       </c>
@@ -22728,7 +24017,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>25</v>
       </c>
@@ -22751,24 +24040,24 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2DE3364-19EF-4DBB-9C60-BFBDC0F3AE34}">
   <dimension ref="A1:AD39"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.88671875" customWidth="1"/>
-    <col min="2" max="2" width="12.6640625" customWidth="1"/>
-    <col min="3" max="3" width="13.6640625" customWidth="1"/>
+    <col min="1" max="1" width="10.85546875" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" customWidth="1"/>
+    <col min="3" max="3" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>29</v>
       </c>
@@ -22851,7 +24140,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1990</v>
       </c>
@@ -22962,7 +24251,7 @@
         <v>253.74799999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>1991</v>
       </c>
@@ -22973,7 +24262,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>1992</v>
       </c>
@@ -22991,7 +24280,7 @@
         <v>754.71479999999997</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>1993</v>
       </c>
@@ -23009,7 +24298,7 @@
         <v>797.41800000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>1994</v>
       </c>
@@ -23027,7 +24316,7 @@
         <v>831.71879999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>1995</v>
       </c>
@@ -23045,7 +24334,7 @@
         <v>861.99119999999994</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>1996</v>
       </c>
@@ -23063,7 +24352,7 @@
         <v>910.35719999999992</v>
       </c>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>1997</v>
       </c>
@@ -23081,7 +24370,7 @@
         <v>960.41160000000002</v>
       </c>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>1998</v>
       </c>
@@ -23099,7 +24388,7 @@
         <v>975.79799999999989</v>
       </c>
     </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>1999</v>
       </c>
@@ -23117,7 +24406,7 @@
         <v>985.77719999999999</v>
       </c>
     </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2000</v>
       </c>
@@ -23135,7 +24424,7 @@
         <v>996.87239999999997</v>
       </c>
     </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2001</v>
       </c>
@@ -23153,7 +24442,7 @@
         <v>943.4556</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2002</v>
       </c>
@@ -23171,7 +24460,7 @@
         <v>956.85839999999985</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2003</v>
       </c>
@@ -23189,7 +24478,7 @@
         <v>942.22439999999995</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2004</v>
       </c>
@@ -23207,7 +24496,7 @@
         <v>938.46600000000001</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2005</v>
       </c>
@@ -23225,7 +24514,7 @@
         <v>907.8696000000001</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2006</v>
       </c>
@@ -23243,7 +24532,7 @@
         <v>896.21999999999991</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>2007</v>
       </c>
@@ -23261,7 +24550,7 @@
         <v>915.36839999999995</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>2008</v>
       </c>
@@ -23279,7 +24568,7 @@
         <v>920.58839999999998</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>2009</v>
       </c>
@@ -23297,7 +24586,7 @@
         <v>939.85919999999999</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2010</v>
       </c>
@@ -23315,7 +24604,7 @@
         <v>935.84879999999998</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>2011</v>
       </c>
@@ -23333,7 +24622,7 @@
         <v>919.18439999999998</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>2012</v>
       </c>
@@ -23351,7 +24640,7 @@
         <v>867.67920000000004</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>2013</v>
       </c>
@@ -23369,7 +24658,7 @@
         <v>894.36959999999999</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>2014</v>
       </c>
@@ -23387,7 +24676,7 @@
         <v>891.07560000000001</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>2015</v>
       </c>
@@ -23405,7 +24694,7 @@
         <v>890.85599999999999</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>2016</v>
       </c>
@@ -23423,7 +24712,7 @@
         <v>913.49279999999999</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>2017</v>
       </c>
@@ -23434,7 +24723,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>2018</v>
       </c>
@@ -23445,7 +24734,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>2019</v>
       </c>
@@ -23456,7 +24745,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>2020</v>
       </c>
@@ -23467,7 +24756,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>2021</v>
       </c>
@@ -23478,7 +24767,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>2022</v>
       </c>
@@ -23489,7 +24778,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>2023</v>
       </c>
@@ -23500,7 +24789,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>2024</v>
       </c>
@@ -23520,12 +24809,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB763C44-0720-4A5D-A285-14210CC2296D}">
   <dimension ref="A2:D7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.33203125" customWidth="1"/>
+    <col min="1" max="1" width="13.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>32</v>
       </c>
@@ -23536,7 +24825,7 @@
         <v>3.5999999999999999E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>31</v>
       </c>
@@ -23544,7 +24833,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>15.5</v>
       </c>
@@ -23553,7 +24842,7 @@
         <v>4305.5555555555557</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -23561,7 +24850,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>3971</v>
       </c>
@@ -23582,14 +24871,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDEB2676-8085-4D3C-98E7-5BF41F1AF8D5}">
   <dimension ref="A1:W49"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.88671875" customWidth="1"/>
-    <col min="2" max="11" width="7.6640625" customWidth="1"/>
-    <col min="14" max="14" width="18.44140625" customWidth="1"/>
+    <col min="1" max="1" width="11.85546875" customWidth="1"/>
+    <col min="2" max="11" width="7.7109375" customWidth="1"/>
+    <col min="14" max="14" width="18.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>34</v>
       </c>
@@ -23624,7 +24913,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>35</v>
       </c>
@@ -23686,7 +24975,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>35</v>
       </c>
@@ -23760,7 +25049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>66</v>
       </c>
@@ -23834,7 +25123,7 @@
         <v>1193.4002561548721</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>66</v>
       </c>
@@ -23908,7 +25197,7 @@
         <v>366.57755802738978</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>36</v>
       </c>
@@ -23982,7 +25271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>36</v>
       </c>
@@ -24056,7 +25345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -24130,7 +25419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>37</v>
       </c>
@@ -24204,7 +25493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>37</v>
       </c>
@@ -24278,7 +25567,7 @@
         <v>2417.2778962392399</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>37</v>
       </c>
@@ -24352,7 +25641,7 @@
         <v>3622.2536445412229</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>38</v>
       </c>
@@ -24426,7 +25715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>38</v>
       </c>
@@ -24500,7 +25789,7 @@
         <v>343.51136363636368</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>38</v>
       </c>
@@ -24574,7 +25863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>39</v>
       </c>
@@ -24648,7 +25937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>39</v>
       </c>
@@ -24691,7 +25980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>39</v>
       </c>
@@ -24726,7 +26015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -24761,7 +26050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>40</v>
       </c>
@@ -24799,7 +26088,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>40</v>
       </c>
@@ -24834,7 +26123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>41</v>
       </c>
@@ -24896,7 +26185,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>41</v>
       </c>
@@ -24970,7 +26259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>41</v>
       </c>
@@ -25044,7 +26333,7 @@
         <v>0.3435113636363637</v>
       </c>
     </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>42</v>
       </c>
@@ -25118,7 +26407,7 @@
         <v>7.5995093549627253</v>
       </c>
     </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>42</v>
       </c>
@@ -25153,7 +26442,7 @@
         <v>2417.2778962392399</v>
       </c>
     </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>42</v>
       </c>
@@ -25188,7 +26477,7 @@
         <v>23.26791557877343</v>
       </c>
     </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>43</v>
       </c>
@@ -25223,7 +26512,7 @@
         <v>8.3938141495607681</v>
       </c>
     </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>43</v>
       </c>
@@ -25258,7 +26547,7 @@
         <v>3622.2536445412229</v>
       </c>
     </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>43</v>
       </c>
@@ -25293,7 +26582,7 @@
         <v>34.866612621252422</v>
       </c>
     </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>44</v>
       </c>
@@ -25328,7 +26617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>44</v>
       </c>
@@ -25363,7 +26652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>44</v>
       </c>
@@ -25398,7 +26687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>45</v>
       </c>
@@ -25433,7 +26722,7 @@
         <v>3.497727272727273</v>
       </c>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>45</v>
       </c>
@@ -25468,7 +26757,7 @@
         <v>343.51136363636368</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>45</v>
       </c>
@@ -25503,7 +26792,7 @@
         <v>13.731818181818181</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>46</v>
       </c>
@@ -25538,7 +26827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>46</v>
       </c>
@@ -25573,7 +26862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>46</v>
       </c>
@@ -25608,7 +26897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>47</v>
       </c>
@@ -25643,7 +26932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>47</v>
       </c>
@@ -25678,7 +26967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>47</v>
       </c>
@@ -25713,7 +27002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
       <c r="N45">
         <v>2007</v>
       </c>
@@ -25733,7 +27022,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
       <c r="M46" t="s">
         <v>4</v>
       </c>
@@ -25756,7 +27045,7 @@
         <v>5.43</v>
       </c>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
       <c r="M47" t="s">
         <v>6</v>
       </c>
@@ -25779,7 +27068,7 @@
         <v>6.24</v>
       </c>
     </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
       <c r="M48" t="s">
         <v>7</v>
       </c>
@@ -25802,7 +27091,7 @@
         <v>24.222999999999999</v>
       </c>
     </row>
-    <row r="49" spans="13:19" x14ac:dyDescent="0.3">
+    <row r="49" spans="13:19" x14ac:dyDescent="0.25">
       <c r="M49" t="s">
         <v>25</v>
       </c>
@@ -25833,24 +27122,24 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95A32E31-20CB-4056-864B-0FCE4F4387EC}">
-  <dimension ref="A1:M72"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:P77"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="10" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="10" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="9.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>34</v>
       </c>
@@ -25888,7 +27177,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>35</v>
       </c>
@@ -25926,9 +27215,9 @@
         <v>3.050924651162791</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B3" t="s">
         <v>56</v>
@@ -25964,9 +27253,9 @@
         <v>7.5127437209302332</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B4" t="s">
         <v>57</v>
@@ -26002,7 +27291,7 @@
         <v>7.6273116279069786</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>36</v>
       </c>
@@ -26040,7 +27329,7 @@
         <v>8.7529633793280031</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>73</v>
       </c>
@@ -26078,7 +27367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>37</v>
       </c>
@@ -26116,9 +27405,9 @@
         <v>14.966633574144</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B8" t="s">
         <v>57</v>
@@ -26154,9 +27443,9 @@
         <v>16.035678829439998</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B9" t="s">
         <v>57</v>
@@ -26192,9 +27481,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B10" t="s">
         <v>57</v>
@@ -26230,7 +27519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>38</v>
       </c>
@@ -26268,7 +27557,7 @@
         <v>4.7310000000000034</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>40</v>
       </c>
@@ -26306,7 +27595,7 @@
         <v>7.1249999999999991</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>58</v>
       </c>
@@ -26344,7 +27633,7 @@
         <v>0.27625</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>59</v>
       </c>
@@ -26382,7 +27671,7 @@
         <v>110.0203463944904</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>33</v>
       </c>
@@ -26420,7 +27709,7 @@
         <v>34.890279572218027</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>41</v>
       </c>
@@ -26458,7 +27747,7 @@
         <v>144.39798261264659</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>42</v>
       </c>
@@ -26496,7 +27785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>43</v>
       </c>
@@ -26534,7 +27823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>68</v>
       </c>
@@ -26572,7 +27861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>44</v>
       </c>
@@ -26610,7 +27899,7 @@
         <v>30.513999999999999</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>45</v>
       </c>
@@ -26648,7 +27937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>60</v>
       </c>
@@ -26686,7 +27975,7 @@
         <v>215.94100000000009</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>69</v>
       </c>
@@ -26724,7 +28013,7 @@
         <v>49.625829926784</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>70</v>
       </c>
@@ -26762,7 +28051,7 @@
         <v>16.2023932122624</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>61</v>
       </c>
@@ -26800,7 +28089,7 @@
         <v>129.83753686095361</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>62</v>
       </c>
@@ -26838,7 +28127,7 @@
         <v>3.6792000000000011</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>63</v>
       </c>
@@ -26876,7 +28165,7 @@
         <v>91.374535654133126</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>64</v>
       </c>
@@ -26914,9 +28203,9 @@
         <v>136.9148652764311</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B29" t="s">
         <v>57</v>
@@ -26952,7 +28241,7 @@
         <v>2.04497403329162</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C33" s="7">
         <v>2007</v>
       </c>
@@ -26984,7 +28273,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
         <v>4</v>
       </c>
@@ -27029,7 +28318,7 @@
         <v>11.856000000000002</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
         <v>6</v>
       </c>
@@ -27074,7 +28363,7 @@
         <v>30.513999999999999</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
         <v>7</v>
       </c>
@@ -27119,7 +28408,7 @@
         <v>184.15325839555859</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
         <v>8</v>
       </c>
@@ -27164,7 +28453,7 @@
         <v>215.94100000000009</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
         <v>9</v>
       </c>
@@ -27209,7 +28498,7 @@
         <v>146.95560000000006</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
         <v>11</v>
       </c>
@@ -27254,7 +28543,7 @@
         <v>18.190980000000003</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
         <v>13</v>
       </c>
@@ -27299,7 +28588,7 @@
         <v>228.28940093056423</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
         <v>65</v>
       </c>
@@ -27344,7 +28633,7 @@
         <v>199.34496000000001</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>67</v>
       </c>
@@ -27389,9 +28678,9 @@
         <v>0.27625</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C45" s="7">
         <v>2007</v>
@@ -27424,7 +28713,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
         <v>4</v>
       </c>
@@ -27459,7 +28748,7 @@
         <v>12.477599999999999</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
         <v>6</v>
       </c>
@@ -27494,7 +28783,7 @@
         <v>32.842799999999997</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
         <v>7</v>
       </c>
@@ -27529,7 +28818,7 @@
         <v>188.3844</v>
       </c>
     </row>
-    <row r="49" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
         <v>8</v>
       </c>
@@ -27564,7 +28853,7 @@
         <v>196.3152</v>
       </c>
     </row>
-    <row r="50" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
         <v>9</v>
       </c>
@@ -27599,7 +28888,7 @@
         <v>146.9556</v>
       </c>
     </row>
-    <row r="51" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
         <v>11</v>
       </c>
@@ -27634,7 +28923,7 @@
         <v>19.148399999999999</v>
       </c>
     </row>
-    <row r="52" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
         <v>13</v>
       </c>
@@ -27669,7 +28958,7 @@
         <v>223.5204</v>
       </c>
     </row>
-    <row r="53" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
         <v>65</v>
       </c>
@@ -27714,7 +29003,7 @@
         <v>209.85119999999998</v>
       </c>
     </row>
-    <row r="54" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
         <v>67</v>
       </c>
@@ -27749,7 +29038,7 @@
         <v>0.87839999999999996</v>
       </c>
     </row>
-    <row r="56" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
         <v>14</v>
       </c>
@@ -27784,7 +29073,7 @@
         <v>193.50719999999998</v>
       </c>
     </row>
-    <row r="57" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
         <v>15</v>
       </c>
@@ -27819,7 +29108,7 @@
         <v>16.344000000000001</v>
       </c>
     </row>
-    <row r="60" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
         <v>71</v>
       </c>
@@ -27854,7 +29143,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="61" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
         <v>4</v>
       </c>
@@ -27899,7 +29188,7 @@
         <v>-4.9817272552413708E-2</v>
       </c>
     </row>
-    <row r="62" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
         <v>6</v>
       </c>
@@ -27944,7 +29233,7 @@
         <v>-7.0907474393169814E-2</v>
       </c>
     </row>
-    <row r="63" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
         <v>7</v>
       </c>
@@ -27989,7 +29278,7 @@
         <v>-2.2460148528441869E-2</v>
       </c>
     </row>
-    <row r="64" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B64" t="s">
         <v>8</v>
       </c>
@@ -28034,7 +29323,7 @@
         <v>9.9970863183289335E-2</v>
       </c>
     </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
         <v>9</v>
       </c>
@@ -28079,7 +29368,7 @@
         <v>3.8680675565142133E-16</v>
       </c>
     </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B66" t="s">
         <v>11</v>
       </c>
@@ -28124,7 +29413,7 @@
         <v>-4.9999999999999767E-2</v>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B67" t="s">
         <v>13</v>
       </c>
@@ -28169,7 +29458,7 @@
         <v>2.1335864335265291E-2</v>
       </c>
     </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B68" t="s">
         <v>65</v>
       </c>
@@ -28214,7 +29503,7 @@
         <v>-5.0065189048239721E-2</v>
       </c>
     </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
         <v>67</v>
       </c>
@@ -28259,9 +29548,9 @@
         <v>-0.68550774134790526</v>
       </c>
     </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B71" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="C71" s="6">
         <f>SUM(C34:C42)-SUM(C46:C54)</f>
@@ -28307,7 +29596,10 @@
         <v>31</v>
       </c>
     </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B72" t="s">
+        <v>81</v>
+      </c>
       <c r="C72" s="5">
         <f>C71/SUM(C46:C54)</f>
         <v>-6.0496328138011915E-3</v>
@@ -28347,6 +29639,79 @@
       <c r="L72" s="5">
         <f t="shared" si="21"/>
         <v>4.995709641472704E-3</v>
+      </c>
+      <c r="N72" s="5">
+        <v>-8.8000000000000005E-3</v>
+      </c>
+      <c r="P72" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="C73">
+        <f>(C72-$N$72)^2</f>
+        <v>7.5645196589191545E-6</v>
+      </c>
+      <c r="D73">
+        <f t="shared" ref="D73:L73" si="22">(D72-$N$72)^2</f>
+        <v>2.9491453605795574E-6</v>
+      </c>
+      <c r="E73">
+        <f t="shared" si="22"/>
+        <v>8.0471724795698227E-5</v>
+      </c>
+      <c r="F73">
+        <f t="shared" si="22"/>
+        <v>1.6650005630574382E-4</v>
+      </c>
+      <c r="G73">
+        <f t="shared" si="22"/>
+        <v>6.3183197796754198E-6</v>
+      </c>
+      <c r="H73">
+        <f t="shared" si="22"/>
+        <v>3.199971262403977E-7</v>
+      </c>
+      <c r="I73">
+        <f t="shared" si="22"/>
+        <v>1.2407631946503741E-4</v>
+      </c>
+      <c r="J73">
+        <f t="shared" si="22"/>
+        <v>2.0066844099059005E-5</v>
+      </c>
+      <c r="K73">
+        <f t="shared" si="22"/>
+        <v>5.295475317452214E-7</v>
+      </c>
+      <c r="L73">
+        <f t="shared" si="22"/>
+        <v>1.9032160451182295E-4</v>
+      </c>
+      <c r="N73" s="5">
+        <f>SQRT(SUM(C73:L73)/10)</f>
+        <v>7.7402718210313592E-3</v>
+      </c>
+      <c r="P73" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="N76" s="9">
+        <f>N72+N73</f>
+        <v>-1.0597281789686414E-3</v>
+      </c>
+      <c r="P76" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="N77" s="9">
+        <f>N72-N73</f>
+        <v>-1.654027182103136E-2</v>
+      </c>
+      <c r="P77" t="s">
+        <v>86</v>
       </c>
     </row>
   </sheetData>
